--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,49 +44,49 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394731163979</t>
+    <t xml:space="preserve">0.235394716262817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249073028564</t>
+    <t xml:space="preserve">0.228249102830887</t>
   </si>
   <si>
     <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581348657608</t>
+    <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21017424762249</t>
+    <t xml:space="preserve">0.210174262523651</t>
   </si>
   <si>
     <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921502828598</t>
+    <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071762084961</t>
+    <t xml:space="preserve">0.227071791887283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293399214745</t>
+    <t xml:space="preserve">0.233293369412422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22841739654541</t>
+    <t xml:space="preserve">0.228417411446571</t>
   </si>
   <si>
     <t xml:space="preserve">0.231527775526047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762196540833</t>
+    <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598274230957</t>
+    <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
@@ -95,79 +95,79 @@
     <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21437780559063</t>
+    <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
     <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767161488533</t>
+    <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563588619232</t>
+    <t xml:space="preserve">0.197563603520393</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612486124039</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722894906998</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607870101929</t>
+    <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912774920464</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218499302864</t>
+    <t xml:space="preserve">0.215218514204025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987585425377</t>
+    <t xml:space="preserve">0.226987600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031852006912</t>
+    <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235454678535</t>
+    <t xml:space="preserve">0.236235439777374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279691457748</t>
+    <t xml:space="preserve">0.241279661655426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483219623566</t>
+    <t xml:space="preserve">0.245483249425888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208888530731</t>
+    <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093893527985</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182396888733</t>
+    <t xml:space="preserve">0.268182456493378</t>
   </si>
   <si>
     <t xml:space="preserve">0.273226678371429</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836488008499</t>
+    <t xml:space="preserve">0.285836458206177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562186717987</t>
+    <t xml:space="preserve">0.292562216520309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29844719171524</t>
+    <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332107305527</t>
+    <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
     <t xml:space="preserve">0.311057776212692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531049251556</t>
+    <t xml:space="preserve">0.317531019449234</t>
   </si>
   <si>
     <t xml:space="preserve">0.322827786207199</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455296278</t>
+    <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
     <t xml:space="preserve">0.36318102478981</t>
@@ -209,22 +209,22 @@
     <t xml:space="preserve">0.378313839435577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034849524498</t>
+    <t xml:space="preserve">0.420348525047302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525621175766</t>
+    <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
     <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471743822098</t>
+    <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400881290436</t>
+    <t xml:space="preserve">0.483400911092758</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49651575088501</t>
+    <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307871580124</t>
+    <t xml:space="preserve">0.492307841777802</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319216251373</t>
+    <t xml:space="preserve">0.715319335460663</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67324161529541</t>
+    <t xml:space="preserve">0.673241674900055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656410574913025</t>
+    <t xml:space="preserve">0.65641051530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618540704250336</t>
+    <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
     <t xml:space="preserve">0.62274843454361</t>
@@ -272,49 +272,49 @@
     <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762311458588</t>
+    <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48810014128685</t>
+    <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008872032166</t>
+    <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
     <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51334673166275</t>
+    <t xml:space="preserve">0.513346791267395</t>
   </si>
   <si>
     <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554461956024</t>
+    <t xml:space="preserve">0.517554521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269130706787</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061340808868</t>
+    <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500723421573639</t>
+    <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853580713272</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684680700302</t>
+    <t xml:space="preserve">0.479684591293335</t>
   </si>
   <si>
-    <t xml:space="preserve">0.43339928984642</t>
+    <t xml:space="preserve">0.433399260044098</t>
   </si>
   <si>
     <t xml:space="preserve">0.437607049942017</t>
@@ -323,13 +323,13 @@
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230360031128</t>
+    <t xml:space="preserve">0.450230330228806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022570133209</t>
+    <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645850419998</t>
+    <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
     <t xml:space="preserve">0.403944969177246</t>
@@ -347,61 +347,61 @@
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677373409271</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381494760513</t>
+    <t xml:space="preserve">0.380381524562836</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360489368439</t>
+    <t xml:space="preserve">0.412360459566116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726661682129</t>
   </si>
   <si>
     <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092923402786</t>
+    <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628085136414</t>
+    <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994287252426</t>
+    <t xml:space="preserve">0.408994257450104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311141490936</t>
+    <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163217067719</t>
+    <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895651102066</t>
+    <t xml:space="preserve">0.398895621299744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578767061234</t>
+    <t xml:space="preserve">0.400578737258911</t>
   </si>
   <si>
     <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261853218079</t>
+    <t xml:space="preserve">0.402261823415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529419183731</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
@@ -410,19 +410,19 @@
     <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311374217271805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620807647705</t>
+    <t xml:space="preserve">0.336620837450027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888373613358</t>
+    <t xml:space="preserve">0.32988840341568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328205287456512</t>
+    <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522201299667</t>
@@ -431,7 +431,7 @@
     <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35345184803009</t>
+    <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
     <t xml:space="preserve">0.360184282064438</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.3500856757164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303953409195</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343353182077408</t>
+    <t xml:space="preserve">0.343353241682053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33325457572937</t>
+    <t xml:space="preserve">0.333254605531693</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
@@ -464,16 +464,16 @@
     <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339987009763718</t>
+    <t xml:space="preserve">0.33998703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916626691818</t>
+    <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36859980225563</t>
+    <t xml:space="preserve">0.368599772453308</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
@@ -482,49 +482,49 @@
     <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212564945221</t>
+    <t xml:space="preserve">0.397212594747543</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747726678848</t>
+    <t xml:space="preserve">0.383747756481171</t>
   </si>
   <si>
     <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698408603668</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064640522003</t>
+    <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332206487656</t>
+    <t xml:space="preserve">0.375332176685333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
     <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385430812835693</t>
+    <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233570337296</t>
+    <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
     <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632182121277</t>
+    <t xml:space="preserve">0.559632062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55121648311615</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783257246017</t>
+    <t xml:space="preserve">0.489783316850662</t>
   </si>
   <si>
     <t xml:space="preserve">0.48473396897316</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466373205185</t>
+    <t xml:space="preserve">0.49146643280983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198866844177</t>
+    <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741276264191</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494715690613</t>
+    <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520079135894775</t>
+    <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
     <t xml:space="preserve">0.526811540126801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910176277161</t>
+    <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128424167633</t>
@@ -566,19 +566,19 @@
     <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663615703583</t>
+    <t xml:space="preserve">0.511663675308228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503248155117035</t>
+    <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
     <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501564979553223</t>
+    <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49314945936203</t>
+    <t xml:space="preserve">0.493149489164352</t>
   </si>
   <si>
     <t xml:space="preserve">0.509980499744415</t>
@@ -590,31 +590,31 @@
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227119922638</t>
+    <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107388973236</t>
+    <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
     <t xml:space="preserve">0.550374984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860828399658</t>
+    <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396019935608</t>
+    <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671302318573</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
     <t xml:space="preserve">0.533544063568115</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">0.530068159103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281956195831</t>
+    <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592314243317</t>
+    <t xml:space="preserve">0.526592254638672</t>
   </si>
   <si>
     <t xml:space="preserve">0.528330206871033</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971478939056</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503999173641205</t>
+    <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833746433258</t>
+    <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
     <t xml:space="preserve">0.493571698665619</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419748306274</t>
+    <t xml:space="preserve">0.587419807910919</t>
   </si>
   <si>
     <t xml:space="preserve">0.601323187351227</t>
@@ -722,10 +722,10 @@
     <t xml:space="preserve">0.58915764093399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557659626007</t>
+    <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102311134338</t>
+    <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288532733917</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702471256256</t>
+    <t xml:space="preserve">0.618702530860901</t>
   </si>
   <si>
     <t xml:space="preserve">0.632605910301208</t>
@@ -770,10 +770,10 @@
     <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178316116333</t>
+    <t xml:space="preserve">0.622178375720978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012888908386</t>
+    <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
     <t xml:space="preserve">0.583943903446198</t>
@@ -794,34 +794,34 @@
     <t xml:space="preserve">0.50573718547821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557874977588654</t>
+    <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109449863434</t>
+    <t xml:space="preserve">0.596109390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750841140747</t>
+    <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
     <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985253810883</t>
+    <t xml:space="preserve">0.649985194206238</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081755161285</t>
+    <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
     <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957559108734</t>
+    <t xml:space="preserve">0.689957499504089</t>
   </si>
   <si>
     <t xml:space="preserve">0.688219606876373</t>
@@ -830,7 +830,7 @@
     <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150621414185</t>
+    <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
     <t xml:space="preserve">0.674316227436066</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674895763397</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509408950806</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606536984443665</t>
+    <t xml:space="preserve">0.60653692483902</t>
   </si>
   <si>
     <t xml:space="preserve">0.615226626396179</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788482666016</t>
+    <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -866,10 +866,13 @@
     <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629239618778229</t>
+    <t xml:space="preserve">0.629239559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
@@ -893,7 +896,7 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
     <t xml:space="preserve">0.623861491680145</t>
@@ -908,7 +911,7 @@
     <t xml:space="preserve">0.604141712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588007390499115</t>
+    <t xml:space="preserve">0.58800733089447</t>
   </si>
   <si>
     <t xml:space="preserve">0.589800119400024</t>
@@ -920,7 +923,7 @@
     <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573665738105774</t>
+    <t xml:space="preserve">0.573665678501129</t>
   </si>
   <si>
     <t xml:space="preserve">0.580836534500122</t>
@@ -938,7 +941,7 @@
     <t xml:space="preserve">0.56828761100769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552153289318085</t>
+    <t xml:space="preserve">0.55215322971344</t>
   </si>
   <si>
     <t xml:space="preserve">0.571873009204865</t>
@@ -953,7 +956,7 @@
     <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -962,10 +965,10 @@
     <t xml:space="preserve">0.611312508583069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605934381484985</t>
+    <t xml:space="preserve">0.60593444108963</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
@@ -983,13 +986,13 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203084468842</t>
+    <t xml:space="preserve">0.638203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -1019,7 +1022,7 @@
     <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
     <t xml:space="preserve">0.645373940467834</t>
@@ -1031,49 +1034,49 @@
     <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020710945129</t>
+    <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191626548767</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71528947353363</t>
+    <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
     <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711704075336456</t>
+    <t xml:space="preserve">0.711704015731812</t>
   </si>
   <si>
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009253025055</t>
   </si>
   <si>
     <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765507221222</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1085,7 +1088,7 @@
     <t xml:space="preserve">0.742180049419403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708118677139282</t>
+    <t xml:space="preserve">0.708118617534637</t>
   </si>
   <si>
     <t xml:space="preserve">0.704533219337463</t>
@@ -1094,19 +1097,19 @@
     <t xml:space="preserve">0.713496744632721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700947821140289</t>
+    <t xml:space="preserve">0.700947761535645</t>
   </si>
   <si>
     <t xml:space="preserve">0.706325948238373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697362422943115</t>
+    <t xml:space="preserve">0.69736236333847</t>
   </si>
   <si>
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252939224243</t>
+    <t xml:space="preserve">0.724252998828888</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
@@ -1121,7 +1124,7 @@
     <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667541027069</t>
+    <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
     <t xml:space="preserve">0.726045668125153</t>
@@ -1142,25 +1145,25 @@
     <t xml:space="preserve">0.665459334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659898400306702</t>
+    <t xml:space="preserve">0.659898459911346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650630235671997</t>
+    <t xml:space="preserve">0.650630176067352</t>
   </si>
   <si>
     <t xml:space="preserve">0.658044755458832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652483880519867</t>
+    <t xml:space="preserve">0.652483820915222</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.663605690002441</t>
+    <t xml:space="preserve">0.663605749607086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646922945976257</t>
+    <t xml:space="preserve">0.646922886371613</t>
   </si>
   <si>
     <t xml:space="preserve">0.645069241523743</t>
@@ -1181,7 +1184,7 @@
     <t xml:space="preserve">0.643215596675873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635801017284393</t>
+    <t xml:space="preserve">0.635800957679749</t>
   </si>
   <si>
     <t xml:space="preserve">0.633947372436523</t>
@@ -1196,7 +1199,7 @@
     <t xml:space="preserve">0.62097179889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626532733440399</t>
+    <t xml:space="preserve">0.626532793045044</t>
   </si>
   <si>
     <t xml:space="preserve">0.613557279109955</t>
@@ -1208,7 +1211,7 @@
     <t xml:space="preserve">0.572776973247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583898842334747</t>
+    <t xml:space="preserve">0.583898901939392</t>
   </si>
   <si>
     <t xml:space="preserve">0.578337907791138</t>
@@ -1220,16 +1223,16 @@
     <t xml:space="preserve">0.602435350418091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604289054870605</t>
+    <t xml:space="preserve">0.604288995265961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593167126178741</t>
+    <t xml:space="preserve">0.593167066574097</t>
   </si>
   <si>
     <t xml:space="preserve">0.600581705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595020771026611</t>
+    <t xml:space="preserve">0.595020830631256</t>
   </si>
   <si>
     <t xml:space="preserve">0.589459776878357</t>
@@ -1247,7 +1250,7 @@
     <t xml:space="preserve">0.557947814464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541264951229095</t>
+    <t xml:space="preserve">0.54126501083374</t>
   </si>
   <si>
     <t xml:space="preserve">0.546825885772705</t>
@@ -1262,10 +1265,10 @@
     <t xml:space="preserve">0.563508749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570923388004303</t>
+    <t xml:space="preserve">0.570923328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61726450920105</t>
+    <t xml:space="preserve">0.617264568805695</t>
   </si>
   <si>
     <t xml:space="preserve">0.624679148197174</t>
@@ -1533,6 +1536,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.568000018596649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.572000026702881</t>
   </si>
 </sst>
 </file>
@@ -44425,7 +44431,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44451,7 +44457,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44477,7 +44483,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44503,7 +44509,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44529,7 +44535,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44555,7 +44561,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44581,7 +44587,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44607,7 +44613,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44633,7 +44639,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44659,7 +44665,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44711,7 +44717,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44737,7 +44743,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44763,7 +44769,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44789,7 +44795,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44815,7 +44821,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44841,7 +44847,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44867,7 +44873,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44893,7 +44899,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44919,7 +44925,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44945,7 +44951,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44971,7 +44977,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -44997,7 +45003,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45023,7 +45029,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45049,7 +45055,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45075,7 +45081,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45101,7 +45107,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45127,7 +45133,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45153,7 +45159,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45179,7 +45185,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45205,7 +45211,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45231,7 +45237,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45257,7 +45263,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45283,7 +45289,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45309,7 +45315,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45335,7 +45341,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45361,7 +45367,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45387,7 +45393,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45413,7 +45419,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45439,7 +45445,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45465,7 +45471,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45491,7 +45497,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45517,7 +45523,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45543,7 +45549,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45569,7 +45575,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45595,7 +45601,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45647,7 +45653,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45699,7 +45705,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45725,7 +45731,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45751,7 +45757,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45777,7 +45783,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45803,7 +45809,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45829,7 +45835,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45855,7 +45861,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45881,7 +45887,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45907,7 +45913,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45933,7 +45939,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45959,7 +45965,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45985,7 +45991,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46011,7 +46017,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46037,7 +46043,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46063,7 +46069,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46089,7 +46095,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46115,7 +46121,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46141,7 +46147,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46167,7 +46173,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46193,7 +46199,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46219,7 +46225,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46245,7 +46251,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46271,7 +46277,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46297,7 +46303,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46323,7 +46329,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46349,7 +46355,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46375,7 +46381,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46401,7 +46407,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46427,7 +46433,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46453,7 +46459,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46479,7 +46485,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46505,7 +46511,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46531,7 +46537,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46557,7 +46563,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46583,7 +46589,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46609,7 +46615,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46635,7 +46641,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46661,7 +46667,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46687,7 +46693,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46713,7 +46719,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46739,7 +46745,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46765,7 +46771,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46791,7 +46797,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46817,7 +46823,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46843,7 +46849,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46869,7 +46875,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46895,7 +46901,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46921,7 +46927,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46947,7 +46953,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46973,7 +46979,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -46999,7 +47005,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47025,7 +47031,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47051,7 +47057,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47077,7 +47083,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47103,7 +47109,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47129,7 +47135,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47155,7 +47161,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47181,7 +47187,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47207,7 +47213,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47233,7 +47239,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47259,7 +47265,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47311,7 +47317,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47337,7 +47343,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47363,7 +47369,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47389,7 +47395,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47415,7 +47421,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47441,7 +47447,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47467,7 +47473,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47493,7 +47499,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47519,7 +47525,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47545,7 +47551,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47597,7 +47603,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47623,7 +47629,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47649,7 +47655,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47675,7 +47681,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47701,7 +47707,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47727,7 +47733,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47753,7 +47759,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47779,7 +47785,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47805,7 +47811,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47857,7 +47863,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47883,7 +47889,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47909,7 +47915,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47935,7 +47941,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47961,7 +47967,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48013,7 +48019,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48039,7 +48045,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48065,7 +48071,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48117,7 +48123,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48221,7 +48227,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48247,7 +48253,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48273,7 +48279,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48299,7 +48305,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48325,7 +48331,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48351,7 +48357,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48377,7 +48383,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48403,7 +48409,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48429,7 +48435,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48455,7 +48461,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48481,7 +48487,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48507,7 +48513,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48533,7 +48539,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48559,7 +48565,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48585,7 +48591,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48611,7 +48617,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48637,7 +48643,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48663,7 +48669,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48689,7 +48695,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48715,7 +48721,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48741,7 +48747,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48793,7 +48799,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48819,7 +48825,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48845,7 +48851,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48871,7 +48877,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48897,7 +48903,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48923,7 +48929,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48949,7 +48955,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48975,7 +48981,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49001,7 +49007,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49027,7 +49033,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49053,7 +49059,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49079,7 +49085,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49105,7 +49111,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49131,7 +49137,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49157,7 +49163,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49183,7 +49189,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49209,7 +49215,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49235,7 +49241,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49261,7 +49267,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49287,7 +49293,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49313,7 +49319,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49339,7 +49345,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49365,7 +49371,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49391,7 +49397,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49417,7 +49423,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49443,7 +49449,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49469,7 +49475,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49495,7 +49501,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49521,7 +49527,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49547,7 +49553,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49573,7 +49579,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49599,7 +49605,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49625,7 +49631,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49651,7 +49657,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49677,7 +49683,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49703,7 +49709,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49729,7 +49735,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49755,7 +49761,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49781,7 +49787,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49807,7 +49813,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49833,7 +49839,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49859,7 +49865,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49885,7 +49891,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49911,7 +49917,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49937,7 +49943,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49963,7 +49969,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49989,7 +49995,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50015,7 +50021,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50041,7 +50047,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50067,7 +50073,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50093,7 +50099,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50119,7 +50125,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50145,7 +50151,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50171,7 +50177,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50197,7 +50203,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50223,7 +50229,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50249,7 +50255,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50275,7 +50281,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50301,7 +50307,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50327,7 +50333,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50353,7 +50359,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50379,7 +50385,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50405,7 +50411,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50431,7 +50437,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50457,7 +50463,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50483,7 +50489,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50509,7 +50515,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50535,7 +50541,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50561,7 +50567,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50587,7 +50593,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50613,7 +50619,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50639,7 +50645,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50665,7 +50671,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50691,7 +50697,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50717,7 +50723,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50743,7 +50749,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50769,7 +50775,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50795,7 +50801,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50821,7 +50827,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50847,7 +50853,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50873,7 +50879,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50899,7 +50905,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50925,7 +50931,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50951,7 +50957,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50977,7 +50983,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51003,7 +51009,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51029,7 +51035,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51055,7 +51061,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51081,7 +51087,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51107,7 +51113,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51133,7 +51139,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51159,7 +51165,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51185,7 +51191,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51211,7 +51217,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51237,7 +51243,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51263,7 +51269,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51289,7 +51295,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51315,7 +51321,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51341,7 +51347,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51367,7 +51373,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51393,7 +51399,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51419,7 +51425,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51445,7 +51451,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51471,7 +51477,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51497,7 +51503,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51523,7 +51529,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51549,7 +51555,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51575,7 +51581,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51601,7 +51607,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51627,7 +51633,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51653,7 +51659,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51679,7 +51685,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51705,7 +51711,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51731,7 +51737,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51757,7 +51763,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51783,7 +51789,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51809,7 +51815,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51835,7 +51841,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51861,7 +51867,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51887,7 +51893,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51913,7 +51919,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51939,7 +51945,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -51965,7 +51971,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -51991,7 +51997,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52017,7 +52023,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52043,7 +52049,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52069,7 +52075,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52095,7 +52101,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52121,7 +52127,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52147,7 +52153,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52173,7 +52179,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52199,7 +52205,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52225,7 +52231,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52251,7 +52257,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52277,7 +52283,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52303,7 +52309,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52329,7 +52335,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52355,7 +52361,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52381,7 +52387,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52407,7 +52413,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52433,7 +52439,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52459,7 +52465,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52485,7 +52491,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -52511,7 +52517,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52537,7 +52543,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52563,7 +52569,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52589,7 +52595,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52615,7 +52621,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52641,7 +52647,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52667,7 +52673,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52693,7 +52699,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52719,7 +52725,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52745,7 +52751,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52771,7 +52777,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52797,7 +52803,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52823,7 +52829,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52849,7 +52855,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52875,7 +52881,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52901,7 +52907,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52927,7 +52933,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52953,7 +52959,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52979,7 +52985,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53005,7 +53011,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53031,7 +53037,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53057,7 +53063,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53083,7 +53089,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53109,7 +53115,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53135,7 +53141,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53161,7 +53167,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53187,7 +53193,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53213,7 +53219,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53239,7 +53245,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53265,7 +53271,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53291,7 +53297,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53317,7 +53323,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53343,7 +53349,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53369,7 +53375,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53395,7 +53401,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53421,7 +53427,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53447,7 +53453,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53473,7 +53479,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53499,7 +53505,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53525,7 +53531,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53551,7 +53557,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53577,7 +53583,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53603,7 +53609,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53629,7 +53635,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53655,7 +53661,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53681,7 +53687,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53707,7 +53713,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53733,7 +53739,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53759,7 +53765,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53785,7 +53791,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53811,7 +53817,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53837,7 +53843,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53863,7 +53869,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53889,7 +53895,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53915,7 +53921,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53941,7 +53947,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53967,7 +53973,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53993,7 +53999,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54019,7 +54025,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54045,7 +54051,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54071,7 +54077,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54097,7 +54103,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54123,7 +54129,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54149,7 +54155,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54175,7 +54181,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54201,7 +54207,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54227,7 +54233,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54253,7 +54259,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54279,7 +54285,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54305,7 +54311,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54331,7 +54337,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54357,7 +54363,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54383,7 +54389,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54409,7 +54415,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54435,7 +54441,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54461,7 +54467,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54487,7 +54493,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54513,7 +54519,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54539,7 +54545,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -54565,7 +54571,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54591,7 +54597,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54617,7 +54623,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54643,7 +54649,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54669,7 +54675,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54695,7 +54701,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54721,7 +54727,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54747,7 +54753,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54773,7 +54779,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54799,7 +54805,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54825,7 +54831,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54851,7 +54857,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54877,7 +54883,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54903,7 +54909,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54929,7 +54935,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54955,7 +54961,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54981,7 +54987,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55007,7 +55013,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55033,7 +55039,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55059,7 +55065,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55085,7 +55091,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55111,7 +55117,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55137,7 +55143,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55163,7 +55169,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55189,7 +55195,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55215,7 +55221,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55241,7 +55247,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55267,7 +55273,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55293,7 +55299,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55319,7 +55325,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55345,7 +55351,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55371,7 +55377,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55397,7 +55403,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55423,7 +55429,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55449,7 +55455,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55475,7 +55481,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55501,7 +55507,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55527,7 +55533,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55553,7 +55559,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55579,7 +55585,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55605,7 +55611,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55631,7 +55637,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55657,7 +55663,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55683,7 +55689,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55709,7 +55715,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55735,7 +55741,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55761,7 +55767,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55787,7 +55793,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55813,7 +55819,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55839,7 +55845,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55865,7 +55871,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55891,7 +55897,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55917,7 +55923,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55943,7 +55949,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55969,7 +55975,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -55995,7 +56001,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56021,7 +56027,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56047,7 +56053,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56073,7 +56079,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56099,7 +56105,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56125,7 +56131,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56151,7 +56157,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56177,7 +56183,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56203,7 +56209,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56229,7 +56235,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56255,7 +56261,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56281,7 +56287,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56307,7 +56313,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56333,7 +56339,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56359,7 +56365,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56385,7 +56391,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56411,7 +56417,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56437,7 +56443,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56463,7 +56469,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56489,7 +56495,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56515,7 +56521,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56541,7 +56547,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56567,7 +56573,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56593,7 +56599,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56619,7 +56625,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56645,7 +56651,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56671,7 +56677,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56697,7 +56703,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56723,7 +56729,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56749,7 +56755,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56775,7 +56781,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56801,7 +56807,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56827,7 +56833,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56853,7 +56859,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56879,7 +56885,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56905,7 +56911,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56931,7 +56937,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56957,7 +56963,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56983,7 +56989,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57009,7 +57015,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57035,7 +57041,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57061,7 +57067,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57087,7 +57093,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57113,7 +57119,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57139,7 +57145,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -57165,7 +57171,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57191,7 +57197,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57217,7 +57223,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57243,7 +57249,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57269,7 +57275,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57295,7 +57301,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57321,7 +57327,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57347,7 +57353,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57373,7 +57379,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57399,7 +57405,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57425,7 +57431,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57451,7 +57457,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57477,7 +57483,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57503,7 +57509,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57529,7 +57535,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57555,7 +57561,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57581,7 +57587,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57607,7 +57613,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57633,7 +57639,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57659,7 +57665,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57685,7 +57691,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57711,7 +57717,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57737,7 +57743,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57763,7 +57769,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57789,7 +57795,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57815,7 +57821,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57841,7 +57847,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57867,7 +57873,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57893,7 +57899,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57919,7 +57925,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57945,7 +57951,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57971,7 +57977,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -57997,7 +58003,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58023,7 +58029,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58049,7 +58055,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58075,7 +58081,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58101,7 +58107,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58127,7 +58133,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -58153,7 +58159,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58179,7 +58185,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58205,7 +58211,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58231,7 +58237,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58257,7 +58263,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58283,7 +58289,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58309,7 +58315,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58335,7 +58341,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58361,7 +58367,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58387,7 +58393,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58413,7 +58419,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58439,7 +58445,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58465,7 +58471,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58491,7 +58497,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58517,7 +58523,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58543,7 +58549,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58569,7 +58575,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58595,7 +58601,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58621,7 +58627,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58647,7 +58653,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58673,7 +58679,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58699,7 +58705,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58725,7 +58731,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58751,7 +58757,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58777,7 +58783,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58803,7 +58809,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58829,7 +58835,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58855,7 +58861,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58881,7 +58887,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58907,7 +58913,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58933,7 +58939,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58959,7 +58965,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58985,7 +58991,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59011,7 +59017,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59037,7 +59043,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59063,7 +59069,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59089,7 +59095,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59115,7 +59121,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59141,7 +59147,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59167,7 +59173,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59193,7 +59199,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59219,7 +59225,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59245,7 +59251,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59271,7 +59277,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59297,7 +59303,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59323,7 +59329,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59349,7 +59355,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59375,7 +59381,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59401,7 +59407,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59427,7 +59433,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59453,7 +59459,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59479,7 +59485,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59505,7 +59511,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59531,7 +59537,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59557,7 +59563,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59583,7 +59589,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59609,7 +59615,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59635,7 +59641,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59661,7 +59667,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59687,7 +59693,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59713,7 +59719,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59739,7 +59745,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59765,7 +59771,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59791,7 +59797,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59817,7 +59823,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59843,7 +59849,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59869,7 +59875,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59895,7 +59901,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59921,7 +59927,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59947,7 +59953,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59973,7 +59979,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -59999,7 +60005,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60025,7 +60031,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60051,7 +60057,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60077,7 +60083,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60103,7 +60109,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60129,7 +60135,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60155,7 +60161,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60181,7 +60187,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60207,7 +60213,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60233,7 +60239,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60259,7 +60265,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60285,7 +60291,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60311,7 +60317,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60337,7 +60343,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60363,7 +60369,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60389,7 +60395,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60415,7 +60421,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60441,7 +60447,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60467,7 +60473,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60493,7 +60499,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60519,7 +60525,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60545,7 +60551,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60571,7 +60577,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60597,7 +60603,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60623,7 +60629,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60649,7 +60655,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60675,7 +60681,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60701,7 +60707,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60727,7 +60733,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60753,7 +60759,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60779,7 +60785,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60805,7 +60811,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60831,7 +60837,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60857,7 +60863,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60883,7 +60889,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60909,7 +60915,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60935,7 +60941,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60961,7 +60967,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60987,7 +60993,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61013,7 +61019,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61039,7 +61045,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61065,7 +61071,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61091,7 +61097,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61117,7 +61123,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61143,7 +61149,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61169,7 +61175,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61195,7 +61201,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61221,7 +61227,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61247,7 +61253,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61273,7 +61279,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61299,7 +61305,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61325,7 +61331,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61351,7 +61357,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61377,7 +61383,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61403,7 +61409,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61429,7 +61435,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61455,7 +61461,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61481,7 +61487,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61507,7 +61513,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61533,7 +61539,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61559,7 +61565,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61585,7 +61591,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61611,7 +61617,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61637,7 +61643,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61663,7 +61669,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61689,7 +61695,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61715,7 +61721,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61741,7 +61747,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61767,7 +61773,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61793,7 +61799,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61819,7 +61825,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61845,7 +61851,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61871,7 +61877,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61897,7 +61903,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61923,7 +61929,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61949,7 +61955,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61975,7 +61981,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62001,7 +62007,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62027,7 +62033,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62053,7 +62059,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62079,7 +62085,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62105,7 +62111,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62131,7 +62137,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62157,7 +62163,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62183,7 +62189,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62209,7 +62215,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62235,7 +62241,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62261,7 +62267,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62287,7 +62293,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62313,7 +62319,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62339,7 +62345,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62365,7 +62371,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62391,7 +62397,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62417,7 +62423,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62443,7 +62449,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62469,7 +62475,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62495,7 +62501,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62521,7 +62527,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62547,7 +62553,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62573,7 +62579,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62599,7 +62605,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62625,7 +62631,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62651,7 +62657,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62677,7 +62683,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62703,7 +62709,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62729,7 +62735,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62755,7 +62761,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62781,7 +62787,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62807,7 +62813,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62833,7 +62839,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62859,7 +62865,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62885,7 +62891,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62911,7 +62917,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62937,7 +62943,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62963,7 +62969,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62989,7 +62995,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63015,7 +63021,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63041,7 +63047,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63067,7 +63073,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63093,7 +63099,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63119,7 +63125,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63145,7 +63151,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63171,7 +63177,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63197,7 +63203,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63223,7 +63229,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63249,7 +63255,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63275,7 +63281,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63301,7 +63307,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63327,7 +63333,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63353,7 +63359,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63379,7 +63385,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63405,7 +63411,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63431,7 +63437,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63457,7 +63463,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63483,7 +63489,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63509,7 +63515,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63535,7 +63541,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63561,7 +63567,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63587,7 +63593,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63613,7 +63619,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63639,7 +63645,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63665,7 +63671,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63691,7 +63697,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63717,7 +63723,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63743,7 +63749,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63769,7 +63775,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63795,7 +63801,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63821,7 +63827,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63847,7 +63853,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63873,7 +63879,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63899,7 +63905,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63925,7 +63931,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63951,7 +63957,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63977,7 +63983,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64003,7 +64009,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64029,7 +64035,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64055,7 +64061,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64081,7 +64087,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64107,7 +64113,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64133,7 +64139,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64159,7 +64165,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64185,7 +64191,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64211,7 +64217,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64237,7 +64243,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64263,7 +64269,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64289,7 +64295,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64315,7 +64321,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64341,7 +64347,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64367,7 +64373,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64393,7 +64399,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64419,7 +64425,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64445,7 +64451,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64471,7 +64477,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64497,7 +64503,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64523,7 +64529,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64549,7 +64555,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64575,7 +64581,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64601,7 +64607,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64627,7 +64633,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64653,7 +64659,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64679,7 +64685,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64705,7 +64711,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64731,7 +64737,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64757,7 +64763,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64783,7 +64789,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64809,7 +64815,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64835,7 +64841,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64861,7 +64867,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64887,7 +64893,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64913,7 +64919,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64939,7 +64945,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64965,7 +64971,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64991,7 +64997,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65017,7 +65023,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65043,7 +65049,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65069,7 +65075,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65095,7 +65101,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65121,7 +65127,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65147,7 +65153,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65173,7 +65179,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65199,7 +65205,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65225,7 +65231,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65251,7 +65257,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65277,7 +65283,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65303,7 +65309,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65329,7 +65335,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65355,7 +65361,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65381,7 +65387,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65407,7 +65413,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65433,7 +65439,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65459,7 +65465,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65485,7 +65491,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65511,7 +65517,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65537,7 +65543,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65563,7 +65569,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65589,7 +65595,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65615,7 +65621,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65641,7 +65647,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65667,7 +65673,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65693,7 +65699,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65719,7 +65725,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65745,7 +65751,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65771,7 +65777,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65797,7 +65803,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65823,7 +65829,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65849,7 +65855,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65875,7 +65881,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65901,7 +65907,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65927,7 +65933,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65953,7 +65959,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65979,7 +65985,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66005,7 +66011,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66031,7 +66037,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66057,7 +66063,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66083,7 +66089,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66109,7 +66115,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66135,7 +66141,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66161,7 +66167,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66187,7 +66193,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66213,7 +66219,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66239,7 +66245,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66265,7 +66271,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66291,7 +66297,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66317,7 +66323,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66343,7 +66349,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66369,7 +66375,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66395,7 +66401,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66421,7 +66427,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66447,7 +66453,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66473,7 +66479,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66499,7 +66505,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66525,7 +66531,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66533,7 +66539,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.2920717593</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>3637</v>
@@ -66551,9 +66557,35 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6449768519</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>3718</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>0.572000026702881</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>0.561999976634979</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>0.572000026702881</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,7 +44,7 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394716262817</t>
+    <t xml:space="preserve">0.235394701361656</t>
   </si>
   <si>
     <t xml:space="preserve">0.228249102830887</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581363558769</t>
+    <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210174262523651</t>
+    <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
     <t xml:space="preserve">0.211099103093147</t>
@@ -65,55 +65,55 @@
     <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921487927437</t>
+    <t xml:space="preserve">0.228921517729759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071806788445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293369412422</t>
+    <t xml:space="preserve">0.233293399214745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228417411446571</t>
+    <t xml:space="preserve">0.22841739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231527775526047</t>
+    <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
     <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598259329796</t>
+    <t xml:space="preserve">0.239598244428635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784891724586</t>
+    <t xml:space="preserve">0.222784906625748</t>
   </si>
   <si>
     <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014956235886</t>
+    <t xml:space="preserve">0.211014941334724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970704555511</t>
+    <t xml:space="preserve">0.205970719456673</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767146587372</t>
+    <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563603520393</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607855200768</t>
+    <t xml:space="preserve">0.202607870101929</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187076210976</t>
+    <t xml:space="preserve">0.202187091112137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214127898216</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
     <t xml:space="preserve">0.208912760019302</t>
@@ -137,37 +137,37 @@
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218514204025</t>
+    <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616598010063</t>
+    <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987600326538</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031866908073</t>
+    <t xml:space="preserve">0.232031852006912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235439777374</t>
+    <t xml:space="preserve">0.236235409975052</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279661655426</t>
+    <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483249425888</t>
+    <t xml:space="preserve">0.245483219623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208918333054</t>
+    <t xml:space="preserve">0.252208948135376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093893527985</t>
+    <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138175010681</t>
+    <t xml:space="preserve">0.263138204813004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182456493378</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
     <t xml:space="preserve">0.273226678371429</t>
@@ -176,22 +176,22 @@
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836458206177</t>
+    <t xml:space="preserve">0.285836517810822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562216520309</t>
+    <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447161912918</t>
+    <t xml:space="preserve">0.29844719171524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332137107849</t>
+    <t xml:space="preserve">0.304332107305527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057776212692</t>
+    <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531019449234</t>
+    <t xml:space="preserve">0.317531049251556</t>
   </si>
   <si>
     <t xml:space="preserve">0.322827786207199</t>
@@ -206,25 +206,25 @@
     <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313839435577</t>
+    <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941409111023</t>
+    <t xml:space="preserve">0.411941438913345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420348525047302</t>
+    <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
     <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684838056564</t>
+    <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400911092758</t>
+    <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011584997177</t>
+    <t xml:space="preserve">0.4960116147995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49651563167572</t>
+    <t xml:space="preserve">0.496515661478043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307841777802</t>
+    <t xml:space="preserve">0.492307901382446</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319335460663</t>
+    <t xml:space="preserve">0.715319275856018</t>
   </si>
   <si>
     <t xml:space="preserve">0.673241674900055</t>
@@ -260,16 +260,16 @@
     <t xml:space="preserve">0.65641051530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61854076385498</t>
+    <t xml:space="preserve">0.618540823459625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274843454361</t>
+    <t xml:space="preserve">0.622748553752899</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525969982147217</t>
+    <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
     <t xml:space="preserve">0.521762192249298</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931271076202</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509138941764832</t>
+    <t xml:space="preserve">0.509139001369476</t>
   </si>
   <si>
     <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346791267395</t>
+    <t xml:space="preserve">0.51334673166275</t>
   </si>
   <si>
     <t xml:space="preserve">0.530177772045135</t>
@@ -311,19 +311,19 @@
     <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684591293335</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433399260044098</t>
+    <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607049942017</t>
+    <t xml:space="preserve">0.437607079744339</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230330228806</t>
+    <t xml:space="preserve">0.450230300426483</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022540330887</t>
@@ -338,40 +338,40 @@
     <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191499948502</t>
+    <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385561943054</t>
+    <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476890802383</t>
+    <t xml:space="preserve">0.475476920604706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677343606949</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409807443619</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381524562836</t>
+    <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360459566116</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726661682129</t>
+    <t xml:space="preserve">0.415726721286774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814780235291</t>
+    <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092893600464</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994257450104</t>
+    <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
     <t xml:space="preserve">0.407311171293259</t>
@@ -389,10 +389,10 @@
     <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895621299744</t>
+    <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578737258911</t>
+    <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
     <t xml:space="preserve">0.393846362829208</t>
@@ -413,13 +413,13 @@
     <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374217271805</t>
+    <t xml:space="preserve">0.31137427687645</t>
   </si>
   <si>
     <t xml:space="preserve">0.336620837450027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32988840341568</t>
+    <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
     <t xml:space="preserve">0.32820525765419</t>
@@ -428,31 +428,31 @@
     <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3248390853405</t>
+    <t xml:space="preserve">0.324839115142822</t>
   </si>
   <si>
     <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184282064438</t>
+    <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
     <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345036327838898</t>
+    <t xml:space="preserve">0.34503635764122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3500856757164</t>
+    <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
     <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571489572525</t>
+    <t xml:space="preserve">0.331571459770203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343353241682053</t>
+    <t xml:space="preserve">0.343353182077408</t>
   </si>
   <si>
     <t xml:space="preserve">0.333254605531693</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212594747543</t>
+    <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747756481171</t>
+    <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797014951706</t>
+    <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698378801346</t>
+    <t xml:space="preserve">0.378698438405991</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332176685333</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
     <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015322446823</t>
+    <t xml:space="preserve">0.377015292644501</t>
   </si>
   <si>
     <t xml:space="preserve">0.371966004371643</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233540534973</t>
+    <t xml:space="preserve">0.365233510732651</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593292236328</t>
+    <t xml:space="preserve">0.538593232631683</t>
   </si>
   <si>
     <t xml:space="preserve">0.559632062911987</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783316850662</t>
+    <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48473396897316</t>
+    <t xml:space="preserve">0.484733939170837</t>
   </si>
   <si>
     <t xml:space="preserve">0.476318418979645</t>
@@ -536,49 +536,49 @@
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49146643280983</t>
+    <t xml:space="preserve">0.491466403007507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198807239532</t>
+    <t xml:space="preserve">0.49819877743721</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494656085968</t>
+    <t xml:space="preserve">0.528494596481323</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520079076290131</t>
+    <t xml:space="preserve">0.520079135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811540126801</t>
+    <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910235881805</t>
+    <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523445308208466</t>
+    <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661426782608</t>
+    <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663675308228</t>
+    <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
     <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297383785248</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.49314945936203</t>
   </si>
   <si>
     <t xml:space="preserve">0.509980499744415</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,25 +599,25 @@
     <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374984741211</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860888004303</t>
+    <t xml:space="preserve">0.531860947608948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396079540253</t>
+    <t xml:space="preserve">0.518396019935608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671302318573</t>
+    <t xml:space="preserve">0.51671290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019789218903</t>
+    <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
     <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533544063568115</t>
+    <t xml:space="preserve">0.533543944358826</t>
   </si>
   <si>
     <t xml:space="preserve">0.530068159103394</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">0.528330206871033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709490776062</t>
+    <t xml:space="preserve">0.545709431171417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661120891571</t>
+    <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.549185395240784</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971598148346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542233645915985</t>
+    <t xml:space="preserve">0.54223358631134</t>
   </si>
   <si>
     <t xml:space="preserve">0.538757741451263</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">0.568302571773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559612929821014</t>
+    <t xml:space="preserve">0.55961287021637</t>
   </si>
   <si>
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378576755524</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514426827430725</t>
+    <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
     <t xml:space="preserve">0.502261281013489</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571698665619</t>
+    <t xml:space="preserve">0.493571668863297</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419807910919</t>
+    <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323187351227</t>
+    <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
     <t xml:space="preserve">0.599585235118866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895652770996</t>
+    <t xml:space="preserve">0.590895593166351</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -719,37 +719,37 @@
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58915764093399</t>
+    <t xml:space="preserve">0.589157700538635</t>
   </si>
   <si>
     <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102370738983</t>
+    <t xml:space="preserve">0.669102430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288532733917</t>
+    <t xml:space="preserve">0.714288592338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392113208771</t>
+    <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702530860901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605910301208</t>
+    <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653461039066315</t>
+    <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
     <t xml:space="preserve">0.6447713971138</t>
@@ -758,16 +758,16 @@
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.625654280185699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440363883972</t>
+    <t xml:space="preserve">0.620440423488617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819707393646</t>
+    <t xml:space="preserve">0.637819766998291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033444881439</t>
+    <t xml:space="preserve">0.643033504486084</t>
   </si>
   <si>
     <t xml:space="preserve">0.622178375720978</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633485794067</t>
+    <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799091815948</t>
+    <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -791,22 +791,22 @@
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50573718547821</t>
+    <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557875037193298</t>
+    <t xml:space="preserve">0.557874977588654</t>
   </si>
   <si>
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109330654144</t>
   </si>
   <si>
     <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343802928925</t>
+    <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
     <t xml:space="preserve">0.649985194206238</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005809783936</t>
+    <t xml:space="preserve">0.68300586938858</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957499504089</t>
@@ -827,10 +827,10 @@
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743762016296</t>
+    <t xml:space="preserve">0.684743702411652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150681018829</t>
+    <t xml:space="preserve">0.662150740623474</t>
   </si>
   <si>
     <t xml:space="preserve">0.674316227436066</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674895763397</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
     <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60653692483902</t>
+    <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
     <t xml:space="preserve">0.615226626396179</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632825016975403</t>
+    <t xml:space="preserve">0.632824957370758</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239559173584</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62565416097641</t>
+    <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592848300934</t>
+    <t xml:space="preserve">0.591592788696289</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602348983287811</t>
+    <t xml:space="preserve">0.602349042892456</t>
   </si>
   <si>
     <t xml:space="preserve">0.607727110385895</t>
@@ -899,25 +899,25 @@
     <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623861491680145</t>
+    <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690635681152</t>
+    <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618483364582062</t>
+    <t xml:space="preserve">0.618483304977417</t>
   </si>
   <si>
     <t xml:space="preserve">0.604141712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58800733089447</t>
+    <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
     <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577251136302948</t>
+    <t xml:space="preserve">0.577251076698303</t>
   </si>
   <si>
     <t xml:space="preserve">0.593385517597198</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">0.580836534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582629263401031</t>
+    <t xml:space="preserve">0.582629203796387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579043924808502</t>
@@ -944,7 +944,7 @@
     <t xml:space="preserve">0.55215322971344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873009204865</t>
+    <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -956,16 +956,16 @@
     <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032288074493</t>
+    <t xml:space="preserve">0.631032347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613105237483978</t>
+    <t xml:space="preserve">0.613105297088623</t>
   </si>
   <si>
     <t xml:space="preserve">0.611312508583069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.60593444108963</t>
+    <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
     <t xml:space="preserve">0.548567831516266</t>
@@ -974,10 +974,10 @@
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738627910614</t>
+    <t xml:space="preserve">0.555738687515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945958614349</t>
+    <t xml:space="preserve">0.553945899009705</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -1004,40 +1004,40 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.654337525367737</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057245254517</t>
+    <t xml:space="preserve">0.674057185649872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661508321762085</t>
+    <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093719959259</t>
+    <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886389255524</t>
+    <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645373940467834</t>
+    <t xml:space="preserve">0.645374000072479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544677257538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643581211566925</t>
+    <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166669368744</t>
+    <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264516353607</t>
+    <t xml:space="preserve">0.672264575958252</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471787452698</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009253025055</t>
+    <t xml:space="preserve">0.73500919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460210323334</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765507221222</t>
+    <t xml:space="preserve">0.745765447616577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73680192232132</t>
+    <t xml:space="preserve">0.736801981925964</t>
   </si>
   <si>
     <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742180049419403</t>
+    <t xml:space="preserve">0.742180109024048</t>
   </si>
   <si>
     <t xml:space="preserve">0.708118617534637</t>
@@ -1094,19 +1094,19 @@
     <t xml:space="preserve">0.704533219337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713496744632721</t>
+    <t xml:space="preserve">0.713496804237366</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700947761535645</t>
+    <t xml:space="preserve">0.700947821140289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706325948238373</t>
+    <t xml:space="preserve">0.706325888633728</t>
   </si>
   <si>
     <t xml:space="preserve">0.69736236333847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71708220243454</t>
+    <t xml:space="preserve">0.717082142829895</t>
   </si>
   <si>
     <t xml:space="preserve">0.724252998828888</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849974155426</t>
+    <t xml:space="preserve">0.675849914550781</t>
   </si>
   <si>
     <t xml:space="preserve">0.720667600631714</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">0.691984295845032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695569694042206</t>
+    <t xml:space="preserve">0.695569753646851</t>
   </si>
   <si>
     <t xml:space="preserve">0.665459334850311</t>
@@ -1155,6 +1155,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483820915222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -51191,7 +51194,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51217,7 +51220,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51243,7 +51246,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51373,7 +51376,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51399,7 +51402,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51451,7 +51454,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51477,7 +51480,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51503,7 +51506,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51555,7 +51558,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51581,7 +51584,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51685,7 +51688,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51711,7 +51714,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51763,7 +51766,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51789,7 +51792,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51841,7 +51844,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51919,7 +51922,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51945,7 +51948,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52023,7 +52026,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52049,7 +52052,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52075,7 +52078,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52101,7 +52104,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52127,7 +52130,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52153,7 +52156,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52179,7 +52182,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52257,7 +52260,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52283,7 +52286,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>330</v>
+        <v>381</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52309,7 +52312,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52361,7 +52364,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52387,7 +52390,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52413,7 +52416,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52439,7 +52442,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52517,7 +52520,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52543,7 +52546,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52569,7 +52572,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52595,7 +52598,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52621,7 +52624,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52647,7 +52650,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52673,7 +52676,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52699,7 +52702,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52725,7 +52728,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52751,7 +52754,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52777,7 +52780,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52803,7 +52806,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52829,7 +52832,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52855,7 +52858,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52881,7 +52884,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52907,7 +52910,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52933,7 +52936,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52959,7 +52962,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52985,7 +52988,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53011,7 +53014,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53037,7 +53040,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53063,7 +53066,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53089,7 +53092,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53115,7 +53118,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53141,7 +53144,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53167,7 +53170,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53193,7 +53196,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53219,7 +53222,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53245,7 +53248,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53271,7 +53274,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53297,7 +53300,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53323,7 +53326,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53349,7 +53352,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53375,7 +53378,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53401,7 +53404,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53427,7 +53430,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53453,7 +53456,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53479,7 +53482,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53505,7 +53508,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53531,7 +53534,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53557,7 +53560,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53583,7 +53586,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53609,7 +53612,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53635,7 +53638,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53661,7 +53664,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53687,7 +53690,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53713,7 +53716,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53739,7 +53742,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53765,7 +53768,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53791,7 +53794,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53817,7 +53820,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53843,7 +53846,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53869,7 +53872,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53895,7 +53898,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53921,7 +53924,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53947,7 +53950,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53973,7 +53976,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53999,7 +54002,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54025,7 +54028,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54051,7 +54054,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54077,7 +54080,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54103,7 +54106,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54129,7 +54132,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54155,7 +54158,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54181,7 +54184,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54207,7 +54210,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54233,7 +54236,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54259,7 +54262,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54285,7 +54288,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54311,7 +54314,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54337,7 +54340,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54363,7 +54366,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54389,7 +54392,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54415,7 +54418,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54441,7 +54444,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54467,7 +54470,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54493,7 +54496,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54571,7 +54574,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54597,7 +54600,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54623,7 +54626,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54649,7 +54652,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54675,7 +54678,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54701,7 +54704,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54727,7 +54730,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54753,7 +54756,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54779,7 +54782,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54805,7 +54808,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54831,7 +54834,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54857,7 +54860,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54883,7 +54886,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54909,7 +54912,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54935,7 +54938,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54961,7 +54964,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54987,7 +54990,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55013,7 +55016,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55039,7 +55042,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55065,7 +55068,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55091,7 +55094,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55117,7 +55120,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55143,7 +55146,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55169,7 +55172,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55195,7 +55198,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55221,7 +55224,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55247,7 +55250,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55273,7 +55276,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55299,7 +55302,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55325,7 +55328,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55351,7 +55354,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55377,7 +55380,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55403,7 +55406,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55429,7 +55432,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55455,7 +55458,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55481,7 +55484,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55507,7 +55510,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55533,7 +55536,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55559,7 +55562,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55585,7 +55588,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55611,7 +55614,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55637,7 +55640,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55663,7 +55666,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55689,7 +55692,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55715,7 +55718,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55741,7 +55744,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55767,7 +55770,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55793,7 +55796,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55819,7 +55822,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55845,7 +55848,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55871,7 +55874,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55897,7 +55900,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55923,7 +55926,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55949,7 +55952,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55975,7 +55978,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56001,7 +56004,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56027,7 +56030,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56053,7 +56056,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56079,7 +56082,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56105,7 +56108,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56131,7 +56134,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56157,7 +56160,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56183,7 +56186,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56209,7 +56212,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56235,7 +56238,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56261,7 +56264,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56287,7 +56290,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56313,7 +56316,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56339,7 +56342,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56365,7 +56368,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56391,7 +56394,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56417,7 +56420,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56443,7 +56446,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56469,7 +56472,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56495,7 +56498,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56521,7 +56524,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56547,7 +56550,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56573,7 +56576,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56599,7 +56602,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56625,7 +56628,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56651,7 +56654,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56677,7 +56680,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56703,7 +56706,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56729,7 +56732,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56755,7 +56758,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56781,7 +56784,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56807,7 +56810,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56833,7 +56836,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56859,7 +56862,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56885,7 +56888,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56911,7 +56914,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56937,7 +56940,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56963,7 +56966,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56989,7 +56992,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57015,7 +57018,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57041,7 +57044,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57093,7 +57096,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57119,7 +57122,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57171,7 +57174,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57197,7 +57200,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57223,7 +57226,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57249,7 +57252,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57275,7 +57278,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57301,7 +57304,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57327,7 +57330,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57353,7 +57356,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57379,7 +57382,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57405,7 +57408,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57431,7 +57434,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57457,7 +57460,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57483,7 +57486,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57509,7 +57512,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57535,7 +57538,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57561,7 +57564,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57587,7 +57590,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57613,7 +57616,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57639,7 +57642,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57665,7 +57668,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57691,7 +57694,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57717,7 +57720,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57743,7 +57746,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57769,7 +57772,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57795,7 +57798,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57821,7 +57824,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57847,7 +57850,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57873,7 +57876,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57899,7 +57902,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57925,7 +57928,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57951,7 +57954,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57977,7 +57980,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58003,7 +58006,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58029,7 +58032,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58055,7 +58058,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58081,7 +58084,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58107,7 +58110,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58159,7 +58162,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58185,7 +58188,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58211,7 +58214,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58237,7 +58240,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58263,7 +58266,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58289,7 +58292,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58315,7 +58318,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58341,7 +58344,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58367,7 +58370,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58393,7 +58396,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58419,7 +58422,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58445,7 +58448,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58471,7 +58474,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58497,7 +58500,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58523,7 +58526,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58549,7 +58552,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58575,7 +58578,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58601,7 +58604,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58627,7 +58630,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58653,7 +58656,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58679,7 +58682,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58705,7 +58708,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58731,7 +58734,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58757,7 +58760,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58783,7 +58786,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58809,7 +58812,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58835,7 +58838,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58861,7 +58864,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58887,7 +58890,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58913,7 +58916,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58939,7 +58942,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58965,7 +58968,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58991,7 +58994,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59017,7 +59020,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59043,7 +59046,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59069,7 +59072,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59095,7 +59098,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59121,7 +59124,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59147,7 +59150,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59173,7 +59176,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59199,7 +59202,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59225,7 +59228,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59251,7 +59254,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59277,7 +59280,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59303,7 +59306,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59329,7 +59332,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59355,7 +59358,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59381,7 +59384,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59407,7 +59410,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59433,7 +59436,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59459,7 +59462,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59485,7 +59488,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59511,7 +59514,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59537,7 +59540,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59563,7 +59566,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59589,7 +59592,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59615,7 +59618,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59641,7 +59644,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59667,7 +59670,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59693,7 +59696,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59719,7 +59722,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59745,7 +59748,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59771,7 +59774,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59797,7 +59800,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59823,7 +59826,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59849,7 +59852,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59875,7 +59878,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59901,7 +59904,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59927,7 +59930,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59953,7 +59956,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59979,7 +59982,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60005,7 +60008,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60031,7 +60034,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60057,7 +60060,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60083,7 +60086,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60109,7 +60112,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60135,7 +60138,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60161,7 +60164,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60187,7 +60190,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60213,7 +60216,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60239,7 +60242,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60265,7 +60268,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60291,7 +60294,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60317,7 +60320,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60343,7 +60346,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60369,7 +60372,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60395,7 +60398,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60421,7 +60424,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60447,7 +60450,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60473,7 +60476,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60499,7 +60502,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60525,7 +60528,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60551,7 +60554,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60577,7 +60580,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60603,7 +60606,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60629,7 +60632,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60655,7 +60658,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60681,7 +60684,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60707,7 +60710,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60733,7 +60736,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60759,7 +60762,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60785,7 +60788,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60811,7 +60814,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60837,7 +60840,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60863,7 +60866,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60889,7 +60892,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60915,7 +60918,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60941,7 +60944,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60967,7 +60970,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60993,7 +60996,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61019,7 +61022,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61045,7 +61048,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61071,7 +61074,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61097,7 +61100,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61123,7 +61126,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61149,7 +61152,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61175,7 +61178,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61201,7 +61204,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61227,7 +61230,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61253,7 +61256,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61279,7 +61282,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61305,7 +61308,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61331,7 +61334,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61357,7 +61360,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61383,7 +61386,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61409,7 +61412,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61435,7 +61438,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61461,7 +61464,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61487,7 +61490,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61513,7 +61516,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61539,7 +61542,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61565,7 +61568,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61591,7 +61594,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61617,7 +61620,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61643,7 +61646,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61669,7 +61672,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61695,7 +61698,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61721,7 +61724,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61747,7 +61750,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61773,7 +61776,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61799,7 +61802,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61825,7 +61828,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61851,7 +61854,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61877,7 +61880,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61903,7 +61906,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61929,7 +61932,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61955,7 +61958,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61981,7 +61984,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62007,7 +62010,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62033,7 +62036,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62059,7 +62062,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62085,7 +62088,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62111,7 +62114,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62137,7 +62140,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62163,7 +62166,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62189,7 +62192,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62215,7 +62218,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62241,7 +62244,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62267,7 +62270,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62293,7 +62296,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62319,7 +62322,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62345,7 +62348,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62371,7 +62374,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62397,7 +62400,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62423,7 +62426,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62449,7 +62452,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62475,7 +62478,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62501,7 +62504,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62527,7 +62530,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62553,7 +62556,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62579,7 +62582,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62605,7 +62608,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62631,7 +62634,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62657,7 +62660,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62683,7 +62686,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62709,7 +62712,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62735,7 +62738,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62761,7 +62764,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62787,7 +62790,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62813,7 +62816,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62839,7 +62842,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62865,7 +62868,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62891,7 +62894,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62917,7 +62920,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62943,7 +62946,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62969,7 +62972,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62995,7 +62998,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63021,7 +63024,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63047,7 +63050,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63073,7 +63076,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63099,7 +63102,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63125,7 +63128,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63151,7 +63154,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63177,7 +63180,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63203,7 +63206,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63229,7 +63232,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63255,7 +63258,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63281,7 +63284,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63307,7 +63310,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63333,7 +63336,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63359,7 +63362,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63385,7 +63388,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63411,7 +63414,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63437,7 +63440,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63463,7 +63466,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63489,7 +63492,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63515,7 +63518,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63541,7 +63544,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63567,7 +63570,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63593,7 +63596,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63619,7 +63622,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63645,7 +63648,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63671,7 +63674,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63697,7 +63700,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63723,7 +63726,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63749,7 +63752,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63775,7 +63778,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63801,7 +63804,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63827,7 +63830,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63853,7 +63856,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63879,7 +63882,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63905,7 +63908,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63931,7 +63934,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63957,7 +63960,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63983,7 +63986,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64009,7 +64012,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64035,7 +64038,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64061,7 +64064,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64087,7 +64090,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64113,7 +64116,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64139,7 +64142,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64165,7 +64168,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64191,7 +64194,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64217,7 +64220,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64243,7 +64246,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64269,7 +64272,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64295,7 +64298,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64321,7 +64324,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64347,7 +64350,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64373,7 +64376,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64399,7 +64402,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64425,7 +64428,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64451,7 +64454,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64477,7 +64480,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64503,7 +64506,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64529,7 +64532,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64555,7 +64558,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64581,7 +64584,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64607,7 +64610,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64633,7 +64636,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64659,7 +64662,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64685,7 +64688,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64711,7 +64714,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64737,7 +64740,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64763,7 +64766,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64789,7 +64792,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64815,7 +64818,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64841,7 +64844,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64867,7 +64870,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64893,7 +64896,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64919,7 +64922,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64945,7 +64948,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64971,7 +64974,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64997,7 +65000,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65023,7 +65026,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65049,7 +65052,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65075,7 +65078,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65101,7 +65104,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65127,7 +65130,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65153,7 +65156,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65179,7 +65182,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65205,7 +65208,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65231,7 +65234,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65257,7 +65260,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65283,7 +65286,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65309,7 +65312,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65335,7 +65338,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65361,7 +65364,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65387,7 +65390,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65413,7 +65416,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65439,7 +65442,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65465,7 +65468,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65491,7 +65494,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65517,7 +65520,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65543,7 +65546,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65569,7 +65572,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65595,7 +65598,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65621,7 +65624,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65647,7 +65650,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65673,7 +65676,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65699,7 +65702,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65725,7 +65728,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65751,7 +65754,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65777,7 +65780,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65803,7 +65806,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65829,7 +65832,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65855,7 +65858,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65881,7 +65884,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65907,7 +65910,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65933,7 +65936,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65959,7 +65962,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65985,7 +65988,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66011,7 +66014,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66037,7 +66040,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66063,7 +66066,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66089,7 +66092,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66115,7 +66118,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66141,7 +66144,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66167,7 +66170,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66193,7 +66196,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66219,7 +66222,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66245,7 +66248,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66271,7 +66274,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66297,7 +66300,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66323,7 +66326,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66349,7 +66352,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66375,7 +66378,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66401,7 +66404,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66427,7 +66430,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66453,7 +66456,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66479,7 +66482,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66505,7 +66508,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66531,7 +66534,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66557,7 +66560,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66565,7 +66568,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6449768519</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>3718</v>
@@ -66583,9 +66586,35 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2489" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6495486111</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>3100</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>0.561999976634979</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>0.561999976634979</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>506</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394701361656</t>
+    <t xml:space="preserve">0.23539474606514</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249102830887</t>
+    <t xml:space="preserve">0.228249117732048</t>
   </si>
   <si>
     <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581348657608</t>
+    <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099103093147</t>
+    <t xml:space="preserve">0.211099117994308</t>
   </si>
   <si>
     <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921517729759</t>
+    <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
     <t xml:space="preserve">0.227071806788445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293399214745</t>
+    <t xml:space="preserve">0.233293354511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.22841739654541</t>
@@ -80,31 +80,31 @@
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762211441994</t>
+    <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598244428635</t>
+    <t xml:space="preserve">0.239598229527473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868219017982</t>
+    <t xml:space="preserve">0.222868204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784906625748</t>
+    <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
     <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014941334724</t>
+    <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970719456673</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767161488533</t>
+    <t xml:space="preserve">0.201767131686211</t>
   </si>
   <si>
     <t xml:space="preserve">0.197563588619232</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
@@ -122,13 +122,13 @@
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607870101929</t>
+    <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187091112137</t>
+    <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
     <t xml:space="preserve">0.208912760019302</t>
@@ -137,34 +137,34 @@
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218499302864</t>
+    <t xml:space="preserve">0.215218484401703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616568207741</t>
   </si>
   <si>
     <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031852006912</t>
+    <t xml:space="preserve">0.232031881809235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235409975052</t>
+    <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
     <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483219623566</t>
+    <t xml:space="preserve">0.245483234524727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208948135376</t>
+    <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
     <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138204813004</t>
+    <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
     <t xml:space="preserve">0.268182426691055</t>
@@ -173,25 +173,25 @@
     <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281632959842682</t>
+    <t xml:space="preserve">0.281632989645004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.29844719171524</t>
+    <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332107305527</t>
+    <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057806015015</t>
+    <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531049251556</t>
+    <t xml:space="preserve">0.317531079053879</t>
   </si>
   <si>
     <t xml:space="preserve">0.322827786207199</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455326080322</t>
+    <t xml:space="preserve">0.356455385684967</t>
   </si>
   <si>
     <t xml:space="preserve">0.36318102478981</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941438913345</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684808254242</t>
+    <t xml:space="preserve">0.439684867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471714019775</t>
+    <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400940895081</t>
+    <t xml:space="preserve">0.483400970697403</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4960116147995</t>
+    <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515661478043</t>
+    <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
     <t xml:space="preserve">0.492307901382446</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">0.589086413383484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63957953453064</t>
+    <t xml:space="preserve">0.639579594135284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319275856018</t>
+    <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241674900055</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641051530838</t>
+    <t xml:space="preserve">0.65641063451767</t>
   </si>
   <si>
     <t xml:space="preserve">0.618540823459625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748553752899</t>
+    <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255373001099</t>
+    <t xml:space="preserve">0.572255313396454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525970041751862</t>
+    <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762192249298</t>
+    <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
     <t xml:space="preserve">0.488100200891495</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008752822876</t>
+    <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
     <t xml:space="preserve">0.509139001369476</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51334673166275</t>
+    <t xml:space="preserve">0.513346672058105</t>
   </si>
   <si>
     <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554521560669</t>
+    <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
     <t xml:space="preserve">0.471269160509109</t>
@@ -311,31 +311,31 @@
     <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684621095657</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607079744339</t>
+    <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230300426483</t>
+    <t xml:space="preserve">0.450230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022540330887</t>
+    <t xml:space="preserve">0.446022570133209</t>
   </si>
   <si>
     <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944969177246</t>
+    <t xml:space="preserve">0.403944909572601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776009559631</t>
+    <t xml:space="preserve">0.420776039361954</t>
   </si>
   <si>
     <t xml:space="preserve">0.429191529750824</t>
@@ -347,28 +347,28 @@
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476920604706</t>
+    <t xml:space="preserve">0.475476831197739</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677343606949</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381494760513</t>
+    <t xml:space="preserve">0.380381554365158</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360489368439</t>
+    <t xml:space="preserve">0.412360519170761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726721286774</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
     <t xml:space="preserve">0.441814810037613</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163246870041</t>
+    <t xml:space="preserve">0.392163217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
@@ -395,34 +395,34 @@
     <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261823415756</t>
+    <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529419183731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113928794861</t>
+    <t xml:space="preserve">0.387113898992538</t>
   </si>
   <si>
     <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155969381332</t>
+    <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31137427687645</t>
+    <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620837450027</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
     <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32820525765419</t>
+    <t xml:space="preserve">0.328205317258835</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522201299667</t>
@@ -431,40 +431,40 @@
     <t xml:space="preserve">0.324839115142822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353451818227768</t>
+    <t xml:space="preserve">0.35345184803009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184252262115</t>
+    <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
     <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34503635764122</t>
+    <t xml:space="preserve">0.345036298036575</t>
   </si>
   <si>
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303923606873</t>
+    <t xml:space="preserve">0.33830389380455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
     <t xml:space="preserve">0.343353182077408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333254605531693</t>
+    <t xml:space="preserve">0.333254635334015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31978976726532</t>
+    <t xml:space="preserve">0.319789797067642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33493772149086</t>
+    <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33998703956604</t>
+    <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
@@ -473,7 +473,7 @@
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599772453308</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212564945221</t>
+    <t xml:space="preserve">0.397212535142899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383747726678848</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698438405991</t>
+    <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282918214798</t>
+    <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
     <t xml:space="preserve">0.371966004371643</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233510732651</t>
+    <t xml:space="preserve">0.365233570337296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593232631683</t>
+    <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632062911987</t>
+    <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
     <t xml:space="preserve">0.551216542720795</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733939170837</t>
+    <t xml:space="preserve">0.484733909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476318418979645</t>
+    <t xml:space="preserve">0.47631847858429</t>
   </si>
   <si>
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466403007507</t>
+    <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49819877743721</t>
+    <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494596481323</t>
+    <t xml:space="preserve">0.528494715690613</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079135894775</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128424167633</t>
+    <t xml:space="preserve">0.525128483772278</t>
   </si>
   <si>
     <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506614327430725</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663615703583</t>
+    <t xml:space="preserve">0.511663556098938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50324809551239</t>
+    <t xml:space="preserve">0.503248035907745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297443389893</t>
+    <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501565039157867</t>
+    <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
     <t xml:space="preserve">0.49314945936203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509980499744415</t>
+    <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
     <t xml:space="preserve">0.515029847621918</t>
@@ -590,49 +590,49 @@
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227060317993</t>
+    <t xml:space="preserve">0.535227119922638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107508182526</t>
+    <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
     <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860947608948</t>
+    <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396019935608</t>
+    <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671290397644</t>
+    <t xml:space="preserve">0.51671302318573</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53180605173111</t>
+    <t xml:space="preserve">0.531806111335754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533543944358826</t>
+    <t xml:space="preserve">0.533544063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068159103394</t>
+    <t xml:space="preserve">0.530068099498749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281896591187</t>
+    <t xml:space="preserve">0.535281956195831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592254638672</t>
+    <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330206871033</t>
+    <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709431171417</t>
+    <t xml:space="preserve">0.545709550380707</t>
   </si>
   <si>
     <t xml:space="preserve">0.552661180496216</t>
@@ -644,16 +644,16 @@
     <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399132728577</t>
+    <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
     <t xml:space="preserve">0.543971598148346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54223358631134</t>
+    <t xml:space="preserve">0.542233645915985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538757741451263</t>
+    <t xml:space="preserve">0.538757801055908</t>
   </si>
   <si>
     <t xml:space="preserve">0.540495693683624</t>
@@ -683,22 +683,22 @@
     <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833686828613</t>
+    <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571668863297</t>
+    <t xml:space="preserve">0.493571698665619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854362010956</t>
+    <t xml:space="preserve">0.524854302406311</t>
   </si>
   <si>
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640564918518</t>
+    <t xml:space="preserve">0.519640505313873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274877071381</t>
+    <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419748306274</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585235118866</t>
+    <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895593166351</t>
+    <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594371497631073</t>
+    <t xml:space="preserve">0.594371557235718</t>
   </si>
   <si>
     <t xml:space="preserve">0.585681855678558</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102430343628</t>
+    <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288592338562</t>
+    <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
     <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061079978943</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702530860901</t>
+    <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
     <t xml:space="preserve">0.632605850696564</t>
@@ -752,25 +752,25 @@
     <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6447713971138</t>
+    <t xml:space="preserve">0.644771337509155</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654280185699</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440423488617</t>
+    <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819766998291</t>
+    <t xml:space="preserve">0.637819647789001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033504486084</t>
+    <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178375720978</t>
+    <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
     <t xml:space="preserve">0.610012829303741</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557874977588654</t>
+    <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109330654144</t>
+    <t xml:space="preserve">0.596109449863434</t>
   </si>
   <si>
     <t xml:space="preserve">0.611750781536102</t>
@@ -809,16 +809,16 @@
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985134601593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247241973877</t>
+    <t xml:space="preserve">0.648247182369232</t>
   </si>
   <si>
     <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68300586938858</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957499504089</t>
@@ -830,31 +830,31 @@
     <t xml:space="preserve">0.684743702411652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150740623474</t>
+    <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
     <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936883926392</t>
+    <t xml:space="preserve">0.656936943531036</t>
   </si>
   <si>
     <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509349346161</t>
+    <t xml:space="preserve">0.646509289741516</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226626396179</t>
+    <t xml:space="preserve">0.615226566791534</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617745876312</t>
+    <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
     <t xml:space="preserve">0.64178854227066</t>
@@ -863,13 +863,13 @@
     <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632824957370758</t>
+    <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629239559173584</t>
+    <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897906780243</t>
+    <t xml:space="preserve">0.614897966384888</t>
   </si>
   <si>
     <t xml:space="preserve">0.625654220581055</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">0.600556254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602349042892456</t>
+    <t xml:space="preserve">0.602348983287811</t>
   </si>
   <si>
     <t xml:space="preserve">0.607727110385895</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618483304977417</t>
+    <t xml:space="preserve">0.618483364582062</t>
   </si>
   <si>
     <t xml:space="preserve">0.604141712188721</t>
@@ -914,16 +914,16 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589800119400024</t>
+    <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251076698303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385517597198</t>
+    <t xml:space="preserve">0.593385457992554</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573665678501129</t>
+    <t xml:space="preserve">0.573665738105774</t>
   </si>
   <si>
     <t xml:space="preserve">0.580836534500122</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">0.582629203796387</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043924808502</t>
+    <t xml:space="preserve">0.579043865203857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324026107788</t>
+    <t xml:space="preserve">0.559324085712433</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55215322971344</t>
+    <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
     <t xml:space="preserve">0.571873068809509</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567831516266</t>
+    <t xml:space="preserve">0.548567891120911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546775162220001</t>
+    <t xml:space="preserve">0.546775102615356</t>
   </si>
   <si>
     <t xml:space="preserve">0.555738687515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945899009705</t>
+    <t xml:space="preserve">0.553945958614349</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -1016,19 +1016,19 @@
     <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
     <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645374000072479</t>
+    <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544677257538</t>
+    <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
     <t xml:space="preserve">0.64358127117157</t>
@@ -1037,19 +1037,19 @@
     <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264575958252</t>
+    <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684813439846039</t>
+    <t xml:space="preserve">0.684813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191626548767</t>
+    <t xml:space="preserve">0.690191566944122</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1058,28 +1058,28 @@
     <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594651222229</t>
+    <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972718715668</t>
+    <t xml:space="preserve">0.743972778320312</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704015731812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727838397026062</t>
+    <t xml:space="preserve">0.727838337421417</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460210323334</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
     <t xml:space="preserve">0.745765447616577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736801981925964</t>
+    <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
     <t xml:space="preserve">0.751143574714661</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">0.742180109024048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708118617534637</t>
+    <t xml:space="preserve">0.708118677139282</t>
   </si>
   <si>
     <t xml:space="preserve">0.704533219337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713496804237366</t>
+    <t xml:space="preserve">0.713496744632721</t>
   </si>
   <si>
     <t xml:space="preserve">0.700947821140289</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">0.706325888633728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.69736236333847</t>
+    <t xml:space="preserve">0.697362422943115</t>
   </si>
   <si>
     <t xml:space="preserve">0.717082142829895</t>
@@ -1115,10 +1115,10 @@
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398838043213</t>
+    <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642643451691</t>
+    <t xml:space="preserve">0.677642703056335</t>
   </si>
   <si>
     <t xml:space="preserve">0.675849914550781</t>
@@ -66594,7 +66594,7 @@
     </row>
     <row r="2490">
       <c r="A2490" s="1" t="n">
-        <v>45945.6495486111</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2490" t="n">
         <v>3100</v>
@@ -66615,6 +66615,32 @@
         <v>506</v>
       </c>
       <c r="H2490" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2491">
+      <c r="A2491" s="1" t="n">
+        <v>45946.6494560185</v>
+      </c>
+      <c r="B2491" t="n">
+        <v>15686</v>
+      </c>
+      <c r="C2491" t="n">
+        <v>0.578000009059906</v>
+      </c>
+      <c r="D2491" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="E2491" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="F2491" t="n">
+        <v>0.578000009059906</v>
+      </c>
+      <c r="G2491" t="s">
+        <v>505</v>
+      </c>
+      <c r="H2491" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815480351448</t>
+    <t xml:space="preserve">0.235815465450287</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249102830887</t>
+    <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899931430817</t>
+    <t xml:space="preserve">0.216899916529655</t>
   </si>
   <si>
     <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21017424762249</t>
+    <t xml:space="preserve">0.210174232721329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099117994308</t>
+    <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
     <t xml:space="preserve">0.217319875955582</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762196540833</t>
+    <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
     <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310569405556</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868219017982</t>
+    <t xml:space="preserve">0.222868204116821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784891724586</t>
+    <t xml:space="preserve">0.222784876823425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21437780559063</t>
+    <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
     <t xml:space="preserve">0.211014971137047</t>
@@ -104,64 +104,64 @@
     <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767161488533</t>
+    <t xml:space="preserve">0.201767131686211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563573718071</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360045552254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20235538482666</t>
+    <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607855200768</t>
+    <t xml:space="preserve">0.202607840299606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187091112137</t>
+    <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214127898216</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912745118141</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762500762939</t>
+    <t xml:space="preserve">0.210762515664101</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218514204025</t>
+    <t xml:space="preserve">0.215218484401703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987615227699</t>
+    <t xml:space="preserve">0.22698763012886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031866908073</t>
+    <t xml:space="preserve">0.232031881809235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235439777374</t>
+    <t xml:space="preserve">0.236235424876213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279676556587</t>
+    <t xml:space="preserve">0.24127970635891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24548327922821</t>
+    <t xml:space="preserve">0.245483234524727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208888530731</t>
+    <t xml:space="preserve">0.252208948135376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093893527985</t>
+    <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447132110596</t>
+    <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
     <t xml:space="preserve">0.304332137107849</t>
@@ -191,67 +191,67 @@
     <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531019449234</t>
+    <t xml:space="preserve">0.317531079053879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827786207199</t>
+    <t xml:space="preserve">0.322827816009521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336279153823853</t>
+    <t xml:space="preserve">0.33627912402153</t>
   </si>
   <si>
     <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36318102478981</t>
+    <t xml:space="preserve">0.363181054592133</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313809633255</t>
+    <t xml:space="preserve">0.378313779830933</t>
   </si>
   <si>
     <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034849524498</t>
+    <t xml:space="preserve">0.420348465442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525591373444</t>
+    <t xml:space="preserve">0.440525561571121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684808254242</t>
+    <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
     <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055836677551</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500215113162994</t>
+    <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
     <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515691280365</t>
+    <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307960987091</t>
+    <t xml:space="preserve">0.492307901382446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670952796936</t>
+    <t xml:space="preserve">0.580670893192291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589086472988129</t>
+    <t xml:space="preserve">0.589086413383484</t>
   </si>
   <si>
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319156646729</t>
+    <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
     <t xml:space="preserve">0.67324161529541</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255432605743</t>
+    <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
     <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762251853943</t>
+    <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100171089172</t>
+    <t xml:space="preserve">0.48810014128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008812427521</t>
@@ -287,43 +287,43 @@
     <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892440795898</t>
+    <t xml:space="preserve">0.483892351388931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346791267395</t>
+    <t xml:space="preserve">0.51334673166275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177772045135</t>
+    <t xml:space="preserve">0.530177712440491</t>
   </si>
   <si>
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269130706787</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061340808868</t>
+    <t xml:space="preserve">0.467061400413513</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853580713272</t>
+    <t xml:space="preserve">0.462853610515594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684680700302</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607020139694</t>
+    <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230360031128</t>
+    <t xml:space="preserve">0.450230330228806</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022570133209</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191499948502</t>
+    <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
     <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542801082134247</t>
+    <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677373409271</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983769655228</t>
+    <t xml:space="preserve">0.424983739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409837245941</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
     <t xml:space="preserve">0.380381524562836</t>
@@ -365,52 +365,52 @@
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360519170761</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814810037613</t>
+    <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628085136414</t>
+    <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
     <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311171293259</t>
+    <t xml:space="preserve">0.407311201095581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163187265396</t>
+    <t xml:space="preserve">0.392163217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578796863556</t>
+    <t xml:space="preserve">0.400578737258911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846333026886</t>
+    <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529419183731</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649090528488</t>
+    <t xml:space="preserve">0.373649120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311374247074127</t>
@@ -419,25 +419,25 @@
     <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888373613358</t>
+    <t xml:space="preserve">0.329888433218002</t>
   </si>
   <si>
     <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522171497345</t>
+    <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
     <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35345184803009</t>
+    <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
     <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768732070923</t>
+    <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036298036575</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303953409195</t>
+    <t xml:space="preserve">0.33830389380455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571519374847</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33325457572937</t>
+    <t xml:space="preserve">0.333254605531693</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339987009763718</t>
+    <t xml:space="preserve">0.339986979961395</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
@@ -473,61 +473,61 @@
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599742650986</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480101108551</t>
+    <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212564945221</t>
+    <t xml:space="preserve">0.397212535142899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797044754028</t>
+    <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698408603668</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064610719681</t>
+    <t xml:space="preserve">0.382064640522003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332236289978</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015322446823</t>
+    <t xml:space="preserve">0.377015292644501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371965974569321</t>
+    <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233570337296</t>
+    <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593232631683</t>
+    <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
     <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216542720795</t>
+    <t xml:space="preserve">0.551216602325439</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733879566193</t>
+    <t xml:space="preserve">0.48473396897316</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198837041855</t>
+    <t xml:space="preserve">0.498198747634888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741216659546</t>
+    <t xml:space="preserve">0.553741276264191</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494656085968</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">0.520079135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811599731445</t>
+    <t xml:space="preserve">0.526811540126801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910235881805</t>
+    <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128543376923</t>
+    <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523445308208466</t>
+    <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506614327430725</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.493149518966675</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
@@ -587,40 +587,40 @@
     <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533543944358826</t>
+    <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227000713348</t>
+    <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107388973236</t>
+    <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374984741211</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860828399658</t>
+    <t xml:space="preserve">0.531860947608948</t>
   </si>
   <si>
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671302318573</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53180605173111</t>
+    <t xml:space="preserve">0.531806111335754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53354400396347</t>
+    <t xml:space="preserve">0.533544063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068099498749</t>
+    <t xml:space="preserve">0.530068159103394</t>
   </si>
   <si>
     <t xml:space="preserve">0.535281956195831</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330147266388</t>
+    <t xml:space="preserve">0.528330206871033</t>
   </si>
   <si>
     <t xml:space="preserve">0.545709490776062</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185335636139</t>
+    <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447502613068</t>
+    <t xml:space="preserve">0.547447383403778</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550923228263855</t>
+    <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378457546234</t>
+    <t xml:space="preserve">0.521378576755524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512688875198364</t>
+    <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514426827430725</t>
+    <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261281013489</t>
+    <t xml:space="preserve">0.502261221408844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50399923324585</t>
+    <t xml:space="preserve">0.503999173641205</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571668863297</t>
+    <t xml:space="preserve">0.493571698665619</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419807910919</t>
+    <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323187351227</t>
+    <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
     <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895593166351</t>
+    <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58915764093399</t>
+    <t xml:space="preserve">0.589157700538635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557659626007</t>
+    <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
     <t xml:space="preserve">0.669102370738983</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364537715912</t>
+    <t xml:space="preserve">0.667364418506622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061020374298</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392172813416</t>
+    <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702471256256</t>
+    <t xml:space="preserve">0.618702411651611</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605910301208</t>
+    <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
     <t xml:space="preserve">0.653461039066315</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440423488617</t>
+    <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
     <t xml:space="preserve">0.637819647789001</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178316116333</t>
+    <t xml:space="preserve">0.622178256511688</t>
   </si>
   <si>
     <t xml:space="preserve">0.610012829303741</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778416633606</t>
+    <t xml:space="preserve">0.571778476238251</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.557874977588654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516368865967</t>
+    <t xml:space="preserve">0.573516428470612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109449863434</t>
   </si>
   <si>
     <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343862533569</t>
+    <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
     <t xml:space="preserve">0.649985194206238</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081695556641</t>
+    <t xml:space="preserve">0.636081755161285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005750179291</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957499504089</t>
+    <t xml:space="preserve">0.689957559108734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688219666481018</t>
+    <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
     <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150740623474</t>
+    <t xml:space="preserve">0.662150621414185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316227436066</t>
+    <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
     <t xml:space="preserve">0.656936883926392</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509289741516</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">0.613488674163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617686271667</t>
+    <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788601875305</t>
+    <t xml:space="preserve">0.641788482666016</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -869,19 +869,22 @@
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897906780243</t>
+    <t xml:space="preserve">0.614897966384888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276033878326</t>
+    <t xml:space="preserve">0.620276093482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592788696289</t>
+    <t xml:space="preserve">0.591592848300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -893,13 +896,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970915794373</t>
+    <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6238614320755</t>
+    <t xml:space="preserve">0.623861491680145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690695285797</t>
+    <t xml:space="preserve">0.616690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -911,13 +914,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58980005979538</t>
+    <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385457992554</t>
+    <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -929,10 +932,10 @@
     <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043865203857</t>
+    <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324085712433</t>
+    <t xml:space="preserve">0.559324026107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -941,19 +944,19 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873068809509</t>
+    <t xml:space="preserve">0.571873009204865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58621472120285</t>
+    <t xml:space="preserve">0.586214661598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178127288818</t>
+    <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032288074493</t>
+    <t xml:space="preserve">0.631032347679138</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -965,7 +968,7 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567831516266</t>
+    <t xml:space="preserve">0.548567891120911</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
@@ -983,13 +986,13 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702212810516</t>
+    <t xml:space="preserve">0.564702153205872</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203144073486</t>
+    <t xml:space="preserve">0.638203084468842</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -1001,64 +1004,64 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337525367737</t>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057185649872</t>
+    <t xml:space="preserve">0.674057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66150826215744</t>
+    <t xml:space="preserve">0.661508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093660354614</t>
+    <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886389255524</t>
+    <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
     <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544796466827</t>
+    <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64358127117157</t>
+    <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166669368744</t>
+    <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471787452698</t>
+    <t xml:space="preserve">0.670471847057343</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020770549774</t>
+    <t xml:space="preserve">0.683020710945129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191507339478</t>
+    <t xml:space="preserve">0.690191566944122</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715289413928986</t>
+    <t xml:space="preserve">0.71528947353363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594591617584</t>
+    <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972718715668</t>
+    <t xml:space="preserve">0.743972778320312</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1067,13 +1070,13 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009133815765</t>
+    <t xml:space="preserve">0.73500919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460329532623</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765388011932</t>
+    <t xml:space="preserve">0.745765447616577</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1106,25 +1109,25 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252998828888</t>
+    <t xml:space="preserve">0.724252939224243</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398897647858</t>
+    <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
     <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849914550781</t>
+    <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667600631714</t>
+    <t xml:space="preserve">0.720667541027069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045727729797</t>
+    <t xml:space="preserve">0.726045668125153</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1152,9 +1155,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -1543,6 +1543,9 @@
   <si>
     <t xml:space="preserve">0.560000002384186</t>
   </si>
+  <si>
+    <t xml:space="preserve">0.565999984741211</t>
+  </si>
 </sst>
 </file>
 
@@ -44434,7 +44437,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44460,7 +44463,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44486,7 +44489,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44512,7 +44515,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44538,7 +44541,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44564,7 +44567,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44590,7 +44593,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44616,7 +44619,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44642,7 +44645,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44668,7 +44671,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44720,7 +44723,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44746,7 +44749,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44772,7 +44775,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44798,7 +44801,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44824,7 +44827,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44850,7 +44853,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44876,7 +44879,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44902,7 +44905,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44928,7 +44931,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44954,7 +44957,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44980,7 +44983,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45006,7 +45009,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45032,7 +45035,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45058,7 +45061,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45084,7 +45087,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45110,7 +45113,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45136,7 +45139,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45162,7 +45165,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45188,7 +45191,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45214,7 +45217,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45240,7 +45243,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45266,7 +45269,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45292,7 +45295,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45318,7 +45321,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45344,7 +45347,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45370,7 +45373,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45396,7 +45399,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45422,7 +45425,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45448,7 +45451,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45474,7 +45477,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45500,7 +45503,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45526,7 +45529,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45552,7 +45555,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45578,7 +45581,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45604,7 +45607,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45656,7 +45659,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45708,7 +45711,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45734,7 +45737,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45760,7 +45763,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45786,7 +45789,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45812,7 +45815,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45838,7 +45841,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45864,7 +45867,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45890,7 +45893,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45916,7 +45919,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45942,7 +45945,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45968,7 +45971,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45994,7 +45997,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46020,7 +46023,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46046,7 +46049,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46072,7 +46075,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46098,7 +46101,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46124,7 +46127,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46150,7 +46153,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46176,7 +46179,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46202,7 +46205,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46228,7 +46231,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46254,7 +46257,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46280,7 +46283,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46306,7 +46309,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46332,7 +46335,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46358,7 +46361,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46384,7 +46387,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46410,7 +46413,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46436,7 +46439,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46462,7 +46465,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46488,7 +46491,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46514,7 +46517,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46540,7 +46543,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46566,7 +46569,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46592,7 +46595,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46618,7 +46621,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46644,7 +46647,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46670,7 +46673,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46696,7 +46699,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46722,7 +46725,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46748,7 +46751,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46774,7 +46777,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46800,7 +46803,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46826,7 +46829,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46852,7 +46855,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46878,7 +46881,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46904,7 +46907,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46930,7 +46933,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46956,7 +46959,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46982,7 +46985,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47008,7 +47011,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47034,7 +47037,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47060,7 +47063,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47086,7 +47089,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47112,7 +47115,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47138,7 +47141,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47164,7 +47167,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47190,7 +47193,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47216,7 +47219,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47242,7 +47245,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47268,7 +47271,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47320,7 +47323,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47346,7 +47349,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47372,7 +47375,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47398,7 +47401,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47424,7 +47427,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47450,7 +47453,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47476,7 +47479,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47502,7 +47505,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47528,7 +47531,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47554,7 +47557,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47606,7 +47609,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47632,7 +47635,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47658,7 +47661,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47684,7 +47687,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47710,7 +47713,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47736,7 +47739,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47762,7 +47765,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47788,7 +47791,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47814,7 +47817,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>248</v>
+        <v>286</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47866,7 +47869,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47892,7 +47895,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47918,7 +47921,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47944,7 +47947,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47970,7 +47973,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48022,7 +48025,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48048,7 +48051,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48074,7 +48077,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48126,7 +48129,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48230,7 +48233,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48256,7 +48259,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48282,7 +48285,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48308,7 +48311,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48334,7 +48337,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48360,7 +48363,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48386,7 +48389,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48412,7 +48415,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48438,7 +48441,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48464,7 +48467,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48490,7 +48493,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48516,7 +48519,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48542,7 +48545,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48568,7 +48571,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48594,7 +48597,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48620,7 +48623,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48646,7 +48649,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48672,7 +48675,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48698,7 +48701,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48724,7 +48727,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48750,7 +48753,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48802,7 +48805,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48828,7 +48831,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48854,7 +48857,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48880,7 +48883,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48906,7 +48909,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48932,7 +48935,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48958,7 +48961,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48984,7 +48987,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49010,7 +49013,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49036,7 +49039,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49062,7 +49065,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49088,7 +49091,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49114,7 +49117,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49140,7 +49143,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49166,7 +49169,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49192,7 +49195,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49218,7 +49221,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49244,7 +49247,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49270,7 +49273,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49296,7 +49299,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49322,7 +49325,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49348,7 +49351,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49374,7 +49377,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49400,7 +49403,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49426,7 +49429,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49452,7 +49455,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49478,7 +49481,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49504,7 +49507,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49530,7 +49533,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49556,7 +49559,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49582,7 +49585,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49608,7 +49611,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49634,7 +49637,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49660,7 +49663,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49686,7 +49689,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49712,7 +49715,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49738,7 +49741,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49764,7 +49767,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49790,7 +49793,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49816,7 +49819,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49842,7 +49845,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49868,7 +49871,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49894,7 +49897,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49920,7 +49923,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49946,7 +49949,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49972,7 +49975,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49998,7 +50001,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50024,7 +50027,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50050,7 +50053,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50076,7 +50079,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50102,7 +50105,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50128,7 +50131,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50154,7 +50157,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50180,7 +50183,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50206,7 +50209,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50232,7 +50235,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50258,7 +50261,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50284,7 +50287,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50310,7 +50313,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50336,7 +50339,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50362,7 +50365,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50388,7 +50391,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50414,7 +50417,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50440,7 +50443,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50466,7 +50469,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50492,7 +50495,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50518,7 +50521,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50544,7 +50547,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50570,7 +50573,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50596,7 +50599,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50622,7 +50625,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50648,7 +50651,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50674,7 +50677,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50700,7 +50703,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50726,7 +50729,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50752,7 +50755,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50778,7 +50781,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50804,7 +50807,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50830,7 +50833,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50856,7 +50859,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50882,7 +50885,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50908,7 +50911,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50934,7 +50937,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50960,7 +50963,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50986,7 +50989,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51012,7 +51015,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51038,7 +51041,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51064,7 +51067,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51090,7 +51093,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51116,7 +51119,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51142,7 +51145,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51168,7 +51171,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51194,7 +51197,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51272,7 +51275,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51298,7 +51301,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51324,7 +51327,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51350,7 +51353,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51428,7 +51431,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51532,7 +51535,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51610,7 +51613,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51636,7 +51639,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51662,7 +51665,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51740,7 +51743,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51818,7 +51821,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51844,7 +51847,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51870,7 +51873,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51896,7 +51899,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51974,7 +51977,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52000,7 +52003,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52052,7 +52055,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52130,7 +52133,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52208,7 +52211,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52234,7 +52237,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52286,7 +52289,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>380</v>
+        <v>330</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52338,7 +52341,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52468,7 +52471,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52494,7 +52497,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54522,7 +54525,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54548,7 +54551,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57070,7 +57073,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57148,7 +57151,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58136,7 +58139,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -66672,7 +66675,7 @@
     </row>
     <row r="2493">
       <c r="A2493" s="1" t="n">
-        <v>45950.6493171296</v>
+        <v>45950.2916666667</v>
       </c>
       <c r="B2493" t="n">
         <v>5010</v>
@@ -66681,7 +66684,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="D2493" t="n">
-        <v>0.561999976634979</v>
+        <v>0.560000002384186</v>
       </c>
       <c r="E2493" t="n">
         <v>0.569999992847443</v>
@@ -66693,6 +66696,32 @@
         <v>509</v>
       </c>
       <c r="H2493" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2494">
+      <c r="A2494" s="1" t="n">
+        <v>45951.5750810185</v>
+      </c>
+      <c r="B2494" t="n">
+        <v>25978</v>
+      </c>
+      <c r="C2494" t="n">
+        <v>0.572000026702881</v>
+      </c>
+      <c r="D2494" t="n">
+        <v>0.554000020027161</v>
+      </c>
+      <c r="E2494" t="n">
+        <v>0.572000026702881</v>
+      </c>
+      <c r="F2494" t="n">
+        <v>0.565999984741211</v>
+      </c>
+      <c r="G2494" t="s">
+        <v>510</v>
+      </c>
+      <c r="H2494" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815465450287</t>
+    <t xml:space="preserve">0.235815480351448</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249087929726</t>
+    <t xml:space="preserve">0.228249102830887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899916529655</t>
+    <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
     <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210174232721329</t>
+    <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099103093147</t>
+    <t xml:space="preserve">0.211099117994308</t>
   </si>
   <si>
     <t xml:space="preserve">0.217319875955582</t>
@@ -80,22 +80,22 @@
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762211441994</t>
+    <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
     <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310569405556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868204116821</t>
+    <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784876823425</t>
+    <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214377820491791</t>
+    <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
     <t xml:space="preserve">0.211014971137047</t>
@@ -104,64 +104,64 @@
     <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767131686211</t>
+    <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563588619232</t>
+    <t xml:space="preserve">0.197563573718071</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360045552254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202355399727821</t>
+    <t xml:space="preserve">0.20235538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607840299606</t>
+    <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187076210976</t>
+    <t xml:space="preserve">0.202187091112137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912760019302</t>
+    <t xml:space="preserve">0.208912745118141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762515664101</t>
+    <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218484401703</t>
+    <t xml:space="preserve">0.215218514204025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616598010063</t>
+    <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22698763012886</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031881809235</t>
+    <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235424876213</t>
+    <t xml:space="preserve">0.236235439777374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24127970635891</t>
+    <t xml:space="preserve">0.241279676556587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483234524727</t>
+    <t xml:space="preserve">0.24548327922821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208948135376</t>
+    <t xml:space="preserve">0.252208888530731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093893527985</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -176,13 +176,13 @@
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836488008499</t>
+    <t xml:space="preserve">0.285836517810822</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447161912918</t>
+    <t xml:space="preserve">0.298447132110596</t>
   </si>
   <si>
     <t xml:space="preserve">0.304332137107849</t>
@@ -191,67 +191,67 @@
     <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531079053879</t>
+    <t xml:space="preserve">0.317531019449234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827816009521</t>
+    <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33627912402153</t>
+    <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
     <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363181054592133</t>
+    <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313779830933</t>
+    <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
     <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420348465442657</t>
+    <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525561571121</t>
+    <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684838056564</t>
+    <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471743822098</t>
+    <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
     <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055896282196</t>
+    <t xml:space="preserve">0.501055836677551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500215172767639</t>
+    <t xml:space="preserve">0.500215113162994</t>
   </si>
   <si>
     <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49651563167572</t>
+    <t xml:space="preserve">0.496515691280365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307901382446</t>
+    <t xml:space="preserve">0.492307960987091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670893192291</t>
+    <t xml:space="preserve">0.580670952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589086413383484</t>
+    <t xml:space="preserve">0.589086472988129</t>
   </si>
   <si>
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319216251373</t>
+    <t xml:space="preserve">0.715319156646729</t>
   </si>
   <si>
     <t xml:space="preserve">0.67324161529541</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255373001099</t>
+    <t xml:space="preserve">0.572255432605743</t>
   </si>
   <si>
     <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762192249298</t>
+    <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48810014128685</t>
+    <t xml:space="preserve">0.488100171089172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931271076202</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008812427521</t>
@@ -287,43 +287,43 @@
     <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892351388931</t>
+    <t xml:space="preserve">0.483892440795898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51334673166275</t>
+    <t xml:space="preserve">0.513346791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177712440491</t>
+    <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269160509109</t>
+    <t xml:space="preserve">0.471269130706787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061400413513</t>
+    <t xml:space="preserve">0.467061340808868</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853610515594</t>
+    <t xml:space="preserve">0.462853580713272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684680700302</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607049942017</t>
+    <t xml:space="preserve">0.437607020139694</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230330228806</t>
+    <t xml:space="preserve">0.450230360031128</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022570133209</t>
@@ -338,25 +338,25 @@
     <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191529750824</t>
+    <t xml:space="preserve">0.429191499948502</t>
   </si>
   <si>
     <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542801022529602</t>
+    <t xml:space="preserve">0.542801082134247</t>
   </si>
   <si>
     <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983739852905</t>
+    <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409837245941</t>
   </si>
   <si>
     <t xml:space="preserve">0.380381524562836</t>
@@ -365,52 +365,52 @@
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360489368439</t>
+    <t xml:space="preserve">0.412360519170761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726661682129</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814780235291</t>
+    <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628055334091</t>
+    <t xml:space="preserve">0.405628085136414</t>
   </si>
   <si>
     <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311201095581</t>
+    <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163217067719</t>
+    <t xml:space="preserve">0.392163187265396</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578737258911</t>
+    <t xml:space="preserve">0.400578796863556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529419183731</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649120330811</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155969381332</t>
+    <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
     <t xml:space="preserve">0.311374247074127</t>
@@ -419,25 +419,25 @@
     <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888433218002</t>
+    <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
     <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522201299667</t>
+    <t xml:space="preserve">0.326522171497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.353451818227768</t>
+    <t xml:space="preserve">0.35345184803009</t>
   </si>
   <si>
     <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036298036575</t>
@@ -446,16 +446,16 @@
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830389380455</t>
+    <t xml:space="preserve">0.338303953409195</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571519374847</t>
+    <t xml:space="preserve">0.331571459770203</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333254605531693</t>
+    <t xml:space="preserve">0.33325457572937</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339986979961395</t>
+    <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
@@ -473,61 +473,61 @@
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36859980225563</t>
+    <t xml:space="preserve">0.368599742650986</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480130910873</t>
+    <t xml:space="preserve">0.390480101108551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212535142899</t>
+    <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797014951706</t>
+    <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698378801346</t>
+    <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064640522003</t>
+    <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332206487656</t>
+    <t xml:space="preserve">0.375332236289978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282918214798</t>
+    <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371966004371643</t>
+    <t xml:space="preserve">0.371965974569321</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233540534973</t>
+    <t xml:space="preserve">0.365233570337296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593292236328</t>
+    <t xml:space="preserve">0.538593232631683</t>
   </si>
   <si>
     <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216602325439</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48473396897316</t>
+    <t xml:space="preserve">0.484733879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198747634888</t>
+    <t xml:space="preserve">0.498198837041855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741276264191</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494656085968</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">0.520079135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811540126801</t>
+    <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910176277161</t>
+    <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128424167633</t>
+    <t xml:space="preserve">0.525128543376923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52344536781311</t>
+    <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661426782608</t>
+    <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149518966675</t>
+    <t xml:space="preserve">0.493149489164352</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
@@ -587,40 +587,40 @@
     <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53354400396347</t>
+    <t xml:space="preserve">0.533543944358826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227060317993</t>
+    <t xml:space="preserve">0.535227000713348</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107508182526</t>
+    <t xml:space="preserve">0.557107388973236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550375044345856</t>
+    <t xml:space="preserve">0.550374984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860947608948</t>
+    <t xml:space="preserve">0.531860828399658</t>
   </si>
   <si>
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671302318573</t>
+    <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533544063568115</t>
+    <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068159103394</t>
+    <t xml:space="preserve">0.530068099498749</t>
   </si>
   <si>
     <t xml:space="preserve">0.535281956195831</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330206871033</t>
+    <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
     <t xml:space="preserve">0.545709490776062</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185395240784</t>
+    <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447502613068</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5509232878685</t>
+    <t xml:space="preserve">0.550923228263855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378576755524</t>
+    <t xml:space="preserve">0.521378457546234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512688815593719</t>
+    <t xml:space="preserve">0.512688875198364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51442676782608</t>
+    <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503999173641205</t>
+    <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571698665619</t>
+    <t xml:space="preserve">0.493571668863297</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419748306274</t>
+    <t xml:space="preserve">0.587419807910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323246955872</t>
+    <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
     <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895652770996</t>
+    <t xml:space="preserve">0.590895593166351</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589157700538635</t>
+    <t xml:space="preserve">0.58915764093399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557600021362</t>
+    <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
     <t xml:space="preserve">0.669102370738983</t>
@@ -731,22 +731,22 @@
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364418506622</t>
+    <t xml:space="preserve">0.667364537715912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061020374298</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392172813416</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702411651611</t>
+    <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605850696564</t>
+    <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
     <t xml:space="preserve">0.653461039066315</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440363883972</t>
+    <t xml:space="preserve">0.620440423488617</t>
   </si>
   <si>
     <t xml:space="preserve">0.637819647789001</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178256511688</t>
+    <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
     <t xml:space="preserve">0.610012829303741</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799091815948</t>
+    <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778476238251</t>
+    <t xml:space="preserve">0.571778416633606</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.557874977588654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516428470612</t>
+    <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109449863434</t>
+    <t xml:space="preserve">0.596109390258789</t>
   </si>
   <si>
     <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343802928925</t>
+    <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
     <t xml:space="preserve">0.649985194206238</t>
@@ -815,25 +815,25 @@
     <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081755161285</t>
+    <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005809783936</t>
+    <t xml:space="preserve">0.683005750179291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957559108734</t>
+    <t xml:space="preserve">0.689957499504089</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688219606876373</t>
+    <t xml:space="preserve">0.688219666481018</t>
   </si>
   <si>
     <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150621414185</t>
+    <t xml:space="preserve">0.662150740623474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316167831421</t>
+    <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
     <t xml:space="preserve">0.656936883926392</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509349346161</t>
+    <t xml:space="preserve">0.646509289741516</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">0.613488674163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617745876312</t>
+    <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788482666016</t>
+    <t xml:space="preserve">0.641788601875305</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -869,22 +869,19 @@
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276093482971</t>
+    <t xml:space="preserve">0.620276033878326</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592848300934</t>
+    <t xml:space="preserve">0.591592788696289</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -896,13 +893,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623861491680145</t>
+    <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690635681152</t>
+    <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -914,13 +911,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589800119400024</t>
+    <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385517597198</t>
+    <t xml:space="preserve">0.593385457992554</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -932,10 +929,10 @@
     <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043924808502</t>
+    <t xml:space="preserve">0.579043865203857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324026107788</t>
+    <t xml:space="preserve">0.559324085712433</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -944,19 +941,19 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873009204865</t>
+    <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586214661598206</t>
+    <t xml:space="preserve">0.58621472120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178186893463</t>
+    <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -968,7 +965,7 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
@@ -986,13 +983,13 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203084468842</t>
+    <t xml:space="preserve">0.638203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -1004,64 +1001,64 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.654337525367737</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057245254517</t>
+    <t xml:space="preserve">0.674057185649872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661508321762085</t>
+    <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093719959259</t>
+    <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
     <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544796466827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643581211566925</t>
+    <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020710945129</t>
+    <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191507339478</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71528947353363</t>
+    <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594651222229</t>
+    <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1070,13 +1067,13 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765388011932</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1109,25 +1106,25 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252939224243</t>
+    <t xml:space="preserve">0.724252998828888</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398838043213</t>
+    <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
     <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849974155426</t>
+    <t xml:space="preserve">0.675849914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667541027069</t>
+    <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045668125153</t>
+    <t xml:space="preserve">0.726045727729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1155,6 +1152,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -44437,7 +44437,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44463,7 +44463,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44489,7 +44489,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44515,7 +44515,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44541,7 +44541,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44567,7 +44567,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44593,7 +44593,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44619,7 +44619,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44645,7 +44645,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44671,7 +44671,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44723,7 +44723,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44749,7 +44749,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44775,7 +44775,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44801,7 +44801,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44827,7 +44827,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44853,7 +44853,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44879,7 +44879,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44905,7 +44905,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44931,7 +44931,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44957,7 +44957,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44983,7 +44983,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45009,7 +45009,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45035,7 +45035,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45061,7 +45061,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45087,7 +45087,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45113,7 +45113,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45139,7 +45139,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45165,7 +45165,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45191,7 +45191,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45217,7 +45217,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45243,7 +45243,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45269,7 +45269,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45295,7 +45295,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45321,7 +45321,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45347,7 +45347,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45373,7 +45373,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45399,7 +45399,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45425,7 +45425,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45451,7 +45451,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45477,7 +45477,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45503,7 +45503,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45529,7 +45529,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45555,7 +45555,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45581,7 +45581,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45607,7 +45607,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45659,7 +45659,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45711,7 +45711,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45737,7 +45737,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45763,7 +45763,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45789,7 +45789,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45815,7 +45815,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45841,7 +45841,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45867,7 +45867,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45893,7 +45893,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45919,7 +45919,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45945,7 +45945,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45971,7 +45971,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45997,7 +45997,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46023,7 +46023,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46049,7 +46049,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46075,7 +46075,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46101,7 +46101,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46127,7 +46127,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46153,7 +46153,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46179,7 +46179,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46205,7 +46205,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46231,7 +46231,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46257,7 +46257,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46283,7 +46283,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46309,7 +46309,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46335,7 +46335,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46361,7 +46361,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46387,7 +46387,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46413,7 +46413,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46439,7 +46439,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46465,7 +46465,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46491,7 +46491,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46517,7 +46517,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46543,7 +46543,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46569,7 +46569,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46595,7 +46595,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46621,7 +46621,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46647,7 +46647,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46673,7 +46673,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46699,7 +46699,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46725,7 +46725,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46751,7 +46751,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46777,7 +46777,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46803,7 +46803,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46829,7 +46829,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46855,7 +46855,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46881,7 +46881,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46907,7 +46907,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46933,7 +46933,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46959,7 +46959,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46985,7 +46985,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47011,7 +47011,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47037,7 +47037,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47063,7 +47063,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47089,7 +47089,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47115,7 +47115,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47141,7 +47141,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47167,7 +47167,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47193,7 +47193,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47219,7 +47219,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47245,7 +47245,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47271,7 +47271,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47323,7 +47323,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47349,7 +47349,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47375,7 +47375,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47401,7 +47401,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47427,7 +47427,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47453,7 +47453,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47479,7 +47479,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47505,7 +47505,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47531,7 +47531,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47557,7 +47557,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47609,7 +47609,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47635,7 +47635,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47661,7 +47661,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47687,7 +47687,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47713,7 +47713,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47739,7 +47739,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47765,7 +47765,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47791,7 +47791,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47817,7 +47817,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>286</v>
+        <v>248</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47869,7 +47869,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47895,7 +47895,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47921,7 +47921,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47947,7 +47947,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47973,7 +47973,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48025,7 +48025,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48051,7 +48051,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48077,7 +48077,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48129,7 +48129,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48233,7 +48233,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48259,7 +48259,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48285,7 +48285,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48311,7 +48311,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48337,7 +48337,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48363,7 +48363,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48389,7 +48389,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48415,7 +48415,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48441,7 +48441,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48467,7 +48467,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48493,7 +48493,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48519,7 +48519,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48545,7 +48545,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48571,7 +48571,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48597,7 +48597,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48623,7 +48623,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48649,7 +48649,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48675,7 +48675,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48701,7 +48701,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48727,7 +48727,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48753,7 +48753,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48805,7 +48805,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48831,7 +48831,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48857,7 +48857,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48883,7 +48883,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48909,7 +48909,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48935,7 +48935,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48961,7 +48961,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48987,7 +48987,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49013,7 +49013,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49039,7 +49039,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49065,7 +49065,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49091,7 +49091,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49117,7 +49117,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49143,7 +49143,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49169,7 +49169,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49195,7 +49195,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49221,7 +49221,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49247,7 +49247,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49273,7 +49273,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49299,7 +49299,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49325,7 +49325,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49351,7 +49351,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49377,7 +49377,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49403,7 +49403,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49429,7 +49429,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49455,7 +49455,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49481,7 +49481,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49507,7 +49507,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49533,7 +49533,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49559,7 +49559,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49585,7 +49585,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49611,7 +49611,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49637,7 +49637,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49663,7 +49663,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49689,7 +49689,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49715,7 +49715,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49741,7 +49741,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49767,7 +49767,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49793,7 +49793,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49819,7 +49819,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49845,7 +49845,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49871,7 +49871,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49897,7 +49897,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49923,7 +49923,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49949,7 +49949,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49975,7 +49975,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50001,7 +50001,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50027,7 +50027,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50053,7 +50053,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50079,7 +50079,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50105,7 +50105,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50131,7 +50131,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50157,7 +50157,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50183,7 +50183,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50209,7 +50209,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50235,7 +50235,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50261,7 +50261,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50287,7 +50287,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50313,7 +50313,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50339,7 +50339,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50365,7 +50365,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50391,7 +50391,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50417,7 +50417,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50443,7 +50443,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50469,7 +50469,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50495,7 +50495,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50521,7 +50521,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50547,7 +50547,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50573,7 +50573,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50599,7 +50599,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50625,7 +50625,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50651,7 +50651,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50677,7 +50677,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50703,7 +50703,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50729,7 +50729,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50755,7 +50755,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50781,7 +50781,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50807,7 +50807,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50833,7 +50833,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50859,7 +50859,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50885,7 +50885,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50911,7 +50911,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50937,7 +50937,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50963,7 +50963,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50989,7 +50989,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51015,7 +51015,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51041,7 +51041,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51067,7 +51067,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51093,7 +51093,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51119,7 +51119,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51145,7 +51145,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51171,7 +51171,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51197,7 +51197,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51275,7 +51275,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51301,7 +51301,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51327,7 +51327,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51353,7 +51353,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51431,7 +51431,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51535,7 +51535,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51613,7 +51613,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51639,7 +51639,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51665,7 +51665,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51743,7 +51743,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51821,7 +51821,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51847,7 +51847,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51873,7 +51873,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51899,7 +51899,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51977,7 +51977,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52003,7 +52003,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52055,7 +52055,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52133,7 +52133,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52211,7 +52211,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52237,7 +52237,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52289,7 +52289,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>330</v>
+        <v>380</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52341,7 +52341,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52471,7 +52471,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52497,7 +52497,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54525,7 +54525,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54551,7 +54551,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57073,7 +57073,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57151,7 +57151,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58139,7 +58139,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -66701,7 +66701,7 @@
     </row>
     <row r="2494">
       <c r="A2494" s="1" t="n">
-        <v>45951.5750810185</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2494" t="n">
         <v>25978</v>
@@ -66722,6 +66722,32 @@
         <v>510</v>
       </c>
       <c r="H2494" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2495">
+      <c r="A2495" s="1" t="n">
+        <v>45952.601412037</v>
+      </c>
+      <c r="B2495" t="n">
+        <v>173588</v>
+      </c>
+      <c r="C2495" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D2495" t="n">
+        <v>0.540000021457672</v>
+      </c>
+      <c r="E2495" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="F2495" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2495" t="s">
+        <v>509</v>
+      </c>
+      <c r="H2495" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="511" uniqueCount="511">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,10 +47,10 @@
     <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249102830887</t>
+    <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899931430817</t>
+    <t xml:space="preserve">0.216899916529655</t>
   </si>
   <si>
     <t xml:space="preserve">0.218581348657608</t>
@@ -59,19 +59,19 @@
     <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099117994308</t>
+    <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217319875955582</t>
+    <t xml:space="preserve">0.21731986105442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921487927437</t>
+    <t xml:space="preserve">0.228921502828598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293369412422</t>
+    <t xml:space="preserve">0.233293384313583</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
@@ -83,16 +83,16 @@
     <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598259329796</t>
+    <t xml:space="preserve">0.239598244428635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310569405556</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784891724586</t>
+    <t xml:space="preserve">0.222784876823425</t>
   </si>
   <si>
     <t xml:space="preserve">0.21437780559063</t>
@@ -104,61 +104,61 @@
     <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767161488533</t>
+    <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563573718071</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360045552254</t>
+    <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
     <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722880005836</t>
+    <t xml:space="preserve">0.196722894906998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20235538482666</t>
+    <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
     <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187091112137</t>
+    <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214127898216</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912745118141</t>
+    <t xml:space="preserve">0.208912774920464</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218514204025</t>
+    <t xml:space="preserve">0.215218484401703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987615227699</t>
+    <t xml:space="preserve">0.226987600326538</t>
   </si>
   <si>
     <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235439777374</t>
+    <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279676556587</t>
+    <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24548327922821</t>
+    <t xml:space="preserve">0.245483249425888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208888530731</t>
+    <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
     <t xml:space="preserve">0.258093893527985</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182426691055</t>
+    <t xml:space="preserve">0.268182396888733</t>
   </si>
   <si>
     <t xml:space="preserve">0.273226678371429</t>
@@ -176,28 +176,28 @@
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447132110596</t>
+    <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
     <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057835817337</t>
+    <t xml:space="preserve">0.311057776212692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531019449234</t>
+    <t xml:space="preserve">0.317531079053879</t>
   </si>
   <si>
     <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336279153823853</t>
+    <t xml:space="preserve">0.33627912402153</t>
   </si>
   <si>
     <t xml:space="preserve">0.356455326080322</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313809633255</t>
+    <t xml:space="preserve">0.378313779830933</t>
   </si>
   <si>
     <t xml:space="preserve">0.411941409111023</t>
@@ -215,46 +215,46 @@
     <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525591373444</t>
+    <t xml:space="preserve">0.440525561571121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684808254242</t>
+    <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
     <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055836677551</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500215113162994</t>
+    <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
     <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515691280365</t>
+    <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307960987091</t>
+    <t xml:space="preserve">0.492307871580124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670952796936</t>
+    <t xml:space="preserve">0.580670893192291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589086472988129</t>
+    <t xml:space="preserve">0.589086413383484</t>
   </si>
   <si>
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319156646729</t>
+    <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67324161529541</t>
+    <t xml:space="preserve">0.673241674900055</t>
   </si>
   <si>
     <t xml:space="preserve">0.65641051530838</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748494148254</t>
+    <t xml:space="preserve">0.62274843454361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255432605743</t>
+    <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
     <t xml:space="preserve">0.525969982147217</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100171089172</t>
+    <t xml:space="preserve">0.48810014128685</t>
   </si>
   <si>
     <t xml:space="preserve">0.504931211471558</t>
@@ -284,25 +284,25 @@
     <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509138941764832</t>
+    <t xml:space="preserve">0.509139001369476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892440795898</t>
+    <t xml:space="preserve">0.483892351388931</t>
   </si>
   <si>
     <t xml:space="preserve">0.513346791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177772045135</t>
+    <t xml:space="preserve">0.530177712440491</t>
   </si>
   <si>
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269130706787</t>
+    <t xml:space="preserve">0.471269190311432</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061340808868</t>
+    <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">0.462853580713272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684680700302</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607020139694</t>
+    <t xml:space="preserve">0.437607079744339</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
@@ -326,28 +326,28 @@
     <t xml:space="preserve">0.450230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022570133209</t>
+    <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
     <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944939374924</t>
+    <t xml:space="preserve">0.403944969177246</t>
   </si>
   <si>
     <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191499948502</t>
+    <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385502338409</t>
+    <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542801082134247</t>
+    <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476890802383</t>
+    <t xml:space="preserve">0.475476861000061</t>
   </si>
   <si>
     <t xml:space="preserve">0.410677373409271</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409837245941</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
     <t xml:space="preserve">0.380381524562836</t>
@@ -365,19 +365,19 @@
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360519170761</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
     <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814810037613</t>
+    <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092893600464</t>
+    <t xml:space="preserve">0.419092923402786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628085136414</t>
+    <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
     <t xml:space="preserve">0.408994287252426</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163187265396</t>
+    <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578796863556</t>
+    <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846333026886</t>
+    <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529419183731</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
@@ -413,10 +413,10 @@
     <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374247074127</t>
+    <t xml:space="preserve">0.311374217271805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620807647705</t>
+    <t xml:space="preserve">0.336620837450027</t>
   </si>
   <si>
     <t xml:space="preserve">0.329888373613358</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522171497345</t>
+    <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
     <t xml:space="preserve">0.3248390853405</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">0.35345184803009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184252262115</t>
+    <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768732070923</t>
+    <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036298036575</t>
@@ -446,10 +446,10 @@
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303953409195</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
@@ -461,61 +461,61 @@
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334937691688538</t>
+    <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
     <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916656494141</t>
+    <t xml:space="preserve">0.366916626691818</t>
   </si>
   <si>
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599742650986</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480101108551</t>
+    <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
     <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747726678848</t>
+    <t xml:space="preserve">0.383747696876526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797044754028</t>
+    <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698408603668</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064610719681</t>
+    <t xml:space="preserve">0.382064640522003</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332236289978</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
     <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015322446823</t>
+    <t xml:space="preserve">0.377015292644501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371965974569321</t>
+    <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385430842638016</t>
+    <t xml:space="preserve">0.385430812835693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233570337296</t>
+    <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593232631683</t>
+    <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
     <t xml:space="preserve">0.559632122516632</t>
@@ -524,10 +524,10 @@
     <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783257246017</t>
+    <t xml:space="preserve">0.489783316850662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733879566193</t>
+    <t xml:space="preserve">0.48473396897316</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
@@ -536,34 +536,34 @@
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466343402863</t>
+    <t xml:space="preserve">0.491466373205185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198837041855</t>
+    <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741216659546</t>
+    <t xml:space="preserve">0.553741276264191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494656085968</t>
+    <t xml:space="preserve">0.528494715690613</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811599731445</t>
+    <t xml:space="preserve">0.526811540126801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910235881805</t>
+    <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128543376923</t>
+    <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
     <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506614327430725</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
@@ -572,31 +572,31 @@
     <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297443389893</t>
+    <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
     <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.49314945936203</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029847621918</t>
+    <t xml:space="preserve">0.515029907226562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533543944358826</t>
+    <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227000713348</t>
+    <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107388973236</t>
+    <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
     <t xml:space="preserve">0.550374984741211</t>
@@ -608,19 +608,19 @@
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671302318573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019848823547</t>
+    <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53180605173111</t>
+    <t xml:space="preserve">0.531806111335754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53354400396347</t>
+    <t xml:space="preserve">0.533544063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068099498749</t>
+    <t xml:space="preserve">0.530068159103394</t>
   </si>
   <si>
     <t xml:space="preserve">0.535281956195831</t>
@@ -629,28 +629,28 @@
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330147266388</t>
+    <t xml:space="preserve">0.528330206871033</t>
   </si>
   <si>
     <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661180496216</t>
+    <t xml:space="preserve">0.552661120891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185335636139</t>
+    <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447502613068</t>
+    <t xml:space="preserve">0.547447383403778</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971478939056</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54223358631134</t>
+    <t xml:space="preserve">0.542233645915985</t>
   </si>
   <si>
     <t xml:space="preserve">0.538757741451263</t>
@@ -665,28 +665,28 @@
     <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550923228263855</t>
+    <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378457546234</t>
+    <t xml:space="preserve">0.521378576755524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512688875198364</t>
+    <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
     <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261281013489</t>
+    <t xml:space="preserve">0.502261221408844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50399923324585</t>
+    <t xml:space="preserve">0.503999173641205</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571668863297</t>
+    <t xml:space="preserve">0.493571698665619</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -698,19 +698,19 @@
     <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274936676025</t>
+    <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419807910919</t>
+    <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
     <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585294723511</t>
+    <t xml:space="preserve">0.599585235118866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895593166351</t>
+    <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102370738983</t>
+    <t xml:space="preserve">0.669102311134338</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364537715912</t>
+    <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061020374298</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392172813416</t>
+    <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62565416097641</t>
+    <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440423488617</t>
+    <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819647789001</t>
+    <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
     <t xml:space="preserve">0.643033444881439</t>
@@ -773,16 +773,16 @@
     <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012829303741</t>
+    <t xml:space="preserve">0.610012888908386</t>
   </si>
   <si>
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633545398712</t>
+    <t xml:space="preserve">0.592633485794067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505737125873566</t>
+    <t xml:space="preserve">0.50573718547821</t>
   </si>
   <si>
     <t xml:space="preserve">0.557874977588654</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109449863434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750781536102</t>
+    <t xml:space="preserve">0.611750841140747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343862533569</t>
+    <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985253810883</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081695556641</t>
+    <t xml:space="preserve">0.636081755161285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005750179291</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957499504089</t>
+    <t xml:space="preserve">0.689957559108734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688219666481018</t>
+    <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
     <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150740623474</t>
+    <t xml:space="preserve">0.662150621414185</t>
   </si>
   <si>
     <t xml:space="preserve">0.674316227436066</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674776554108</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509289741516</t>
+    <t xml:space="preserve">0.646509408950806</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">0.613488674163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617686271667</t>
+    <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788601875305</t>
+    <t xml:space="preserve">0.641788482666016</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897906780243</t>
+    <t xml:space="preserve">0.614897966384888</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276033878326</t>
+    <t xml:space="preserve">0.620276093482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592788696289</t>
+    <t xml:space="preserve">0.591592848300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -893,13 +893,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970915794373</t>
+    <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6238614320755</t>
+    <t xml:space="preserve">0.623861491680145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690695285797</t>
+    <t xml:space="preserve">0.616690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58980005979538</t>
+    <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385457992554</t>
+    <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043865203857</t>
+    <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324085712433</t>
+    <t xml:space="preserve">0.559324026107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -941,19 +941,19 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873068809509</t>
+    <t xml:space="preserve">0.571873009204865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58621472120285</t>
+    <t xml:space="preserve">0.586214661598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178127288818</t>
+    <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032288074493</t>
+    <t xml:space="preserve">0.631032347679138</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -965,7 +965,7 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567831516266</t>
+    <t xml:space="preserve">0.548567891120911</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702212810516</t>
+    <t xml:space="preserve">0.564702153205872</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203144073486</t>
+    <t xml:space="preserve">0.638203084468842</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -1001,64 +1001,64 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337525367737</t>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057185649872</t>
+    <t xml:space="preserve">0.674057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66150826215744</t>
+    <t xml:space="preserve">0.661508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093660354614</t>
+    <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886389255524</t>
+    <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
     <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544796466827</t>
+    <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64358127117157</t>
+    <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166669368744</t>
+    <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471787452698</t>
+    <t xml:space="preserve">0.670471847057343</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020770549774</t>
+    <t xml:space="preserve">0.683020710945129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191507339478</t>
+    <t xml:space="preserve">0.690191566944122</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715289413928986</t>
+    <t xml:space="preserve">0.71528947353363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594591617584</t>
+    <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972718715668</t>
+    <t xml:space="preserve">0.743972778320312</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1067,13 +1067,13 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009133815765</t>
+    <t xml:space="preserve">0.73500919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460329532623</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765388011932</t>
+    <t xml:space="preserve">0.745765447616577</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1106,25 +1106,25 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252998828888</t>
+    <t xml:space="preserve">0.724252939224243</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398897647858</t>
+    <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
     <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849914550781</t>
+    <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667600631714</t>
+    <t xml:space="preserve">0.720667541027069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045727729797</t>
+    <t xml:space="preserve">0.726045668125153</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1152,9 +1152,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -51197,7 +51194,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51223,7 +51220,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51249,7 +51246,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51379,7 +51376,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51405,7 +51402,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51457,7 +51454,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51483,7 +51480,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51509,7 +51506,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51561,7 +51558,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51587,7 +51584,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51691,7 +51688,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51717,7 +51714,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51769,7 +51766,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51795,7 +51792,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51847,7 +51844,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51925,7 +51922,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51951,7 +51948,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52029,7 +52026,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52055,7 +52052,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52081,7 +52078,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52107,7 +52104,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52133,7 +52130,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52159,7 +52156,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52185,7 +52182,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52263,7 +52260,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52289,7 +52286,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>380</v>
+        <v>329</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52315,7 +52312,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52367,7 +52364,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52393,7 +52390,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52419,7 +52416,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52445,7 +52442,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52523,7 +52520,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52549,7 +52546,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52575,7 +52572,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52601,7 +52598,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52627,7 +52624,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52653,7 +52650,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52679,7 +52676,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52705,7 +52702,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52731,7 +52728,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52757,7 +52754,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52783,7 +52780,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52809,7 +52806,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52835,7 +52832,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52861,7 +52858,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52887,7 +52884,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52913,7 +52910,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52939,7 +52936,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52965,7 +52962,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52991,7 +52988,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53017,7 +53014,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53043,7 +53040,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53069,7 +53066,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53095,7 +53092,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53121,7 +53118,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53147,7 +53144,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53173,7 +53170,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53199,7 +53196,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53225,7 +53222,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53251,7 +53248,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53277,7 +53274,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53303,7 +53300,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53329,7 +53326,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53355,7 +53352,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53381,7 +53378,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53407,7 +53404,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53433,7 +53430,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53459,7 +53456,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53485,7 +53482,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53511,7 +53508,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53537,7 +53534,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53563,7 +53560,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53589,7 +53586,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53615,7 +53612,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53641,7 +53638,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53667,7 +53664,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53693,7 +53690,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53719,7 +53716,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53745,7 +53742,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53771,7 +53768,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53797,7 +53794,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53823,7 +53820,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53849,7 +53846,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53875,7 +53872,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53901,7 +53898,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53927,7 +53924,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53953,7 +53950,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53979,7 +53976,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54005,7 +54002,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54031,7 +54028,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54057,7 +54054,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54083,7 +54080,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54109,7 +54106,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54135,7 +54132,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54161,7 +54158,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54187,7 +54184,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54213,7 +54210,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54239,7 +54236,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54265,7 +54262,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54291,7 +54288,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54317,7 +54314,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54343,7 +54340,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54369,7 +54366,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54395,7 +54392,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54421,7 +54418,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54447,7 +54444,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54473,7 +54470,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54499,7 +54496,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54577,7 +54574,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54603,7 +54600,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54629,7 +54626,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54655,7 +54652,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54681,7 +54678,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54707,7 +54704,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54733,7 +54730,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54759,7 +54756,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54785,7 +54782,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54811,7 +54808,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54837,7 +54834,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54863,7 +54860,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54889,7 +54886,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54915,7 +54912,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54941,7 +54938,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54967,7 +54964,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54993,7 +54990,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55019,7 +55016,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55045,7 +55042,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55071,7 +55068,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55097,7 +55094,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55123,7 +55120,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55149,7 +55146,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55175,7 +55172,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55201,7 +55198,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55227,7 +55224,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55253,7 +55250,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55279,7 +55276,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55305,7 +55302,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55331,7 +55328,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55357,7 +55354,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55383,7 +55380,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55409,7 +55406,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55435,7 +55432,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55461,7 +55458,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55487,7 +55484,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55513,7 +55510,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55539,7 +55536,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55565,7 +55562,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55591,7 +55588,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55617,7 +55614,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55643,7 +55640,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55669,7 +55666,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55695,7 +55692,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55721,7 +55718,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55747,7 +55744,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55773,7 +55770,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55799,7 +55796,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55825,7 +55822,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55851,7 +55848,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55877,7 +55874,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55903,7 +55900,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55929,7 +55926,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55955,7 +55952,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55981,7 +55978,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56007,7 +56004,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56033,7 +56030,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56059,7 +56056,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56085,7 +56082,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56111,7 +56108,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56137,7 +56134,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56163,7 +56160,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56189,7 +56186,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56215,7 +56212,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56241,7 +56238,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56267,7 +56264,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56293,7 +56290,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56319,7 +56316,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56345,7 +56342,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56371,7 +56368,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56397,7 +56394,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56423,7 +56420,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56449,7 +56446,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56475,7 +56472,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56501,7 +56498,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56527,7 +56524,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56553,7 +56550,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56579,7 +56576,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56605,7 +56602,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56631,7 +56628,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56657,7 +56654,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56683,7 +56680,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56709,7 +56706,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56735,7 +56732,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56761,7 +56758,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56787,7 +56784,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56813,7 +56810,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56839,7 +56836,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56865,7 +56862,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56891,7 +56888,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56917,7 +56914,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56943,7 +56940,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56969,7 +56966,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56995,7 +56992,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57021,7 +57018,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57047,7 +57044,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57099,7 +57096,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57125,7 +57122,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57177,7 +57174,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57203,7 +57200,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57229,7 +57226,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57255,7 +57252,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57281,7 +57278,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57307,7 +57304,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57333,7 +57330,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57359,7 +57356,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57385,7 +57382,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57411,7 +57408,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57437,7 +57434,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57463,7 +57460,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57489,7 +57486,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57515,7 +57512,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57541,7 +57538,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57567,7 +57564,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57593,7 +57590,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57619,7 +57616,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57645,7 +57642,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57671,7 +57668,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57697,7 +57694,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57723,7 +57720,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57749,7 +57746,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57775,7 +57772,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57801,7 +57798,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57827,7 +57824,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57853,7 +57850,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57879,7 +57876,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57905,7 +57902,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57931,7 +57928,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57957,7 +57954,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57983,7 +57980,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58009,7 +58006,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58035,7 +58032,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58061,7 +58058,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58087,7 +58084,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58113,7 +58110,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58165,7 +58162,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58191,7 +58188,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58217,7 +58214,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58243,7 +58240,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58269,7 +58266,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58295,7 +58292,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58321,7 +58318,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58347,7 +58344,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58373,7 +58370,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58399,7 +58396,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58425,7 +58422,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58451,7 +58448,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58477,7 +58474,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58503,7 +58500,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58529,7 +58526,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58555,7 +58552,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58581,7 +58578,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58607,7 +58604,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58633,7 +58630,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58659,7 +58656,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58685,7 +58682,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58711,7 +58708,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58737,7 +58734,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58763,7 +58760,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58789,7 +58786,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58815,7 +58812,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58841,7 +58838,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58867,7 +58864,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58893,7 +58890,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58919,7 +58916,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58945,7 +58942,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58971,7 +58968,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58997,7 +58994,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59023,7 +59020,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59049,7 +59046,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59075,7 +59072,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59101,7 +59098,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59127,7 +59124,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59153,7 +59150,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59179,7 +59176,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59205,7 +59202,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59231,7 +59228,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59257,7 +59254,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59283,7 +59280,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59309,7 +59306,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59335,7 +59332,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59361,7 +59358,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59387,7 +59384,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59413,7 +59410,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59439,7 +59436,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59465,7 +59462,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59491,7 +59488,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59517,7 +59514,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59543,7 +59540,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59569,7 +59566,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59595,7 +59592,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59621,7 +59618,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59647,7 +59644,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59673,7 +59670,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59699,7 +59696,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59725,7 +59722,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59751,7 +59748,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59777,7 +59774,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59803,7 +59800,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59829,7 +59826,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59855,7 +59852,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59881,7 +59878,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59907,7 +59904,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59933,7 +59930,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59959,7 +59956,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59985,7 +59982,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60011,7 +60008,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60037,7 +60034,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60063,7 +60060,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60089,7 +60086,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60115,7 +60112,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60141,7 +60138,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60167,7 +60164,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60193,7 +60190,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60219,7 +60216,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60245,7 +60242,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60271,7 +60268,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60297,7 +60294,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60323,7 +60320,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60349,7 +60346,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60375,7 +60372,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60401,7 +60398,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60427,7 +60424,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60453,7 +60450,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60479,7 +60476,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60505,7 +60502,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60531,7 +60528,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60557,7 +60554,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60583,7 +60580,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60609,7 +60606,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60635,7 +60632,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60661,7 +60658,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60687,7 +60684,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60713,7 +60710,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60739,7 +60736,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60765,7 +60762,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60791,7 +60788,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60817,7 +60814,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60843,7 +60840,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60869,7 +60866,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60895,7 +60892,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60921,7 +60918,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60947,7 +60944,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60973,7 +60970,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60999,7 +60996,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61025,7 +61022,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61051,7 +61048,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61077,7 +61074,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61103,7 +61100,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61129,7 +61126,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61155,7 +61152,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61181,7 +61178,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61207,7 +61204,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61233,7 +61230,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61259,7 +61256,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61285,7 +61282,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61311,7 +61308,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61337,7 +61334,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61363,7 +61360,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61389,7 +61386,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61415,7 +61412,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61441,7 +61438,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61467,7 +61464,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61493,7 +61490,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61519,7 +61516,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61545,7 +61542,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61571,7 +61568,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61597,7 +61594,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61623,7 +61620,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61649,7 +61646,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61675,7 +61672,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61701,7 +61698,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61727,7 +61724,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61753,7 +61750,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61779,7 +61776,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61805,7 +61802,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61831,7 +61828,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61857,7 +61854,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61883,7 +61880,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61909,7 +61906,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61935,7 +61932,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61961,7 +61958,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61987,7 +61984,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62013,7 +62010,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62039,7 +62036,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62065,7 +62062,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62091,7 +62088,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62117,7 +62114,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62143,7 +62140,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62169,7 +62166,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62195,7 +62192,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62221,7 +62218,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62247,7 +62244,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62273,7 +62270,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62299,7 +62296,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62325,7 +62322,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62351,7 +62348,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62377,7 +62374,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62403,7 +62400,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62429,7 +62426,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62455,7 +62452,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62481,7 +62478,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62507,7 +62504,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62533,7 +62530,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62559,7 +62556,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62585,7 +62582,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62611,7 +62608,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62637,7 +62634,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62663,7 +62660,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62689,7 +62686,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62715,7 +62712,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62741,7 +62738,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62767,7 +62764,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62793,7 +62790,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62819,7 +62816,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62845,7 +62842,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62871,7 +62868,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62897,7 +62894,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62923,7 +62920,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62949,7 +62946,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62975,7 +62972,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63001,7 +62998,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63027,7 +63024,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63053,7 +63050,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63079,7 +63076,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63105,7 +63102,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63131,7 +63128,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63157,7 +63154,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63183,7 +63180,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63209,7 +63206,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63235,7 +63232,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63261,7 +63258,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63287,7 +63284,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63313,7 +63310,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63339,7 +63336,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63365,7 +63362,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63391,7 +63388,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63417,7 +63414,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63443,7 +63440,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63469,7 +63466,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63495,7 +63492,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63521,7 +63518,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63547,7 +63544,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63573,7 +63570,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63599,7 +63596,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63625,7 +63622,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63651,7 +63648,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63677,7 +63674,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63703,7 +63700,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63729,7 +63726,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63755,7 +63752,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63781,7 +63778,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63807,7 +63804,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63833,7 +63830,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63859,7 +63856,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63885,7 +63882,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63911,7 +63908,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63937,7 +63934,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63963,7 +63960,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63989,7 +63986,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64015,7 +64012,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64041,7 +64038,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64067,7 +64064,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64093,7 +64090,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64119,7 +64116,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64145,7 +64142,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64171,7 +64168,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64197,7 +64194,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64223,7 +64220,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64249,7 +64246,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64275,7 +64272,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64301,7 +64298,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64327,7 +64324,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64353,7 +64350,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64379,7 +64376,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64405,7 +64402,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64431,7 +64428,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64457,7 +64454,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64483,7 +64480,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64509,7 +64506,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64535,7 +64532,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64561,7 +64558,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64587,7 +64584,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64613,7 +64610,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64639,7 +64636,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64665,7 +64662,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64691,7 +64688,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64717,7 +64714,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64743,7 +64740,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64769,7 +64766,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64795,7 +64792,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64821,7 +64818,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64847,7 +64844,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64873,7 +64870,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64899,7 +64896,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64925,7 +64922,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64951,7 +64948,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64977,7 +64974,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65003,7 +65000,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65029,7 +65026,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65055,7 +65052,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65081,7 +65078,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65107,7 +65104,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65133,7 +65130,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65159,7 +65156,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65185,7 +65182,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65211,7 +65208,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65237,7 +65234,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65263,7 +65260,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65289,7 +65286,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65315,7 +65312,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65341,7 +65338,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65367,7 +65364,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65393,7 +65390,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65419,7 +65416,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65445,7 +65442,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65471,7 +65468,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65497,7 +65494,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65523,7 +65520,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65549,7 +65546,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65575,7 +65572,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65601,7 +65598,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65627,7 +65624,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65653,7 +65650,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65679,7 +65676,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65705,7 +65702,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65731,7 +65728,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65757,7 +65754,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65783,7 +65780,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65809,7 +65806,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65835,7 +65832,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65861,7 +65858,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65887,7 +65884,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65913,7 +65910,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65939,7 +65936,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65965,7 +65962,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65991,7 +65988,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66017,7 +66014,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66043,7 +66040,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66069,7 +66066,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66095,7 +66092,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66121,7 +66118,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66147,7 +66144,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66173,7 +66170,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66199,7 +66196,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66225,7 +66222,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66251,7 +66248,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66277,7 +66274,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66303,7 +66300,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66329,7 +66326,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66355,7 +66352,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66381,7 +66378,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66407,7 +66404,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66433,7 +66430,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66459,7 +66456,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66485,7 +66482,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66511,7 +66508,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66537,7 +66534,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66563,7 +66560,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66589,7 +66586,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2489" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66615,7 +66612,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2490" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66641,7 +66638,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2491" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66667,7 +66664,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2492" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66693,7 +66690,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2493" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66719,7 +66716,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2494" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66727,7 +66724,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.601412037</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>173588</v>
@@ -66745,9 +66742,35 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2495" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6413310185</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>11818</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>0.574000000953674</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>0.574000000953674</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>506</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815480351448</t>
+    <t xml:space="preserve">0.235815495252609</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
@@ -50,19 +50,19 @@
     <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899916529655</t>
+    <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581348657608</t>
+    <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21017424762249</t>
+    <t xml:space="preserve">0.210174232721329</t>
   </si>
   <si>
     <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319890856743</t>
   </si>
   <si>
     <t xml:space="preserve">0.228921502828598</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293384313583</t>
+    <t xml:space="preserve">0.233293354511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762196540833</t>
+    <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598244428635</t>
+    <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784876823425</t>
+    <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
     <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014971137047</t>
+    <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970704555511</t>
+    <t xml:space="preserve">0.20597068965435</t>
   </si>
   <si>
     <t xml:space="preserve">0.201767146587372</t>
@@ -116,10 +116,10 @@
     <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722894906998</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202355399727821</t>
+    <t xml:space="preserve">0.202355369925499</t>
   </si>
   <si>
     <t xml:space="preserve">0.202607855200768</t>
@@ -128,7 +128,7 @@
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
     <t xml:space="preserve">0.208912774920464</t>
@@ -137,13 +137,13 @@
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218484401703</t>
+    <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
     <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987600326538</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
     <t xml:space="preserve">0.232031866908073</t>
@@ -152,31 +152,31 @@
     <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279691457748</t>
+    <t xml:space="preserve">0.241279676556587</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483249425888</t>
+    <t xml:space="preserve">0.245483234524727</t>
   </si>
   <si>
     <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093893527985</t>
+    <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138175010681</t>
+    <t xml:space="preserve">0.263138204813004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182396888733</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
     <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281632959842682</t>
+    <t xml:space="preserve">0.281632989645004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836488008499</t>
+    <t xml:space="preserve">0.285836458206177</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057776212692</t>
+    <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531079053879</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33627912402153</t>
+    <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455326080322</t>
+    <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
     <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313779830933</t>
+    <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941409111023</t>
+    <t xml:space="preserve">0.411941379308701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034849524498</t>
+    <t xml:space="preserve">0.420348465442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525561571121</t>
+    <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684838056564</t>
+    <t xml:space="preserve">0.439684867858887</t>
   </si>
   <si>
     <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400940895081</t>
+    <t xml:space="preserve">0.483400881290436</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49651563167572</t>
+    <t xml:space="preserve">0.496515691280365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307871580124</t>
+    <t xml:space="preserve">0.492307901382446</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -254,70 +254,70 @@
     <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241674900055</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641051530838</t>
+    <t xml:space="preserve">0.65641063451767</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61854076385498</t>
+    <t xml:space="preserve">0.618540823459625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274843454361</t>
+    <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525969982147217</t>
+    <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762251853943</t>
+    <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48810014128685</t>
+    <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892351388931</t>
+    <t xml:space="preserve">0.483892440795898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346791267395</t>
+    <t xml:space="preserve">0.51334673166275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177712440491</t>
+    <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269190311432</t>
+    <t xml:space="preserve">0.471269130706787</t>
   </si>
   <si>
     <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500723481178284</t>
+    <t xml:space="preserve">0.500723421573639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853580713272</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684680700302</t>
+    <t xml:space="preserve">0.479684621095657</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607079744339</t>
+    <t xml:space="preserve">0.437607020139694</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645880222321</t>
+    <t xml:space="preserve">0.458645850419998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944969177246</t>
+    <t xml:space="preserve">0.403944939374924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776009559631</t>
+    <t xml:space="preserve">0.420776039361954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191529750824</t>
+    <t xml:space="preserve">0.429191499948502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385561943054</t>
+    <t xml:space="preserve">0.534385621547699</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
     <t xml:space="preserve">0.410677373409271</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381524562836</t>
+    <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
@@ -371,10 +371,10 @@
     <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814780235291</t>
+    <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092923402786</t>
+    <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
     <t xml:space="preserve">0.405628055334091</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163246870041</t>
+    <t xml:space="preserve">0.392163187265396</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
@@ -395,40 +395,40 @@
     <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261853218079</t>
+    <t xml:space="preserve">0.402261883020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529419183731</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113928794861</t>
+    <t xml:space="preserve">0.387113898992538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649090528488</t>
+    <t xml:space="preserve">0.373649120330811</t>
   </si>
   <si>
     <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374217271805</t>
+    <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620837450027</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888373613358</t>
+    <t xml:space="preserve">0.32988840341568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32820525765419</t>
+    <t xml:space="preserve">0.328205317258835</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3248390853405</t>
+    <t xml:space="preserve">0.324839115142822</t>
   </si>
   <si>
     <t xml:space="preserve">0.35345184803009</t>
@@ -443,10 +443,10 @@
     <t xml:space="preserve">0.345036298036575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350085645914078</t>
+    <t xml:space="preserve">0.350085616111755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303923606873</t>
+    <t xml:space="preserve">0.33830389380455</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
@@ -455,25 +455,25 @@
     <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33325457572937</t>
+    <t xml:space="preserve">0.333254605531693</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33493772149086</t>
+    <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
     <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916626691818</t>
+    <t xml:space="preserve">0.366916686296463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35850116610527</t>
+    <t xml:space="preserve">0.358501136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36859980225563</t>
+    <t xml:space="preserve">0.368599772453308</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
@@ -485,34 +485,34 @@
     <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747696876526</t>
+    <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
     <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698378801346</t>
+    <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064640522003</t>
+    <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332206487656</t>
+    <t xml:space="preserve">0.375332236289978</t>
   </si>
   <si>
     <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
     <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385430812835693</t>
+    <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233540534973</t>
+    <t xml:space="preserve">0.365233570337296</t>
   </si>
   <si>
     <t xml:space="preserve">0.538593292236328</t>
@@ -524,25 +524,25 @@
     <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783316850662</t>
+    <t xml:space="preserve">0.48978328704834</t>
   </si>
   <si>
     <t xml:space="preserve">0.48473396897316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47631847858429</t>
+    <t xml:space="preserve">0.476318448781967</t>
   </si>
   <si>
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466373205185</t>
+    <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
     <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741276264191</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494715690613</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">0.526811540126801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910176277161</t>
+    <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128424167633</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661426782608</t>
+    <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297383785248</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.501564979553223</t>
@@ -584,13 +584,13 @@
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029907226562</t>
+    <t xml:space="preserve">0.515029788017273</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473740100861</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,25 +599,22 @@
     <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374984741211</t>
+    <t xml:space="preserve">0.5503751039505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860828399658</t>
+    <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671302318573</t>
+    <t xml:space="preserve">0.51671290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019789218903</t>
+    <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533544063568115</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
     <t xml:space="preserve">0.530068159103394</t>
@@ -629,25 +626,25 @@
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330206871033</t>
+    <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709490776062</t>
+    <t xml:space="preserve">0.545709550380707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661120891571</t>
+    <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399132728577</t>
+    <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971478939056</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -659,7 +656,7 @@
     <t xml:space="preserve">0.540495693683624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568302571773529</t>
+    <t xml:space="preserve">0.568302631378174</t>
   </si>
   <si>
     <t xml:space="preserve">0.559612929821014</t>
@@ -668,19 +665,19 @@
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378576755524</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514426827430725</t>
+    <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261340618134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503999173641205</t>
+    <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833746433258</t>
@@ -695,10 +692,10 @@
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640564918518</t>
+    <t xml:space="preserve">0.519640505313873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274877071381</t>
+    <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419748306274</t>
@@ -707,7 +704,7 @@
     <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585235118866</t>
+    <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
     <t xml:space="preserve">0.590895652770996</t>
@@ -719,10 +716,10 @@
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58915764093399</t>
+    <t xml:space="preserve">0.589157700538635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557659626007</t>
+    <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
     <t xml:space="preserve">0.669102311134338</t>
@@ -740,7 +737,7 @@
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
@@ -749,16 +746,16 @@
     <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653461039066315</t>
+    <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6447713971138</t>
+    <t xml:space="preserve">0.644771337509155</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
     <t xml:space="preserve">0.620440363883972</t>
@@ -770,19 +767,19 @@
     <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178316116333</t>
+    <t xml:space="preserve">0.622178375720978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012888908386</t>
+    <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633485794067</t>
+    <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799091815948</t>
+    <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -791,28 +788,28 @@
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50573718547821</t>
+    <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557874977588654</t>
+    <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109449863434</t>
+    <t xml:space="preserve">0.596109390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750841140747</t>
+    <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343802928925</t>
+    <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985253810883</t>
+    <t xml:space="preserve">0.649985134601593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247241973877</t>
+    <t xml:space="preserve">0.648247182369232</t>
   </si>
   <si>
     <t xml:space="preserve">0.636081755161285</t>
@@ -830,34 +827,34 @@
     <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150621414185</t>
+    <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316227436066</t>
+    <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
     <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509408950806</t>
+    <t xml:space="preserve">0.646509289741516</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226626396179</t>
+    <t xml:space="preserve">0.615226566791534</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617745876312</t>
+    <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788482666016</t>
+    <t xml:space="preserve">0.641788601875305</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -869,19 +866,19 @@
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276093482971</t>
+    <t xml:space="preserve">0.620276033878326</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592848300934</t>
+    <t xml:space="preserve">0.591592788696289</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -893,13 +890,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623861491680145</t>
+    <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690635681152</t>
+    <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -911,13 +908,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589800119400024</t>
+    <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385517597198</t>
+    <t xml:space="preserve">0.593385457992554</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -929,10 +926,10 @@
     <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043924808502</t>
+    <t xml:space="preserve">0.579043865203857</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324026107788</t>
+    <t xml:space="preserve">0.559324085712433</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -941,19 +938,19 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873009204865</t>
+    <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586214661598206</t>
+    <t xml:space="preserve">0.58621472120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178186893463</t>
+    <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -965,7 +962,7 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
@@ -983,13 +980,13 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203084468842</t>
+    <t xml:space="preserve">0.638203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -1001,64 +998,64 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.654337525367737</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057245254517</t>
+    <t xml:space="preserve">0.674057185649872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661508321762085</t>
+    <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093719959259</t>
+    <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
     <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544796466827</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643581211566925</t>
+    <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020710945129</t>
+    <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191507339478</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71528947353363</t>
+    <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594651222229</t>
+    <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1067,13 +1064,13 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765388011932</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1106,25 +1103,25 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252939224243</t>
+    <t xml:space="preserve">0.724252998828888</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398838043213</t>
+    <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
     <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849974155426</t>
+    <t xml:space="preserve">0.675849914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667541027069</t>
+    <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045668125153</t>
+    <t xml:space="preserve">0.726045727729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1152,6 +1149,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -38818,7 +38818,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1421" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38844,7 +38844,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1422" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38870,7 +38870,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1423" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38896,7 +38896,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1424" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38974,7 +38974,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1427" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39000,7 +39000,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1428" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39026,7 +39026,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1429" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39052,7 +39052,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1430" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39130,7 +39130,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1433" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39156,7 +39156,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1434" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39234,7 +39234,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1437" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39260,7 +39260,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1438" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39286,7 +39286,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1439" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39312,7 +39312,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1440" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39338,7 +39338,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1441" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39364,7 +39364,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1442" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39390,7 +39390,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1443" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39416,7 +39416,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1444" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39442,7 +39442,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39468,7 +39468,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1446" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39494,7 +39494,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1447" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39520,7 +39520,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1448" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39546,7 +39546,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1449" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39572,7 +39572,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1450" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39598,7 +39598,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1451" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39650,7 +39650,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1453" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39676,7 +39676,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1454" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39728,7 +39728,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39754,7 +39754,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1457" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39780,7 +39780,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1458" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39806,7 +39806,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1459" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39858,7 +39858,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1461" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39884,7 +39884,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1462" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39910,7 +39910,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1463" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39936,7 +39936,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1464" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39962,7 +39962,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1465" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39988,7 +39988,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40014,7 +40014,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1467" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40040,7 +40040,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1468" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40066,7 +40066,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1469" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40092,7 +40092,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1470" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40118,7 +40118,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1471" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40144,7 +40144,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1472" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40170,7 +40170,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1473" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40196,7 +40196,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1474" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40222,7 +40222,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1475" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40248,7 +40248,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1476" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40274,7 +40274,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1477" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40300,7 +40300,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1478" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40352,7 +40352,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1480" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40378,7 +40378,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1481" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40404,7 +40404,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1482" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40430,7 +40430,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1483" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40456,7 +40456,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1484" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40482,7 +40482,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1485" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40508,7 +40508,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1486" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40534,7 +40534,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1487" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40560,7 +40560,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1488" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40586,7 +40586,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1489" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40612,7 +40612,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1490" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40638,7 +40638,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1491" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40690,7 +40690,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1493" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40716,7 +40716,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1494" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40742,7 +40742,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1495" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40768,7 +40768,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1496" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40794,7 +40794,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1497" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40820,7 +40820,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1498" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40846,7 +40846,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1499" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40872,7 +40872,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1500" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40898,7 +40898,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1501" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40924,7 +40924,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1502" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40950,7 +40950,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1503" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40976,7 +40976,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1504" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41002,7 +41002,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1505" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41028,7 +41028,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1506" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41054,7 +41054,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1507" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41080,7 +41080,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1508" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41106,7 +41106,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1509" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41132,7 +41132,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1510" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41158,7 +41158,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1511" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41184,7 +41184,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1512" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41210,7 +41210,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1513" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41236,7 +41236,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1514" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41262,7 +41262,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41288,7 +41288,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1516" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41314,7 +41314,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1517" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41340,7 +41340,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41366,7 +41366,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1519" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41392,7 +41392,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1520" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41418,7 +41418,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1521" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41444,7 +41444,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1522" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41470,7 +41470,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1523" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41496,7 +41496,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1524" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41522,7 +41522,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1525" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41548,7 +41548,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41574,7 +41574,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1527" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41600,7 +41600,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1528" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41626,7 +41626,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1529" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41652,7 +41652,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41678,7 +41678,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1531" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41704,7 +41704,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1532" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41730,7 +41730,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1533" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41756,7 +41756,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1534" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41782,7 +41782,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1535" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41808,7 +41808,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1536" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41834,7 +41834,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41860,7 +41860,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1538" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41886,7 +41886,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1539" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41912,7 +41912,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1540" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41938,7 +41938,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1541" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41964,7 +41964,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1542" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41990,7 +41990,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1543" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42016,7 +42016,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1544" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42042,7 +42042,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42068,7 +42068,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1546" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42094,7 +42094,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1547" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42120,7 +42120,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1548" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42146,7 +42146,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1549" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42172,7 +42172,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1550" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42198,7 +42198,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1551" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42224,7 +42224,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1552" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42250,7 +42250,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1553" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42276,7 +42276,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1554" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42302,7 +42302,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1555" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42328,7 +42328,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1556" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42354,7 +42354,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1557" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42380,7 +42380,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42406,7 +42406,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42432,7 +42432,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1560" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42458,7 +42458,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1561" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42484,7 +42484,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42510,7 +42510,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1563" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42536,7 +42536,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1564" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42562,7 +42562,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1565" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42588,7 +42588,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1566" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42614,7 +42614,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1567" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42640,7 +42640,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42666,7 +42666,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1569" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42692,7 +42692,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1570" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42718,7 +42718,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1571" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42744,7 +42744,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1572" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42770,7 +42770,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1573" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42796,7 +42796,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1574" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42822,7 +42822,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1575" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42848,7 +42848,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1576" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42874,7 +42874,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1577" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42900,7 +42900,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1578" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42926,7 +42926,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1579" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42952,7 +42952,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1580" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42978,7 +42978,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1581" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43004,7 +43004,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1582" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43030,7 +43030,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1583" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43056,7 +43056,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1584" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43082,7 +43082,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1585" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43108,7 +43108,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43134,7 +43134,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1587" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43160,7 +43160,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1588" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43186,7 +43186,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1589" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43212,7 +43212,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43238,7 +43238,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1591" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43264,7 +43264,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1592" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43290,7 +43290,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1593" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43316,7 +43316,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1594" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43342,7 +43342,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1595" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43368,7 +43368,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1596" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43394,7 +43394,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43420,7 +43420,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1598" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43446,7 +43446,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1599" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43472,7 +43472,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1600" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43498,7 +43498,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1601" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43524,7 +43524,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1602" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43550,7 +43550,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1603" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43576,7 +43576,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1604" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43602,7 +43602,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1605" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43628,7 +43628,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1606" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43654,7 +43654,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1607" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43680,7 +43680,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1608" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43706,7 +43706,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1609" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43732,7 +43732,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1610" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43758,7 +43758,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1611" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43784,7 +43784,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1612" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43810,7 +43810,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1613" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43836,7 +43836,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1614" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43862,7 +43862,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1615" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43888,7 +43888,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1616" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43914,7 +43914,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1617" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43940,7 +43940,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43966,7 +43966,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43992,7 +43992,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44018,7 +44018,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1621" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44044,7 +44044,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1622" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44070,7 +44070,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44096,7 +44096,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1624" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44122,7 +44122,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1625" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44148,7 +44148,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1626" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44174,7 +44174,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1627" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44200,7 +44200,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1628" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44226,7 +44226,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1629" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44252,7 +44252,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1630" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44278,7 +44278,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1631" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44304,7 +44304,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1632" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44330,7 +44330,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1633" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44356,7 +44356,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1634" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44382,7 +44382,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1635" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44408,7 +44408,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1636" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44434,7 +44434,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44460,7 +44460,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44486,7 +44486,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44512,7 +44512,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44538,7 +44538,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44564,7 +44564,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44590,7 +44590,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44616,7 +44616,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44642,7 +44642,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44668,7 +44668,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44694,7 +44694,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1647" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44720,7 +44720,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44746,7 +44746,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44772,7 +44772,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44798,7 +44798,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44824,7 +44824,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44850,7 +44850,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44876,7 +44876,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44902,7 +44902,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44928,7 +44928,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44954,7 +44954,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44980,7 +44980,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45006,7 +45006,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45032,7 +45032,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45058,7 +45058,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45084,7 +45084,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45110,7 +45110,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45136,7 +45136,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45162,7 +45162,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45188,7 +45188,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45214,7 +45214,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45240,7 +45240,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45266,7 +45266,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45292,7 +45292,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45318,7 +45318,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45344,7 +45344,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45370,7 +45370,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45396,7 +45396,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45422,7 +45422,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45448,7 +45448,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45474,7 +45474,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45500,7 +45500,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45526,7 +45526,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45552,7 +45552,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45578,7 +45578,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45604,7 +45604,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45630,7 +45630,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1683" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45656,7 +45656,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45682,7 +45682,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1685" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45708,7 +45708,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45734,7 +45734,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45760,7 +45760,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45786,7 +45786,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45812,7 +45812,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45838,7 +45838,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45864,7 +45864,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45890,7 +45890,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45916,7 +45916,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45942,7 +45942,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45968,7 +45968,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -45994,7 +45994,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46020,7 +46020,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46046,7 +46046,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46072,7 +46072,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46098,7 +46098,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46124,7 +46124,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46150,7 +46150,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46176,7 +46176,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46202,7 +46202,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46228,7 +46228,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46254,7 +46254,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46280,7 +46280,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46306,7 +46306,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46332,7 +46332,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46358,7 +46358,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46384,7 +46384,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46410,7 +46410,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46436,7 +46436,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46462,7 +46462,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46488,7 +46488,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46514,7 +46514,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46540,7 +46540,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46566,7 +46566,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46592,7 +46592,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46618,7 +46618,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46644,7 +46644,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46670,7 +46670,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46696,7 +46696,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46722,7 +46722,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46748,7 +46748,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46774,7 +46774,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46800,7 +46800,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46826,7 +46826,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46852,7 +46852,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46878,7 +46878,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46904,7 +46904,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46930,7 +46930,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46956,7 +46956,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46982,7 +46982,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47008,7 +47008,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47034,7 +47034,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47060,7 +47060,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47086,7 +47086,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47112,7 +47112,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47138,7 +47138,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47164,7 +47164,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47190,7 +47190,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47216,7 +47216,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47242,7 +47242,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47268,7 +47268,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47294,7 +47294,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1747" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47320,7 +47320,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47346,7 +47346,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47372,7 +47372,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47398,7 +47398,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47424,7 +47424,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47450,7 +47450,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47476,7 +47476,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47502,7 +47502,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47528,7 +47528,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47554,7 +47554,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47580,7 +47580,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1758" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47606,7 +47606,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47632,7 +47632,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47658,7 +47658,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47684,7 +47684,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47710,7 +47710,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47736,7 +47736,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47762,7 +47762,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47788,7 +47788,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47814,7 +47814,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47840,7 +47840,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1768" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47866,7 +47866,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47892,7 +47892,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47918,7 +47918,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47944,7 +47944,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47970,7 +47970,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -47996,7 +47996,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1774" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48022,7 +48022,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48048,7 +48048,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48074,7 +48074,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48100,7 +48100,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1778" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48126,7 +48126,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48152,7 +48152,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48178,7 +48178,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1781" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48204,7 +48204,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1782" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48230,7 +48230,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48256,7 +48256,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48282,7 +48282,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48308,7 +48308,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48334,7 +48334,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48360,7 +48360,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48386,7 +48386,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48412,7 +48412,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48438,7 +48438,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48464,7 +48464,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48490,7 +48490,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48516,7 +48516,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48542,7 +48542,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48568,7 +48568,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48594,7 +48594,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48620,7 +48620,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48646,7 +48646,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48672,7 +48672,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48698,7 +48698,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48724,7 +48724,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48750,7 +48750,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48776,7 +48776,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1804" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48802,7 +48802,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48828,7 +48828,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48854,7 +48854,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48880,7 +48880,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48906,7 +48906,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48932,7 +48932,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48958,7 +48958,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48984,7 +48984,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49010,7 +49010,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49036,7 +49036,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49062,7 +49062,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49088,7 +49088,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49114,7 +49114,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49140,7 +49140,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49166,7 +49166,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49192,7 +49192,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49218,7 +49218,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49244,7 +49244,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49270,7 +49270,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49296,7 +49296,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49322,7 +49322,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49348,7 +49348,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49374,7 +49374,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49400,7 +49400,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49426,7 +49426,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49452,7 +49452,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49478,7 +49478,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49504,7 +49504,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49530,7 +49530,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49556,7 +49556,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49582,7 +49582,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49608,7 +49608,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49634,7 +49634,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49660,7 +49660,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49686,7 +49686,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49712,7 +49712,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49738,7 +49738,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49764,7 +49764,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49790,7 +49790,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49816,7 +49816,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49842,7 +49842,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49868,7 +49868,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49894,7 +49894,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49920,7 +49920,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49946,7 +49946,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49972,7 +49972,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -49998,7 +49998,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50024,7 +50024,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50050,7 +50050,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50076,7 +50076,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50102,7 +50102,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50128,7 +50128,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50154,7 +50154,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50180,7 +50180,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50206,7 +50206,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50232,7 +50232,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50258,7 +50258,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50284,7 +50284,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50310,7 +50310,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50336,7 +50336,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50362,7 +50362,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50388,7 +50388,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50414,7 +50414,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50440,7 +50440,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50466,7 +50466,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50492,7 +50492,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50518,7 +50518,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50544,7 +50544,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50570,7 +50570,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50596,7 +50596,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50622,7 +50622,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50648,7 +50648,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50674,7 +50674,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50700,7 +50700,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50726,7 +50726,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50752,7 +50752,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50778,7 +50778,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50804,7 +50804,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50830,7 +50830,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50856,7 +50856,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50882,7 +50882,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50908,7 +50908,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50934,7 +50934,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50960,7 +50960,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50986,7 +50986,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51012,7 +51012,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51038,7 +51038,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51064,7 +51064,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51090,7 +51090,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51116,7 +51116,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51142,7 +51142,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51168,7 +51168,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51194,7 +51194,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51272,7 +51272,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51298,7 +51298,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51324,7 +51324,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51350,7 +51350,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51428,7 +51428,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51532,7 +51532,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51610,7 +51610,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51636,7 +51636,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51662,7 +51662,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51740,7 +51740,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51818,7 +51818,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51844,7 +51844,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51870,7 +51870,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51896,7 +51896,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51974,7 +51974,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52000,7 +52000,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52052,7 +52052,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52130,7 +52130,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52208,7 +52208,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52234,7 +52234,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52286,7 +52286,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52338,7 +52338,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52468,7 +52468,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52494,7 +52494,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54522,7 +54522,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54548,7 +54548,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57070,7 +57070,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57148,7 +57148,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58136,7 +58136,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -66750,7 +66750,7 @@
     </row>
     <row r="2496">
       <c r="A2496" s="1" t="n">
-        <v>45953.6413310185</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2496" t="n">
         <v>11818</v>
@@ -66771,6 +66771,32 @@
         <v>506</v>
       </c>
       <c r="H2496" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2497">
+      <c r="A2497" s="1" t="n">
+        <v>45954.6494097222</v>
+      </c>
+      <c r="B2497" t="n">
+        <v>22528</v>
+      </c>
+      <c r="C2497" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="D2497" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2497" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="F2497" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="G2497" t="s">
+        <v>506</v>
+      </c>
+      <c r="H2497" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -59,7 +59,7 @@
     <t xml:space="preserve">0.210174232721329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099103093147</t>
+    <t xml:space="preserve">0.211099088191986</t>
   </si>
   <si>
     <t xml:space="preserve">0.217319890856743</t>
@@ -68,25 +68,25 @@
     <t xml:space="preserve">0.228921502828598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071776986122</t>
+    <t xml:space="preserve">0.227071791887283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293354511261</t>
+    <t xml:space="preserve">0.233293369412422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228417411446571</t>
+    <t xml:space="preserve">0.228417426347733</t>
   </si>
   <si>
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762211441994</t>
+    <t xml:space="preserve">0.229762226343155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598274230957</t>
+    <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
@@ -98,37 +98,37 @@
     <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014956235886</t>
+    <t xml:space="preserve">0.211014941334724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767146587372</t>
+    <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
     <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360030651093</t>
+    <t xml:space="preserve">0.193360045552254</t>
   </si>
   <si>
     <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722880005836</t>
+    <t xml:space="preserve">0.196722865104675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202355369925499</t>
+    <t xml:space="preserve">0.20235538482666</t>
   </si>
   <si>
     <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187076210976</t>
+    <t xml:space="preserve">0.202187091112137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214127898216</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
     <t xml:space="preserve">0.208912774920464</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279676556587</t>
+    <t xml:space="preserve">0.241279721260071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483234524727</t>
+    <t xml:space="preserve">0.245483249425888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208918333054</t>
+    <t xml:space="preserve">0.252208888530731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093953132629</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138204813004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182426691055</t>
+    <t xml:space="preserve">0.268182396888733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226678371429</t>
+    <t xml:space="preserve">0.273226708173752</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632989645004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836458206177</t>
+    <t xml:space="preserve">0.285836517810822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562186717987</t>
+    <t xml:space="preserve">0.292562216520309</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057835817337</t>
+    <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531079053879</t>
+    <t xml:space="preserve">0.317531049251556</t>
   </si>
   <si>
     <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336279153823853</t>
+    <t xml:space="preserve">0.33627912402153</t>
   </si>
   <si>
     <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36318102478981</t>
+    <t xml:space="preserve">0.363180994987488</t>
   </si>
   <si>
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
     <t xml:space="preserve">0.420348465442657</t>
@@ -224,7 +224,7 @@
     <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400881290436</t>
+    <t xml:space="preserve">0.483400970697403</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -233,10 +233,10 @@
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011584997177</t>
+    <t xml:space="preserve">0.4960116147995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515691280365</t>
+    <t xml:space="preserve">0.496515661478043</t>
   </si>
   <si>
     <t xml:space="preserve">0.492307901382446</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319216251373</t>
+    <t xml:space="preserve">0.715319275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67324161529541</t>
+    <t xml:space="preserve">0.673241674900055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641063451767</t>
+    <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618540823459625</t>
+    <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
     <t xml:space="preserve">0.622748494148254</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525970041751862</t>
+    <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">0.521762192249298</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931271076202</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008812427521</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892440795898</t>
+    <t xml:space="preserve">0.483892470598221</t>
   </si>
   <si>
     <t xml:space="preserve">0.51334673166275</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269130706787</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
     <t xml:space="preserve">0.467061370611191</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">0.437607020139694</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454438090324402</t>
+    <t xml:space="preserve">0.454438120126724</t>
   </si>
   <si>
     <t xml:space="preserve">0.450230360031128</t>
@@ -332,16 +332,16 @@
     <t xml:space="preserve">0.458645850419998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944939374924</t>
+    <t xml:space="preserve">0.403944998979568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776039361954</t>
+    <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
     <t xml:space="preserve">0.429191499948502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385621547699</t>
+    <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983769655228</t>
+    <t xml:space="preserve">0.424983739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409807443619</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
     <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414043605327606</t>
+    <t xml:space="preserve">0.414043575525284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360489368439</t>
+    <t xml:space="preserve">0.412360519170761</t>
   </si>
   <si>
     <t xml:space="preserve">0.415726691484451</t>
@@ -374,10 +374,10 @@
     <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092893600464</t>
+    <t xml:space="preserve">0.419092863798141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628055334091</t>
+    <t xml:space="preserve">0.405628085136414</t>
   </si>
   <si>
     <t xml:space="preserve">0.408994287252426</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163187265396</t>
+    <t xml:space="preserve">0.392163217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578767061234</t>
+    <t xml:space="preserve">0.400578796863556</t>
   </si>
   <si>
     <t xml:space="preserve">0.393846333026886</t>
@@ -401,34 +401,34 @@
     <t xml:space="preserve">0.402261883020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529478788376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113898992538</t>
+    <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
     <t xml:space="preserve">0.373649120330811</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620807647705</t>
+    <t xml:space="preserve">0.336620837450027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32988840341568</t>
+    <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328205317258835</t>
+    <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522201299667</t>
+    <t xml:space="preserve">0.326522171497345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324839115142822</t>
+    <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
     <t xml:space="preserve">0.35345184803009</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036298036575</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.350085616111755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830389380455</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">0.366916686296463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358501136302948</t>
+    <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
     <t xml:space="preserve">0.368599772453308</t>
@@ -488,22 +488,22 @@
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797014951706</t>
+    <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
     <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064610719681</t>
+    <t xml:space="preserve">0.382064580917358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332236289978</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015322446823</t>
+    <t xml:space="preserve">0.377015292644501</t>
   </si>
   <si>
     <t xml:space="preserve">0.371966004371643</t>
@@ -518,19 +518,19 @@
     <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632122516632</t>
+    <t xml:space="preserve">0.559632062911987</t>
   </si>
   <si>
     <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48978328704834</t>
+    <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48473396897316</t>
+    <t xml:space="preserve">0.484733998775482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476318448781967</t>
+    <t xml:space="preserve">0.47631847858429</t>
   </si>
   <si>
     <t xml:space="preserve">0.494832575321198</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198807239532</t>
+    <t xml:space="preserve">0.49819877743721</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
@@ -557,19 +557,19 @@
     <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128424167633</t>
+    <t xml:space="preserve">0.525128483772278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523445308208466</t>
+    <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
     <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663615703583</t>
+    <t xml:space="preserve">0.511663556098938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50324809551239</t>
+    <t xml:space="preserve">0.503248035907745</t>
   </si>
   <si>
     <t xml:space="preserve">0.508297443389893</t>
@@ -584,31 +584,31 @@
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029788017273</t>
+    <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473740100861</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107508182526</t>
+    <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
     <t xml:space="preserve">0.5503751039505</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860888004303</t>
+    <t xml:space="preserve">0.531860947608948</t>
   </si>
   <si>
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671290397644</t>
+    <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019848823547</t>
@@ -66776,7 +66776,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6494097222</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>22528</v>
@@ -66797,6 +66797,32 @@
         <v>506</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.4715509259</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>7006</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>0.564000010490417</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815495252609</t>
+    <t xml:space="preserve">0.235815480351448</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249087929726</t>
+    <t xml:space="preserve">0.228249117732048</t>
   </si>
   <si>
     <t xml:space="preserve">0.216899931430817</t>
@@ -56,73 +56,73 @@
     <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210174232721329</t>
+    <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099088191986</t>
+    <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217319890856743</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921502828598</t>
+    <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071806788445</t>
   </si>
   <si>
     <t xml:space="preserve">0.233293369412422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228417426347733</t>
+    <t xml:space="preserve">0.22841739654541</t>
   </si>
   <si>
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762226343155</t>
+    <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598259329796</t>
+    <t xml:space="preserve">0.239598244428635</t>
   </si>
   <si>
     <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868219017982</t>
+    <t xml:space="preserve">0.222868204116821</t>
   </si>
   <si>
     <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21437780559063</t>
+    <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
     <t xml:space="preserve">0.211014941334724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970704555511</t>
+    <t xml:space="preserve">0.205970719456673</t>
   </si>
   <si>
     <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563588619232</t>
+    <t xml:space="preserve">0.197563573718071</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360045552254</t>
+    <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722865104675</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20235538482666</t>
+    <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607855200768</t>
+    <t xml:space="preserve">0.202607870101929</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187091112137</t>
@@ -131,64 +131,64 @@
     <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912774920464</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218499302864</t>
+    <t xml:space="preserve">0.215218484401703</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616598010063</t>
+    <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
     <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031866908073</t>
+    <t xml:space="preserve">0.232031881809235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235454678535</t>
+    <t xml:space="preserve">0.236235439777374</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279721260071</t>
+    <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
     <t xml:space="preserve">0.245483249425888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208888530731</t>
+    <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093953132629</t>
+    <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138204813004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182396888733</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226708173752</t>
+    <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281632989645004</t>
+    <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
     <t xml:space="preserve">0.285836517810822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562216520309</t>
+    <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332137107849</t>
+    <t xml:space="preserve">0.304332077503204</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057806015015</t>
+    <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
@@ -209,10 +209,10 @@
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941409111023</t>
+    <t xml:space="preserve">0.411941438913345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420348465442657</t>
+    <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
     <t xml:space="preserve">0.440525591373444</t>
@@ -221,10 +221,10 @@
     <t xml:space="preserve">0.439684867858887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471743822098</t>
+    <t xml:space="preserve">0.472471714019775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400970697403</t>
+    <t xml:space="preserve">0.483401000499725</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">0.496515661478043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307901382446</t>
+    <t xml:space="preserve">0.492307960987091</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61854076385498</t>
+    <t xml:space="preserve">0.618540823459625</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748494148254</t>
+    <t xml:space="preserve">0.622748553752899</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
@@ -278,19 +278,19 @@
     <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931151866913</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008812427521</t>
+    <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509138941764832</t>
+    <t xml:space="preserve">0.509139001369476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892470598221</t>
+    <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51334673166275</t>
+    <t xml:space="preserve">0.513346672058105</t>
   </si>
   <si>
     <t xml:space="preserve">0.530177772045135</t>
@@ -305,34 +305,34 @@
     <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500723421573639</t>
+    <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
     <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684621095657</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607020139694</t>
+    <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454438120126724</t>
+    <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
     <t xml:space="preserve">0.450230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022540330887</t>
+    <t xml:space="preserve">0.446022570133209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645850419998</t>
+    <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944998979568</t>
+    <t xml:space="preserve">0.403944969177246</t>
   </si>
   <si>
     <t xml:space="preserve">0.420776009559631</t>
@@ -341,43 +341,43 @@
     <t xml:space="preserve">0.429191499948502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385561943054</t>
+    <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476890802383</t>
+    <t xml:space="preserve">0.475476861000061</t>
   </si>
   <si>
     <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983739852905</t>
+    <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381494760513</t>
+    <t xml:space="preserve">0.380381524562836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414043575525284</t>
+    <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
     <t xml:space="preserve">0.412360519170761</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726721286774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814810037613</t>
+    <t xml:space="preserve">0.441814839839935</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092863798141</t>
+    <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628085136414</t>
+    <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
     <t xml:space="preserve">0.408994287252426</t>
@@ -392,28 +392,28 @@
     <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578796863556</t>
+    <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
     <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261883020401</t>
+    <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529478788376</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649120330811</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155969381332</t>
+    <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374247074127</t>
+    <t xml:space="preserve">0.31137427687645</t>
   </si>
   <si>
     <t xml:space="preserve">0.336620837450027</t>
@@ -425,10 +425,10 @@
     <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522171497345</t>
+    <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3248390853405</t>
+    <t xml:space="preserve">0.324839115142822</t>
   </si>
   <si>
     <t xml:space="preserve">0.35345184803009</t>
@@ -437,22 +437,22 @@
     <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768732070923</t>
+    <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345036298036575</t>
+    <t xml:space="preserve">0.345036327838898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350085616111755</t>
+    <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
     <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571489572525</t>
+    <t xml:space="preserve">0.331571459770203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34335321187973</t>
+    <t xml:space="preserve">0.343353182077408</t>
   </si>
   <si>
     <t xml:space="preserve">0.333254605531693</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916686296463</t>
+    <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">0.35850116610527</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212564945221</t>
+    <t xml:space="preserve">0.397212535142899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383747726678848</t>
@@ -491,10 +491,10 @@
     <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698408603668</t>
+    <t xml:space="preserve">0.378698438405991</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064580917358</t>
+    <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
     <t xml:space="preserve">0.375332206487656</t>
@@ -503,16 +503,16 @@
     <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015262842178</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371966004371643</t>
+    <t xml:space="preserve">0.371965974569321</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233570337296</t>
+    <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
     <t xml:space="preserve">0.538593292236328</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">0.559632062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216542720795</t>
+    <t xml:space="preserve">0.551216602325439</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733998775482</t>
+    <t xml:space="preserve">0.484733939170837</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">0.49819877743721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741216659546</t>
+    <t xml:space="preserve">0.553741157054901</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494715690613</t>
+    <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079135894775</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811540126801</t>
+    <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910235881805</t>
+    <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128483772278</t>
@@ -569,7 +569,7 @@
     <t xml:space="preserve">0.511663556098938</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503248035907745</t>
+    <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
     <t xml:space="preserve">0.508297443389893</t>
@@ -581,16 +581,16 @@
     <t xml:space="preserve">0.49314945936203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50998055934906</t>
+    <t xml:space="preserve">0.509980499744415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029847621918</t>
+    <t xml:space="preserve">0.515029907226562</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5503751039505</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860947608948</t>
@@ -614,22 +614,22 @@
     <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53180605173111</t>
+    <t xml:space="preserve">0.531806111335754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068159103394</t>
+    <t xml:space="preserve">0.530068099498749</t>
   </si>
   <si>
     <t xml:space="preserve">0.535281956195831</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592314243317</t>
+    <t xml:space="preserve">0.526592254638672</t>
   </si>
   <si>
     <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709550380707</t>
+    <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
     <t xml:space="preserve">0.552661180496216</t>
@@ -641,10 +641,10 @@
     <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399192333221</t>
+    <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971598148346</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -656,16 +656,16 @@
     <t xml:space="preserve">0.540495693683624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568302631378174</t>
+    <t xml:space="preserve">0.568302571773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559612929821014</t>
+    <t xml:space="preserve">0.55961287021637</t>
   </si>
   <si>
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378517150879</t>
+    <t xml:space="preserve">0.521378457546234</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261340618134</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
     <t xml:space="preserve">0.50399923324585</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571698665619</t>
+    <t xml:space="preserve">0.493571668863297</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -692,22 +692,22 @@
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640505313873</t>
+    <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274936676025</t>
+    <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323187351227</t>
+    <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
     <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895652770996</t>
+    <t xml:space="preserve">0.590895593166351</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102311134338</t>
+    <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364478111267</t>
+    <t xml:space="preserve">0.667364537715912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392113208771</t>
+    <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702471256256</t>
+    <t xml:space="preserve">0.618702530860901</t>
   </si>
   <si>
     <t xml:space="preserve">0.632605910301208</t>
@@ -749,31 +749,31 @@
     <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644771337509155</t>
+    <t xml:space="preserve">0.6447713971138</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62565416097641</t>
+    <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440363883972</t>
+    <t xml:space="preserve">0.620440423488617</t>
   </si>
   <si>
     <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033444881439</t>
+    <t xml:space="preserve">0.643033504486084</t>
   </si>
   <si>
     <t xml:space="preserve">0.622178375720978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012829303741</t>
+    <t xml:space="preserve">0.610012888908386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943903446198</t>
+    <t xml:space="preserve">0.583943843841553</t>
   </si>
   <si>
     <t xml:space="preserve">0.592633545398712</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778416633606</t>
+    <t xml:space="preserve">0.571778357028961</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557875037193298</t>
+    <t xml:space="preserve">0.557874977588654</t>
   </si>
   <si>
     <t xml:space="preserve">0.573516368865967</t>
@@ -806,37 +806,37 @@
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985134601593</t>
+    <t xml:space="preserve">0.649985194206238</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247182369232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081755161285</t>
+    <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005809783936</t>
+    <t xml:space="preserve">0.68300586938858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957559108734</t>
+    <t xml:space="preserve">0.689957499504089</t>
   </si>
   <si>
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743762016296</t>
+    <t xml:space="preserve">0.684743702411652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150681018829</t>
+    <t xml:space="preserve">0.662150740623474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316167831421</t>
+    <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936883926392</t>
+    <t xml:space="preserve">0.656936943531036</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674776554108</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
     <t xml:space="preserve">0.646509289741516</t>
@@ -848,13 +848,13 @@
     <t xml:space="preserve">0.615226566791534</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613488674163818</t>
+    <t xml:space="preserve">0.613488733768463</t>
   </si>
   <si>
     <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788601875305</t>
+    <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -866,13 +866,13 @@
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897906780243</t>
+    <t xml:space="preserve">0.614897966384888</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276033878326</t>
+    <t xml:space="preserve">0.620276093482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
@@ -911,7 +911,7 @@
     <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577251136302948</t>
+    <t xml:space="preserve">0.577251076698303</t>
   </si>
   <si>
     <t xml:space="preserve">0.593385457992554</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">0.580836534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582629263401031</t>
+    <t xml:space="preserve">0.582629203796387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579043865203857</t>
@@ -941,19 +941,19 @@
     <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58621472120285</t>
+    <t xml:space="preserve">0.586214661598206</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178127288818</t>
+    <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032288074493</t>
+    <t xml:space="preserve">0.631032347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613105237483978</t>
+    <t xml:space="preserve">0.613105297088623</t>
   </si>
   <si>
     <t xml:space="preserve">0.611312508583069</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567831516266</t>
+    <t xml:space="preserve">0.548567891120911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546775162220001</t>
+    <t xml:space="preserve">0.546775102615356</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738627910614</t>
+    <t xml:space="preserve">0.555738687515259</t>
   </si>
   <si>
     <t xml:space="preserve">0.553945958614349</t>
@@ -1010,7 +1010,7 @@
     <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
     <t xml:space="preserve">0.665093660354614</t>
@@ -1022,13 +1022,13 @@
     <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544796466827</t>
+    <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
     <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166669368744</t>
+    <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
@@ -1037,13 +1037,13 @@
     <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684813439846039</t>
+    <t xml:space="preserve">0.684813499450684</t>
   </si>
   <si>
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191507339478</t>
+    <t xml:space="preserve">0.690191566944122</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1055,22 +1055,22 @@
     <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972718715668</t>
+    <t xml:space="preserve">0.743972778320312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711704075336456</t>
+    <t xml:space="preserve">0.711704015731812</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727838397026062</t>
+    <t xml:space="preserve">0.727838337421417</t>
   </si>
   <si>
     <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460329532623</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765388011932</t>
+    <t xml:space="preserve">0.745765447616577</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742180049419403</t>
+    <t xml:space="preserve">0.742180109024048</t>
   </si>
   <si>
     <t xml:space="preserve">0.708118677139282</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">0.700947821140289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706325948238373</t>
+    <t xml:space="preserve">0.706325888633728</t>
   </si>
   <si>
     <t xml:space="preserve">0.697362422943115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71708220243454</t>
+    <t xml:space="preserve">0.717082142829895</t>
   </si>
   <si>
     <t xml:space="preserve">0.724252998828888</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642643451691</t>
+    <t xml:space="preserve">0.677642703056335</t>
   </si>
   <si>
     <t xml:space="preserve">0.675849914550781</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045727729797</t>
+    <t xml:space="preserve">0.726045668125153</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">0.691984295845032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695569694042206</t>
+    <t xml:space="preserve">0.695569753646851</t>
   </si>
   <si>
     <t xml:space="preserve">0.665459334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659898400306702</t>
+    <t xml:space="preserve">0.659898459911346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650630235671997</t>
+    <t xml:space="preserve">0.650630176067352</t>
   </si>
   <si>
     <t xml:space="preserve">0.658044755458832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652483880519867</t>
+    <t xml:space="preserve">0.652483820915222</t>
   </si>
   <si>
     <t xml:space="preserve">0.654337465763092</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">0.661752045154572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.663605690002441</t>
+    <t xml:space="preserve">0.663605749607086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646922945976257</t>
+    <t xml:space="preserve">0.646922886371613</t>
   </si>
   <si>
     <t xml:space="preserve">0.645069241523743</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">0.643215596675873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635801017284393</t>
+    <t xml:space="preserve">0.635800957679749</t>
   </si>
   <si>
     <t xml:space="preserve">0.633947372436523</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">0.62097179889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626532733440399</t>
+    <t xml:space="preserve">0.626532793045044</t>
   </si>
   <si>
     <t xml:space="preserve">0.613557279109955</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">0.572776973247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583898842334747</t>
+    <t xml:space="preserve">0.583898901939392</t>
   </si>
   <si>
     <t xml:space="preserve">0.578337907791138</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">0.602435350418091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604289054870605</t>
+    <t xml:space="preserve">0.604288995265961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593167126178741</t>
+    <t xml:space="preserve">0.593167066574097</t>
   </si>
   <si>
     <t xml:space="preserve">0.600581705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595020771026611</t>
+    <t xml:space="preserve">0.595020830631256</t>
   </si>
   <si>
     <t xml:space="preserve">0.589459776878357</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">0.557947814464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541264951229095</t>
+    <t xml:space="preserve">0.54126501083374</t>
   </si>
   <si>
     <t xml:space="preserve">0.546825885772705</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">0.563508749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570923388004303</t>
+    <t xml:space="preserve">0.570923328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61726450920105</t>
+    <t xml:space="preserve">0.617264568805695</t>
   </si>
   <si>
     <t xml:space="preserve">0.624679148197174</t>
@@ -66802,7 +66802,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.4715509259</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>7006</v>
@@ -66823,6 +66823,32 @@
         <v>508</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6023611111</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>3624</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>0.565999984741211</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>0.565999984741211</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,58 +38,58 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815480351448</t>
+    <t xml:space="preserve">0.23581551015377</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394731163979</t>
+    <t xml:space="preserve">0.235394716262817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249117732048</t>
+    <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899931430817</t>
+    <t xml:space="preserve">0.216899916529655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581363558769</t>
+    <t xml:space="preserve">0.218581333756447</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099103093147</t>
+    <t xml:space="preserve">0.211099088191986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217319875955582</t>
+    <t xml:space="preserve">0.21731986105442</t>
   </si>
   <si>
     <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071806788445</t>
+    <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293369412422</t>
+    <t xml:space="preserve">0.233293399214745</t>
   </si>
   <si>
     <t xml:space="preserve">0.22841739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231527790427208</t>
+    <t xml:space="preserve">0.231527775526047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762211441994</t>
+    <t xml:space="preserve">0.229762226343155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598244428635</t>
+    <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868204116821</t>
+    <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
     <t xml:space="preserve">0.222784891724586</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014941334724</t>
+    <t xml:space="preserve">0.211014971137047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970719456673</t>
+    <t xml:space="preserve">0.20597068965435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767161488533</t>
+    <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563573718071</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
@@ -116,13 +116,13 @@
     <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722880005836</t>
+    <t xml:space="preserve">0.196722894906998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202355399727821</t>
+    <t xml:space="preserve">0.20235538482666</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607870101929</t>
+    <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187091112137</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912760019302</t>
+    <t xml:space="preserve">0.208912774920464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762500762939</t>
+    <t xml:space="preserve">0.210762485861778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218484401703</t>
+    <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
     <t xml:space="preserve">0.222616583108902</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031881809235</t>
+    <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
     <t xml:space="preserve">0.236235439777374</t>
@@ -161,34 +161,34 @@
     <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093893527985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138204813004</t>
+    <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182426691055</t>
+    <t xml:space="preserve">0.268182456493378</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226678371429</t>
+    <t xml:space="preserve">0.273226648569107</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562186717987</t>
+    <t xml:space="preserve">0.292562216520309</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332077503204</t>
+    <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057835817337</t>
+    <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33627912402153</t>
+    <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
     <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363180994987488</t>
+    <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313809633255</t>
+    <t xml:space="preserve">0.378313839435577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941438913345</t>
+    <t xml:space="preserve">0.411941379308701</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525591373444</t>
+    <t xml:space="preserve">0.440525561571121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684867858887</t>
+    <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471714019775</t>
+    <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483401000499725</t>
+    <t xml:space="preserve">0.483400911092758</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055896282196</t>
@@ -233,13 +233,13 @@
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4960116147995</t>
+    <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515661478043</t>
+    <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307960987091</t>
+    <t xml:space="preserve">0.492307871580124</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -254,22 +254,22 @@
     <t xml:space="preserve">0.715319275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241674900055</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656410574913025</t>
+    <t xml:space="preserve">0.65641051530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618540823459625</t>
+    <t xml:space="preserve">0.618540704250336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748553752899</t>
+    <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525969982147217</t>
+    <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
     <t xml:space="preserve">0.521762192249298</t>
@@ -278,37 +278,37 @@
     <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931151866913</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
     <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346672058105</t>
+    <t xml:space="preserve">0.51334673166275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177772045135</t>
+    <t xml:space="preserve">0.530177712440491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554461956024</t>
+    <t xml:space="preserve">0.517554521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269160509109</t>
+    <t xml:space="preserve">0.471269100904465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061370611191</t>
+    <t xml:space="preserve">0.467061340808868</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853640317917</t>
+    <t xml:space="preserve">0.462853610515594</t>
   </si>
   <si>
     <t xml:space="preserve">0.47968465089798</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">0.450230360031128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022570133209</t>
+    <t xml:space="preserve">0.446022510528564</t>
   </si>
   <si>
     <t xml:space="preserve">0.458645880222321</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191499948502</t>
+    <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385502338409</t>
+    <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677373409271</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
@@ -359,25 +359,25 @@
     <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381524562836</t>
+    <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360519170761</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726721286774</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814839839935</t>
+    <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092893600464</t>
+    <t xml:space="preserve">0.419092923402786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628055334091</t>
+    <t xml:space="preserve">0.405628085136414</t>
   </si>
   <si>
     <t xml:space="preserve">0.408994287252426</t>
@@ -386,7 +386,7 @@
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163217067719</t>
+    <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846333026886</t>
+    <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
@@ -407,37 +407,37 @@
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649090528488</t>
+    <t xml:space="preserve">0.373649060726166</t>
   </si>
   <si>
     <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31137427687645</t>
+    <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620837450027</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888373613358</t>
+    <t xml:space="preserve">0.32988840341568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328205287456512</t>
+    <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324839115142822</t>
+    <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35345184803009</t>
+    <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
     <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036327838898</t>
@@ -449,19 +449,19 @@
     <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343353182077408</t>
+    <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333254605531693</t>
+    <t xml:space="preserve">0.33325457572937</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334937691688538</t>
+    <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
     <t xml:space="preserve">0.339987009763718</t>
@@ -482,31 +482,31 @@
     <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212535142899</t>
+    <t xml:space="preserve">0.397212594747543</t>
   </si>
   <si>
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797044754028</t>
+    <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698438405991</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332206487656</t>
+    <t xml:space="preserve">0.375332176685333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282918214798</t>
+    <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015262842178</t>
+    <t xml:space="preserve">0.377015292644501</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371965974569321</t>
+    <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
@@ -521,76 +521,76 @@
     <t xml:space="preserve">0.559632062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216602325439</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733939170837</t>
+    <t xml:space="preserve">0.484733909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47631847858429</t>
+    <t xml:space="preserve">0.476318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494832575321198</t>
+    <t xml:space="preserve">0.494832515716553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466343402863</t>
+    <t xml:space="preserve">0.491466373205185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49819877743721</t>
+    <t xml:space="preserve">0.498198747634888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741157054901</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520079135894775</t>
+    <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811599731445</t>
+    <t xml:space="preserve">0.526811480522156</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910176277161</t>
+    <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128483772278</t>
+    <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52344536781311</t>
+    <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
     <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663556098938</t>
+    <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50324809551239</t>
+    <t xml:space="preserve">0.503248035907745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297443389893</t>
+    <t xml:space="preserve">0.508297324180603</t>
   </si>
   <si>
     <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49314945936203</t>
+    <t xml:space="preserve">0.493149489164352</t>
   </si>
   <si>
     <t xml:space="preserve">0.509980499744415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029907226562</t>
+    <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473740100861</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,10 +599,10 @@
     <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550375044345856</t>
+    <t xml:space="preserve">0.550374984741211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860947608948</t>
+    <t xml:space="preserve">0.531860828399658</t>
   </si>
   <si>
     <t xml:space="preserve">0.518396079540253</t>
@@ -611,16 +611,16 @@
     <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019848823547</t>
+    <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
     <t xml:space="preserve">0.530068099498749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281956195831</t>
+    <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
     <t xml:space="preserve">0.526592254638672</t>
@@ -632,19 +632,19 @@
     <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661180496216</t>
+    <t xml:space="preserve">0.552661120891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185395240784</t>
+    <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447443008423</t>
+    <t xml:space="preserve">0.547447383403778</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971598148346</t>
+    <t xml:space="preserve">0.543971478939056</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">0.568302571773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55961287021637</t>
+    <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378457546234</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
@@ -680,79 +680,79 @@
     <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833746433258</t>
+    <t xml:space="preserve">0.491833627223969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571668863297</t>
+    <t xml:space="preserve">0.493571639060974</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854362010956</t>
+    <t xml:space="preserve">0.524854302406311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523116409778595</t>
+    <t xml:space="preserve">0.52311646938324</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640564918518</t>
+    <t xml:space="preserve">0.519640505313873</t>
   </si>
   <si>
     <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419748306274</t>
+    <t xml:space="preserve">0.587419807910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323246955872</t>
+    <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585294723511</t>
+    <t xml:space="preserve">0.599585235118866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895593166351</t>
+    <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585681855678558</t>
+    <t xml:space="preserve">0.585681915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589157700538635</t>
+    <t xml:space="preserve">0.58915764093399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557600021362</t>
+    <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
     <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288532733917</t>
+    <t xml:space="preserve">0.714288473129272</t>
   </si>
   <si>
     <t xml:space="preserve">0.667364537715912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061079978943</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702530860901</t>
+    <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
     <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65346097946167</t>
+    <t xml:space="preserve">0.653461039066315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6447713971138</t>
+    <t xml:space="preserve">0.644771337509155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629130005836487</t>
+    <t xml:space="preserve">0.629130065441132</t>
   </si>
   <si>
     <t xml:space="preserve">0.625654220581055</t>
@@ -773,19 +773,19 @@
     <t xml:space="preserve">0.610012888908386</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943843841553</t>
+    <t xml:space="preserve">0.583943963050842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633545398712</t>
+    <t xml:space="preserve">0.592633605003357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778357028961</t>
+    <t xml:space="preserve">0.571778416633606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582205951213837</t>
+    <t xml:space="preserve">0.582206010818481</t>
   </si>
   <si>
     <t xml:space="preserve">0.505737125873566</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109449863434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750781536102</t>
+    <t xml:space="preserve">0.611750841140747</t>
   </si>
   <si>
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985253810883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247182369232</t>
+    <t xml:space="preserve">0.648247301578522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081695556641</t>
+    <t xml:space="preserve">0.636081755161285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68300586938858</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957499504089</t>
+    <t xml:space="preserve">0.689957559108734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688219606876373</t>
+    <t xml:space="preserve">0.688219547271729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743702411652</t>
+    <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
     <t xml:space="preserve">0.662150740623474</t>
@@ -833,28 +833,28 @@
     <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936943531036</t>
+    <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
     <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509289741516</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226566791534</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613488733768463</t>
+    <t xml:space="preserve">0.613488674163818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617686271667</t>
+    <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64178854227066</t>
+    <t xml:space="preserve">0.641788482666016</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592788696289</t>
+    <t xml:space="preserve">0.591592848300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970915794373</t>
+    <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6238614320755</t>
+    <t xml:space="preserve">0.623861491680145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690695285797</t>
+    <t xml:space="preserve">0.616690635681152</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58980005979538</t>
+    <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577251076698303</t>
+    <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385457992554</t>
+    <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -923,13 +923,13 @@
     <t xml:space="preserve">0.580836534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582629203796387</t>
+    <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043865203857</t>
+    <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324085712433</t>
+    <t xml:space="preserve">0.559324026107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873068809509</t>
+    <t xml:space="preserve">0.571873009204865</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -953,7 +953,7 @@
     <t xml:space="preserve">0.631032347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613105297088623</t>
+    <t xml:space="preserve">0.613105237483978</t>
   </si>
   <si>
     <t xml:space="preserve">0.611312508583069</t>
@@ -965,10 +965,10 @@
     <t xml:space="preserve">0.548567891120911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546775102615356</t>
+    <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
     <t xml:space="preserve">0.553945958614349</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702212810516</t>
+    <t xml:space="preserve">0.564702153205872</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203144073486</t>
+    <t xml:space="preserve">0.638203084468842</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -998,25 +998,25 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337525367737</t>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057185649872</t>
+    <t xml:space="preserve">0.674057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66150826215744</t>
+    <t xml:space="preserve">0.661508321762085</t>
   </si>
   <si>
     <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093660354614</t>
+    <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886389255524</t>
+    <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
     <t xml:space="preserve">0.645373940467834</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64358127117157</t>
+    <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
     <t xml:space="preserve">0.647166609764099</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471787452698</t>
+    <t xml:space="preserve">0.670471847057343</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684813499450684</t>
+    <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020770549774</t>
+    <t xml:space="preserve">0.683020710945129</t>
   </si>
   <si>
     <t xml:space="preserve">0.690191566944122</t>
@@ -1049,22 +1049,22 @@
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715289413928986</t>
+    <t xml:space="preserve">0.71528947353363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594591617584</t>
+    <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
     <t xml:space="preserve">0.743972778320312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711704015731812</t>
+    <t xml:space="preserve">0.711704075336456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727838337421417</t>
+    <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009133815765</t>
+    <t xml:space="preserve">0.73500919342041</t>
   </si>
   <si>
     <t xml:space="preserve">0.722460269927979</t>
@@ -1079,7 +1079,7 @@
     <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742180109024048</t>
+    <t xml:space="preserve">0.742180049419403</t>
   </si>
   <si>
     <t xml:space="preserve">0.708118677139282</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">0.700947821140289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706325888633728</t>
+    <t xml:space="preserve">0.706325948238373</t>
   </si>
   <si>
     <t xml:space="preserve">0.697362422943115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717082142829895</t>
+    <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252998828888</t>
+    <t xml:space="preserve">0.724252939224243</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398897647858</t>
+    <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642703056335</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849914550781</t>
+    <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667600631714</t>
+    <t xml:space="preserve">0.720667541027069</t>
   </si>
   <si>
     <t xml:space="preserve">0.726045668125153</t>
@@ -1133,34 +1133,31 @@
     <t xml:space="preserve">0.691984295845032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695569753646851</t>
+    <t xml:space="preserve">0.695569694042206</t>
   </si>
   <si>
     <t xml:space="preserve">0.665459334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659898459911346</t>
+    <t xml:space="preserve">0.659898400306702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650630176067352</t>
+    <t xml:space="preserve">0.650630235671997</t>
   </si>
   <si>
     <t xml:space="preserve">0.658044755458832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652483820915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.652483880519867</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.663605749607086</t>
+    <t xml:space="preserve">0.663605690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646922886371613</t>
+    <t xml:space="preserve">0.646922945976257</t>
   </si>
   <si>
     <t xml:space="preserve">0.645069241523743</t>
@@ -1181,7 +1178,7 @@
     <t xml:space="preserve">0.643215596675873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635800957679749</t>
+    <t xml:space="preserve">0.635801017284393</t>
   </si>
   <si>
     <t xml:space="preserve">0.633947372436523</t>
@@ -1196,7 +1193,7 @@
     <t xml:space="preserve">0.62097179889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626532793045044</t>
+    <t xml:space="preserve">0.626532733440399</t>
   </si>
   <si>
     <t xml:space="preserve">0.613557279109955</t>
@@ -1208,7 +1205,7 @@
     <t xml:space="preserve">0.572776973247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583898901939392</t>
+    <t xml:space="preserve">0.583898842334747</t>
   </si>
   <si>
     <t xml:space="preserve">0.578337907791138</t>
@@ -1220,16 +1217,16 @@
     <t xml:space="preserve">0.602435350418091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604288995265961</t>
+    <t xml:space="preserve">0.604289054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593167066574097</t>
+    <t xml:space="preserve">0.593167126178741</t>
   </si>
   <si>
     <t xml:space="preserve">0.600581705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595020830631256</t>
+    <t xml:space="preserve">0.595020771026611</t>
   </si>
   <si>
     <t xml:space="preserve">0.589459776878357</t>
@@ -1247,7 +1244,7 @@
     <t xml:space="preserve">0.557947814464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54126501083374</t>
+    <t xml:space="preserve">0.541264951229095</t>
   </si>
   <si>
     <t xml:space="preserve">0.546825885772705</t>
@@ -1262,10 +1259,10 @@
     <t xml:space="preserve">0.563508749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570923328399658</t>
+    <t xml:space="preserve">0.570923388004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617264568805695</t>
+    <t xml:space="preserve">0.61726450920105</t>
   </si>
   <si>
     <t xml:space="preserve">0.624679148197174</t>
@@ -51194,7 +51191,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51220,7 +51217,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51246,7 +51243,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51376,7 +51373,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51402,7 +51399,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51454,7 +51451,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51480,7 +51477,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51506,7 +51503,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51558,7 +51555,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51584,7 +51581,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51688,7 +51685,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51714,7 +51711,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51766,7 +51763,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51792,7 +51789,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51844,7 +51841,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51922,7 +51919,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51948,7 +51945,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52026,7 +52023,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52052,7 +52049,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52078,7 +52075,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52104,7 +52101,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52130,7 +52127,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52156,7 +52153,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52182,7 +52179,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52260,7 +52257,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52286,7 +52283,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52312,7 +52309,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52364,7 +52361,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52390,7 +52387,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52416,7 +52413,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52442,7 +52439,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52520,7 +52517,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52546,7 +52543,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52572,7 +52569,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52598,7 +52595,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52624,7 +52621,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52650,7 +52647,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52676,7 +52673,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52702,7 +52699,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52728,7 +52725,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52754,7 +52751,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52780,7 +52777,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52806,7 +52803,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52832,7 +52829,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52858,7 +52855,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52884,7 +52881,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52910,7 +52907,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52936,7 +52933,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52962,7 +52959,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52988,7 +52985,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53014,7 +53011,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53040,7 +53037,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53066,7 +53063,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53092,7 +53089,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53118,7 +53115,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53144,7 +53141,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53170,7 +53167,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53196,7 +53193,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53222,7 +53219,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53248,7 +53245,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53274,7 +53271,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53300,7 +53297,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53326,7 +53323,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53352,7 +53349,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53378,7 +53375,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53404,7 +53401,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53430,7 +53427,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53456,7 +53453,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53482,7 +53479,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53508,7 +53505,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53534,7 +53531,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53560,7 +53557,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53586,7 +53583,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53612,7 +53609,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53638,7 +53635,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53664,7 +53661,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53690,7 +53687,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53716,7 +53713,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53742,7 +53739,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53768,7 +53765,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53794,7 +53791,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53820,7 +53817,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53846,7 +53843,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53872,7 +53869,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53898,7 +53895,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53924,7 +53921,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53950,7 +53947,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53976,7 +53973,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54002,7 +53999,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54028,7 +54025,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54054,7 +54051,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54080,7 +54077,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54106,7 +54103,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54132,7 +54129,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54158,7 +54155,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54184,7 +54181,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54210,7 +54207,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54236,7 +54233,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54262,7 +54259,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54288,7 +54285,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54314,7 +54311,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54340,7 +54337,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54366,7 +54363,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54392,7 +54389,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54418,7 +54415,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54444,7 +54441,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54470,7 +54467,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54496,7 +54493,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54574,7 +54571,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54600,7 +54597,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54626,7 +54623,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54652,7 +54649,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54678,7 +54675,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54704,7 +54701,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54730,7 +54727,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54756,7 +54753,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54782,7 +54779,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54808,7 +54805,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54834,7 +54831,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54860,7 +54857,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54886,7 +54883,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54912,7 +54909,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54938,7 +54935,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54964,7 +54961,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54990,7 +54987,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55016,7 +55013,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55042,7 +55039,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55068,7 +55065,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55094,7 +55091,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55120,7 +55117,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55146,7 +55143,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55172,7 +55169,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55198,7 +55195,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55224,7 +55221,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55250,7 +55247,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55276,7 +55273,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55302,7 +55299,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55328,7 +55325,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55354,7 +55351,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55380,7 +55377,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55406,7 +55403,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55432,7 +55429,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55458,7 +55455,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55484,7 +55481,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55510,7 +55507,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55536,7 +55533,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55562,7 +55559,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55588,7 +55585,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55614,7 +55611,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55640,7 +55637,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55666,7 +55663,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55692,7 +55689,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55718,7 +55715,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55744,7 +55741,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55770,7 +55767,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55796,7 +55793,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55822,7 +55819,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55848,7 +55845,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55874,7 +55871,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55900,7 +55897,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55926,7 +55923,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55952,7 +55949,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55978,7 +55975,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56004,7 +56001,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56030,7 +56027,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56056,7 +56053,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56082,7 +56079,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56108,7 +56105,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56134,7 +56131,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56160,7 +56157,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56186,7 +56183,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56212,7 +56209,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56238,7 +56235,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56264,7 +56261,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56290,7 +56287,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56316,7 +56313,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56342,7 +56339,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56368,7 +56365,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56394,7 +56391,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56420,7 +56417,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56446,7 +56443,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56472,7 +56469,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56498,7 +56495,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56524,7 +56521,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56550,7 +56547,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56576,7 +56573,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56602,7 +56599,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56628,7 +56625,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56654,7 +56651,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56680,7 +56677,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56706,7 +56703,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56732,7 +56729,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56758,7 +56755,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56784,7 +56781,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56810,7 +56807,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56836,7 +56833,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56862,7 +56859,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56888,7 +56885,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56914,7 +56911,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56940,7 +56937,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56966,7 +56963,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56992,7 +56989,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57018,7 +57015,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57044,7 +57041,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57096,7 +57093,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57122,7 +57119,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57174,7 +57171,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57200,7 +57197,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57226,7 +57223,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57252,7 +57249,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57278,7 +57275,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57304,7 +57301,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57330,7 +57327,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57356,7 +57353,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57382,7 +57379,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57408,7 +57405,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57434,7 +57431,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57460,7 +57457,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57486,7 +57483,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57512,7 +57509,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57538,7 +57535,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57564,7 +57561,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57590,7 +57587,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57616,7 +57613,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57642,7 +57639,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57668,7 +57665,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57694,7 +57691,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57720,7 +57717,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57746,7 +57743,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57772,7 +57769,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57798,7 +57795,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57824,7 +57821,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57850,7 +57847,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57876,7 +57873,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57902,7 +57899,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57928,7 +57925,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57954,7 +57951,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57980,7 +57977,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58006,7 +58003,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58032,7 +58029,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58058,7 +58055,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58084,7 +58081,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58110,7 +58107,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58162,7 +58159,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58188,7 +58185,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58214,7 +58211,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58240,7 +58237,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58266,7 +58263,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58292,7 +58289,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58318,7 +58315,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58344,7 +58341,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58370,7 +58367,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58396,7 +58393,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58422,7 +58419,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58448,7 +58445,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58474,7 +58471,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58500,7 +58497,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58526,7 +58523,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58552,7 +58549,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58578,7 +58575,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58604,7 +58601,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58630,7 +58627,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58656,7 +58653,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58682,7 +58679,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58708,7 +58705,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58734,7 +58731,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58760,7 +58757,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58786,7 +58783,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58812,7 +58809,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58838,7 +58835,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58864,7 +58861,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58890,7 +58887,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58916,7 +58913,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58942,7 +58939,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58968,7 +58965,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58994,7 +58991,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59020,7 +59017,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59046,7 +59043,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59072,7 +59069,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59098,7 +59095,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59124,7 +59121,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59150,7 +59147,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59176,7 +59173,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59202,7 +59199,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59228,7 +59225,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59254,7 +59251,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59280,7 +59277,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59306,7 +59303,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59332,7 +59329,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59358,7 +59355,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59384,7 +59381,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59410,7 +59407,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59436,7 +59433,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59462,7 +59459,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59488,7 +59485,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59514,7 +59511,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59540,7 +59537,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59566,7 +59563,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59592,7 +59589,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59618,7 +59615,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59644,7 +59641,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59670,7 +59667,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59696,7 +59693,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59722,7 +59719,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59748,7 +59745,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59774,7 +59771,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59800,7 +59797,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59826,7 +59823,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59852,7 +59849,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59878,7 +59875,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59904,7 +59901,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59930,7 +59927,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59956,7 +59953,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59982,7 +59979,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60008,7 +60005,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60034,7 +60031,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60060,7 +60057,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60086,7 +60083,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60112,7 +60109,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60138,7 +60135,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60164,7 +60161,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60190,7 +60187,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60216,7 +60213,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60242,7 +60239,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60268,7 +60265,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60294,7 +60291,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60320,7 +60317,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60346,7 +60343,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60372,7 +60369,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60398,7 +60395,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60424,7 +60421,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60450,7 +60447,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60476,7 +60473,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60502,7 +60499,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60528,7 +60525,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60554,7 +60551,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60580,7 +60577,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60606,7 +60603,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60632,7 +60629,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60658,7 +60655,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60684,7 +60681,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60710,7 +60707,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60736,7 +60733,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60762,7 +60759,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60788,7 +60785,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60814,7 +60811,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60840,7 +60837,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60866,7 +60863,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60892,7 +60889,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60918,7 +60915,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60944,7 +60941,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60970,7 +60967,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60996,7 +60993,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61022,7 +61019,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61048,7 +61045,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61074,7 +61071,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61100,7 +61097,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61126,7 +61123,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61152,7 +61149,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61178,7 +61175,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61204,7 +61201,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61230,7 +61227,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61256,7 +61253,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61282,7 +61279,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61308,7 +61305,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61334,7 +61331,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61360,7 +61357,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61386,7 +61383,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61412,7 +61409,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61438,7 +61435,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61464,7 +61461,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61490,7 +61487,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61516,7 +61513,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61542,7 +61539,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61568,7 +61565,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61594,7 +61591,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61620,7 +61617,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61646,7 +61643,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61672,7 +61669,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61698,7 +61695,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61724,7 +61721,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61750,7 +61747,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61776,7 +61773,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61802,7 +61799,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61828,7 +61825,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61854,7 +61851,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61880,7 +61877,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61906,7 +61903,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61932,7 +61929,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61958,7 +61955,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61984,7 +61981,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62010,7 +62007,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62036,7 +62033,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62062,7 +62059,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62088,7 +62085,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62114,7 +62111,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62140,7 +62137,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62166,7 +62163,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62192,7 +62189,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62218,7 +62215,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62244,7 +62241,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62270,7 +62267,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62296,7 +62293,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62322,7 +62319,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62348,7 +62345,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62374,7 +62371,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62400,7 +62397,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62426,7 +62423,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62452,7 +62449,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62478,7 +62475,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62504,7 +62501,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62530,7 +62527,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62556,7 +62553,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62582,7 +62579,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62608,7 +62605,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62634,7 +62631,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62660,7 +62657,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62686,7 +62683,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62712,7 +62709,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62738,7 +62735,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62764,7 +62761,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62790,7 +62787,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62816,7 +62813,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62842,7 +62839,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62868,7 +62865,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62894,7 +62891,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62920,7 +62917,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62946,7 +62943,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62972,7 +62969,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62998,7 +62995,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63024,7 +63021,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63050,7 +63047,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63076,7 +63073,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63102,7 +63099,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63128,7 +63125,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63154,7 +63151,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63180,7 +63177,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63206,7 +63203,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63232,7 +63229,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63258,7 +63255,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63284,7 +63281,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63310,7 +63307,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63336,7 +63333,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63362,7 +63359,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63388,7 +63385,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63414,7 +63411,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63440,7 +63437,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63466,7 +63463,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63492,7 +63489,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63518,7 +63515,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63544,7 +63541,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63570,7 +63567,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63596,7 +63593,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63622,7 +63619,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63648,7 +63645,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63674,7 +63671,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63700,7 +63697,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63726,7 +63723,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63752,7 +63749,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63778,7 +63775,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63804,7 +63801,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63830,7 +63827,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63856,7 +63853,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63882,7 +63879,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63908,7 +63905,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63934,7 +63931,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63960,7 +63957,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63986,7 +63983,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64012,7 +64009,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64038,7 +64035,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64064,7 +64061,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64090,7 +64087,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64116,7 +64113,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64142,7 +64139,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64168,7 +64165,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64194,7 +64191,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64220,7 +64217,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64246,7 +64243,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64272,7 +64269,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64298,7 +64295,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64324,7 +64321,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64350,7 +64347,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64376,7 +64373,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64402,7 +64399,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64428,7 +64425,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64454,7 +64451,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64480,7 +64477,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64506,7 +64503,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64532,7 +64529,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64558,7 +64555,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64584,7 +64581,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64610,7 +64607,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64636,7 +64633,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64662,7 +64659,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64688,7 +64685,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64714,7 +64711,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64740,7 +64737,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64766,7 +64763,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64792,7 +64789,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64818,7 +64815,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64844,7 +64841,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64870,7 +64867,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64896,7 +64893,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64922,7 +64919,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64948,7 +64945,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64974,7 +64971,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65000,7 +64997,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65026,7 +65023,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65052,7 +65049,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65078,7 +65075,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65104,7 +65101,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65130,7 +65127,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65156,7 +65153,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65182,7 +65179,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65208,7 +65205,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65234,7 +65231,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65260,7 +65257,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65286,7 +65283,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65312,7 +65309,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65338,7 +65335,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65364,7 +65361,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65390,7 +65387,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65416,7 +65413,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65442,7 +65439,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65468,7 +65465,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65494,7 +65491,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65520,7 +65517,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65546,7 +65543,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65572,7 +65569,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65598,7 +65595,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65624,7 +65621,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65650,7 +65647,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65676,7 +65673,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65702,7 +65699,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65728,7 +65725,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65754,7 +65751,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65780,7 +65777,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65806,7 +65803,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65832,7 +65829,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65858,7 +65855,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65884,7 +65881,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65910,7 +65907,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65936,7 +65933,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65962,7 +65959,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65988,7 +65985,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66014,7 +66011,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66040,7 +66037,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66066,7 +66063,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66092,7 +66089,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66118,7 +66115,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66144,7 +66141,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66170,7 +66167,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66196,7 +66193,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66222,7 +66219,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66248,7 +66245,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66274,7 +66271,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66300,7 +66297,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66326,7 +66323,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66352,7 +66349,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66378,7 +66375,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66404,7 +66401,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66430,7 +66427,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66456,7 +66453,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66482,7 +66479,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66508,7 +66505,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66534,7 +66531,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66560,7 +66557,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66586,7 +66583,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2489" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66612,7 +66609,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2490" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66638,7 +66635,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2491" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66664,7 +66661,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2492" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66690,7 +66687,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2493" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66716,7 +66713,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2494" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66742,7 +66739,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2495" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66768,7 +66765,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2496" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66794,7 +66791,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2497" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66820,7 +66817,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2498" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66828,7 +66825,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6023611111</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>3624</v>
@@ -66846,9 +66843,35 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2499" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6683101852</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>36131</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>0.555999994277954</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>503</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="509" uniqueCount="509">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="510">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23581551015377</t>
+    <t xml:space="preserve">0.235815465450287</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394716262817</t>
+    <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
     <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899916529655</t>
+    <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581333756447</t>
+    <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21017424762249</t>
+    <t xml:space="preserve">0.210174232721329</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099088191986</t>
+    <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
     <t xml:space="preserve">0.228921487927437</t>
@@ -71,28 +71,28 @@
     <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293399214745</t>
+    <t xml:space="preserve">0.233293369412422</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22841739654541</t>
+    <t xml:space="preserve">0.228417411446571</t>
   </si>
   <si>
     <t xml:space="preserve">0.231527775526047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762226343155</t>
+    <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598259329796</t>
+    <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784891724586</t>
+    <t xml:space="preserve">0.222784876823425</t>
   </si>
   <si>
     <t xml:space="preserve">0.214377820491791</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">0.211014971137047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
     <t xml:space="preserve">0.201767146587372</t>
@@ -113,34 +113,34 @@
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.193612530827522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722894906998</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20235538482666</t>
+    <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
     <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187091112137</t>
+    <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214157700539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912774920464</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762485861778</t>
+    <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
     <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
     <t xml:space="preserve">0.226987615227699</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235439777374</t>
+    <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279691457748</t>
+    <t xml:space="preserve">0.24127970635891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483249425888</t>
+    <t xml:space="preserve">0.245483219623566</t>
   </si>
   <si>
     <t xml:space="preserve">0.252208918333054</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182456493378</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226648569107</t>
+    <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632959842682</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562216520309</t>
+    <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531049251556</t>
+    <t xml:space="preserve">0.317531019449234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827786207199</t>
+    <t xml:space="preserve">0.322827816009521</t>
   </si>
   <si>
     <t xml:space="preserve">0.336279153823853</t>
@@ -206,43 +206,43 @@
     <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313839435577</t>
+    <t xml:space="preserve">0.378313779830933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034849524498</t>
+    <t xml:space="preserve">0.420348465442657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525561571121</t>
+    <t xml:space="preserve">0.440525531768799</t>
   </si>
   <si>
     <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471684217453</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400911092758</t>
+    <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055896282196</t>
+    <t xml:space="preserve">0.501055836677551</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011584997177</t>
+    <t xml:space="preserve">0.496011644601822</t>
   </si>
   <si>
     <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307871580124</t>
+    <t xml:space="preserve">0.492307960987091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670893192291</t>
+    <t xml:space="preserve">0.580670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">0.589086413383484</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">0.65641051530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618540704250336</t>
+    <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748494148254</t>
+    <t xml:space="preserve">0.62274843454361</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
@@ -272,46 +272,46 @@
     <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762192249298</t>
+    <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100200891495</t>
+    <t xml:space="preserve">0.488100111484528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008752822876</t>
+    <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
     <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892410993576</t>
+    <t xml:space="preserve">0.483892351388931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51334673166275</t>
+    <t xml:space="preserve">0.513346791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177712440491</t>
+    <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554521560669</t>
+    <t xml:space="preserve">0.517554402351379</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269100904465</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061340808868</t>
+    <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853610515594</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684680700302</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
@@ -323,16 +323,16 @@
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230360031128</t>
+    <t xml:space="preserve">0.450230330228806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022510528564</t>
+    <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
     <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944969177246</t>
+    <t xml:space="preserve">0.403944939374924</t>
   </si>
   <si>
     <t xml:space="preserve">0.420776009559631</t>
@@ -341,52 +341,52 @@
     <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385561943054</t>
+    <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476890802383</t>
+    <t xml:space="preserve">0.475476861000061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409807443619</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381494760513</t>
+    <t xml:space="preserve">0.380381554365158</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360489368439</t>
+    <t xml:space="preserve">0.412360459566116</t>
   </si>
   <si>
     <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814810037613</t>
+    <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092923402786</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628085136414</t>
+    <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994287252426</t>
+    <t xml:space="preserve">0.408994257450104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311171293259</t>
+    <t xml:space="preserve">0.407311201095581</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163246870041</t>
+    <t xml:space="preserve">0.392163187265396</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261853218079</t>
+    <t xml:space="preserve">0.402261883020401</t>
   </si>
   <si>
     <t xml:space="preserve">0.395529448986053</t>
@@ -407,13 +407,13 @@
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649060726166</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374247074127</t>
+    <t xml:space="preserve">0.311374217271805</t>
   </si>
   <si>
     <t xml:space="preserve">0.336620807647705</t>
@@ -437,19 +437,19 @@
     <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768732070923</t>
+    <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345036327838898</t>
+    <t xml:space="preserve">0.345036298036575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350085645914078</t>
+    <t xml:space="preserve">0.350085616111755</t>
   </si>
   <si>
     <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571489572525</t>
+    <t xml:space="preserve">0.331571459770203</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
@@ -464,31 +464,31 @@
     <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339987009763718</t>
+    <t xml:space="preserve">0.33998703956604</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35850116610527</t>
+    <t xml:space="preserve">0.358501136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599772453308</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36355048418045</t>
+    <t xml:space="preserve">0.363550513982773</t>
   </si>
   <si>
     <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212594747543</t>
+    <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747726678848</t>
+    <t xml:space="preserve">0.383747696876526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797014951706</t>
+    <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
     <t xml:space="preserve">0.378698378801346</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332176685333</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282858610153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371966004371643</t>
+    <t xml:space="preserve">0.371965974569321</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
@@ -518,28 +518,28 @@
     <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632062911987</t>
+    <t xml:space="preserve">0.559632182121277</t>
   </si>
   <si>
     <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783257246017</t>
+    <t xml:space="preserve">0.489783316850662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733909368515</t>
+    <t xml:space="preserve">0.484733939170837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476318359375</t>
+    <t xml:space="preserve">0.476318448781967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494832515716553</t>
+    <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466373205185</t>
+    <t xml:space="preserve">0.491466403007507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198747634888</t>
+    <t xml:space="preserve">0.49819877743721</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
@@ -548,31 +548,31 @@
     <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520079076290131</t>
+    <t xml:space="preserve">0.520079016685486</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811480522156</t>
+    <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910235881805</t>
+    <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128424167633</t>
+    <t xml:space="preserve">0.525128483772278</t>
   </si>
   <si>
     <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506614327430725</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503248035907745</t>
+    <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297324180603</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.501564979553223</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473740100861</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,52 +599,52 @@
     <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374984741211</t>
+    <t xml:space="preserve">0.550374925136566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860828399658</t>
+    <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019789218903</t>
+    <t xml:space="preserve">0.537019729614258</t>
   </si>
   <si>
     <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068099498749</t>
+    <t xml:space="preserve">0.530068159103394</t>
   </si>
   <si>
     <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592254638672</t>
+    <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
     <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709490776062</t>
+    <t xml:space="preserve">0.545709550380707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661120891571</t>
+    <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971478939056</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -674,46 +674,46 @@
     <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261281013489</t>
+    <t xml:space="preserve">0.502261221408844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50399923324585</t>
+    <t xml:space="preserve">0.503999173641205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833627223969</t>
+    <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571639060974</t>
+    <t xml:space="preserve">0.493571668863297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854302406311</t>
+    <t xml:space="preserve">0.524854362010956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52311646938324</t>
+    <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640505313873</t>
+    <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
     <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419807910919</t>
+    <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
     <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585235118866</t>
+    <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
     <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594371497631073</t>
+    <t xml:space="preserve">0.594371557235718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585681915283203</t>
+    <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
     <t xml:space="preserve">0.58915764093399</t>
@@ -722,16 +722,16 @@
     <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102370738983</t>
+    <t xml:space="preserve">0.669102430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288473129272</t>
+    <t xml:space="preserve">0.714288592338562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364537715912</t>
+    <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605910301208</t>
+    <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653461039066315</t>
+    <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644771337509155</t>
+    <t xml:space="preserve">0.6447713971138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629130065441132</t>
+    <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
     <t xml:space="preserve">0.625654220581055</t>
@@ -764,31 +764,31 @@
     <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033504486084</t>
+    <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178375720978</t>
+    <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012888908386</t>
+    <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943963050842</t>
+    <t xml:space="preserve">0.583943843841553</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633605003357</t>
+    <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799091815948</t>
+    <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582206010818481</t>
+    <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505737125873566</t>
+    <t xml:space="preserve">0.50573718547821</t>
   </si>
   <si>
     <t xml:space="preserve">0.557874977588654</t>
@@ -797,34 +797,34 @@
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109449863434</t>
+    <t xml:space="preserve">0.596109390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750841140747</t>
+    <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985253810883</t>
+    <t xml:space="preserve">0.649985194206238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247301578522</t>
+    <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081755161285</t>
+    <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005809783936</t>
+    <t xml:space="preserve">0.683005750179291</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957559108734</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688219547271729</t>
+    <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743762016296</t>
+    <t xml:space="preserve">0.684743702411652</t>
   </si>
   <si>
     <t xml:space="preserve">0.662150740623474</t>
@@ -833,19 +833,19 @@
     <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936883926392</t>
+    <t xml:space="preserve">0.656936824321747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509349346161</t>
+    <t xml:space="preserve">0.646509408950806</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226626396179</t>
+    <t xml:space="preserve">0.615226686000824</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788482666016</t>
+    <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410415172577</t>
+    <t xml:space="preserve">0.636410355567932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632825016975403</t>
+    <t xml:space="preserve">0.632824957370758</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239618778229</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276093482971</t>
+    <t xml:space="preserve">0.620276033878326</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592848300934</t>
+    <t xml:space="preserve">0.591592788696289</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -893,7 +893,7 @@
     <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623861491680145</t>
+    <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
     <t xml:space="preserve">0.616690635681152</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589800119400024</t>
+    <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385517597198</t>
+    <t xml:space="preserve">0.593385457992554</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -929,7 +929,7 @@
     <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324026107788</t>
+    <t xml:space="preserve">0.559324085712433</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873009204865</t>
+    <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -947,7 +947,7 @@
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178186893463</t>
+    <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
     <t xml:space="preserve">0.631032347679138</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738627910614</t>
+    <t xml:space="preserve">0.555738687515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945958614349</t>
+    <t xml:space="preserve">0.553945899009705</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -986,7 +986,7 @@
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203084468842</t>
+    <t xml:space="preserve">0.638203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -995,43 +995,43 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752067565918</t>
+    <t xml:space="preserve">0.650752127170563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.654337525367737</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057245254517</t>
+    <t xml:space="preserve">0.674057185649872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661508321762085</t>
+    <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093719959259</t>
+    <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
     <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645373940467834</t>
+    <t xml:space="preserve">0.645374000072479</t>
   </si>
   <si>
     <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643581211566925</t>
+    <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264516353607</t>
+    <t xml:space="preserve">0.672264456748962</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471847057343</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020710945129</t>
+    <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
     <t xml:space="preserve">0.690191566944122</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71528947353363</t>
+    <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594651222229</t>
+    <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1064,10 +1064,10 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
     <t xml:space="preserve">0.745765447616577</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143574714661</t>
+    <t xml:space="preserve">0.751143515110016</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252939224243</t>
+    <t xml:space="preserve">0.724252998828888</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642643451691</t>
+    <t xml:space="preserve">0.677642583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849974155426</t>
+    <t xml:space="preserve">0.675849914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667541027069</t>
+    <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045668125153</t>
+    <t xml:space="preserve">0.726045727729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1149,6 +1149,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -51191,7 +51194,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51217,7 +51220,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51243,7 +51246,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51373,7 +51376,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51399,7 +51402,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51451,7 +51454,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51477,7 +51480,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51503,7 +51506,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51555,7 +51558,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51581,7 +51584,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51685,7 +51688,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51711,7 +51714,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51763,7 +51766,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51789,7 +51792,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51841,7 +51844,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51919,7 +51922,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51945,7 +51948,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52023,7 +52026,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52049,7 +52052,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52075,7 +52078,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52101,7 +52104,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52127,7 +52130,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52153,7 +52156,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52179,7 +52182,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52257,7 +52260,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52283,7 +52286,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>328</v>
+        <v>379</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52309,7 +52312,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52361,7 +52364,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52387,7 +52390,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52413,7 +52416,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52439,7 +52442,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52517,7 +52520,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52543,7 +52546,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52569,7 +52572,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52595,7 +52598,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52621,7 +52624,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52647,7 +52650,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52673,7 +52676,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52699,7 +52702,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52725,7 +52728,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52751,7 +52754,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52777,7 +52780,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52803,7 +52806,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52829,7 +52832,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52855,7 +52858,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52881,7 +52884,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52907,7 +52910,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52933,7 +52936,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52959,7 +52962,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -52985,7 +52988,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53011,7 +53014,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53037,7 +53040,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53063,7 +53066,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53089,7 +53092,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53115,7 +53118,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53141,7 +53144,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53167,7 +53170,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53193,7 +53196,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53219,7 +53222,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53245,7 +53248,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53271,7 +53274,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53297,7 +53300,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53323,7 +53326,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53349,7 +53352,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53375,7 +53378,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53401,7 +53404,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53427,7 +53430,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53453,7 +53456,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53479,7 +53482,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53505,7 +53508,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53531,7 +53534,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53557,7 +53560,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53583,7 +53586,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53609,7 +53612,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53635,7 +53638,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53661,7 +53664,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53687,7 +53690,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53713,7 +53716,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53739,7 +53742,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53765,7 +53768,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53791,7 +53794,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53817,7 +53820,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53843,7 +53846,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53869,7 +53872,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53895,7 +53898,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53921,7 +53924,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53947,7 +53950,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53973,7 +53976,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -53999,7 +54002,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54025,7 +54028,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54051,7 +54054,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54077,7 +54080,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54103,7 +54106,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54129,7 +54132,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54155,7 +54158,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54181,7 +54184,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54207,7 +54210,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54233,7 +54236,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54259,7 +54262,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54285,7 +54288,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54311,7 +54314,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54337,7 +54340,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54363,7 +54366,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54389,7 +54392,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54415,7 +54418,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54441,7 +54444,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54467,7 +54470,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54493,7 +54496,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54571,7 +54574,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54597,7 +54600,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54623,7 +54626,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54649,7 +54652,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54675,7 +54678,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54701,7 +54704,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54727,7 +54730,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54753,7 +54756,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54779,7 +54782,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54805,7 +54808,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54831,7 +54834,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54857,7 +54860,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54883,7 +54886,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54909,7 +54912,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54935,7 +54938,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54961,7 +54964,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -54987,7 +54990,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55013,7 +55016,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55039,7 +55042,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55065,7 +55068,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55091,7 +55094,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55117,7 +55120,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55143,7 +55146,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55169,7 +55172,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55195,7 +55198,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55221,7 +55224,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55247,7 +55250,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55273,7 +55276,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55299,7 +55302,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55325,7 +55328,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55351,7 +55354,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55377,7 +55380,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55403,7 +55406,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55429,7 +55432,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55455,7 +55458,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55481,7 +55484,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55507,7 +55510,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55533,7 +55536,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55559,7 +55562,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55585,7 +55588,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55611,7 +55614,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55637,7 +55640,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55663,7 +55666,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55689,7 +55692,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55715,7 +55718,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55741,7 +55744,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55767,7 +55770,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55793,7 +55796,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55819,7 +55822,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55845,7 +55848,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55871,7 +55874,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55897,7 +55900,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55923,7 +55926,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55949,7 +55952,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55975,7 +55978,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56001,7 +56004,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56027,7 +56030,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56053,7 +56056,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56079,7 +56082,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56105,7 +56108,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56131,7 +56134,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56157,7 +56160,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56183,7 +56186,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56209,7 +56212,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56235,7 +56238,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56261,7 +56264,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56287,7 +56290,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56313,7 +56316,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56339,7 +56342,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56365,7 +56368,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56391,7 +56394,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56417,7 +56420,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56443,7 +56446,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56469,7 +56472,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56495,7 +56498,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56521,7 +56524,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56547,7 +56550,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56573,7 +56576,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56599,7 +56602,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56625,7 +56628,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56651,7 +56654,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56677,7 +56680,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56703,7 +56706,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56729,7 +56732,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56755,7 +56758,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56781,7 +56784,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56807,7 +56810,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56833,7 +56836,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56859,7 +56862,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56885,7 +56888,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56911,7 +56914,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56937,7 +56940,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56963,7 +56966,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -56989,7 +56992,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57015,7 +57018,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57041,7 +57044,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57093,7 +57096,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57119,7 +57122,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57171,7 +57174,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57197,7 +57200,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57223,7 +57226,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57249,7 +57252,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57275,7 +57278,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57301,7 +57304,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57327,7 +57330,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57353,7 +57356,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57379,7 +57382,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57405,7 +57408,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57431,7 +57434,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57457,7 +57460,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57483,7 +57486,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57509,7 +57512,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57535,7 +57538,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57561,7 +57564,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57587,7 +57590,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57613,7 +57616,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57639,7 +57642,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57665,7 +57668,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57691,7 +57694,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57717,7 +57720,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57743,7 +57746,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57769,7 +57772,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57795,7 +57798,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57821,7 +57824,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57847,7 +57850,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57873,7 +57876,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57899,7 +57902,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57925,7 +57928,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57951,7 +57954,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57977,7 +57980,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58003,7 +58006,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58029,7 +58032,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58055,7 +58058,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58081,7 +58084,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58107,7 +58110,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58159,7 +58162,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58185,7 +58188,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58211,7 +58214,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58237,7 +58240,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58263,7 +58266,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58289,7 +58292,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58315,7 +58318,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58341,7 +58344,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58367,7 +58370,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58393,7 +58396,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58419,7 +58422,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58445,7 +58448,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58471,7 +58474,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58497,7 +58500,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58523,7 +58526,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58549,7 +58552,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58575,7 +58578,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58601,7 +58604,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58627,7 +58630,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58653,7 +58656,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58679,7 +58682,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58705,7 +58708,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58731,7 +58734,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58757,7 +58760,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58783,7 +58786,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58809,7 +58812,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58835,7 +58838,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58861,7 +58864,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58887,7 +58890,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58913,7 +58916,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58939,7 +58942,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58965,7 +58968,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -58991,7 +58994,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59017,7 +59020,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59043,7 +59046,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59069,7 +59072,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59095,7 +59098,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59121,7 +59124,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59147,7 +59150,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59173,7 +59176,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59199,7 +59202,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59225,7 +59228,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59251,7 +59254,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59277,7 +59280,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59303,7 +59306,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59329,7 +59332,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59355,7 +59358,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59381,7 +59384,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59407,7 +59410,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59433,7 +59436,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59459,7 +59462,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59485,7 +59488,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59511,7 +59514,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59537,7 +59540,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59563,7 +59566,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59589,7 +59592,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59615,7 +59618,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59641,7 +59644,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59667,7 +59670,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59693,7 +59696,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59719,7 +59722,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59745,7 +59748,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59771,7 +59774,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59797,7 +59800,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59823,7 +59826,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59849,7 +59852,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59875,7 +59878,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59901,7 +59904,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59927,7 +59930,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59953,7 +59956,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59979,7 +59982,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60005,7 +60008,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60031,7 +60034,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60057,7 +60060,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60083,7 +60086,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60109,7 +60112,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60135,7 +60138,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60161,7 +60164,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60187,7 +60190,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60213,7 +60216,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60239,7 +60242,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60265,7 +60268,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60291,7 +60294,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60317,7 +60320,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60343,7 +60346,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60369,7 +60372,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60395,7 +60398,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60421,7 +60424,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60447,7 +60450,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60473,7 +60476,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60499,7 +60502,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60525,7 +60528,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60551,7 +60554,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60577,7 +60580,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60603,7 +60606,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60629,7 +60632,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60655,7 +60658,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60681,7 +60684,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60707,7 +60710,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60733,7 +60736,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60759,7 +60762,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60785,7 +60788,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60811,7 +60814,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60837,7 +60840,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60863,7 +60866,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60889,7 +60892,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60915,7 +60918,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60941,7 +60944,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60967,7 +60970,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -60993,7 +60996,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61019,7 +61022,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61045,7 +61048,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61071,7 +61074,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61097,7 +61100,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61123,7 +61126,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61149,7 +61152,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61175,7 +61178,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61201,7 +61204,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61227,7 +61230,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61253,7 +61256,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61279,7 +61282,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61305,7 +61308,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61331,7 +61334,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61357,7 +61360,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61383,7 +61386,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61409,7 +61412,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61435,7 +61438,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61461,7 +61464,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61487,7 +61490,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61513,7 +61516,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61539,7 +61542,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61565,7 +61568,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61591,7 +61594,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61617,7 +61620,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61643,7 +61646,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61669,7 +61672,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61695,7 +61698,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61721,7 +61724,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61747,7 +61750,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61773,7 +61776,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61799,7 +61802,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61825,7 +61828,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61851,7 +61854,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61877,7 +61880,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61903,7 +61906,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61929,7 +61932,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61955,7 +61958,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61981,7 +61984,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62007,7 +62010,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62033,7 +62036,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62059,7 +62062,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62085,7 +62088,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62111,7 +62114,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62137,7 +62140,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62163,7 +62166,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62189,7 +62192,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62215,7 +62218,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62241,7 +62244,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62267,7 +62270,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62293,7 +62296,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62319,7 +62322,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62345,7 +62348,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62371,7 +62374,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62397,7 +62400,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62423,7 +62426,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62449,7 +62452,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62475,7 +62478,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62501,7 +62504,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62527,7 +62530,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62553,7 +62556,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62579,7 +62582,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62605,7 +62608,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62631,7 +62634,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62657,7 +62660,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62683,7 +62686,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62709,7 +62712,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62735,7 +62738,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62761,7 +62764,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62787,7 +62790,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62813,7 +62816,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62839,7 +62842,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62865,7 +62868,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62891,7 +62894,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62917,7 +62920,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62943,7 +62946,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62969,7 +62972,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -62995,7 +62998,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63021,7 +63024,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63047,7 +63050,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63073,7 +63076,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63099,7 +63102,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63125,7 +63128,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63151,7 +63154,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63177,7 +63180,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63203,7 +63206,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63229,7 +63232,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63255,7 +63258,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63281,7 +63284,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63307,7 +63310,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63333,7 +63336,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63359,7 +63362,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63385,7 +63388,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63411,7 +63414,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63437,7 +63440,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63463,7 +63466,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63489,7 +63492,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63515,7 +63518,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63541,7 +63544,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63567,7 +63570,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63593,7 +63596,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63619,7 +63622,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63645,7 +63648,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63671,7 +63674,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63697,7 +63700,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63723,7 +63726,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63749,7 +63752,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63775,7 +63778,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63801,7 +63804,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63827,7 +63830,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63853,7 +63856,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63879,7 +63882,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63905,7 +63908,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63931,7 +63934,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63957,7 +63960,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63983,7 +63986,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64009,7 +64012,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64035,7 +64038,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64061,7 +64064,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64087,7 +64090,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64113,7 +64116,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64139,7 +64142,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64165,7 +64168,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64191,7 +64194,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64217,7 +64220,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64243,7 +64246,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64269,7 +64272,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64295,7 +64298,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64321,7 +64324,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64347,7 +64350,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64373,7 +64376,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64399,7 +64402,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64425,7 +64428,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64451,7 +64454,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64477,7 +64480,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64503,7 +64506,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64529,7 +64532,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64555,7 +64558,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64581,7 +64584,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64607,7 +64610,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64633,7 +64636,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64659,7 +64662,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64685,7 +64688,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64711,7 +64714,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64737,7 +64740,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64763,7 +64766,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64789,7 +64792,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64815,7 +64818,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64841,7 +64844,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64867,7 +64870,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64893,7 +64896,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64919,7 +64922,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64945,7 +64948,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64971,7 +64974,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -64997,7 +65000,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65023,7 +65026,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65049,7 +65052,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65075,7 +65078,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65101,7 +65104,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65127,7 +65130,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65153,7 +65156,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65179,7 +65182,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65205,7 +65208,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65231,7 +65234,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65257,7 +65260,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65283,7 +65286,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65309,7 +65312,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65335,7 +65338,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65361,7 +65364,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65387,7 +65390,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65413,7 +65416,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65439,7 +65442,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65465,7 +65468,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65491,7 +65494,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65517,7 +65520,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65543,7 +65546,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65569,7 +65572,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65595,7 +65598,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65621,7 +65624,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65647,7 +65650,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65673,7 +65676,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65699,7 +65702,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65725,7 +65728,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65751,7 +65754,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65777,7 +65780,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65803,7 +65806,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65829,7 +65832,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65855,7 +65858,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65881,7 +65884,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65907,7 +65910,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65933,7 +65936,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65959,7 +65962,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -65985,7 +65988,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66011,7 +66014,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66037,7 +66040,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66063,7 +66066,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66089,7 +66092,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66115,7 +66118,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66141,7 +66144,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66167,7 +66170,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66193,7 +66196,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66219,7 +66222,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66245,7 +66248,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66271,7 +66274,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66297,7 +66300,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66323,7 +66326,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66349,7 +66352,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66375,7 +66378,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66401,7 +66404,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66427,7 +66430,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66453,7 +66456,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66479,7 +66482,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66505,7 +66508,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66531,7 +66534,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66557,7 +66560,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66583,7 +66586,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2489" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66609,7 +66612,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2490" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66635,7 +66638,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2491" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66661,7 +66664,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2492" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66687,7 +66690,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2493" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66713,7 +66716,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2494" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66739,7 +66742,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2495" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66765,7 +66768,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2496" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66791,7 +66794,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2497" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66817,7 +66820,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2498" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66843,7 +66846,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2499" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66851,7 +66854,7 @@
     </row>
     <row r="2500">
       <c r="A2500" s="1" t="n">
-        <v>45959.6683101852</v>
+        <v>45959.3333333333</v>
       </c>
       <c r="B2500" t="n">
         <v>36131</v>
@@ -66869,9 +66872,35 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2500" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="H2500" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2501">
+      <c r="A2501" s="1" t="n">
+        <v>45960.63875</v>
+      </c>
+      <c r="B2501" t="n">
+        <v>20300</v>
+      </c>
+      <c r="C2501" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2501" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2501" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2501" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2501" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2501" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -44,34 +44,34 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394701361656</t>
+    <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249117732048</t>
+    <t xml:space="preserve">0.228249102830887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899931430817</t>
+    <t xml:space="preserve">0.216899946331978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581333756447</t>
+    <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21017424762249</t>
+    <t xml:space="preserve">0.210174232721329</t>
   </si>
   <si>
     <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921487927437</t>
+    <t xml:space="preserve">0.228921502828598</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293384313583</t>
+    <t xml:space="preserve">0.233293354511261</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310569405556</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360045552254</t>
+    <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722894906998</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202355399727821</t>
+    <t xml:space="preserve">0.202355369925499</t>
   </si>
   <si>
     <t xml:space="preserve">0.202607855200768</t>
@@ -128,10 +128,10 @@
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214157700539</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912745118141</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">0.215218514204025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22698763012886</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031881809235</t>
+    <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235424876213</t>
+    <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
     <t xml:space="preserve">0.24127970635891</t>
@@ -158,25 +158,25 @@
     <t xml:space="preserve">0.245483219623566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208918333054</t>
+    <t xml:space="preserve">0.252208888530731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093863725662</t>
+    <t xml:space="preserve">0.258093893527985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138145208359</t>
+    <t xml:space="preserve">0.263138204813004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182396888733</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226648569107</t>
+    <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057806015015</t>
+    <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827816009521</t>
+    <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
     <t xml:space="preserve">0.336279153823853</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36318102478981</t>
+    <t xml:space="preserve">0.363180994987488</t>
   </si>
   <si>
     <t xml:space="preserve">0.378313809633255</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">0.411941379308701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42034849524498</t>
+    <t xml:space="preserve">0.420348465442657</t>
   </si>
   <si>
     <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684808254242</t>
+    <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
     <t xml:space="preserve">0.472471743822098</t>
@@ -227,7 +227,7 @@
     <t xml:space="preserve">0.483400881290436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055836677551</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">0.496011644601822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49651563167572</t>
+    <t xml:space="preserve">0.496515691280365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307901382446</t>
+    <t xml:space="preserve">0.492307960987091</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589086413383484</t>
+    <t xml:space="preserve">0.589086472988129</t>
   </si>
   <si>
     <t xml:space="preserve">0.63957953453064</t>
@@ -257,7 +257,7 @@
     <t xml:space="preserve">0.673241674900055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641051530838</t>
+    <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
     <t xml:space="preserve">0.61854076385498</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762251853943</t>
+    <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">0.488100171089172</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892381191254</t>
+    <t xml:space="preserve">0.483892440795898</t>
   </si>
   <si>
     <t xml:space="preserve">0.51334673166275</t>
@@ -302,13 +302,13 @@
     <t xml:space="preserve">0.471269100904465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061430215836</t>
+    <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853580713272</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
     <t xml:space="preserve">0.479684621095657</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607079744339</t>
+    <t xml:space="preserve">0.437607020139694</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
@@ -335,13 +335,13 @@
     <t xml:space="preserve">0.403944969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776009559631</t>
+    <t xml:space="preserve">0.420776039361954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191529750824</t>
+    <t xml:space="preserve">0.429191499948502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385502338409</t>
+    <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
@@ -368,28 +368,28 @@
     <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726661682129</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814750432968</t>
+    <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092923402786</t>
+    <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
     <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994257450104</t>
+    <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163217067719</t>
+    <t xml:space="preserve">0.392163187265396</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895680904388</t>
+    <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
     <t xml:space="preserve">0.400578767061234</t>
@@ -398,16 +398,16 @@
     <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261853218079</t>
+    <t xml:space="preserve">0.402261883020401</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529478788376</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649060726166</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
     <t xml:space="preserve">0.323155999183655</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">0.336620837450027</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32988840341568</t>
+    <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32820525765419</t>
+    <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522171497345</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184252262115</t>
+    <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345036327838898</t>
+    <t xml:space="preserve">0.345036298036575</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350085645914078</t>
+    <t xml:space="preserve">0.350085616111755</t>
   </si>
   <si>
     <t xml:space="preserve">0.338303923606873</t>
@@ -467,16 +467,16 @@
     <t xml:space="preserve">0.33998703956604</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916656494141</t>
+    <t xml:space="preserve">0.366916686296463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358501195907593</t>
+    <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
     <t xml:space="preserve">0.368599772453308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550513982773</t>
+    <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
     <t xml:space="preserve">0.390480130910873</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698378801346</t>
+    <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
@@ -500,10 +500,10 @@
     <t xml:space="preserve">0.375332236289978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282858610153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015352249146</t>
+    <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
     <t xml:space="preserve">0.371965974569321</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216602325439</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783316850662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733879566193</t>
+    <t xml:space="preserve">0.484733939170837</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">0.498198837041855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741276264191</t>
+    <t xml:space="preserve">0.553741157054901</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494715690613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.520079076290131</t>
+    <t xml:space="preserve">0.520079135894775</t>
   </si>
   <si>
     <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910176277161</t>
+    <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128424167633</t>
@@ -572,25 +572,25 @@
     <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297383785248</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501564979553223</t>
+    <t xml:space="preserve">0.501564919948578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.493149429559708</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029907226562</t>
+    <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,19 +599,19 @@
     <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374925136566</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396079540253</t>
+    <t xml:space="preserve">0.518396139144897</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671290397644</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019789218903</t>
+    <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
     <t xml:space="preserve">0.53180605173111</t>
@@ -638,7 +638,7 @@
     <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399192333221</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.54223358631134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538757801055908</t>
+    <t xml:space="preserve">0.538757741451263</t>
   </si>
   <si>
     <t xml:space="preserve">0.540495693683624</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512688815593719</t>
+    <t xml:space="preserve">0.512688875198364</t>
   </si>
   <si>
     <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
     <t xml:space="preserve">0.503999173641205</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571609258652</t>
+    <t xml:space="preserve">0.493571668863297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854302406311</t>
+    <t xml:space="preserve">0.524854362010956</t>
   </si>
   <si>
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640564918518</t>
+    <t xml:space="preserve">0.519640505313873</t>
   </si>
   <si>
     <t xml:space="preserve">0.608274936676025</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102430343628</t>
+    <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288592338562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364478111267</t>
+    <t xml:space="preserve">0.667364537715912</t>
   </si>
   <si>
     <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61696445941925</t>
+    <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
     <t xml:space="preserve">0.627392113208771</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605850696564</t>
+    <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
     <t xml:space="preserve">0.653461039066315</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
     <t xml:space="preserve">0.620440363883972</t>
@@ -767,7 +767,7 @@
     <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178316116333</t>
+    <t xml:space="preserve">0.622178375720978</t>
   </si>
   <si>
     <t xml:space="preserve">0.610012829303741</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">0.604798972606659</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778416633606</t>
+    <t xml:space="preserve">0.571778357028961</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
@@ -797,16 +797,16 @@
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109330654144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750781536102</t>
+    <t xml:space="preserve">0.611750721931458</t>
   </si>
   <si>
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985134601593</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247241973877</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936824321747</t>
+    <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
     <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509408950806</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606537044048309</t>
+    <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226686000824</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613488674163818</t>
+    <t xml:space="preserve">0.613488733768463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617745876312</t>
+    <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64178854227066</t>
+    <t xml:space="preserve">0.641788601875305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410355567932</t>
+    <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632824957370758</t>
+    <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
     <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690635681152</t>
+    <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043924808502</t>
+    <t xml:space="preserve">0.579043865203857</t>
   </si>
   <si>
     <t xml:space="preserve">0.559324085712433</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586214661598206</t>
+    <t xml:space="preserve">0.58621472120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945899009705</t>
+    <t xml:space="preserve">0.553945958614349</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752127170563</t>
+    <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.654337525367737</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645374000072479</t>
+    <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544796466827</t>
   </si>
   <si>
     <t xml:space="preserve">0.64358127117157</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264456748962</t>
+    <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191507339478</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765388011932</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143515110016</t>
+    <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398838043213</t>
+    <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642583847046</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
     <t xml:space="preserve">0.675849914550781</t>
@@ -66987,25 +66987,25 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45966.6754398148</v>
+        <v>45967.6856134259</v>
       </c>
       <c r="B2505" t="n">
-        <v>649048</v>
+        <v>21760</v>
       </c>
       <c r="C2505" t="n">
-        <v>0.561999976634979</v>
+        <v>0.568000018596649</v>
       </c>
       <c r="D2505" t="n">
-        <v>0.560000002384186</v>
+        <v>0.558000028133392</v>
       </c>
       <c r="E2505" t="n">
         <v>0.560000002384186</v>
       </c>
       <c r="F2505" t="n">
-        <v>0.561999976634979</v>
+        <v>0.568000018596649</v>
       </c>
       <c r="G2505" t="s">
-        <v>510</v>
+        <v>506</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815465450287</t>
+    <t xml:space="preserve">0.235815495252609</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.23539474606514</t>
+    <t xml:space="preserve">0.235394731163979</t>
   </si>
   <si>
     <t xml:space="preserve">0.228249117732048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899931430817</t>
+    <t xml:space="preserve">0.216899946331978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581363558769</t>
+    <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210174232721329</t>
+    <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099103093147</t>
+    <t xml:space="preserve">0.211099117994308</t>
   </si>
   <si>
     <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921502828598</t>
+    <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293354511261</t>
+    <t xml:space="preserve">0.233293384313583</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231527790427208</t>
+    <t xml:space="preserve">0.231527805328369</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762196540833</t>
+    <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598229527473</t>
+    <t xml:space="preserve">0.239598244428635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868204116821</t>
+    <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
     <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214377820491791</t>
+    <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
     <t xml:space="preserve">0.211014956235886</t>
@@ -104,64 +104,64 @@
     <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767131686211</t>
+    <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563573718071</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202355399727821</t>
+    <t xml:space="preserve">0.202355369925499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607870101929</t>
+    <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187091112137</t>
+    <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912774920464</t>
+    <t xml:space="preserve">0.208912745118141</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218499302864</t>
+    <t xml:space="preserve">0.215218514204025</t>
   </si>
   <si>
     <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987615227699</t>
+    <t xml:space="preserve">0.22698763012886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031881809235</t>
+    <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235469579697</t>
+    <t xml:space="preserve">0.236235454678535</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279691457748</t>
+    <t xml:space="preserve">0.24127970635891</t>
   </si>
   <si>
     <t xml:space="preserve">0.245483249425888</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208918333054</t>
+    <t xml:space="preserve">0.252208888530731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093893527985</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">0.268182396888733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226708173752</t>
+    <t xml:space="preserve">0.273226648569107</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281632989645004</t>
+    <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447161912918</t>
+    <t xml:space="preserve">0.298447132110596</t>
   </si>
   <si>
     <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057806015015</t>
+    <t xml:space="preserve">0.311057835817337</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33627912402153</t>
+    <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455355882645</t>
+    <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36318102478981</t>
+    <t xml:space="preserve">0.363180994987488</t>
   </si>
   <si>
     <t xml:space="preserve">0.378313809633255</t>
@@ -212,70 +212,70 @@
     <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420348465442657</t>
+    <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
     <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684867858887</t>
+    <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400970697403</t>
+    <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055955886841</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
-    <t xml:space="preserve">0.500215172767639</t>
+    <t xml:space="preserve">0.500215113162994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4960116147995</t>
+    <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515661478043</t>
+    <t xml:space="preserve">0.496515691280365</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307931184769</t>
+    <t xml:space="preserve">0.492307960987091</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589086413383484</t>
+    <t xml:space="preserve">0.589086472988129</t>
   </si>
   <si>
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319216251373</t>
+    <t xml:space="preserve">0.715319156646729</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241674900055</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641063451767</t>
+    <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
     <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274843454361</t>
+    <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255373001099</t>
+    <t xml:space="preserve">0.572255432605743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525969982147217</t>
+    <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762251853943</t>
+    <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100200891495</t>
+    <t xml:space="preserve">0.488100171089172</t>
   </si>
   <si>
     <t xml:space="preserve">0.504931211471558</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">0.483892440795898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346672058105</t>
+    <t xml:space="preserve">0.51334673166275</t>
   </si>
   <si>
     <t xml:space="preserve">0.530177772045135</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269160509109</t>
+    <t xml:space="preserve">0.471269100904465</t>
   </si>
   <si>
     <t xml:space="preserve">0.467061370611191</t>
@@ -308,13 +308,13 @@
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853640317917</t>
+    <t xml:space="preserve">0.462853580713272</t>
   </si>
   <si>
     <t xml:space="preserve">0.479684621095657</t>
   </si>
   <si>
-    <t xml:space="preserve">0.433399260044098</t>
+    <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
     <t xml:space="preserve">0.437607020139694</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944909572601</t>
+    <t xml:space="preserve">0.403944969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776039361954</t>
+    <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
     <t xml:space="preserve">0.429191499948502</t>
@@ -347,10 +347,10 @@
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476831197739</t>
+    <t xml:space="preserve">0.475476861000061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
@@ -377,16 +377,16 @@
     <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.405628085136414</t>
+    <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994287252426</t>
+    <t xml:space="preserve">0.408994257450104</t>
   </si>
   <si>
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163246870041</t>
+    <t xml:space="preserve">0.392163217067719</t>
   </si>
   <si>
     <t xml:space="preserve">0.398895651102066</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529478788376</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
@@ -413,16 +413,16 @@
     <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374217271805</t>
+    <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620837450027</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
     <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328205317258835</t>
+    <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522171497345</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35345184803009</t>
+    <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184282064438</t>
+    <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.3517687022686</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036298036575</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303923606873</t>
+    <t xml:space="preserve">0.338303953409195</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
@@ -455,7 +455,7 @@
     <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333254605531693</t>
+    <t xml:space="preserve">0.33325457572937</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339987009763718</t>
+    <t xml:space="preserve">0.33998703956604</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35850116610527</t>
+    <t xml:space="preserve">0.358501195907593</t>
   </si>
   <si>
     <t xml:space="preserve">0.368599772453308</t>
@@ -479,25 +479,25 @@
     <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480130910873</t>
+    <t xml:space="preserve">0.390480101108551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212535142899</t>
+    <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747696876526</t>
+    <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
     <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698408603668</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332176685333</t>
+    <t xml:space="preserve">0.375332236289978</t>
   </si>
   <si>
     <t xml:space="preserve">0.370282888412476</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">0.377015322446823</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371966004371643</t>
+    <t xml:space="preserve">0.371965974569321</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
@@ -515,37 +515,37 @@
     <t xml:space="preserve">0.365233570337296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593292236328</t>
+    <t xml:space="preserve">0.538593232631683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632062911987</t>
+    <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
     <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783227443695</t>
+    <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733909368515</t>
+    <t xml:space="preserve">0.484733879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49483260512352</t>
+    <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
     <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49819877743721</t>
+    <t xml:space="preserve">0.498198837041855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741157054901</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494715690613</t>
+    <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079135894775</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128424167633</t>
+    <t xml:space="preserve">0.525128483772278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52344536781311</t>
+    <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661426782608</t>
+    <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663556098938</t>
+    <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503248035907745</t>
+    <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297383785248</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501564979553223</t>
+    <t xml:space="preserve">0.501564919948578</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49314945936203</t>
+    <t xml:space="preserve">0.493149489164352</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
@@ -590,16 +590,16 @@
     <t xml:space="preserve">0.533543944358826</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107448577881</t>
+    <t xml:space="preserve">0.557107388973236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550375044345856</t>
+    <t xml:space="preserve">0.550374984741211</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
@@ -608,49 +608,49 @@
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671302318573</t>
+    <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068099498749</t>
+    <t xml:space="preserve">0.530068159103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281956195831</t>
+    <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592254638672</t>
+    <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
     <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709490776062</t>
+    <t xml:space="preserve">0.545709550380707</t>
   </si>
   <si>
     <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185395240784</t>
+    <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
     <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399132728577</t>
+    <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971598148346</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542233645915985</t>
+    <t xml:space="preserve">0.54223358631134</t>
   </si>
   <si>
     <t xml:space="preserve">0.538757741451263</t>
@@ -662,25 +662,25 @@
     <t xml:space="preserve">0.568302571773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55961287021637</t>
+    <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5509232878685</t>
+    <t xml:space="preserve">0.550923228263855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378457546234</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512688815593719</t>
+    <t xml:space="preserve">0.512688875198364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51442676782608</t>
+    <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
     <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50399923324585</t>
+    <t xml:space="preserve">0.503999173641205</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833746433258</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640564918518</t>
+    <t xml:space="preserve">0.519640505313873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274877071381</t>
+    <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323246955872</t>
+    <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
     <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895593166351</t>
+    <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589157700538635</t>
+    <t xml:space="preserve">0.58915764093399</t>
   </si>
   <si>
     <t xml:space="preserve">0.639557600021362</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288532733917</t>
+    <t xml:space="preserve">0.714288592338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.667364537715912</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618702530860901</t>
+    <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
     <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65346097946167</t>
+    <t xml:space="preserve">0.653461039066315</t>
   </si>
   <si>
     <t xml:space="preserve">0.6447713971138</t>
@@ -758,31 +758,31 @@
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440423488617</t>
+    <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
     <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033504486084</t>
+    <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
     <t xml:space="preserve">0.622178375720978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012888908386</t>
+    <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943843841553</t>
+    <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
     <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604798972606659</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778357028961</t>
@@ -791,7 +791,7 @@
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505737125873566</t>
+    <t xml:space="preserve">0.50573718547821</t>
   </si>
   <si>
     <t xml:space="preserve">0.557874977588654</t>
@@ -800,25 +800,25 @@
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109330654144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750781536102</t>
+    <t xml:space="preserve">0.611750721931458</t>
   </si>
   <si>
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985134601593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247182369232</t>
+    <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081695556641</t>
+    <t xml:space="preserve">0.636081755161285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.68300586938858</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957499504089</t>
@@ -827,28 +827,28 @@
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743702411652</t>
+    <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
     <t xml:space="preserve">0.662150740623474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316227436066</t>
+    <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936943531036</t>
+    <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509289741516</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226566791534</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488733768463</t>
@@ -857,7 +857,7 @@
     <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64178854227066</t>
+    <t xml:space="preserve">0.641788601875305</t>
   </si>
   <si>
     <t xml:space="preserve">0.636410415172577</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276093482971</t>
+    <t xml:space="preserve">0.620276033878326</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
@@ -914,7 +914,7 @@
     <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577251076698303</t>
+    <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
     <t xml:space="preserve">0.593385457992554</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">0.580836534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582629203796387</t>
+    <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
     <t xml:space="preserve">0.579043865203857</t>
@@ -944,19 +944,19 @@
     <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586214661598206</t>
+    <t xml:space="preserve">0.58621472120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178186893463</t>
+    <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613105297088623</t>
+    <t xml:space="preserve">0.613105237483978</t>
   </si>
   <si>
     <t xml:space="preserve">0.611312508583069</t>
@@ -965,13 +965,13 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.546775102615356</t>
+    <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
     <t xml:space="preserve">0.553945958614349</t>
@@ -1013,7 +1013,7 @@
     <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
     <t xml:space="preserve">0.665093660354614</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544796466827</t>
   </si>
   <si>
     <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
     <t xml:space="preserve">0.672264516353607</t>
@@ -1040,13 +1040,13 @@
     <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684813499450684</t>
+    <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191507339478</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1058,22 +1058,22 @@
     <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711704015731812</t>
+    <t xml:space="preserve">0.711704075336456</t>
   </si>
   <si>
-    <t xml:space="preserve">0.727838337421417</t>
+    <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
     <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765388011932</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742180109024048</t>
+    <t xml:space="preserve">0.742180049419403</t>
   </si>
   <si>
     <t xml:space="preserve">0.708118677139282</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">0.700947821140289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706325888633728</t>
+    <t xml:space="preserve">0.706325948238373</t>
   </si>
   <si>
     <t xml:space="preserve">0.697362422943115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717082142829895</t>
+    <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
     <t xml:space="preserve">0.724252998828888</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642703056335</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
     <t xml:space="preserve">0.675849914550781</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045668125153</t>
+    <t xml:space="preserve">0.726045727729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1136,22 +1136,22 @@
     <t xml:space="preserve">0.691984295845032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695569753646851</t>
+    <t xml:space="preserve">0.695569694042206</t>
   </si>
   <si>
     <t xml:space="preserve">0.665459334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659898459911346</t>
+    <t xml:space="preserve">0.659898400306702</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650630176067352</t>
+    <t xml:space="preserve">0.650630235671997</t>
   </si>
   <si>
     <t xml:space="preserve">0.658044755458832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652483820915222</t>
+    <t xml:space="preserve">0.652483880519867</t>
   </si>
   <si>
     <t xml:space="preserve">0.654337465763092</t>
@@ -1160,10 +1160,10 @@
     <t xml:space="preserve">0.661752045154572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.663605749607086</t>
+    <t xml:space="preserve">0.663605690002441</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646922886371613</t>
+    <t xml:space="preserve">0.646922945976257</t>
   </si>
   <si>
     <t xml:space="preserve">0.645069241523743</t>
@@ -1184,7 +1184,7 @@
     <t xml:space="preserve">0.643215596675873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635800957679749</t>
+    <t xml:space="preserve">0.635801017284393</t>
   </si>
   <si>
     <t xml:space="preserve">0.633947372436523</t>
@@ -1199,7 +1199,7 @@
     <t xml:space="preserve">0.62097179889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626532793045044</t>
+    <t xml:space="preserve">0.626532733440399</t>
   </si>
   <si>
     <t xml:space="preserve">0.613557279109955</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">0.572776973247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583898901939392</t>
+    <t xml:space="preserve">0.583898842334747</t>
   </si>
   <si>
     <t xml:space="preserve">0.578337907791138</t>
@@ -1223,16 +1223,16 @@
     <t xml:space="preserve">0.602435350418091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604288995265961</t>
+    <t xml:space="preserve">0.604289054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593167066574097</t>
+    <t xml:space="preserve">0.593167126178741</t>
   </si>
   <si>
     <t xml:space="preserve">0.600581705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595020830631256</t>
+    <t xml:space="preserve">0.595020771026611</t>
   </si>
   <si>
     <t xml:space="preserve">0.589459776878357</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">0.557947814464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54126501083374</t>
+    <t xml:space="preserve">0.541264951229095</t>
   </si>
   <si>
     <t xml:space="preserve">0.546825885772705</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">0.563508749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570923328399658</t>
+    <t xml:space="preserve">0.570923388004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.617264568805695</t>
+    <t xml:space="preserve">0.61726450920105</t>
   </si>
   <si>
     <t xml:space="preserve">0.624679148197174</t>
@@ -1548,6 +1548,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.561999976634979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.554000020027161</t>
   </si>
 </sst>
 </file>
@@ -66990,27 +66993,105 @@
     </row>
     <row r="2505">
       <c r="A2505" s="1" t="n">
-        <v>45968.6343402778</v>
+        <v>45966.3333333333</v>
       </c>
       <c r="B2505" t="n">
+        <v>649048</v>
+      </c>
+      <c r="C2505" t="n">
+        <v>0.561999976634979</v>
+      </c>
+      <c r="D2505" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2505" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2505" t="n">
+        <v>0.561999976634979</v>
+      </c>
+      <c r="G2505" t="s">
+        <v>511</v>
+      </c>
+      <c r="H2505" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2506">
+      <c r="A2506" s="1" t="n">
+        <v>45967.3333333333</v>
+      </c>
+      <c r="B2506" t="n">
+        <v>21760</v>
+      </c>
+      <c r="C2506" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="D2506" t="n">
+        <v>0.558000028133392</v>
+      </c>
+      <c r="E2506" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2506" t="n">
+        <v>0.568000018596649</v>
+      </c>
+      <c r="G2506" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2506" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2507">
+      <c r="A2507" s="1" t="n">
+        <v>45968.3333333333</v>
+      </c>
+      <c r="B2507" t="n">
         <v>54752</v>
       </c>
-      <c r="C2505" t="n">
+      <c r="C2507" t="n">
         <v>0.565999984741211</v>
       </c>
-      <c r="D2505" t="n">
+      <c r="D2507" t="n">
         <v>0.554000020027161</v>
       </c>
-      <c r="E2505" t="n">
+      <c r="E2507" t="n">
         <v>0.565999984741211</v>
       </c>
-      <c r="F2505" t="n">
+      <c r="F2507" t="n">
         <v>0.560000002384186</v>
       </c>
-      <c r="G2505" t="s">
+      <c r="G2507" t="s">
         <v>509</v>
       </c>
-      <c r="H2505" t="s">
+      <c r="H2507" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2508">
+      <c r="A2508" s="1" t="n">
+        <v>45971.6804861111</v>
+      </c>
+      <c r="B2508" t="n">
+        <v>15803</v>
+      </c>
+      <c r="C2508" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2508" t="n">
+        <v>0.547999978065491</v>
+      </c>
+      <c r="E2508" t="n">
+        <v>0.547999978065491</v>
+      </c>
+      <c r="F2508" t="n">
+        <v>0.554000020027161</v>
+      </c>
+      <c r="G2508" t="s">
+        <v>512</v>
+      </c>
+      <c r="H2508" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394701361656</t>
+    <t xml:space="preserve">0.235394716262817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249087929726</t>
+    <t xml:space="preserve">0.228249102830887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899931430817</t>
+    <t xml:space="preserve">0.216899916529655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581318855286</t>
+    <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">0.211099088191986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
     <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071776986122</t>
+    <t xml:space="preserve">0.227071791887283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293399214745</t>
+    <t xml:space="preserve">0.233293369412422</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
@@ -80,43 +80,43 @@
     <t xml:space="preserve">0.231527775526047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762226343155</t>
+    <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598274230957</t>
+    <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784906625748</t>
+    <t xml:space="preserve">0.222784876823425</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21437780559063</t>
+    <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014956235886</t>
+    <t xml:space="preserve">0.211014971137047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767161488533</t>
+    <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563573718071</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722880005836</t>
+    <t xml:space="preserve">0.196722894906998</t>
   </si>
   <si>
     <t xml:space="preserve">0.202355399727821</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187091112137</t>
+    <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2052141726017</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912774920464</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762485861778</t>
+    <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
     <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22698763012886</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
     <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235395073891</t>
+    <t xml:space="preserve">0.236235439777374</t>
   </si>
   <si>
     <t xml:space="preserve">0.241279691457748</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093863725662</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226648569107</t>
+    <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836547613144</t>
+    <t xml:space="preserve">0.285836458206177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562186717987</t>
+    <t xml:space="preserve">0.292562216520309</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332107305527</t>
+    <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057806015015</t>
+    <t xml:space="preserve">0.311057776212692</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455355882645</t>
+    <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
     <t xml:space="preserve">0.36318102478981</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471743822098</t>
+    <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400881290436</t>
+    <t xml:space="preserve">0.483400911092758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055836677551</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.4960116147995</t>
+    <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515661478043</t>
+    <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307841777802</t>
+    <t xml:space="preserve">0.492307871580124</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -263,43 +263,43 @@
     <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748553752899</t>
+    <t xml:space="preserve">0.62274843454361</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525970041751862</t>
+    <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100200891495</t>
+    <t xml:space="preserve">0.48810014128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892410993576</t>
+    <t xml:space="preserve">0.483892351388931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346672058105</t>
+    <t xml:space="preserve">0.513346791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177772045135</t>
+    <t xml:space="preserve">0.530177712440491</t>
   </si>
   <si>
     <t xml:space="preserve">0.517554521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269071102142</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
     <t xml:space="preserve">0.467061370611191</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853640317917</t>
+    <t xml:space="preserve">0.462853610515594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684710502625</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607079744339</t>
+    <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45023038983345</t>
+    <t xml:space="preserve">0.450230330228806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022510528564</t>
+    <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
     <t xml:space="preserve">0.458645880222321</t>
@@ -341,37 +341,37 @@
     <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385561943054</t>
+    <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677373409271</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.42498379945755</t>
+    <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409807443619</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381494760513</t>
+    <t xml:space="preserve">0.380381524562836</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360489368439</t>
+    <t xml:space="preserve">0.412360459566116</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814810037613</t>
+    <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092893600464</t>
@@ -380,40 +380,40 @@
     <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994257450104</t>
+    <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311171293259</t>
+    <t xml:space="preserve">0.407311201095581</t>
   </si>
   <si>
     <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895651102066</t>
+    <t xml:space="preserve">0.398895621299744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578767061234</t>
+    <t xml:space="preserve">0.400578737258911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846333026886</t>
+    <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529419183731</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649060726166</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31137427687645</t>
+    <t xml:space="preserve">0.311374217271805</t>
   </si>
   <si>
     <t xml:space="preserve">0.336620837450027</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">0.35345184803009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184252262115</t>
+    <t xml:space="preserve">0.360184282064438</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768732070923</t>
+    <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34503635764122</t>
+    <t xml:space="preserve">0.345036298036575</t>
   </si>
   <si>
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303923606873</t>
+    <t xml:space="preserve">0.33830389380455</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334937691688538</t>
+    <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
     <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916686296463</t>
+    <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599772453308</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698438405991</t>
+    <t xml:space="preserve">0.378698348999023</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332206487656</t>
+    <t xml:space="preserve">0.375332176685333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
     <t xml:space="preserve">0.377015292644501</t>
@@ -515,58 +515,58 @@
     <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593232631683</t>
+    <t xml:space="preserve">0.538593351840973</t>
   </si>
   <si>
     <t xml:space="preserve">0.559632062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216542720795</t>
+    <t xml:space="preserve">0.551216602325439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783257246017</t>
+    <t xml:space="preserve">0.489783316850662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733939170837</t>
+    <t xml:space="preserve">0.48473396897316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476318359375</t>
+    <t xml:space="preserve">0.47631847858429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494832545518875</t>
+    <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466403007507</t>
+    <t xml:space="preserve">0.491466373205185</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49819877743721</t>
+    <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494715690613</t>
+    <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811540126801</t>
+    <t xml:space="preserve">0.526811480522156</t>
   </si>
   <si>
     <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128483772278</t>
+    <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52344536781311</t>
+    <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661438703537</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663556098938</t>
+    <t xml:space="preserve">0.511663675308228</t>
   </si>
   <si>
     <t xml:space="preserve">0.50324809551239</t>
@@ -575,76 +575,79 @@
     <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501565039157867</t>
+    <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149518966675</t>
+    <t xml:space="preserve">0.493149489164352</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029847621918</t>
+    <t xml:space="preserve">0.515029907226562</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107448577881</t>
+    <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550375044345856</t>
+    <t xml:space="preserve">0.550374984741211</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396019935608</t>
+    <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671302318573</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53180605173111</t>
+    <t xml:space="preserve">0.531806111335754</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068099498749</t>
+    <t xml:space="preserve">0.533544063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281896591187</t>
+    <t xml:space="preserve">0.530068159103394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.535281956195831</t>
   </si>
   <si>
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330147266388</t>
+    <t xml:space="preserve">0.528330206871033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709550380707</t>
+    <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661180496216</t>
+    <t xml:space="preserve">0.552661120891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185335636139</t>
+    <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447443008423</t>
+    <t xml:space="preserve">0.547447383403778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399192333221</t>
+    <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971478939056</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -665,31 +668,31 @@
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378517150879</t>
+    <t xml:space="preserve">0.521378576755524</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51442676782608</t>
+    <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261281013489</t>
+    <t xml:space="preserve">0.502261221408844</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50399923324585</t>
+    <t xml:space="preserve">0.503999173641205</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833627223969</t>
+    <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571668863297</t>
+    <t xml:space="preserve">0.493571698665619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854302406311</t>
+    <t xml:space="preserve">0.524854362010956</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52311646938324</t>
+    <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
     <t xml:space="preserve">0.519640564918518</t>
@@ -722,34 +725,34 @@
     <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102430343628</t>
+    <t xml:space="preserve">0.669102311134338</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364537715912</t>
+    <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061079978943</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392113208771</t>
+    <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605850696564</t>
+    <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
     <t xml:space="preserve">0.653461039066315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644771337509155</t>
+    <t xml:space="preserve">0.6447713971138</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
@@ -758,28 +761,28 @@
     <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440423488617</t>
+    <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
     <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033504486084</t>
+    <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
     <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012829303741</t>
+    <t xml:space="preserve">0.610012888908386</t>
   </si>
   <si>
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633605003357</t>
+    <t xml:space="preserve">0.592633485794067</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -788,34 +791,34 @@
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.505737125873566</t>
+    <t xml:space="preserve">0.50573718547821</t>
   </si>
   <si>
     <t xml:space="preserve">0.557874977588654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516428470612</t>
+    <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109449863434</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750781536102</t>
+    <t xml:space="preserve">0.611750841140747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343862533569</t>
+    <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985253810883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247301578522</t>
+    <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081695556641</t>
+    <t xml:space="preserve">0.636081755161285</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005750179291</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957559108734</t>
@@ -824,28 +827,28 @@
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743702411652</t>
+    <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150800228119</t>
+    <t xml:space="preserve">0.662150621414185</t>
   </si>
   <si>
     <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936824321747</t>
+    <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674776554108</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509349346161</t>
+    <t xml:space="preserve">0.646509408950806</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226686000824</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
@@ -854,13 +857,13 @@
     <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64178854227066</t>
+    <t xml:space="preserve">0.641788482666016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410355567932</t>
+    <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632824957370758</t>
+    <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239618778229</t>
@@ -872,13 +875,13 @@
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276033878326</t>
+    <t xml:space="preserve">0.620276093482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592788696289</t>
+    <t xml:space="preserve">0.591592848300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -893,7 +896,7 @@
     <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6238614320755</t>
+    <t xml:space="preserve">0.623861491680145</t>
   </si>
   <si>
     <t xml:space="preserve">0.616690635681152</t>
@@ -908,13 +911,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58980005979538</t>
+    <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385457992554</t>
+    <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -929,7 +932,7 @@
     <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324085712433</t>
+    <t xml:space="preserve">0.559324026107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -938,7 +941,7 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873068809509</t>
+    <t xml:space="preserve">0.571873009204865</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -947,7 +950,7 @@
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178127288818</t>
+    <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
     <t xml:space="preserve">0.631032347679138</t>
@@ -962,16 +965,16 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567831516266</t>
+    <t xml:space="preserve">0.548567891120911</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945899009705</t>
+    <t xml:space="preserve">0.553945958614349</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -986,7 +989,7 @@
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203144073486</t>
+    <t xml:space="preserve">0.638203084468842</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -995,43 +998,43 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752127170563</t>
+    <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337525367737</t>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057185649872</t>
+    <t xml:space="preserve">0.674057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66150826215744</t>
+    <t xml:space="preserve">0.661508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093660354614</t>
+    <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
     <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645374000072479</t>
+    <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
     <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64358127117157</t>
+    <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166669368744</t>
+    <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264456748962</t>
+    <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471847057343</t>
@@ -1040,7 +1043,7 @@
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020770549774</t>
+    <t xml:space="preserve">0.683020710945129</t>
   </si>
   <si>
     <t xml:space="preserve">0.690191566944122</t>
@@ -1049,13 +1052,13 @@
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715289413928986</t>
+    <t xml:space="preserve">0.71528947353363</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594591617584</t>
+    <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972718715668</t>
+    <t xml:space="preserve">0.743972778320312</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1064,10 +1067,10 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009133815765</t>
+    <t xml:space="preserve">0.73500919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460329532623</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
     <t xml:space="preserve">0.745765447616577</t>
@@ -1076,7 +1079,7 @@
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143515110016</t>
+    <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
@@ -1103,7 +1106,7 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252998828888</t>
+    <t xml:space="preserve">0.724252939224243</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
@@ -1112,16 +1115,16 @@
     <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642583847046</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849914550781</t>
+    <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667600631714</t>
+    <t xml:space="preserve">0.720667541027069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045727729797</t>
+    <t xml:space="preserve">0.726045668125153</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1149,9 +1152,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -38824,7 +38824,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1421" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38850,7 +38850,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1422" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38876,7 +38876,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1423" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38902,7 +38902,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1424" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38980,7 +38980,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1427" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39006,7 +39006,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1428" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39032,7 +39032,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1429" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39058,7 +39058,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1430" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39136,7 +39136,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1433" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39162,7 +39162,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1434" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39240,7 +39240,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1437" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39266,7 +39266,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1438" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39292,7 +39292,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1439" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39318,7 +39318,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1440" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39344,7 +39344,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1441" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39370,7 +39370,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1442" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39396,7 +39396,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1443" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39422,7 +39422,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1444" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39448,7 +39448,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39474,7 +39474,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1446" t="s">
-        <v>209</v>
+        <v>210</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39500,7 +39500,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1447" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39526,7 +39526,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1448" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39552,7 +39552,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1449" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39578,7 +39578,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1450" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39604,7 +39604,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1451" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39656,7 +39656,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1453" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39682,7 +39682,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1454" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39734,7 +39734,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39760,7 +39760,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1457" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39786,7 +39786,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1458" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39812,7 +39812,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1459" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39864,7 +39864,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1461" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39890,7 +39890,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1462" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39916,7 +39916,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1463" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39942,7 +39942,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1464" t="s">
-        <v>206</v>
+        <v>207</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39968,7 +39968,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1465" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39994,7 +39994,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40020,7 +40020,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1467" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40046,7 +40046,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1468" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40072,7 +40072,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1469" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40098,7 +40098,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1470" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40124,7 +40124,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1471" t="s">
-        <v>210</v>
+        <v>211</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40150,7 +40150,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1472" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40176,7 +40176,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1473" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40202,7 +40202,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1474" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40228,7 +40228,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1475" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40254,7 +40254,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1476" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40280,7 +40280,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1477" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40306,7 +40306,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1478" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40358,7 +40358,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1480" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40384,7 +40384,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1481" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40410,7 +40410,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1482" t="s">
-        <v>205</v>
+        <v>206</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40436,7 +40436,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1483" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40462,7 +40462,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1484" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40488,7 +40488,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1485" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40514,7 +40514,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1486" t="s">
-        <v>207</v>
+        <v>208</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40540,7 +40540,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1487" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40566,7 +40566,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1488" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40592,7 +40592,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1489" t="s">
-        <v>208</v>
+        <v>209</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40618,7 +40618,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1490" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40644,7 +40644,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1491" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40696,7 +40696,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1493" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40722,7 +40722,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1494" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40748,7 +40748,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1495" t="s">
-        <v>191</v>
+        <v>201</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40774,7 +40774,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1496" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40800,7 +40800,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1497" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40826,7 +40826,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1498" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40852,7 +40852,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1499" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40878,7 +40878,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1500" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40904,7 +40904,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1501" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40930,7 +40930,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1502" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40956,7 +40956,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1503" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40982,7 +40982,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1504" t="s">
-        <v>223</v>
+        <v>224</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41008,7 +41008,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1505" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41034,7 +41034,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1506" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41060,7 +41060,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1507" t="s">
-        <v>224</v>
+        <v>225</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41086,7 +41086,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1508" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41112,7 +41112,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1509" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41138,7 +41138,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1510" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41164,7 +41164,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1511" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41190,7 +41190,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1512" t="s">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41216,7 +41216,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1513" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41242,7 +41242,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1514" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41268,7 +41268,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41294,7 +41294,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1516" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41320,7 +41320,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1517" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41346,7 +41346,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>225</v>
+        <v>226</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41372,7 +41372,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1519" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41398,7 +41398,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1520" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41424,7 +41424,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1521" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41450,7 +41450,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1522" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41476,7 +41476,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1523" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41502,7 +41502,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1524" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41528,7 +41528,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1525" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41554,7 +41554,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41580,7 +41580,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1527" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41606,7 +41606,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1528" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41632,7 +41632,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1529" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41658,7 +41658,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>230</v>
+        <v>231</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41684,7 +41684,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1531" t="s">
-        <v>231</v>
+        <v>232</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41710,7 +41710,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1532" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41736,7 +41736,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1533" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41762,7 +41762,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1534" t="s">
-        <v>228</v>
+        <v>229</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41788,7 +41788,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1535" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41814,7 +41814,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1536" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41840,7 +41840,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>235</v>
+        <v>236</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41866,7 +41866,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1538" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41892,7 +41892,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1539" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41918,7 +41918,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1540" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41944,7 +41944,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1541" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41970,7 +41970,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1542" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41996,7 +41996,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1543" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42022,7 +42022,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1544" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42048,7 +42048,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42074,7 +42074,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1546" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42100,7 +42100,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1547" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42126,7 +42126,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1548" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42152,7 +42152,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1549" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42178,7 +42178,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1550" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42204,7 +42204,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1551" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42230,7 +42230,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1552" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42256,7 +42256,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1553" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42282,7 +42282,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1554" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42308,7 +42308,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1555" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42334,7 +42334,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1556" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42360,7 +42360,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1557" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42386,7 +42386,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42412,7 +42412,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42438,7 +42438,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1560" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42464,7 +42464,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1561" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42490,7 +42490,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42516,7 +42516,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1563" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42542,7 +42542,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1564" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42568,7 +42568,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1565" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42594,7 +42594,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1566" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42620,7 +42620,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1567" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42646,7 +42646,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42672,7 +42672,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1569" t="s">
-        <v>233</v>
+        <v>234</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42698,7 +42698,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1570" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42724,7 +42724,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1571" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42750,7 +42750,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1572" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42776,7 +42776,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1573" t="s">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42802,7 +42802,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1574" t="s">
-        <v>211</v>
+        <v>212</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42828,7 +42828,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1575" t="s">
-        <v>201</v>
+        <v>202</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42854,7 +42854,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1576" t="s">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42880,7 +42880,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1577" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42906,7 +42906,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1578" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42932,7 +42932,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1579" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42958,7 +42958,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1580" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42984,7 +42984,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1581" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43010,7 +43010,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1582" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43036,7 +43036,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1583" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43062,7 +43062,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1584" t="s">
-        <v>234</v>
+        <v>235</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43088,7 +43088,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1585" t="s">
-        <v>229</v>
+        <v>230</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43114,7 +43114,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43140,7 +43140,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1587" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43166,7 +43166,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1588" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43192,7 +43192,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1589" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43218,7 +43218,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43244,7 +43244,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1591" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43270,7 +43270,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1592" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43296,7 +43296,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1593" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43322,7 +43322,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1594" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43348,7 +43348,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1595" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43374,7 +43374,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1596" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43400,7 +43400,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43426,7 +43426,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1598" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43452,7 +43452,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1599" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43478,7 +43478,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1600" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43504,7 +43504,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1601" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43530,7 +43530,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1602" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43556,7 +43556,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1603" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43582,7 +43582,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1604" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43608,7 +43608,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1605" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43634,7 +43634,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1606" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43660,7 +43660,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1607" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43686,7 +43686,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1608" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43712,7 +43712,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1609" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43738,7 +43738,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1610" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43764,7 +43764,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1611" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43790,7 +43790,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1612" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43816,7 +43816,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1613" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43842,7 +43842,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1614" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43868,7 +43868,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1615" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43894,7 +43894,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1616" t="s">
-        <v>227</v>
+        <v>228</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43920,7 +43920,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1617" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43946,7 +43946,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43972,7 +43972,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43998,7 +43998,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="s">
-        <v>251</v>
+        <v>252</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44024,7 +44024,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1621" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44050,7 +44050,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1622" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44076,7 +44076,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44102,7 +44102,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1624" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44128,7 +44128,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1625" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44154,7 +44154,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1626" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44180,7 +44180,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1627" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44206,7 +44206,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1628" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44232,7 +44232,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1629" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44258,7 +44258,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1630" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44284,7 +44284,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1631" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44310,7 +44310,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1632" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44336,7 +44336,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1633" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44362,7 +44362,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1634" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44388,7 +44388,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1635" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44414,7 +44414,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1636" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44440,7 +44440,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44466,7 +44466,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44492,7 +44492,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44518,7 +44518,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44544,7 +44544,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44570,7 +44570,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44596,7 +44596,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44622,7 +44622,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44648,7 +44648,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44674,7 +44674,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44700,7 +44700,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1647" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44726,7 +44726,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44752,7 +44752,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44778,7 +44778,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44804,7 +44804,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44830,7 +44830,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44856,7 +44856,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44882,7 +44882,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44908,7 +44908,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44934,7 +44934,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44960,7 +44960,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44986,7 +44986,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45012,7 +45012,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45038,7 +45038,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45064,7 +45064,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45090,7 +45090,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45116,7 +45116,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45142,7 +45142,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45168,7 +45168,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45194,7 +45194,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45220,7 +45220,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45246,7 +45246,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45272,7 +45272,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45298,7 +45298,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45324,7 +45324,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45350,7 +45350,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45376,7 +45376,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45402,7 +45402,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45428,7 +45428,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45454,7 +45454,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45480,7 +45480,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45506,7 +45506,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45532,7 +45532,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45558,7 +45558,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45584,7 +45584,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45610,7 +45610,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45636,7 +45636,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1683" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45662,7 +45662,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45688,7 +45688,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1685" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45714,7 +45714,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45740,7 +45740,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45766,7 +45766,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45792,7 +45792,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45818,7 +45818,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45844,7 +45844,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45870,7 +45870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45896,7 +45896,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45922,7 +45922,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45948,7 +45948,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45974,7 +45974,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46000,7 +46000,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46026,7 +46026,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46052,7 +46052,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46078,7 +46078,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46104,7 +46104,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46130,7 +46130,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46156,7 +46156,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46182,7 +46182,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46208,7 +46208,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46234,7 +46234,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46260,7 +46260,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46286,7 +46286,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46312,7 +46312,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46338,7 +46338,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46364,7 +46364,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46390,7 +46390,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46416,7 +46416,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46442,7 +46442,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46468,7 +46468,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46494,7 +46494,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46520,7 +46520,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46546,7 +46546,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46572,7 +46572,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46598,7 +46598,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46624,7 +46624,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46650,7 +46650,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46676,7 +46676,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46702,7 +46702,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46728,7 +46728,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46754,7 +46754,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46780,7 +46780,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46806,7 +46806,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46832,7 +46832,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46858,7 +46858,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46884,7 +46884,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46910,7 +46910,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46936,7 +46936,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46962,7 +46962,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46988,7 +46988,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47014,7 +47014,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47040,7 +47040,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47066,7 +47066,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47092,7 +47092,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47118,7 +47118,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47144,7 +47144,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47170,7 +47170,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47196,7 +47196,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47222,7 +47222,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47248,7 +47248,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47274,7 +47274,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47300,7 +47300,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1747" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47326,7 +47326,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47352,7 +47352,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47378,7 +47378,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47404,7 +47404,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47430,7 +47430,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47456,7 +47456,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47482,7 +47482,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47508,7 +47508,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47534,7 +47534,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47560,7 +47560,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47586,7 +47586,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1758" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47612,7 +47612,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47638,7 +47638,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47664,7 +47664,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47690,7 +47690,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47716,7 +47716,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47742,7 +47742,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47768,7 +47768,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47794,7 +47794,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47820,7 +47820,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47846,7 +47846,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1768" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47872,7 +47872,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47898,7 +47898,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47924,7 +47924,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47950,7 +47950,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47976,7 +47976,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48002,7 +48002,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1774" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48028,7 +48028,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48054,7 +48054,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48080,7 +48080,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48106,7 +48106,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1778" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48132,7 +48132,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48158,7 +48158,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48184,7 +48184,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1781" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48210,7 +48210,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1782" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48236,7 +48236,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48262,7 +48262,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48288,7 +48288,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48314,7 +48314,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48340,7 +48340,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48366,7 +48366,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48392,7 +48392,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48418,7 +48418,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48444,7 +48444,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48470,7 +48470,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48496,7 +48496,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48522,7 +48522,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48548,7 +48548,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48574,7 +48574,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48600,7 +48600,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48626,7 +48626,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48652,7 +48652,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48678,7 +48678,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48704,7 +48704,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48730,7 +48730,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48756,7 +48756,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48782,7 +48782,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1804" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48808,7 +48808,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48834,7 +48834,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48860,7 +48860,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48886,7 +48886,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48912,7 +48912,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48938,7 +48938,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48964,7 +48964,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48990,7 +48990,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49016,7 +49016,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49042,7 +49042,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49068,7 +49068,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49094,7 +49094,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49120,7 +49120,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49146,7 +49146,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49172,7 +49172,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49198,7 +49198,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49224,7 +49224,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49250,7 +49250,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49276,7 +49276,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49302,7 +49302,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49328,7 +49328,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49354,7 +49354,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49380,7 +49380,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49406,7 +49406,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49432,7 +49432,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49458,7 +49458,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49484,7 +49484,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49510,7 +49510,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49536,7 +49536,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49562,7 +49562,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49588,7 +49588,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49614,7 +49614,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49640,7 +49640,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49666,7 +49666,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49692,7 +49692,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49718,7 +49718,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49744,7 +49744,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49770,7 +49770,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49796,7 +49796,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49822,7 +49822,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49848,7 +49848,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49874,7 +49874,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49900,7 +49900,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49926,7 +49926,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49952,7 +49952,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49978,7 +49978,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50004,7 +50004,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50030,7 +50030,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50056,7 +50056,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50082,7 +50082,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50108,7 +50108,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50134,7 +50134,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50160,7 +50160,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50186,7 +50186,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50212,7 +50212,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50238,7 +50238,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50264,7 +50264,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50290,7 +50290,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50316,7 +50316,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50342,7 +50342,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50368,7 +50368,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50394,7 +50394,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50420,7 +50420,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50446,7 +50446,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50472,7 +50472,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50498,7 +50498,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50524,7 +50524,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50550,7 +50550,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50576,7 +50576,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50602,7 +50602,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50628,7 +50628,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50654,7 +50654,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50680,7 +50680,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50706,7 +50706,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50732,7 +50732,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50758,7 +50758,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50784,7 +50784,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50810,7 +50810,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50836,7 +50836,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50862,7 +50862,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50888,7 +50888,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50914,7 +50914,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50940,7 +50940,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50966,7 +50966,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50992,7 +50992,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51018,7 +51018,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51044,7 +51044,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51070,7 +51070,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51096,7 +51096,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51122,7 +51122,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51148,7 +51148,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51174,7 +51174,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51200,7 +51200,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51278,7 +51278,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51304,7 +51304,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51330,7 +51330,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51356,7 +51356,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51434,7 +51434,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51538,7 +51538,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51616,7 +51616,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51642,7 +51642,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51668,7 +51668,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51746,7 +51746,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51824,7 +51824,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51850,7 +51850,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51876,7 +51876,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51902,7 +51902,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51980,7 +51980,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52006,7 +52006,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52058,7 +52058,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52136,7 +52136,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52214,7 +52214,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52240,7 +52240,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52292,7 +52292,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>379</v>
+        <v>329</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52344,7 +52344,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52474,7 +52474,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52500,7 +52500,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54528,7 +54528,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54554,7 +54554,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57076,7 +57076,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57154,7 +57154,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58142,7 +58142,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -67094,7 +67094,7 @@
     </row>
     <row r="2509">
       <c r="A2509" s="1" t="n">
-        <v>45972.3757407407</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2509" t="n">
         <v>24000</v>
@@ -67115,6 +67115,32 @@
         <v>508</v>
       </c>
       <c r="H2509" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2510">
+      <c r="A2510" s="1" t="n">
+        <v>45973.3335763889</v>
+      </c>
+      <c r="B2510" t="n">
+        <v>20000</v>
+      </c>
+      <c r="C2510" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2510" t="n">
+        <v>0.558000028133392</v>
+      </c>
+      <c r="E2510" t="n">
+        <v>0.558000028133392</v>
+      </c>
+      <c r="F2510" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2510" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2510" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -44,16 +44,16 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394716262817</t>
+    <t xml:space="preserve">0.235394701361656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249102830887</t>
+    <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899916529655</t>
+    <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581348657608</t>
+    <t xml:space="preserve">0.218581318855286</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">0.211099088191986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217319875955582</t>
+    <t xml:space="preserve">0.21731986105442</t>
   </si>
   <si>
     <t xml:space="preserve">0.228921487927437</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071776986122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293369412422</t>
+    <t xml:space="preserve">0.233293399214745</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
@@ -80,43 +80,43 @@
     <t xml:space="preserve">0.231527775526047</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762211441994</t>
+    <t xml:space="preserve">0.229762226343155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598259329796</t>
+    <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784876823425</t>
+    <t xml:space="preserve">0.222784906625748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214377820491791</t>
+    <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014971137047</t>
+    <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970704555511</t>
+    <t xml:space="preserve">0.20597068965435</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767146587372</t>
+    <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563588619232</t>
+    <t xml:space="preserve">0.197563573718071</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722894906998</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
     <t xml:space="preserve">0.202355399727821</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202187076210976</t>
+    <t xml:space="preserve">0.202187091112137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.2052141726017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912760019302</t>
+    <t xml:space="preserve">0.208912774920464</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762500762939</t>
+    <t xml:space="preserve">0.210762485861778</t>
   </si>
   <si>
     <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616598010063</t>
+    <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987615227699</t>
+    <t xml:space="preserve">0.22698763012886</t>
   </si>
   <si>
     <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235439777374</t>
+    <t xml:space="preserve">0.236235395073891</t>
   </si>
   <si>
     <t xml:space="preserve">0.241279691457748</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093863725662</t>
+    <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226678371429</t>
+    <t xml:space="preserve">0.273226648569107</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836458206177</t>
+    <t xml:space="preserve">0.285836547613144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562216520309</t>
+    <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332137107849</t>
+    <t xml:space="preserve">0.304332107305527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057776212692</t>
+    <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455326080322</t>
+    <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
     <t xml:space="preserve">0.36318102478981</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941409111023</t>
+    <t xml:space="preserve">0.411941379308701</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">0.439684838056564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400911092758</t>
+    <t xml:space="preserve">0.483400881290436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055896282196</t>
+    <t xml:space="preserve">0.501055836677551</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011584997177</t>
+    <t xml:space="preserve">0.4960116147995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49651563167572</t>
+    <t xml:space="preserve">0.496515661478043</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307871580124</t>
+    <t xml:space="preserve">0.492307841777802</t>
   </si>
   <si>
     <t xml:space="preserve">0.580670893192291</t>
@@ -263,43 +263,43 @@
     <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274843454361</t>
+    <t xml:space="preserve">0.622748553752899</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525969982147217</t>
+    <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
     <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48810014128685</t>
+    <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931271076202</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509138941764832</t>
+    <t xml:space="preserve">0.509139001369476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892351388931</t>
+    <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346791267395</t>
+    <t xml:space="preserve">0.513346672058105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177712440491</t>
+    <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
     <t xml:space="preserve">0.517554521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269160509109</t>
+    <t xml:space="preserve">0.471269071102142</t>
   </si>
   <si>
     <t xml:space="preserve">0.467061370611191</t>
@@ -308,25 +308,25 @@
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853610515594</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684710502625</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607049942017</t>
+    <t xml:space="preserve">0.437607079744339</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230330228806</t>
+    <t xml:space="preserve">0.45023038983345</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022540330887</t>
+    <t xml:space="preserve">0.446022510528564</t>
   </si>
   <si>
     <t xml:space="preserve">0.458645880222321</t>
@@ -341,37 +341,37 @@
     <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385502338409</t>
+    <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476890802383</t>
+    <t xml:space="preserve">0.475476861000061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983769655228</t>
+    <t xml:space="preserve">0.42498379945755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381524562836</t>
+    <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360459566116</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726661682129</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814780235291</t>
+    <t xml:space="preserve">0.441814810037613</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092893600464</t>
@@ -380,40 +380,40 @@
     <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994287252426</t>
+    <t xml:space="preserve">0.408994257450104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311201095581</t>
+    <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
     <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895621299744</t>
+    <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578737258911</t>
+    <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529419183731</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649090528488</t>
+    <t xml:space="preserve">0.373649060726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155969381332</t>
+    <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374217271805</t>
+    <t xml:space="preserve">0.31137427687645</t>
   </si>
   <si>
     <t xml:space="preserve">0.336620837450027</t>
@@ -434,22 +434,22 @@
     <t xml:space="preserve">0.35345184803009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184282064438</t>
+    <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345036298036575</t>
+    <t xml:space="preserve">0.34503635764122</t>
   </si>
   <si>
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830389380455</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571489572525</t>
+    <t xml:space="preserve">0.331571459770203</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33493772149086</t>
+    <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
     <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
-    <t xml:space="preserve">0.366916656494141</t>
+    <t xml:space="preserve">0.366916686296463</t>
   </si>
   <si>
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36859980225563</t>
+    <t xml:space="preserve">0.368599772453308</t>
   </si>
   <si>
     <t xml:space="preserve">0.36355048418045</t>
@@ -491,16 +491,16 @@
     <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698348999023</t>
+    <t xml:space="preserve">0.378698438405991</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332176685333</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282918214798</t>
+    <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
     <t xml:space="preserve">0.377015292644501</t>
@@ -515,58 +515,58 @@
     <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593351840973</t>
+    <t xml:space="preserve">0.538593232631683</t>
   </si>
   <si>
     <t xml:space="preserve">0.559632062911987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216602325439</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783316850662</t>
+    <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48473396897316</t>
+    <t xml:space="preserve">0.484733939170837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47631847858429</t>
+    <t xml:space="preserve">0.476318359375</t>
   </si>
   <si>
-    <t xml:space="preserve">0.494832575321198</t>
+    <t xml:space="preserve">0.494832545518875</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466373205185</t>
+    <t xml:space="preserve">0.491466403007507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198807239532</t>
+    <t xml:space="preserve">0.49819877743721</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494656085968</t>
+    <t xml:space="preserve">0.528494715690613</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811480522156</t>
+    <t xml:space="preserve">0.526811540126801</t>
   </si>
   <si>
     <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128424167633</t>
+    <t xml:space="preserve">0.525128483772278</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523445308208466</t>
+    <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661426782608</t>
+    <t xml:space="preserve">0.50661438703537</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663675308228</t>
+    <t xml:space="preserve">0.511663556098938</t>
   </si>
   <si>
     <t xml:space="preserve">0.50324809551239</t>
@@ -575,79 +575,76 @@
     <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501564979553223</t>
+    <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.493149518966675</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029907226562</t>
+    <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107508182526</t>
+    <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374984741211</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396079540253</t>
+    <t xml:space="preserve">0.518396019935608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671302318573</t>
+    <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
-    <t xml:space="preserve">0.533544063568115</t>
+    <t xml:space="preserve">0.530068099498749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530068159103394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.535281956195831</t>
+    <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330206871033</t>
+    <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709490776062</t>
+    <t xml:space="preserve">0.545709550380707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661120891571</t>
+    <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185395240784</t>
+    <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399132728577</t>
+    <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971478939056</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
@@ -668,31 +665,31 @@
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378576755524</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514426827430725</t>
+    <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503999173641205</t>
+    <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833746433258</t>
+    <t xml:space="preserve">0.491833627223969</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571698665619</t>
+    <t xml:space="preserve">0.493571668863297</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854362010956</t>
+    <t xml:space="preserve">0.524854302406311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523116409778595</t>
+    <t xml:space="preserve">0.52311646938324</t>
   </si>
   <si>
     <t xml:space="preserve">0.519640564918518</t>
@@ -725,34 +722,34 @@
     <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102311134338</t>
+    <t xml:space="preserve">0.669102430343628</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364478111267</t>
+    <t xml:space="preserve">0.667364537715912</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605910301208</t>
+    <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
     <t xml:space="preserve">0.653461039066315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6447713971138</t>
+    <t xml:space="preserve">0.644771337509155</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
@@ -761,28 +758,28 @@
     <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440363883972</t>
+    <t xml:space="preserve">0.620440423488617</t>
   </si>
   <si>
     <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643033444881439</t>
+    <t xml:space="preserve">0.643033504486084</t>
   </si>
   <si>
     <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012888908386</t>
+    <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633485794067</t>
+    <t xml:space="preserve">0.592633605003357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799091815948</t>
+    <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -791,34 +788,34 @@
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50573718547821</t>
+    <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
     <t xml:space="preserve">0.557874977588654</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516368865967</t>
+    <t xml:space="preserve">0.573516428470612</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109449863434</t>
+    <t xml:space="preserve">0.596109390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750841140747</t>
+    <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343802928925</t>
+    <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985253810883</t>
+    <t xml:space="preserve">0.649985194206238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247241973877</t>
+    <t xml:space="preserve">0.648247301578522</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081755161285</t>
+    <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005809783936</t>
+    <t xml:space="preserve">0.683005750179291</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957559108734</t>
@@ -827,28 +824,28 @@
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743762016296</t>
+    <t xml:space="preserve">0.684743702411652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150621414185</t>
+    <t xml:space="preserve">0.662150800228119</t>
   </si>
   <si>
     <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936883926392</t>
+    <t xml:space="preserve">0.656936824321747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509408950806</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226626396179</t>
+    <t xml:space="preserve">0.615226686000824</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
@@ -857,13 +854,13 @@
     <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788482666016</t>
+    <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410415172577</t>
+    <t xml:space="preserve">0.636410355567932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632825016975403</t>
+    <t xml:space="preserve">0.632824957370758</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239618778229</t>
@@ -875,13 +872,13 @@
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276093482971</t>
+    <t xml:space="preserve">0.620276033878326</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592848300934</t>
+    <t xml:space="preserve">0.591592788696289</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -896,7 +893,7 @@
     <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623861491680145</t>
+    <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
     <t xml:space="preserve">0.616690635681152</t>
@@ -911,13 +908,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589800119400024</t>
+    <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385517597198</t>
+    <t xml:space="preserve">0.593385457992554</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -932,7 +929,7 @@
     <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324026107788</t>
+    <t xml:space="preserve">0.559324085712433</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -941,7 +938,7 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873009204865</t>
+    <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -950,7 +947,7 @@
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178186893463</t>
+    <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
     <t xml:space="preserve">0.631032347679138</t>
@@ -965,16 +962,16 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738627910614</t>
+    <t xml:space="preserve">0.555738687515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945958614349</t>
+    <t xml:space="preserve">0.553945899009705</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -989,7 +986,7 @@
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203084468842</t>
+    <t xml:space="preserve">0.638203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -998,43 +995,43 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752067565918</t>
+    <t xml:space="preserve">0.650752127170563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.654337525367737</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057245254517</t>
+    <t xml:space="preserve">0.674057185649872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661508321762085</t>
+    <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093719959259</t>
+    <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
     <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645373940467834</t>
+    <t xml:space="preserve">0.645374000072479</t>
   </si>
   <si>
     <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643581211566925</t>
+    <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264516353607</t>
+    <t xml:space="preserve">0.672264456748962</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471847057343</t>
@@ -1043,7 +1040,7 @@
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020710945129</t>
+    <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
     <t xml:space="preserve">0.690191566944122</t>
@@ -1052,13 +1049,13 @@
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71528947353363</t>
+    <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594651222229</t>
+    <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1067,10 +1064,10 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
     <t xml:space="preserve">0.745765447616577</t>
@@ -1079,7 +1076,7 @@
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143574714661</t>
+    <t xml:space="preserve">0.751143515110016</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
@@ -1106,7 +1103,7 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252939224243</t>
+    <t xml:space="preserve">0.724252998828888</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
@@ -1115,16 +1112,16 @@
     <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642643451691</t>
+    <t xml:space="preserve">0.677642583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849974155426</t>
+    <t xml:space="preserve">0.675849914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667541027069</t>
+    <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045668125153</t>
+    <t xml:space="preserve">0.726045727729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1152,6 +1149,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -38824,7 +38824,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1421" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38850,7 +38850,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1422" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38876,7 +38876,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1423" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38902,7 +38902,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1424" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38980,7 +38980,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1427" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39006,7 +39006,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1428" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39032,7 +39032,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1429" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39058,7 +39058,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1430" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39136,7 +39136,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1433" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39162,7 +39162,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1434" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39240,7 +39240,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1437" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39266,7 +39266,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1438" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39292,7 +39292,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1439" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39318,7 +39318,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1440" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39344,7 +39344,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1441" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39370,7 +39370,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1442" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39396,7 +39396,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1443" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39422,7 +39422,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1444" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39448,7 +39448,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39474,7 +39474,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1446" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39500,7 +39500,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1447" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39526,7 +39526,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1448" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39552,7 +39552,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1449" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39578,7 +39578,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1450" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39604,7 +39604,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1451" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39656,7 +39656,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1453" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39682,7 +39682,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1454" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39734,7 +39734,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39760,7 +39760,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1457" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39786,7 +39786,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1458" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39812,7 +39812,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1459" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39864,7 +39864,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1461" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39890,7 +39890,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1462" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39916,7 +39916,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1463" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39942,7 +39942,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1464" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39968,7 +39968,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1465" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -39994,7 +39994,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40020,7 +40020,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1467" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40046,7 +40046,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1468" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40072,7 +40072,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1469" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40098,7 +40098,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1470" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40124,7 +40124,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1471" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40150,7 +40150,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1472" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40176,7 +40176,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1473" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40202,7 +40202,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1474" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40228,7 +40228,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1475" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40254,7 +40254,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1476" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40280,7 +40280,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1477" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40306,7 +40306,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1478" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40358,7 +40358,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1480" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40384,7 +40384,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1481" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40410,7 +40410,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1482" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40436,7 +40436,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1483" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40462,7 +40462,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1484" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40488,7 +40488,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1485" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40514,7 +40514,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1486" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40540,7 +40540,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1487" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40566,7 +40566,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1488" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40592,7 +40592,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1489" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40618,7 +40618,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1490" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40644,7 +40644,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1491" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40696,7 +40696,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1493" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40722,7 +40722,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1494" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40748,7 +40748,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1495" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40774,7 +40774,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1496" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40800,7 +40800,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1497" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40826,7 +40826,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1498" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40852,7 +40852,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1499" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40878,7 +40878,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1500" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40904,7 +40904,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1501" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40930,7 +40930,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1502" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40956,7 +40956,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1503" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40982,7 +40982,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1504" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41008,7 +41008,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1505" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41034,7 +41034,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1506" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41060,7 +41060,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1507" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41086,7 +41086,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1508" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41112,7 +41112,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1509" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41138,7 +41138,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1510" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41164,7 +41164,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1511" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41190,7 +41190,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1512" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41216,7 +41216,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1513" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41242,7 +41242,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1514" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41268,7 +41268,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41294,7 +41294,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1516" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41320,7 +41320,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1517" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41346,7 +41346,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41372,7 +41372,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1519" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41398,7 +41398,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1520" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41424,7 +41424,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1521" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41450,7 +41450,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1522" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41476,7 +41476,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1523" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41502,7 +41502,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1524" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41528,7 +41528,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1525" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41554,7 +41554,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41580,7 +41580,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1527" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41606,7 +41606,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1528" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41632,7 +41632,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1529" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41658,7 +41658,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41684,7 +41684,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1531" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41710,7 +41710,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1532" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41736,7 +41736,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1533" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41762,7 +41762,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1534" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41788,7 +41788,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1535" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41814,7 +41814,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1536" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41840,7 +41840,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41866,7 +41866,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1538" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41892,7 +41892,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1539" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41918,7 +41918,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1540" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41944,7 +41944,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1541" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41970,7 +41970,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1542" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -41996,7 +41996,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1543" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42022,7 +42022,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1544" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42048,7 +42048,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42074,7 +42074,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1546" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42100,7 +42100,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1547" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42126,7 +42126,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1548" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42152,7 +42152,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1549" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42178,7 +42178,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1550" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42204,7 +42204,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1551" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42230,7 +42230,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1552" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42256,7 +42256,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1553" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42282,7 +42282,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1554" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42308,7 +42308,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1555" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42334,7 +42334,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1556" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42360,7 +42360,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1557" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42386,7 +42386,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42412,7 +42412,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42438,7 +42438,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1560" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42464,7 +42464,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1561" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42490,7 +42490,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42516,7 +42516,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1563" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42542,7 +42542,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1564" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42568,7 +42568,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1565" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42594,7 +42594,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1566" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42620,7 +42620,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1567" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42646,7 +42646,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42672,7 +42672,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1569" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42698,7 +42698,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1570" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42724,7 +42724,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1571" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42750,7 +42750,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1572" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42776,7 +42776,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1573" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42802,7 +42802,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1574" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42828,7 +42828,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1575" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42854,7 +42854,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1576" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42880,7 +42880,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1577" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42906,7 +42906,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1578" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42932,7 +42932,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1579" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42958,7 +42958,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1580" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42984,7 +42984,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1581" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43010,7 +43010,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1582" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43036,7 +43036,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1583" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43062,7 +43062,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1584" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43088,7 +43088,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1585" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43114,7 +43114,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43140,7 +43140,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1587" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43166,7 +43166,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1588" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43192,7 +43192,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1589" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43218,7 +43218,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43244,7 +43244,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1591" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43270,7 +43270,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1592" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43296,7 +43296,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1593" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43322,7 +43322,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1594" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43348,7 +43348,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1595" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43374,7 +43374,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1596" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43400,7 +43400,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43426,7 +43426,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1598" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43452,7 +43452,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1599" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43478,7 +43478,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1600" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43504,7 +43504,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1601" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43530,7 +43530,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1602" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43556,7 +43556,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1603" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43582,7 +43582,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1604" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43608,7 +43608,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1605" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43634,7 +43634,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1606" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43660,7 +43660,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1607" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43686,7 +43686,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1608" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43712,7 +43712,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1609" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43738,7 +43738,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1610" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43764,7 +43764,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1611" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43790,7 +43790,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1612" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43816,7 +43816,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1613" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43842,7 +43842,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1614" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43868,7 +43868,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1615" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43894,7 +43894,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1616" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43920,7 +43920,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1617" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43946,7 +43946,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43972,7 +43972,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -43998,7 +43998,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44024,7 +44024,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1621" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44050,7 +44050,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1622" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44076,7 +44076,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44102,7 +44102,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1624" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44128,7 +44128,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1625" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44154,7 +44154,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1626" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44180,7 +44180,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1627" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44206,7 +44206,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1628" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44232,7 +44232,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1629" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44258,7 +44258,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1630" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44284,7 +44284,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1631" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44310,7 +44310,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1632" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44336,7 +44336,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1633" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44362,7 +44362,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1634" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44388,7 +44388,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1635" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44414,7 +44414,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1636" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44440,7 +44440,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44466,7 +44466,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44492,7 +44492,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44518,7 +44518,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44544,7 +44544,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44570,7 +44570,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44596,7 +44596,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44622,7 +44622,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44648,7 +44648,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44674,7 +44674,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44700,7 +44700,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1647" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44726,7 +44726,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44752,7 +44752,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44778,7 +44778,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44804,7 +44804,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44830,7 +44830,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44856,7 +44856,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44882,7 +44882,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44908,7 +44908,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44934,7 +44934,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44960,7 +44960,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44986,7 +44986,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45012,7 +45012,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45038,7 +45038,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45064,7 +45064,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45090,7 +45090,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45116,7 +45116,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45142,7 +45142,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45168,7 +45168,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45194,7 +45194,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45220,7 +45220,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45246,7 +45246,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45272,7 +45272,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45298,7 +45298,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45324,7 +45324,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45350,7 +45350,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45376,7 +45376,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45402,7 +45402,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45428,7 +45428,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45454,7 +45454,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45480,7 +45480,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45506,7 +45506,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45532,7 +45532,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45558,7 +45558,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45584,7 +45584,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45610,7 +45610,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45636,7 +45636,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1683" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45662,7 +45662,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45688,7 +45688,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1685" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45714,7 +45714,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45740,7 +45740,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45766,7 +45766,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45792,7 +45792,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45818,7 +45818,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45844,7 +45844,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45870,7 +45870,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45896,7 +45896,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45922,7 +45922,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45948,7 +45948,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45974,7 +45974,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46000,7 +46000,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46026,7 +46026,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46052,7 +46052,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46078,7 +46078,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46104,7 +46104,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46130,7 +46130,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46156,7 +46156,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46182,7 +46182,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46208,7 +46208,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46234,7 +46234,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46260,7 +46260,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46286,7 +46286,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46312,7 +46312,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46338,7 +46338,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46364,7 +46364,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46390,7 +46390,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46416,7 +46416,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46442,7 +46442,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46468,7 +46468,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46494,7 +46494,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46520,7 +46520,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46546,7 +46546,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46572,7 +46572,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46598,7 +46598,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46624,7 +46624,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46650,7 +46650,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46676,7 +46676,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46702,7 +46702,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46728,7 +46728,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46754,7 +46754,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46780,7 +46780,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46806,7 +46806,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46832,7 +46832,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46858,7 +46858,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46884,7 +46884,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46910,7 +46910,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46936,7 +46936,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46962,7 +46962,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46988,7 +46988,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47014,7 +47014,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47040,7 +47040,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47066,7 +47066,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47092,7 +47092,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47118,7 +47118,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47144,7 +47144,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47170,7 +47170,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47196,7 +47196,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47222,7 +47222,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47248,7 +47248,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47274,7 +47274,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47300,7 +47300,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1747" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47326,7 +47326,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47352,7 +47352,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47378,7 +47378,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47404,7 +47404,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47430,7 +47430,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47456,7 +47456,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47482,7 +47482,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47508,7 +47508,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47534,7 +47534,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47560,7 +47560,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47586,7 +47586,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1758" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47612,7 +47612,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47638,7 +47638,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47664,7 +47664,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47690,7 +47690,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47716,7 +47716,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47742,7 +47742,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47768,7 +47768,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47794,7 +47794,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47820,7 +47820,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47846,7 +47846,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1768" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47872,7 +47872,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47898,7 +47898,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47924,7 +47924,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47950,7 +47950,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47976,7 +47976,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48002,7 +48002,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1774" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48028,7 +48028,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48054,7 +48054,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48080,7 +48080,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48106,7 +48106,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1778" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48132,7 +48132,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48158,7 +48158,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48184,7 +48184,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1781" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48210,7 +48210,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1782" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48236,7 +48236,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48262,7 +48262,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48288,7 +48288,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48314,7 +48314,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48340,7 +48340,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48366,7 +48366,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48392,7 +48392,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48418,7 +48418,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48444,7 +48444,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48470,7 +48470,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48496,7 +48496,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48522,7 +48522,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48548,7 +48548,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48574,7 +48574,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48600,7 +48600,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48626,7 +48626,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48652,7 +48652,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48678,7 +48678,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48704,7 +48704,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48730,7 +48730,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48756,7 +48756,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48782,7 +48782,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1804" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48808,7 +48808,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48834,7 +48834,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48860,7 +48860,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48886,7 +48886,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48912,7 +48912,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48938,7 +48938,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48964,7 +48964,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48990,7 +48990,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49016,7 +49016,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49042,7 +49042,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49068,7 +49068,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49094,7 +49094,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49120,7 +49120,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49146,7 +49146,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49172,7 +49172,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49198,7 +49198,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49224,7 +49224,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49250,7 +49250,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49276,7 +49276,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49302,7 +49302,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49328,7 +49328,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49354,7 +49354,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49380,7 +49380,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49406,7 +49406,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49432,7 +49432,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49458,7 +49458,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49484,7 +49484,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49510,7 +49510,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49536,7 +49536,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49562,7 +49562,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49588,7 +49588,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49614,7 +49614,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49640,7 +49640,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49666,7 +49666,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49692,7 +49692,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49718,7 +49718,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49744,7 +49744,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49770,7 +49770,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49796,7 +49796,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49822,7 +49822,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49848,7 +49848,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49874,7 +49874,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49900,7 +49900,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49926,7 +49926,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49952,7 +49952,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49978,7 +49978,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50004,7 +50004,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50030,7 +50030,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50056,7 +50056,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50082,7 +50082,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50108,7 +50108,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50134,7 +50134,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50160,7 +50160,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50186,7 +50186,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50212,7 +50212,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50238,7 +50238,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50264,7 +50264,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50290,7 +50290,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50316,7 +50316,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50342,7 +50342,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50368,7 +50368,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50394,7 +50394,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50420,7 +50420,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50446,7 +50446,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50472,7 +50472,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50498,7 +50498,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50524,7 +50524,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50550,7 +50550,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50576,7 +50576,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50602,7 +50602,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50628,7 +50628,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50654,7 +50654,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50680,7 +50680,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50706,7 +50706,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50732,7 +50732,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50758,7 +50758,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50784,7 +50784,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50810,7 +50810,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50836,7 +50836,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50862,7 +50862,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50888,7 +50888,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50914,7 +50914,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50940,7 +50940,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50966,7 +50966,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -50992,7 +50992,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51018,7 +51018,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51044,7 +51044,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51070,7 +51070,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51096,7 +51096,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51122,7 +51122,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51148,7 +51148,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51174,7 +51174,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51200,7 +51200,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51278,7 +51278,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51304,7 +51304,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51330,7 +51330,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51356,7 +51356,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51434,7 +51434,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51538,7 +51538,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51616,7 +51616,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51642,7 +51642,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51668,7 +51668,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51746,7 +51746,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51824,7 +51824,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51850,7 +51850,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51876,7 +51876,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51902,7 +51902,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51980,7 +51980,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52006,7 +52006,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52058,7 +52058,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52136,7 +52136,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52214,7 +52214,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52240,7 +52240,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52292,7 +52292,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52344,7 +52344,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52474,7 +52474,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52500,7 +52500,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54528,7 +54528,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54554,7 +54554,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57076,7 +57076,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57154,7 +57154,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58142,7 +58142,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -67120,7 +67120,7 @@
     </row>
     <row r="2510">
       <c r="A2510" s="1" t="n">
-        <v>45973.3335763889</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2510" t="n">
         <v>20000</v>
@@ -67141,6 +67141,32 @@
         <v>508</v>
       </c>
       <c r="H2510" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2511">
+      <c r="A2511" s="1" t="n">
+        <v>45974.6784027778</v>
+      </c>
+      <c r="B2511" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C2511" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2511" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="E2511" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="F2511" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2511" t="s">
+        <v>508</v>
+      </c>
+      <c r="H2511" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="512" uniqueCount="512">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -62,10 +62,10 @@
     <t xml:space="preserve">0.211099088191986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921487927437</t>
+    <t xml:space="preserve">0.228921473026276</t>
   </si>
   <si>
     <t xml:space="preserve">0.227071776986122</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">0.229762226343155</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598274230957</t>
+    <t xml:space="preserve">0.239598244428635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310569405556</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
@@ -98,16 +98,16 @@
     <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014956235886</t>
+    <t xml:space="preserve">0.211014941334724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
     <t xml:space="preserve">0.201767161488533</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563573718071</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
     <t xml:space="preserve">0.193360030651093</t>
@@ -116,19 +116,19 @@
     <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722880005836</t>
+    <t xml:space="preserve">0.196722865104675</t>
   </si>
   <si>
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607855200768</t>
+    <t xml:space="preserve">0.202607870101929</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187091112137</t>
   </si>
   <si>
-    <t xml:space="preserve">0.2052141726017</t>
+    <t xml:space="preserve">0.205214157700539</t>
   </si>
   <si>
     <t xml:space="preserve">0.208912774920464</t>
@@ -149,7 +149,7 @@
     <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235395073891</t>
+    <t xml:space="preserve">0.236235424876213</t>
   </si>
   <si>
     <t xml:space="preserve">0.241279691457748</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">0.252208918333054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093953132629</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836547613144</t>
+    <t xml:space="preserve">0.285836517810822</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
@@ -206,10 +206,10 @@
     <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378313809633255</t>
+    <t xml:space="preserve">0.378313779830933</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
@@ -218,13 +218,13 @@
     <t xml:space="preserve">0.440525561571121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684838056564</t>
+    <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
     <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400881290436</t>
+    <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
     <t xml:space="preserve">0.501055836677551</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">0.4960116147995</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496515661478043</t>
+    <t xml:space="preserve">0.496515721082687</t>
   </si>
   <si>
     <t xml:space="preserve">0.492307841777802</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">0.715319275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241674900055</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641051530838</t>
+    <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
     <t xml:space="preserve">0.61854076385498</t>
@@ -269,34 +269,34 @@
     <t xml:space="preserve">0.572255373001099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525970041751862</t>
+    <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762192249298</t>
+    <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
     <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931151866913</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509139060974121</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892410993576</t>
+    <t xml:space="preserve">0.483892381191254</t>
   </si>
   <si>
     <t xml:space="preserve">0.513346672058105</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177772045135</t>
+    <t xml:space="preserve">0.53017783164978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554521560669</t>
+    <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
     <t xml:space="preserve">0.471269071102142</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853640317917</t>
+    <t xml:space="preserve">0.462853670120239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684710502625</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
@@ -320,34 +320,34 @@
     <t xml:space="preserve">0.437607079744339</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454438090324402</t>
+    <t xml:space="preserve">0.454438120126724</t>
   </si>
   <si>
-    <t xml:space="preserve">0.45023038983345</t>
+    <t xml:space="preserve">0.450230330228806</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645880222321</t>
+    <t xml:space="preserve">0.458645850419998</t>
   </si>
   <si>
     <t xml:space="preserve">0.403944969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776009559631</t>
+    <t xml:space="preserve">0.420776039361954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191529750824</t>
+    <t xml:space="preserve">0.429191499948502</t>
   </si>
   <si>
     <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542801022529602</t>
+    <t xml:space="preserve">0.542801082134247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476920604706</t>
   </si>
   <si>
     <t xml:space="preserve">0.410677373409271</t>
@@ -362,13 +362,13 @@
     <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
-    <t xml:space="preserve">0.414043605327606</t>
+    <t xml:space="preserve">0.414043575525284</t>
   </si>
   <si>
     <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726721286774</t>
   </si>
   <si>
     <t xml:space="preserve">0.441814810037613</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163246870041</t>
+    <t xml:space="preserve">0.392163217067719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895651102066</t>
+    <t xml:space="preserve">0.398895680904388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578767061234</t>
+    <t xml:space="preserve">0.400578796863556</t>
   </si>
   <si>
     <t xml:space="preserve">0.393846333026886</t>
@@ -404,31 +404,31 @@
     <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113928794861</t>
+    <t xml:space="preserve">0.387113958597183</t>
   </si>
   <si>
     <t xml:space="preserve">0.373649060726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
     <t xml:space="preserve">0.31137427687645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620837450027</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
     <t xml:space="preserve">0.32988840341568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32820525765419</t>
+    <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
     <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3248390853405</t>
+    <t xml:space="preserve">0.324839055538177</t>
   </si>
   <si>
     <t xml:space="preserve">0.35345184803009</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
@@ -470,7 +470,7 @@
     <t xml:space="preserve">0.366916686296463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35850116610527</t>
+    <t xml:space="preserve">0.358501136302948</t>
   </si>
   <si>
     <t xml:space="preserve">0.368599772453308</t>
@@ -479,22 +479,22 @@
     <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480130910873</t>
+    <t xml:space="preserve">0.390480101108551</t>
   </si>
   <si>
-    <t xml:space="preserve">0.397212564945221</t>
+    <t xml:space="preserve">0.397212535142899</t>
   </si>
   <si>
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797014951706</t>
+    <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698438405991</t>
+    <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064610719681</t>
+    <t xml:space="preserve">0.382064640522003</t>
   </si>
   <si>
     <t xml:space="preserve">0.375332206487656</t>
@@ -512,7 +512,7 @@
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233540534973</t>
+    <t xml:space="preserve">0.365233570337296</t>
   </si>
   <si>
     <t xml:space="preserve">0.538593232631683</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733939170837</t>
+    <t xml:space="preserve">0.484733998775482</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476318359375</t>
+    <t xml:space="preserve">0.476318418979645</t>
   </si>
   <si>
     <t xml:space="preserve">0.494832545518875</t>
@@ -539,19 +539,19 @@
     <t xml:space="preserve">0.491466403007507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49819877743721</t>
+    <t xml:space="preserve">0.498198837041855</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494715690613</t>
+    <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811540126801</t>
+    <t xml:space="preserve">0.526811480522156</t>
   </si>
   <si>
     <t xml:space="preserve">0.536910235881805</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661438703537</t>
+    <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663556098938</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501565039157867</t>
+    <t xml:space="preserve">0.501564979553223</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149518966675</t>
+    <t xml:space="preserve">0.49314945936203</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473620891571</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
@@ -599,13 +599,13 @@
     <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550375044345856</t>
+    <t xml:space="preserve">0.550374984741211</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396019935608</t>
+    <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
     <t xml:space="preserve">0.516712963581085</t>
@@ -620,7 +620,7 @@
     <t xml:space="preserve">0.530068099498749</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281896591187</t>
+    <t xml:space="preserve">0.535281956195831</t>
   </si>
   <si>
     <t xml:space="preserve">0.526592314243317</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709550380707</t>
+    <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
     <t xml:space="preserve">0.552661180496216</t>
@@ -638,25 +638,25 @@
     <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447443008423</t>
+    <t xml:space="preserve">0.547447502613068</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971478939056</t>
   </si>
   <si>
     <t xml:space="preserve">0.542233645915985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538757741451263</t>
+    <t xml:space="preserve">0.538757801055908</t>
   </si>
   <si>
     <t xml:space="preserve">0.540495693683624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568302571773529</t>
+    <t xml:space="preserve">0.568302512168884</t>
   </si>
   <si>
     <t xml:space="preserve">0.559612929821014</t>
@@ -665,13 +665,13 @@
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378517150879</t>
+    <t xml:space="preserve">0.521378457546234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.512688815593719</t>
+    <t xml:space="preserve">0.512688875198364</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51442676782608</t>
+    <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
     <t xml:space="preserve">0.502261281013489</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833627223969</t>
+    <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
     <t xml:space="preserve">0.493571668863297</t>
@@ -689,13 +689,13 @@
     <t xml:space="preserve">0.524854302406311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52311646938324</t>
+    <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
     <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274877071381</t>
+    <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419748306274</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">0.599585235118866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895652770996</t>
+    <t xml:space="preserve">0.590895593166351</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.585681855678558</t>
+    <t xml:space="preserve">0.585681915283203</t>
   </si>
   <si>
     <t xml:space="preserve">0.58915764093399</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364537715912</t>
+    <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
     <t xml:space="preserve">0.603061079978943</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392113208771</t>
+    <t xml:space="preserve">0.627392172813416</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
     <t xml:space="preserve">0.620440423488617</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819707393646</t>
+    <t xml:space="preserve">0.637819647789001</t>
   </si>
   <si>
     <t xml:space="preserve">0.643033504486084</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">0.592633605003357</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">0.649985194206238</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247301578522</t>
+    <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
     <t xml:space="preserve">0.636081695556641</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">0.683005750179291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957559108734</t>
+    <t xml:space="preserve">0.689957499504089</t>
   </si>
   <si>
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743702411652</t>
+    <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
     <t xml:space="preserve">0.662150800228119</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">0.656936824321747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674776554108</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
     <t xml:space="preserve">0.646509349346161</t>
@@ -845,28 +845,28 @@
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226686000824</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613488674163818</t>
+    <t xml:space="preserve">0.613488614559174</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634617745876312</t>
+    <t xml:space="preserve">0.634617686271667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64178854227066</t>
+    <t xml:space="preserve">0.641788601875305</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410355567932</t>
+    <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632824957370758</t>
+    <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239618778229</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
     <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690635681152</t>
+    <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
     <t xml:space="preserve">0.618483364582062</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
-    <t xml:space="preserve">0.579043924808502</t>
+    <t xml:space="preserve">0.579043865203857</t>
   </si>
   <si>
     <t xml:space="preserve">0.559324085712433</t>
@@ -941,7 +941,7 @@
     <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
-    <t xml:space="preserve">0.586214661598206</t>
+    <t xml:space="preserve">0.58621472120285</t>
   </si>
   <si>
     <t xml:space="preserve">0.598763585090637</t>
@@ -950,7 +950,7 @@
     <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945899009705</t>
+    <t xml:space="preserve">0.553945958614349</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752127170563</t>
+    <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.654337525367737</t>
@@ -1016,13 +1016,13 @@
     <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645374000072479</t>
+    <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544796466827</t>
   </si>
   <si>
     <t xml:space="preserve">0.64358127117157</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264456748962</t>
+    <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191507339478</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765388011932</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143515110016</t>
+    <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
@@ -1109,10 +1109,10 @@
     <t xml:space="preserve">0.709911346435547</t>
   </si>
   <si>
-    <t xml:space="preserve">0.688398838043213</t>
+    <t xml:space="preserve">0.688398897647858</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642583847046</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
     <t xml:space="preserve">0.675849914550781</t>
@@ -1549,6 +1549,9 @@
   <si>
     <t xml:space="preserve">0.554000020027161</t>
   </si>
+  <si>
+    <t xml:space="preserve">0.550000011920929</t>
+  </si>
 </sst>
 </file>
 
@@ -67146,7 +67149,7 @@
     </row>
     <row r="2511">
       <c r="A2511" s="1" t="n">
-        <v>45974.6784027778</v>
+        <v>45974.3333333333</v>
       </c>
       <c r="B2511" t="n">
         <v>10000</v>
@@ -67167,6 +67170,32 @@
         <v>508</v>
       </c>
       <c r="H2511" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2512">
+      <c r="A2512" s="1" t="n">
+        <v>45975.5856597222</v>
+      </c>
+      <c r="B2512" t="n">
+        <v>11250</v>
+      </c>
+      <c r="C2512" t="n">
+        <v>0.561999976634979</v>
+      </c>
+      <c r="D2512" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E2512" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="F2512" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="G2512" t="s">
+        <v>512</v>
+      </c>
+      <c r="H2512" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="513" uniqueCount="513">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,34 +38,34 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815465450287</t>
+    <t xml:space="preserve">0.23581551015377</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394731163979</t>
+    <t xml:space="preserve">0.235394701361656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249102830887</t>
+    <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
     <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581333756447</t>
+    <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210174232721329</t>
+    <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
     <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921487927437</t>
+    <t xml:space="preserve">0.228921517729759</t>
   </si>
   <si>
     <t xml:space="preserve">0.227071791887283</t>
@@ -86,34 +86,34 @@
     <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310569405556</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868219017982</t>
+    <t xml:space="preserve">0.222868233919144</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784876823425</t>
+    <t xml:space="preserve">0.222784906625748</t>
   </si>
   <si>
     <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014971137047</t>
+    <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
     <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563588619232</t>
+    <t xml:space="preserve">0.197563603520393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360030651093</t>
+    <t xml:space="preserve">0.193360045552254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612530827522</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
@@ -122,43 +122,43 @@
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607855200768</t>
+    <t xml:space="preserve">0.202607870101929</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214157700539</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912745118141</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762500762939</t>
+    <t xml:space="preserve">0.210762515664101</t>
   </si>
   <si>
     <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22698763012886</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031881809235</t>
+    <t xml:space="preserve">0.232031852006912</t>
   </si>
   <si>
     <t xml:space="preserve">0.236235424876213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24127970635891</t>
+    <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483219623566</t>
+    <t xml:space="preserve">0.245483234524727</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208918333054</t>
+    <t xml:space="preserve">0.252208948135376</t>
   </si>
   <si>
     <t xml:space="preserve">0.258093893527985</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182396888733</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
     <t xml:space="preserve">0.273226678371429</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">0.292562156915665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447132110596</t>
+    <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332137107849</t>
+    <t xml:space="preserve">0.304332166910172</t>
   </si>
   <si>
     <t xml:space="preserve">0.311057806015015</t>
@@ -200,49 +200,49 @@
     <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455355882645</t>
+    <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36318102478981</t>
+    <t xml:space="preserve">0.363181054592133</t>
   </si>
   <si>
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420348465442657</t>
+    <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525561571121</t>
+    <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
     <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471743822098</t>
+    <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
     <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055896282196</t>
+    <t xml:space="preserve">0.501055836677551</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011644601822</t>
+    <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
     <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307901382446</t>
+    <t xml:space="preserve">0.492307871580124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670952796936</t>
+    <t xml:space="preserve">0.580670833587646</t>
   </si>
   <si>
     <t xml:space="preserve">0.589086413383484</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67324161529541</t>
+    <t xml:space="preserve">0.673241555690765</t>
   </si>
   <si>
     <t xml:space="preserve">0.65641051530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61854076385498</t>
+    <t xml:space="preserve">0.618540704250336</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274843454361</t>
+    <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255432605743</t>
+    <t xml:space="preserve">0.572255313396454</t>
   </si>
   <si>
     <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762311458588</t>
+    <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100171089172</t>
+    <t xml:space="preserve">0.48810014128685</t>
   </si>
   <si>
     <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008752822876</t>
+    <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
     <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892381191254</t>
+    <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
     <t xml:space="preserve">0.51334673166275</t>
@@ -299,43 +299,43 @@
     <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269100904465</t>
+    <t xml:space="preserve">0.471269130706787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061430215836</t>
+    <t xml:space="preserve">0.467061340808868</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853610515594</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684621095657</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607079744339</t>
+    <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454438120126724</t>
+    <t xml:space="preserve">0.454438060522079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230330228806</t>
+    <t xml:space="preserve">0.450230300426483</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645850419998</t>
+    <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
     <t xml:space="preserve">0.403944939374924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776009559631</t>
+    <t xml:space="preserve">0.420775979757309</t>
   </si>
   <si>
     <t xml:space="preserve">0.429191529750824</t>
@@ -347,16 +347,16 @@
     <t xml:space="preserve">0.542801082134247</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677343606949</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983769655228</t>
+    <t xml:space="preserve">0.424983739852905</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409807443619</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
     <t xml:space="preserve">0.380381524562836</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360459566116</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814750432968</t>
+    <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
     <t xml:space="preserve">0.419092923402786</t>
@@ -383,73 +383,73 @@
     <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311201095581</t>
+    <t xml:space="preserve">0.407311141490936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163187265396</t>
+    <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895680904388</t>
+    <t xml:space="preserve">0.398895621299744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578796863556</t>
+    <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
     <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261853218079</t>
+    <t xml:space="preserve">0.402261823415756</t>
   </si>
   <si>
     <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113958597183</t>
+    <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649060726166</t>
+    <t xml:space="preserve">0.373649120330811</t>
   </si>
   <si>
     <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374217271805</t>
+    <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620807647705</t>
+    <t xml:space="preserve">0.336620777845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888373613358</t>
+    <t xml:space="preserve">0.32988840341568</t>
   </si>
   <si>
     <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522201299667</t>
+    <t xml:space="preserve">0.32652223110199</t>
   </si>
   <si>
     <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35345184803009</t>
+    <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184282064438</t>
+    <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036327838898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350085616111755</t>
+    <t xml:space="preserve">0.3500856757164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830389380455</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.331571459770203</t>
+    <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
     <t xml:space="preserve">0.34335321187973</t>
@@ -464,7 +464,7 @@
     <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33998703956604</t>
+    <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599772453308</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550513982773</t>
+    <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480130910873</t>
+    <t xml:space="preserve">0.390480101108551</t>
   </si>
   <si>
     <t xml:space="preserve">0.397212564945221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.383747696876526</t>
+    <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
     <t xml:space="preserve">0.388797044754028</t>
@@ -494,22 +494,22 @@
     <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064640522003</t>
+    <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332236289978</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282858610153</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015322446823</t>
+    <t xml:space="preserve">0.377015352249146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371965974569321</t>
+    <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
-    <t xml:space="preserve">0.385430812835693</t>
+    <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
     <t xml:space="preserve">0.365233540534973</t>
@@ -521,28 +521,28 @@
     <t xml:space="preserve">0.559632182121277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216602325439</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733939170837</t>
+    <t xml:space="preserve">0.48473396897316</t>
   </si>
   <si>
-    <t xml:space="preserve">0.476318448781967</t>
+    <t xml:space="preserve">0.476318418979645</t>
   </si>
   <si>
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466343402863</t>
+    <t xml:space="preserve">0.491466403007507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198837041855</t>
+    <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741276264191</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494656085968</t>
@@ -551,19 +551,19 @@
     <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811540126801</t>
+    <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
     <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525128483772278</t>
+    <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523445308208466</t>
+    <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506614327430725</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
@@ -575,43 +575,43 @@
     <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501564979553223</t>
+    <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.493149518966675</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509980499744415</t>
+    <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
     <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53354400396347</t>
+    <t xml:space="preserve">0.533544063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473740100861</t>
   </si>
   <si>
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107448577881</t>
+    <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374925136566</t>
+    <t xml:space="preserve">0.5503751039505</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396079540253</t>
+    <t xml:space="preserve">0.518396019935608</t>
   </si>
   <si>
     <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019729614258</t>
+    <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
     <t xml:space="preserve">0.53180605173111</t>
@@ -623,19 +623,19 @@
     <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592314243317</t>
+    <t xml:space="preserve">0.526592254638672</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330147266388</t>
+    <t xml:space="preserve">0.528330206871033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709550380707</t>
+    <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
     <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185335636139</t>
+    <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
     <t xml:space="preserve">0.547447443008423</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971598148346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542233645915985</t>
+    <t xml:space="preserve">0.54223358631134</t>
   </si>
   <si>
     <t xml:space="preserve">0.538757741451263</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378517150879</t>
+    <t xml:space="preserve">0.521378576755524</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
@@ -674,16 +674,16 @@
     <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503999173641205</t>
+    <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571668863297</t>
+    <t xml:space="preserve">0.493571698665619</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274877071381</t>
+    <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419748306274</t>
+    <t xml:space="preserve">0.587419807910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323187351227</t>
+    <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
     <t xml:space="preserve">0.599585294723511</t>
@@ -710,28 +710,28 @@
     <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594371557235718</t>
+    <t xml:space="preserve">0.594371497631073</t>
   </si>
   <si>
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58915764093399</t>
+    <t xml:space="preserve">0.589157700538635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557659626007</t>
+    <t xml:space="preserve">0.639557540416718</t>
   </si>
   <si>
     <t xml:space="preserve">0.669102430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288592338562</t>
+    <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364478111267</t>
+    <t xml:space="preserve">0.667364418506622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061079978943</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65346097946167</t>
+    <t xml:space="preserve">0.653461039066315</t>
   </si>
   <si>
     <t xml:space="preserve">0.6447713971138</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620440423488617</t>
+    <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819707393646</t>
+    <t xml:space="preserve">0.637819647789001</t>
   </si>
   <si>
     <t xml:space="preserve">0.643033444881439</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943843841553</t>
+    <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
     <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778416633606</t>
+    <t xml:space="preserve">0.571778476238251</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50573718547821</t>
+    <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557874977588654</t>
+    <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516368865967</t>
+    <t xml:space="preserve">0.573516428470612</t>
   </si>
   <si>
     <t xml:space="preserve">0.596109390258789</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343862533569</t>
+    <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985134601593</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247241973877</t>
@@ -815,37 +815,37 @@
     <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005750179291</t>
+    <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957559108734</t>
+    <t xml:space="preserve">0.689957499504089</t>
   </si>
   <si>
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743702411652</t>
+    <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150740623474</t>
+    <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316227436066</t>
+    <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936824321747</t>
+    <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674776554108</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509408950806</t>
+    <t xml:space="preserve">0.646509289741516</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226686000824</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410355567932</t>
+    <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632824957370758</t>
+    <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629239618778229</t>
+    <t xml:space="preserve">0.629239559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276033878326</t>
+    <t xml:space="preserve">0.620276093482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592788696289</t>
+    <t xml:space="preserve">0.591592848300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -890,10 +890,10 @@
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6238614320755</t>
+    <t xml:space="preserve">0.623861491680145</t>
   </si>
   <si>
     <t xml:space="preserve">0.616690635681152</t>
@@ -905,19 +905,19 @@
     <t xml:space="preserve">0.604141712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588007390499115</t>
+    <t xml:space="preserve">0.58800733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58980005979538</t>
+    <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385457992554</t>
+    <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573665738105774</t>
+    <t xml:space="preserve">0.573665678501129</t>
   </si>
   <si>
     <t xml:space="preserve">0.580836534500122</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324085712433</t>
+    <t xml:space="preserve">0.559324026107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552153289318085</t>
+    <t xml:space="preserve">0.55215322971344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873068809509</t>
+    <t xml:space="preserve">0.571873009204865</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -947,10 +947,10 @@
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178127288818</t>
+    <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
     <t xml:space="preserve">0.613105237483978</t>
@@ -959,7 +959,7 @@
     <t xml:space="preserve">0.611312508583069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605934381484985</t>
+    <t xml:space="preserve">0.60593444108963</t>
   </si>
   <si>
     <t xml:space="preserve">0.548567831516266</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945899009705</t>
+    <t xml:space="preserve">0.553945958614349</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
@@ -995,46 +995,46 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752127170563</t>
+    <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337525367737</t>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057185649872</t>
+    <t xml:space="preserve">0.674057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66150826215744</t>
+    <t xml:space="preserve">0.661508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093660354614</t>
+    <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645374000072479</t>
+    <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
     <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64358127117157</t>
+    <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
     <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264456748962</t>
+    <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191626548767</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1052,37 +1052,37 @@
     <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594591617584</t>
+    <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
     <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711704075336456</t>
+    <t xml:space="preserve">0.711704015731812</t>
   </si>
   <si>
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009133815765</t>
+    <t xml:space="preserve">0.735009253025055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460329532623</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765507221222</t>
   </si>
   <si>
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143515110016</t>
+    <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708118677139282</t>
+    <t xml:space="preserve">0.708118617534637</t>
   </si>
   <si>
     <t xml:space="preserve">0.704533219337463</t>
@@ -1091,13 +1091,13 @@
     <t xml:space="preserve">0.713496744632721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700947821140289</t>
+    <t xml:space="preserve">0.700947761535645</t>
   </si>
   <si>
     <t xml:space="preserve">0.706325948238373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697362422943115</t>
+    <t xml:space="preserve">0.69736236333847</t>
   </si>
   <si>
     <t xml:space="preserve">0.71708220243454</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642583847046</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849914550781</t>
+    <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
     <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045727729797</t>
+    <t xml:space="preserve">0.726045668125153</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1139,28 +1139,25 @@
     <t xml:space="preserve">0.665459334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659898400306702</t>
+    <t xml:space="preserve">0.659898459911346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650630235671997</t>
+    <t xml:space="preserve">0.650630176067352</t>
   </si>
   <si>
     <t xml:space="preserve">0.658044755458832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652483880519867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.652483820915222</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.663605690002441</t>
+    <t xml:space="preserve">0.663605749607086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646922945976257</t>
+    <t xml:space="preserve">0.646922886371613</t>
   </si>
   <si>
     <t xml:space="preserve">0.645069241523743</t>
@@ -1181,7 +1178,7 @@
     <t xml:space="preserve">0.643215596675873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635801017284393</t>
+    <t xml:space="preserve">0.635800957679749</t>
   </si>
   <si>
     <t xml:space="preserve">0.633947372436523</t>
@@ -1196,7 +1193,7 @@
     <t xml:space="preserve">0.62097179889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626532733440399</t>
+    <t xml:space="preserve">0.626532793045044</t>
   </si>
   <si>
     <t xml:space="preserve">0.613557279109955</t>
@@ -1208,7 +1205,7 @@
     <t xml:space="preserve">0.572776973247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583898842334747</t>
+    <t xml:space="preserve">0.583898901939392</t>
   </si>
   <si>
     <t xml:space="preserve">0.578337907791138</t>
@@ -1220,16 +1217,16 @@
     <t xml:space="preserve">0.602435350418091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604289054870605</t>
+    <t xml:space="preserve">0.604288995265961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593167126178741</t>
+    <t xml:space="preserve">0.593167066574097</t>
   </si>
   <si>
     <t xml:space="preserve">0.600581705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595020771026611</t>
+    <t xml:space="preserve">0.595020830631256</t>
   </si>
   <si>
     <t xml:space="preserve">0.589459776878357</t>
@@ -1247,7 +1244,7 @@
     <t xml:space="preserve">0.557947814464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541264951229095</t>
+    <t xml:space="preserve">0.54126501083374</t>
   </si>
   <si>
     <t xml:space="preserve">0.546825885772705</t>
@@ -1262,10 +1259,10 @@
     <t xml:space="preserve">0.563508749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570923388004303</t>
+    <t xml:space="preserve">0.570923328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61726450920105</t>
+    <t xml:space="preserve">0.617264568805695</t>
   </si>
   <si>
     <t xml:space="preserve">0.624679148197174</t>
@@ -51206,7 +51203,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51232,7 +51229,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51258,7 +51255,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51388,7 +51385,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51414,7 +51411,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51466,7 +51463,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51492,7 +51489,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51518,7 +51515,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51570,7 +51567,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51596,7 +51593,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51700,7 +51697,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51726,7 +51723,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51778,7 +51775,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51804,7 +51801,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51856,7 +51853,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51934,7 +51931,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51960,7 +51957,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52038,7 +52035,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52064,7 +52061,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52090,7 +52087,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52116,7 +52113,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52142,7 +52139,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52168,7 +52165,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52194,7 +52191,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52272,7 +52269,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52298,7 +52295,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52324,7 +52321,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52376,7 +52373,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52402,7 +52399,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52428,7 +52425,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52454,7 +52451,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52532,7 +52529,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52558,7 +52555,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52584,7 +52581,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52610,7 +52607,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52636,7 +52633,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52662,7 +52659,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52688,7 +52685,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52714,7 +52711,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52740,7 +52737,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52766,7 +52763,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52792,7 +52789,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52818,7 +52815,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52844,7 +52841,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52870,7 +52867,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52896,7 +52893,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52922,7 +52919,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52948,7 +52945,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52974,7 +52971,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53000,7 +52997,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53026,7 +53023,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53052,7 +53049,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53078,7 +53075,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53104,7 +53101,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53130,7 +53127,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53156,7 +53153,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53182,7 +53179,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53208,7 +53205,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53234,7 +53231,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53260,7 +53257,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53286,7 +53283,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53312,7 +53309,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53338,7 +53335,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53364,7 +53361,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53390,7 +53387,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53416,7 +53413,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53442,7 +53439,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53468,7 +53465,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53494,7 +53491,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53520,7 +53517,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53546,7 +53543,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53572,7 +53569,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53598,7 +53595,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53624,7 +53621,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53650,7 +53647,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53676,7 +53673,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53702,7 +53699,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53728,7 +53725,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53754,7 +53751,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53780,7 +53777,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53806,7 +53803,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53832,7 +53829,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53858,7 +53855,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53884,7 +53881,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53910,7 +53907,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53936,7 +53933,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53962,7 +53959,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53988,7 +53985,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54014,7 +54011,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54040,7 +54037,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54066,7 +54063,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54092,7 +54089,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54118,7 +54115,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54144,7 +54141,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54170,7 +54167,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54196,7 +54193,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54222,7 +54219,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54248,7 +54245,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54274,7 +54271,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54300,7 +54297,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54326,7 +54323,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54352,7 +54349,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54378,7 +54375,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54404,7 +54401,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54430,7 +54427,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54456,7 +54453,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54482,7 +54479,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54508,7 +54505,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54586,7 +54583,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54612,7 +54609,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54638,7 +54635,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54664,7 +54661,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54690,7 +54687,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54716,7 +54713,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54742,7 +54739,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54768,7 +54765,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54794,7 +54791,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54820,7 +54817,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54846,7 +54843,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54872,7 +54869,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54898,7 +54895,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54924,7 +54921,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54950,7 +54947,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54976,7 +54973,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55002,7 +54999,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55028,7 +55025,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55054,7 +55051,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55080,7 +55077,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55106,7 +55103,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55132,7 +55129,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55158,7 +55155,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55184,7 +55181,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55210,7 +55207,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55236,7 +55233,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55262,7 +55259,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55288,7 +55285,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55314,7 +55311,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55340,7 +55337,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55366,7 +55363,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55392,7 +55389,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55418,7 +55415,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55444,7 +55441,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55470,7 +55467,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55496,7 +55493,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55522,7 +55519,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55548,7 +55545,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55574,7 +55571,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55600,7 +55597,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55626,7 +55623,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55652,7 +55649,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55678,7 +55675,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55704,7 +55701,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55730,7 +55727,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55756,7 +55753,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55782,7 +55779,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55808,7 +55805,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55834,7 +55831,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55860,7 +55857,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55886,7 +55883,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55912,7 +55909,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55938,7 +55935,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55964,7 +55961,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55990,7 +55987,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56016,7 +56013,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56042,7 +56039,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56068,7 +56065,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56094,7 +56091,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56120,7 +56117,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56146,7 +56143,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56172,7 +56169,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56198,7 +56195,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56224,7 +56221,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56250,7 +56247,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56276,7 +56273,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56302,7 +56299,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56328,7 +56325,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56354,7 +56351,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56380,7 +56377,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56406,7 +56403,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56432,7 +56429,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56458,7 +56455,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56484,7 +56481,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56510,7 +56507,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56536,7 +56533,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56562,7 +56559,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56588,7 +56585,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56614,7 +56611,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56640,7 +56637,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56666,7 +56663,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56692,7 +56689,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56718,7 +56715,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56744,7 +56741,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56770,7 +56767,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56796,7 +56793,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56822,7 +56819,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56848,7 +56845,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56874,7 +56871,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56900,7 +56897,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56926,7 +56923,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56952,7 +56949,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56978,7 +56975,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57004,7 +57001,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57030,7 +57027,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57056,7 +57053,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57108,7 +57105,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57134,7 +57131,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57186,7 +57183,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57212,7 +57209,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57238,7 +57235,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57264,7 +57261,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57290,7 +57287,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57316,7 +57313,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57342,7 +57339,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57368,7 +57365,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57394,7 +57391,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57420,7 +57417,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57446,7 +57443,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57472,7 +57469,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57498,7 +57495,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57524,7 +57521,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57550,7 +57547,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57576,7 +57573,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57602,7 +57599,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57628,7 +57625,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57654,7 +57651,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57680,7 +57677,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57706,7 +57703,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57732,7 +57729,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57758,7 +57755,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57784,7 +57781,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57810,7 +57807,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57836,7 +57833,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57862,7 +57859,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57888,7 +57885,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57914,7 +57911,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57940,7 +57937,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57966,7 +57963,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57992,7 +57989,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58018,7 +58015,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58044,7 +58041,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58070,7 +58067,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58096,7 +58093,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58122,7 +58119,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58174,7 +58171,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58200,7 +58197,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58226,7 +58223,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58252,7 +58249,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58278,7 +58275,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58304,7 +58301,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58330,7 +58327,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58356,7 +58353,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58382,7 +58379,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58408,7 +58405,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58434,7 +58431,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58460,7 +58457,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58486,7 +58483,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58512,7 +58509,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58538,7 +58535,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58564,7 +58561,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58590,7 +58587,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58616,7 +58613,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58642,7 +58639,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58668,7 +58665,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58694,7 +58691,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58720,7 +58717,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58746,7 +58743,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58772,7 +58769,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58798,7 +58795,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58824,7 +58821,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58850,7 +58847,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58876,7 +58873,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58902,7 +58899,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58928,7 +58925,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58954,7 +58951,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58980,7 +58977,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59006,7 +59003,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59032,7 +59029,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59058,7 +59055,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59084,7 +59081,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59110,7 +59107,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59136,7 +59133,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59162,7 +59159,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59188,7 +59185,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59214,7 +59211,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59240,7 +59237,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59266,7 +59263,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59292,7 +59289,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59318,7 +59315,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59344,7 +59341,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59370,7 +59367,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59396,7 +59393,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59422,7 +59419,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59448,7 +59445,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59474,7 +59471,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59500,7 +59497,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59526,7 +59523,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59552,7 +59549,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59578,7 +59575,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59604,7 +59601,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59630,7 +59627,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59656,7 +59653,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59682,7 +59679,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59708,7 +59705,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59734,7 +59731,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59760,7 +59757,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59786,7 +59783,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59812,7 +59809,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59838,7 +59835,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59864,7 +59861,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59890,7 +59887,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59916,7 +59913,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59942,7 +59939,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59968,7 +59965,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59994,7 +59991,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60020,7 +60017,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60046,7 +60043,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60072,7 +60069,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60098,7 +60095,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60124,7 +60121,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60150,7 +60147,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60176,7 +60173,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60202,7 +60199,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60228,7 +60225,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60254,7 +60251,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60280,7 +60277,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60306,7 +60303,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60332,7 +60329,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60358,7 +60355,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60384,7 +60381,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60410,7 +60407,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60436,7 +60433,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60462,7 +60459,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60488,7 +60485,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60514,7 +60511,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60540,7 +60537,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60566,7 +60563,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60592,7 +60589,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60618,7 +60615,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60644,7 +60641,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60670,7 +60667,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60696,7 +60693,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60722,7 +60719,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60748,7 +60745,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60774,7 +60771,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60800,7 +60797,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60826,7 +60823,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60852,7 +60849,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60878,7 +60875,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60904,7 +60901,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60930,7 +60927,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60956,7 +60953,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60982,7 +60979,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61008,7 +61005,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61034,7 +61031,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61060,7 +61057,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61086,7 +61083,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61112,7 +61109,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61138,7 +61135,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61164,7 +61161,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61190,7 +61187,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61216,7 +61213,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61242,7 +61239,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61268,7 +61265,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61294,7 +61291,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61320,7 +61317,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61346,7 +61343,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61372,7 +61369,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61398,7 +61395,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61424,7 +61421,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61450,7 +61447,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61476,7 +61473,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61502,7 +61499,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61528,7 +61525,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61554,7 +61551,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61580,7 +61577,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61606,7 +61603,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61632,7 +61629,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61658,7 +61655,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61684,7 +61681,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61710,7 +61707,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61736,7 +61733,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61762,7 +61759,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61788,7 +61785,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61814,7 +61811,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61840,7 +61837,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61866,7 +61863,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61892,7 +61889,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61918,7 +61915,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61944,7 +61941,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61970,7 +61967,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61996,7 +61993,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62022,7 +62019,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62048,7 +62045,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62074,7 +62071,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62100,7 +62097,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62126,7 +62123,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62152,7 +62149,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62178,7 +62175,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62204,7 +62201,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62230,7 +62227,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62256,7 +62253,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62282,7 +62279,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62308,7 +62305,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62334,7 +62331,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62360,7 +62357,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62386,7 +62383,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62412,7 +62409,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62438,7 +62435,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62464,7 +62461,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62490,7 +62487,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62516,7 +62513,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62542,7 +62539,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62568,7 +62565,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62594,7 +62591,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62620,7 +62617,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62646,7 +62643,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62672,7 +62669,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62698,7 +62695,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62724,7 +62721,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62750,7 +62747,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62776,7 +62773,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62802,7 +62799,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62828,7 +62825,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62854,7 +62851,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62880,7 +62877,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62906,7 +62903,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62932,7 +62929,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62958,7 +62955,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62984,7 +62981,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63010,7 +63007,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63036,7 +63033,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63062,7 +63059,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63088,7 +63085,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63114,7 +63111,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63140,7 +63137,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63166,7 +63163,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63192,7 +63189,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63218,7 +63215,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63244,7 +63241,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63270,7 +63267,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63296,7 +63293,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63322,7 +63319,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63348,7 +63345,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63374,7 +63371,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63400,7 +63397,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63426,7 +63423,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63452,7 +63449,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63478,7 +63475,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63504,7 +63501,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63530,7 +63527,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63556,7 +63553,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63582,7 +63579,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63608,7 +63605,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63634,7 +63631,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63660,7 +63657,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63686,7 +63683,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63712,7 +63709,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63738,7 +63735,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63764,7 +63761,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63790,7 +63787,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63816,7 +63813,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63842,7 +63839,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63868,7 +63865,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63894,7 +63891,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63920,7 +63917,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63946,7 +63943,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63972,7 +63969,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -63998,7 +63995,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64024,7 +64021,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64050,7 +64047,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64076,7 +64073,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64102,7 +64099,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64128,7 +64125,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64154,7 +64151,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64180,7 +64177,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64206,7 +64203,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64232,7 +64229,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64258,7 +64255,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64284,7 +64281,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64310,7 +64307,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64336,7 +64333,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64362,7 +64359,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64388,7 +64385,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64414,7 +64411,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64440,7 +64437,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64466,7 +64463,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64492,7 +64489,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64518,7 +64515,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64544,7 +64541,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64570,7 +64567,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64596,7 +64593,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64622,7 +64619,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64648,7 +64645,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64674,7 +64671,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64700,7 +64697,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64726,7 +64723,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64752,7 +64749,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64778,7 +64775,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64804,7 +64801,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64830,7 +64827,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64856,7 +64853,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64882,7 +64879,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64908,7 +64905,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64934,7 +64931,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64960,7 +64957,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64986,7 +64983,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65012,7 +65009,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65038,7 +65035,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65064,7 +65061,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65090,7 +65087,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65116,7 +65113,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65142,7 +65139,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65168,7 +65165,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65194,7 +65191,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65220,7 +65217,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65246,7 +65243,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65272,7 +65269,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65298,7 +65295,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65324,7 +65321,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65350,7 +65347,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65376,7 +65373,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65402,7 +65399,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65428,7 +65425,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65454,7 +65451,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65480,7 +65477,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65506,7 +65503,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65532,7 +65529,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65558,7 +65555,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65584,7 +65581,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65610,7 +65607,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65636,7 +65633,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65662,7 +65659,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65688,7 +65685,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65714,7 +65711,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65740,7 +65737,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65766,7 +65763,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65792,7 +65789,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65818,7 +65815,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65844,7 +65841,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65870,7 +65867,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65896,7 +65893,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65922,7 +65919,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65948,7 +65945,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65974,7 +65971,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66000,7 +65997,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66026,7 +66023,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66052,7 +66049,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66078,7 +66075,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66104,7 +66101,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66130,7 +66127,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66156,7 +66153,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66182,7 +66179,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66208,7 +66205,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66234,7 +66231,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66260,7 +66257,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66286,7 +66283,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66312,7 +66309,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66338,7 +66335,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66364,7 +66361,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66390,7 +66387,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66416,7 +66413,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66442,7 +66439,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66468,7 +66465,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66494,7 +66491,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66520,7 +66517,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66546,7 +66543,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66572,7 +66569,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66598,7 +66595,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2489" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66624,7 +66621,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2490" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66650,7 +66647,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2491" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66676,7 +66673,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2492" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66702,7 +66699,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2493" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66728,7 +66725,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2494" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66754,7 +66751,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2495" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66780,7 +66777,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2496" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66806,7 +66803,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2497" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66832,7 +66829,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2498" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66858,7 +66855,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2499" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66884,7 +66881,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2500" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66910,7 +66907,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2501" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66936,7 +66933,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2502" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66962,7 +66959,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2503" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66988,7 +66985,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2504" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67014,7 +67011,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2505" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67040,7 +67037,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2506" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67066,7 +67063,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2507" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67092,7 +67089,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2508" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67118,7 +67115,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2509" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67144,7 +67141,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2510" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67170,7 +67167,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2511" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67196,7 +67193,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2512" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67222,7 +67219,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2513" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67230,7 +67227,7 @@
     </row>
     <row r="2514">
       <c r="A2514" s="1" t="n">
-        <v>45979.6824884259</v>
+        <v>45979.3333333333</v>
       </c>
       <c r="B2514" t="n">
         <v>6530</v>
@@ -67248,9 +67245,35 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2514" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2514" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2515">
+      <c r="A2515" s="1" t="n">
+        <v>45980.6910300926</v>
+      </c>
+      <c r="B2515" t="n">
+        <v>53619</v>
+      </c>
+      <c r="C2515" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="D2515" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E2515" t="n">
+        <v>0.555999994277954</v>
+      </c>
+      <c r="F2515" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2515" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2515" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815480351448</t>
+    <t xml:space="preserve">0.235815495252609</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394716262817</t>
+    <t xml:space="preserve">0.235394701361656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249102830887</t>
+    <t xml:space="preserve">0.228249117732048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.216899916529655</t>
+    <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581348657608</t>
+    <t xml:space="preserve">0.218581333756447</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099088191986</t>
+    <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
-    <t xml:space="preserve">0.217319875955582</t>
+    <t xml:space="preserve">0.21731986105442</t>
   </si>
   <si>
     <t xml:space="preserve">0.228921487927437</t>
@@ -71,37 +71,37 @@
     <t xml:space="preserve">0.227071791887283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293369412422</t>
+    <t xml:space="preserve">0.233293384313583</t>
   </si>
   <si>
     <t xml:space="preserve">0.228417411446571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231527775526047</t>
+    <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
     <t xml:space="preserve">0.229762211441994</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598259329796</t>
+    <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310569405556</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784876823425</t>
+    <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
-    <t xml:space="preserve">0.214377820491791</t>
+    <t xml:space="preserve">0.21437780559063</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211014971137047</t>
+    <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205970704555511</t>
+    <t xml:space="preserve">0.20597068965435</t>
   </si>
   <si>
     <t xml:space="preserve">0.201767146587372</t>
@@ -110,10 +110,10 @@
     <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360030651093</t>
+    <t xml:space="preserve">0.193360045552254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722894906998</t>
@@ -128,34 +128,34 @@
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214142799377</t>
+    <t xml:space="preserve">0.205214157700539</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912760019302</t>
+    <t xml:space="preserve">0.208912745118141</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218499302864</t>
+    <t xml:space="preserve">0.215218514204025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616598010063</t>
+    <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987615227699</t>
+    <t xml:space="preserve">0.22698763012886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031866908073</t>
+    <t xml:space="preserve">0.232031881809235</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235439777374</t>
+    <t xml:space="preserve">0.236235424876213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.241279691457748</t>
+    <t xml:space="preserve">0.24127970635891</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483249425888</t>
+    <t xml:space="preserve">0.245483219623566</t>
   </si>
   <si>
     <t xml:space="preserve">0.252208918333054</t>
@@ -164,43 +164,43 @@
     <t xml:space="preserve">0.258093863725662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138175010681</t>
+    <t xml:space="preserve">0.263138145208359</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182426691055</t>
+    <t xml:space="preserve">0.268182396888733</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226678371429</t>
+    <t xml:space="preserve">0.273226648569107</t>
   </si>
   <si>
     <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836458206177</t>
+    <t xml:space="preserve">0.285836517810822</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562216520309</t>
+    <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447161912918</t>
+    <t xml:space="preserve">0.298447132110596</t>
   </si>
   <si>
     <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057776212692</t>
+    <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
     <t xml:space="preserve">0.317531049251556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827786207199</t>
+    <t xml:space="preserve">0.322827816009521</t>
   </si>
   <si>
     <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455326080322</t>
+    <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
     <t xml:space="preserve">0.36318102478981</t>
@@ -209,40 +209,40 @@
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941409111023</t>
+    <t xml:space="preserve">0.411941379308701</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.440525561571121</t>
+    <t xml:space="preserve">0.440525591373444</t>
   </si>
   <si>
-    <t xml:space="preserve">0.439684838056564</t>
+    <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47247177362442</t>
+    <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400911092758</t>
+    <t xml:space="preserve">0.483400881290436</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055896282196</t>
+    <t xml:space="preserve">0.501055836677551</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011584997177</t>
+    <t xml:space="preserve">0.496011644601822</t>
   </si>
   <si>
     <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307871580124</t>
+    <t xml:space="preserve">0.492307901382446</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670893192291</t>
+    <t xml:space="preserve">0.580670952796936</t>
   </si>
   <si>
     <t xml:space="preserve">0.589086413383484</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319275856018</t>
+    <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
     <t xml:space="preserve">0.673241674900055</t>
@@ -263,73 +263,73 @@
     <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62274843454361</t>
+    <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255373001099</t>
+    <t xml:space="preserve">0.572255432605743</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525969982147217</t>
+    <t xml:space="preserve">0.525970041751862</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762192249298</t>
+    <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48810014128685</t>
+    <t xml:space="preserve">0.488100171089172</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931271076202</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
     <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509138941764832</t>
+    <t xml:space="preserve">0.509139001369476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892351388931</t>
+    <t xml:space="preserve">0.483892381191254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.513346791267395</t>
+    <t xml:space="preserve">0.51334673166275</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177712440491</t>
+    <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554521560669</t>
+    <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269160509109</t>
+    <t xml:space="preserve">0.471269100904465</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061370611191</t>
+    <t xml:space="preserve">0.467061430215836</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853610515594</t>
+    <t xml:space="preserve">0.462853580713272</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684621095657</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607049942017</t>
+    <t xml:space="preserve">0.437607079744339</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230330228806</t>
+    <t xml:space="preserve">0.450230360031128</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645880222321</t>
+    <t xml:space="preserve">0.458645850419998</t>
   </si>
   <si>
     <t xml:space="preserve">0.403944969177246</t>
@@ -347,73 +347,73 @@
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476890802383</t>
+    <t xml:space="preserve">0.475476861000061</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381524562836</t>
+    <t xml:space="preserve">0.380381494760513</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
   </si>
   <si>
-    <t xml:space="preserve">0.412360459566116</t>
+    <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
     <t xml:space="preserve">0.415726661682129</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814780235291</t>
+    <t xml:space="preserve">0.441814750432968</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092893600464</t>
+    <t xml:space="preserve">0.419092923402786</t>
   </si>
   <si>
     <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994287252426</t>
+    <t xml:space="preserve">0.408994257450104</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311201095581</t>
+    <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163246870041</t>
+    <t xml:space="preserve">0.392163217067719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895621299744</t>
+    <t xml:space="preserve">0.398895680904388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578737258911</t>
+    <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261853218079</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529419183731</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649090528488</t>
+    <t xml:space="preserve">0.373649060726166</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155969381332</t>
+    <t xml:space="preserve">0.323155999183655</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374217271805</t>
+    <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
     <t xml:space="preserve">0.336620837450027</t>
@@ -425,28 +425,28 @@
     <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522201299667</t>
+    <t xml:space="preserve">0.326522171497345</t>
   </si>
   <si>
     <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35345184803009</t>
+    <t xml:space="preserve">0.353451818227768</t>
   </si>
   <si>
-    <t xml:space="preserve">0.360184282064438</t>
+    <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
     <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
-    <t xml:space="preserve">0.345036298036575</t>
+    <t xml:space="preserve">0.345036327838898</t>
   </si>
   <si>
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830389380455</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
@@ -455,28 +455,28 @@
     <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333254605531693</t>
+    <t xml:space="preserve">0.33325457572937</t>
   </si>
   <si>
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33493772149086</t>
+    <t xml:space="preserve">0.334937691688538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339987009763718</t>
+    <t xml:space="preserve">0.33998703956604</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.35850116610527</t>
+    <t xml:space="preserve">0.358501195907593</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36859980225563</t>
+    <t xml:space="preserve">0.368599772453308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36355048418045</t>
+    <t xml:space="preserve">0.363550513982773</t>
   </si>
   <si>
     <t xml:space="preserve">0.390480130910873</t>
@@ -491,34 +491,34 @@
     <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698348999023</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332176685333</t>
+    <t xml:space="preserve">0.375332236289978</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282918214798</t>
+    <t xml:space="preserve">0.370282888412476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015292644501</t>
+    <t xml:space="preserve">0.377015352249146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371966004371643</t>
+    <t xml:space="preserve">0.371965974569321</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233540534973</t>
+    <t xml:space="preserve">0.365233570337296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593351840973</t>
+    <t xml:space="preserve">0.538593232631683</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632062911987</t>
+    <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
     <t xml:space="preserve">0.551216602325439</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">0.489783316850662</t>
   </si>
   <si>
-    <t xml:space="preserve">0.48473396897316</t>
+    <t xml:space="preserve">0.484733879566193</t>
   </si>
   <si>
     <t xml:space="preserve">0.47631847858429</t>
@@ -536,25 +536,25 @@
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466373205185</t>
+    <t xml:space="preserve">0.491466343402863</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198807239532</t>
+    <t xml:space="preserve">0.498198837041855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741216659546</t>
+    <t xml:space="preserve">0.553741276264191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494656085968</t>
+    <t xml:space="preserve">0.528494715690613</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811480522156</t>
+    <t xml:space="preserve">0.526811599731445</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910235881805</t>
+    <t xml:space="preserve">0.536910176277161</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128424167633</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50661426782608</t>
+    <t xml:space="preserve">0.506614327430725</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663675308228</t>
+    <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
     <t xml:space="preserve">0.50324809551239</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107508182526</t>
+    <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374984741211</t>
+    <t xml:space="preserve">0.550374925136566</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
@@ -608,52 +608,49 @@
     <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51671302318573</t>
+    <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
     <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531806111335754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.533544063568115</t>
+    <t xml:space="preserve">0.53180605173111</t>
   </si>
   <si>
     <t xml:space="preserve">0.530068159103394</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535281956195831</t>
+    <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330206871033</t>
+    <t xml:space="preserve">0.528330147266388</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709490776062</t>
+    <t xml:space="preserve">0.545709550380707</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661120891571</t>
+    <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185395240784</t>
+    <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
     <t xml:space="preserve">0.547447383403778</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399132728577</t>
+    <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971478939056</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542233645915985</t>
+    <t xml:space="preserve">0.54223358631134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538757741451263</t>
+    <t xml:space="preserve">0.538757801055908</t>
   </si>
   <si>
     <t xml:space="preserve">0.540495693683624</t>
@@ -665,10 +662,10 @@
     <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5509232878685</t>
+    <t xml:space="preserve">0.550923228263855</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378576755524</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
@@ -686,10 +683,10 @@
     <t xml:space="preserve">0.491833746433258</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571698665619</t>
+    <t xml:space="preserve">0.493571609258652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854362010956</t>
+    <t xml:space="preserve">0.524854302406311</t>
   </si>
   <si>
     <t xml:space="preserve">0.523116409778595</t>
@@ -698,7 +695,7 @@
     <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274877071381</t>
+    <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419748306274</t>
@@ -707,7 +704,7 @@
     <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585235118866</t>
+    <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
     <t xml:space="preserve">0.590895652770996</t>
@@ -722,31 +719,31 @@
     <t xml:space="preserve">0.58915764093399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557659626007</t>
+    <t xml:space="preserve">0.639557600021362</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102311134338</t>
+    <t xml:space="preserve">0.669102430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288532733917</t>
+    <t xml:space="preserve">0.714288592338562</t>
   </si>
   <si>
     <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616964519023895</t>
+    <t xml:space="preserve">0.61696445941925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605910301208</t>
+    <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
     <t xml:space="preserve">0.653461039066315</t>
@@ -773,16 +770,16 @@
     <t xml:space="preserve">0.622178316116333</t>
   </si>
   <si>
-    <t xml:space="preserve">0.610012888908386</t>
+    <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633485794067</t>
+    <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799091815948</t>
+    <t xml:space="preserve">0.604798972606659</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778416633606</t>
@@ -800,16 +797,16 @@
     <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109449863434</t>
+    <t xml:space="preserve">0.596109390258789</t>
   </si>
   <si>
-    <t xml:space="preserve">0.611750841140747</t>
+    <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343802928925</t>
+    <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985253810883</t>
+    <t xml:space="preserve">0.649985194206238</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247241973877</t>
@@ -821,7 +818,7 @@
     <t xml:space="preserve">0.683005809783936</t>
   </si>
   <si>
-    <t xml:space="preserve">0.689957559108734</t>
+    <t xml:space="preserve">0.689957499504089</t>
   </si>
   <si>
     <t xml:space="preserve">0.688219606876373</t>
@@ -830,25 +827,25 @@
     <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150621414185</t>
+    <t xml:space="preserve">0.662150740623474</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316227436066</t>
+    <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936883926392</t>
+    <t xml:space="preserve">0.656936824321747</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674776554108</t>
   </si>
   <si>
     <t xml:space="preserve">0.646509408950806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606536984443665</t>
+    <t xml:space="preserve">0.606537044048309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226626396179</t>
+    <t xml:space="preserve">0.615226686000824</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
@@ -857,13 +854,13 @@
     <t xml:space="preserve">0.634617745876312</t>
   </si>
   <si>
-    <t xml:space="preserve">0.641788482666016</t>
+    <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410415172577</t>
+    <t xml:space="preserve">0.636410355567932</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632825016975403</t>
+    <t xml:space="preserve">0.632824957370758</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239618778229</t>
@@ -875,13 +872,13 @@
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276093482971</t>
+    <t xml:space="preserve">0.620276033878326</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592848300934</t>
+    <t xml:space="preserve">0.591592788696289</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
@@ -896,7 +893,7 @@
     <t xml:space="preserve">0.596970856189728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.623861491680145</t>
+    <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
     <t xml:space="preserve">0.616690635681152</t>
@@ -911,13 +908,13 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589800119400024</t>
+    <t xml:space="preserve">0.58980005979538</t>
   </si>
   <si>
     <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385517597198</t>
+    <t xml:space="preserve">0.593385457992554</t>
   </si>
   <si>
     <t xml:space="preserve">0.573665738105774</t>
@@ -932,7 +929,7 @@
     <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324026107788</t>
+    <t xml:space="preserve">0.559324085712433</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
@@ -941,7 +938,7 @@
     <t xml:space="preserve">0.552153289318085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873009204865</t>
+    <t xml:space="preserve">0.571873068809509</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -950,7 +947,7 @@
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178186893463</t>
+    <t xml:space="preserve">0.595178127288818</t>
   </si>
   <si>
     <t xml:space="preserve">0.631032347679138</t>
@@ -965,16 +962,16 @@
     <t xml:space="preserve">0.605934381484985</t>
   </si>
   <si>
-    <t xml:space="preserve">0.548567891120911</t>
+    <t xml:space="preserve">0.548567831516266</t>
   </si>
   <si>
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738627910614</t>
+    <t xml:space="preserve">0.555738687515259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945958614349</t>
+    <t xml:space="preserve">0.553945899009705</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -989,7 +986,7 @@
     <t xml:space="preserve">0.622068762779236</t>
   </si>
   <si>
-    <t xml:space="preserve">0.638203084468842</t>
+    <t xml:space="preserve">0.638203144073486</t>
   </si>
   <si>
     <t xml:space="preserve">0.639995813369751</t>
@@ -998,43 +995,43 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752067565918</t>
+    <t xml:space="preserve">0.650752127170563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337465763092</t>
+    <t xml:space="preserve">0.654337525367737</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057245254517</t>
+    <t xml:space="preserve">0.674057185649872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.661508321762085</t>
+    <t xml:space="preserve">0.66150826215744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922863960266</t>
+    <t xml:space="preserve">0.657922923564911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093719959259</t>
+    <t xml:space="preserve">0.665093660354614</t>
   </si>
   <si>
     <t xml:space="preserve">0.666886448860168</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645373940467834</t>
+    <t xml:space="preserve">0.645374000072479</t>
   </si>
   <si>
     <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.643581211566925</t>
+    <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264516353607</t>
+    <t xml:space="preserve">0.672264456748962</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471847057343</t>
@@ -1043,7 +1040,7 @@
     <t xml:space="preserve">0.684813439846039</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683020710945129</t>
+    <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
     <t xml:space="preserve">0.690191566944122</t>
@@ -1052,13 +1049,13 @@
     <t xml:space="preserve">0.681228041648865</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71528947353363</t>
+    <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594651222229</t>
+    <t xml:space="preserve">0.738594591617584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.743972778320312</t>
+    <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
     <t xml:space="preserve">0.711704075336456</t>
@@ -1067,10 +1064,10 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009133815765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460269927979</t>
+    <t xml:space="preserve">0.722460329532623</t>
   </si>
   <si>
     <t xml:space="preserve">0.745765447616577</t>
@@ -1079,7 +1076,7 @@
     <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143574714661</t>
+    <t xml:space="preserve">0.751143515110016</t>
   </si>
   <si>
     <t xml:space="preserve">0.742180049419403</t>
@@ -1106,7 +1103,7 @@
     <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.724252939224243</t>
+    <t xml:space="preserve">0.724252998828888</t>
   </si>
   <si>
     <t xml:space="preserve">0.709911346435547</t>
@@ -1115,16 +1112,16 @@
     <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642643451691</t>
+    <t xml:space="preserve">0.677642583847046</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849974155426</t>
+    <t xml:space="preserve">0.675849914550781</t>
   </si>
   <si>
-    <t xml:space="preserve">0.720667541027069</t>
+    <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045668125153</t>
+    <t xml:space="preserve">0.726045727729797</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1152,6 +1149,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483880519867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -38833,7 +38833,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1421" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1421" t="s">
         <v>9</v>
@@ -38859,7 +38859,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1422" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1422" t="s">
         <v>9</v>
@@ -38885,7 +38885,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1423" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1423" t="s">
         <v>9</v>
@@ -38911,7 +38911,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1424" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1424" t="s">
         <v>9</v>
@@ -38989,7 +38989,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1427" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1427" t="s">
         <v>9</v>
@@ -39015,7 +39015,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1428" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1428" t="s">
         <v>9</v>
@@ -39041,7 +39041,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1429" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1429" t="s">
         <v>9</v>
@@ -39067,7 +39067,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1430" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H1430" t="s">
         <v>9</v>
@@ -39145,7 +39145,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1433" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1433" t="s">
         <v>9</v>
@@ -39171,7 +39171,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1434" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1434" t="s">
         <v>9</v>
@@ -39249,7 +39249,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1437" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1437" t="s">
         <v>9</v>
@@ -39275,7 +39275,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1438" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1438" t="s">
         <v>9</v>
@@ -39301,7 +39301,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1439" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1439" t="s">
         <v>9</v>
@@ -39327,7 +39327,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1440" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1440" t="s">
         <v>9</v>
@@ -39353,7 +39353,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1441" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1441" t="s">
         <v>9</v>
@@ -39379,7 +39379,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1442" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1442" t="s">
         <v>9</v>
@@ -39405,7 +39405,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1443" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1443" t="s">
         <v>9</v>
@@ -39431,7 +39431,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1444" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1444" t="s">
         <v>9</v>
@@ -39457,7 +39457,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1445" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1445" t="s">
         <v>9</v>
@@ -39483,7 +39483,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1446" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="H1446" t="s">
         <v>9</v>
@@ -39509,7 +39509,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1447" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1447" t="s">
         <v>9</v>
@@ -39535,7 +39535,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1448" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1448" t="s">
         <v>9</v>
@@ -39561,7 +39561,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1449" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1449" t="s">
         <v>9</v>
@@ -39587,7 +39587,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1450" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1450" t="s">
         <v>9</v>
@@ -39613,7 +39613,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1451" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1451" t="s">
         <v>9</v>
@@ -39665,7 +39665,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1453" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1453" t="s">
         <v>9</v>
@@ -39691,7 +39691,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1454" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1454" t="s">
         <v>9</v>
@@ -39743,7 +39743,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1456" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1456" t="s">
         <v>9</v>
@@ -39769,7 +39769,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1457" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1457" t="s">
         <v>9</v>
@@ -39795,7 +39795,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1458" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1458" t="s">
         <v>9</v>
@@ -39821,7 +39821,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1459" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1459" t="s">
         <v>9</v>
@@ -39873,7 +39873,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1461" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1461" t="s">
         <v>9</v>
@@ -39899,7 +39899,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1462" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="H1462" t="s">
         <v>9</v>
@@ -39925,7 +39925,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1463" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="H1463" t="s">
         <v>9</v>
@@ -39951,7 +39951,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1464" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="H1464" t="s">
         <v>9</v>
@@ -39977,7 +39977,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1465" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1465" t="s">
         <v>9</v>
@@ -40003,7 +40003,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1466" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1466" t="s">
         <v>9</v>
@@ -40029,7 +40029,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1467" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1467" t="s">
         <v>9</v>
@@ -40055,7 +40055,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1468" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1468" t="s">
         <v>9</v>
@@ -40081,7 +40081,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1469" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1469" t="s">
         <v>9</v>
@@ -40107,7 +40107,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1470" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1470" t="s">
         <v>9</v>
@@ -40133,7 +40133,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G1471" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="H1471" t="s">
         <v>9</v>
@@ -40159,7 +40159,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1472" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1472" t="s">
         <v>9</v>
@@ -40185,7 +40185,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1473" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1473" t="s">
         <v>9</v>
@@ -40211,7 +40211,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1474" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1474" t="s">
         <v>9</v>
@@ -40237,7 +40237,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1475" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1475" t="s">
         <v>9</v>
@@ -40263,7 +40263,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1476" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1476" t="s">
         <v>9</v>
@@ -40289,7 +40289,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1477" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1477" t="s">
         <v>9</v>
@@ -40315,7 +40315,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1478" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1478" t="s">
         <v>9</v>
@@ -40367,7 +40367,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1480" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1480" t="s">
         <v>9</v>
@@ -40393,7 +40393,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1481" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1481" t="s">
         <v>9</v>
@@ -40419,7 +40419,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G1482" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="H1482" t="s">
         <v>9</v>
@@ -40445,7 +40445,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1483" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1483" t="s">
         <v>9</v>
@@ -40471,7 +40471,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1484" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1484" t="s">
         <v>9</v>
@@ -40497,7 +40497,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1485" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1485" t="s">
         <v>9</v>
@@ -40523,7 +40523,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1486" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H1486" t="s">
         <v>9</v>
@@ -40549,7 +40549,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1487" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1487" t="s">
         <v>9</v>
@@ -40575,7 +40575,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1488" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1488" t="s">
         <v>9</v>
@@ -40601,7 +40601,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1489" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="H1489" t="s">
         <v>9</v>
@@ -40627,7 +40627,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1490" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1490" t="s">
         <v>9</v>
@@ -40653,7 +40653,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1491" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1491" t="s">
         <v>9</v>
@@ -40705,7 +40705,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1493" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1493" t="s">
         <v>9</v>
@@ -40731,7 +40731,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1494" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1494" t="s">
         <v>9</v>
@@ -40757,7 +40757,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G1495" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="H1495" t="s">
         <v>9</v>
@@ -40783,7 +40783,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1496" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1496" t="s">
         <v>9</v>
@@ -40809,7 +40809,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1497" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1497" t="s">
         <v>9</v>
@@ -40835,7 +40835,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1498" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1498" t="s">
         <v>9</v>
@@ -40861,7 +40861,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G1499" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="H1499" t="s">
         <v>9</v>
@@ -40887,7 +40887,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G1500" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="H1500" t="s">
         <v>9</v>
@@ -40913,7 +40913,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G1501" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H1501" t="s">
         <v>9</v>
@@ -40939,7 +40939,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1502" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1502" t="s">
         <v>9</v>
@@ -40965,7 +40965,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G1503" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H1503" t="s">
         <v>9</v>
@@ -40991,7 +40991,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G1504" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="H1504" t="s">
         <v>9</v>
@@ -41017,7 +41017,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1505" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1505" t="s">
         <v>9</v>
@@ -41043,7 +41043,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G1506" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="H1506" t="s">
         <v>9</v>
@@ -41069,7 +41069,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1507" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="H1507" t="s">
         <v>9</v>
@@ -41095,7 +41095,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1508" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1508" t="s">
         <v>9</v>
@@ -41121,7 +41121,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1509" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1509" t="s">
         <v>9</v>
@@ -41147,7 +41147,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1510" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1510" t="s">
         <v>9</v>
@@ -41173,7 +41173,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1511" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1511" t="s">
         <v>9</v>
@@ -41199,7 +41199,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G1512" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="H1512" t="s">
         <v>9</v>
@@ -41225,7 +41225,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1513" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1513" t="s">
         <v>9</v>
@@ -41251,7 +41251,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1514" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1514" t="s">
         <v>9</v>
@@ -41277,7 +41277,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1515" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1515" t="s">
         <v>9</v>
@@ -41303,7 +41303,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1516" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H1516" t="s">
         <v>9</v>
@@ -41329,7 +41329,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1517" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1517" t="s">
         <v>9</v>
@@ -41355,7 +41355,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1518" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H1518" t="s">
         <v>9</v>
@@ -41381,7 +41381,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1519" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1519" t="s">
         <v>9</v>
@@ -41407,7 +41407,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1520" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="H1520" t="s">
         <v>9</v>
@@ -41433,7 +41433,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1521" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1521" t="s">
         <v>9</v>
@@ -41459,7 +41459,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1522" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1522" t="s">
         <v>9</v>
@@ -41485,7 +41485,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1523" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1523" t="s">
         <v>9</v>
@@ -41511,7 +41511,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1524" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1524" t="s">
         <v>9</v>
@@ -41537,7 +41537,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G1525" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="H1525" t="s">
         <v>9</v>
@@ -41563,7 +41563,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1526" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H1526" t="s">
         <v>9</v>
@@ -41589,7 +41589,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1527" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1527" t="s">
         <v>9</v>
@@ -41615,7 +41615,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1528" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H1528" t="s">
         <v>9</v>
@@ -41641,7 +41641,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1529" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1529" t="s">
         <v>9</v>
@@ -41667,7 +41667,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1530" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="H1530" t="s">
         <v>9</v>
@@ -41693,7 +41693,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1531" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H1531" t="s">
         <v>9</v>
@@ -41719,7 +41719,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1532" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="H1532" t="s">
         <v>9</v>
@@ -41745,7 +41745,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1533" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1533" t="s">
         <v>9</v>
@@ -41771,7 +41771,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1534" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="H1534" t="s">
         <v>9</v>
@@ -41797,7 +41797,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1535" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1535" t="s">
         <v>9</v>
@@ -41823,7 +41823,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1536" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1536" t="s">
         <v>9</v>
@@ -41849,7 +41849,7 @@
         <v>0.736000001430511</v>
       </c>
       <c r="G1537" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="H1537" t="s">
         <v>9</v>
@@ -41875,7 +41875,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1538" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1538" t="s">
         <v>9</v>
@@ -41901,7 +41901,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1539" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="H1539" t="s">
         <v>9</v>
@@ -41927,7 +41927,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1540" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="H1540" t="s">
         <v>9</v>
@@ -41953,7 +41953,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1541" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1541" t="s">
         <v>9</v>
@@ -41979,7 +41979,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1542" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1542" t="s">
         <v>9</v>
@@ -42005,7 +42005,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1543" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1543" t="s">
         <v>9</v>
@@ -42031,7 +42031,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1544" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="H1544" t="s">
         <v>9</v>
@@ -42057,7 +42057,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1545" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1545" t="s">
         <v>9</v>
@@ -42083,7 +42083,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1546" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1546" t="s">
         <v>9</v>
@@ -42109,7 +42109,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1547" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1547" t="s">
         <v>9</v>
@@ -42135,7 +42135,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1548" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1548" t="s">
         <v>9</v>
@@ -42161,7 +42161,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1549" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="H1549" t="s">
         <v>9</v>
@@ -42187,7 +42187,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1550" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1550" t="s">
         <v>9</v>
@@ -42213,7 +42213,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1551" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="H1551" t="s">
         <v>9</v>
@@ -42239,7 +42239,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1552" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1552" t="s">
         <v>9</v>
@@ -42265,7 +42265,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1553" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1553" t="s">
         <v>9</v>
@@ -42291,7 +42291,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1554" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1554" t="s">
         <v>9</v>
@@ -42317,7 +42317,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1555" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1555" t="s">
         <v>9</v>
@@ -42343,7 +42343,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1556" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1556" t="s">
         <v>9</v>
@@ -42369,7 +42369,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1557" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="H1557" t="s">
         <v>9</v>
@@ -42395,7 +42395,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1558" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1558" t="s">
         <v>9</v>
@@ -42421,7 +42421,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1559" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1559" t="s">
         <v>9</v>
@@ -42447,7 +42447,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1560" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1560" t="s">
         <v>9</v>
@@ -42473,7 +42473,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1561" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="H1561" t="s">
         <v>9</v>
@@ -42499,7 +42499,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1562" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="H1562" t="s">
         <v>9</v>
@@ -42525,7 +42525,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1563" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1563" t="s">
         <v>9</v>
@@ -42551,7 +42551,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1564" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1564" t="s">
         <v>9</v>
@@ -42577,7 +42577,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1565" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="H1565" t="s">
         <v>9</v>
@@ -42603,7 +42603,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1566" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="H1566" t="s">
         <v>9</v>
@@ -42629,7 +42629,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1567" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="H1567" t="s">
         <v>9</v>
@@ -42655,7 +42655,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1568" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1568" t="s">
         <v>9</v>
@@ -42681,7 +42681,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1569" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="H1569" t="s">
         <v>9</v>
@@ -42707,7 +42707,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1570" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1570" t="s">
         <v>9</v>
@@ -42733,7 +42733,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1571" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="H1571" t="s">
         <v>9</v>
@@ -42759,7 +42759,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G1572" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="H1572" t="s">
         <v>9</v>
@@ -42785,7 +42785,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G1573" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="H1573" t="s">
         <v>9</v>
@@ -42811,7 +42811,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1574" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="H1574" t="s">
         <v>9</v>
@@ -42837,7 +42837,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1575" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
       <c r="H1575" t="s">
         <v>9</v>
@@ -42863,7 +42863,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1576" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="H1576" t="s">
         <v>9</v>
@@ -42889,7 +42889,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1577" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="H1577" t="s">
         <v>9</v>
@@ -42915,7 +42915,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1578" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="H1578" t="s">
         <v>9</v>
@@ -42941,7 +42941,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1579" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="H1579" t="s">
         <v>9</v>
@@ -42967,7 +42967,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1580" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="H1580" t="s">
         <v>9</v>
@@ -42993,7 +42993,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1581" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1581" t="s">
         <v>9</v>
@@ -43019,7 +43019,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1582" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H1582" t="s">
         <v>9</v>
@@ -43045,7 +43045,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1583" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="H1583" t="s">
         <v>9</v>
@@ -43071,7 +43071,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1584" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="H1584" t="s">
         <v>9</v>
@@ -43097,7 +43097,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1585" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="H1585" t="s">
         <v>9</v>
@@ -43123,7 +43123,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1586" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1586" t="s">
         <v>9</v>
@@ -43149,7 +43149,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1587" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="H1587" t="s">
         <v>9</v>
@@ -43175,7 +43175,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1588" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1588" t="s">
         <v>9</v>
@@ -43201,7 +43201,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1589" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1589" t="s">
         <v>9</v>
@@ -43227,7 +43227,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1590" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1590" t="s">
         <v>9</v>
@@ -43253,7 +43253,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1591" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1591" t="s">
         <v>9</v>
@@ -43279,7 +43279,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1592" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="H1592" t="s">
         <v>9</v>
@@ -43305,7 +43305,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1593" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1593" t="s">
         <v>9</v>
@@ -43331,7 +43331,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1594" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="H1594" t="s">
         <v>9</v>
@@ -43357,7 +43357,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1595" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="H1595" t="s">
         <v>9</v>
@@ -43383,7 +43383,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1596" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="H1596" t="s">
         <v>9</v>
@@ -43409,7 +43409,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1597" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="H1597" t="s">
         <v>9</v>
@@ -43435,7 +43435,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1598" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="H1598" t="s">
         <v>9</v>
@@ -43461,7 +43461,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1599" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1599" t="s">
         <v>9</v>
@@ -43487,7 +43487,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1600" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="H1600" t="s">
         <v>9</v>
@@ -43513,7 +43513,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1601" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1601" t="s">
         <v>9</v>
@@ -43539,7 +43539,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1602" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1602" t="s">
         <v>9</v>
@@ -43565,7 +43565,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1603" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="H1603" t="s">
         <v>9</v>
@@ -43591,7 +43591,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1604" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="H1604" t="s">
         <v>9</v>
@@ -43617,7 +43617,7 @@
         <v>0.758000016212463</v>
       </c>
       <c r="G1605" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="H1605" t="s">
         <v>9</v>
@@ -43643,7 +43643,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1606" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1606" t="s">
         <v>9</v>
@@ -43669,7 +43669,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1607" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="H1607" t="s">
         <v>9</v>
@@ -43695,7 +43695,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1608" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1608" t="s">
         <v>9</v>
@@ -43721,7 +43721,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1609" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1609" t="s">
         <v>9</v>
@@ -43747,7 +43747,7 @@
         <v>0.745999991893768</v>
       </c>
       <c r="G1610" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="H1610" t="s">
         <v>9</v>
@@ -43773,7 +43773,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1611" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="H1611" t="s">
         <v>9</v>
@@ -43799,7 +43799,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1612" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="H1612" t="s">
         <v>9</v>
@@ -43825,7 +43825,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1613" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1613" t="s">
         <v>9</v>
@@ -43851,7 +43851,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1614" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="H1614" t="s">
         <v>9</v>
@@ -43877,7 +43877,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1615" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="H1615" t="s">
         <v>9</v>
@@ -43903,7 +43903,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1616" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="H1616" t="s">
         <v>9</v>
@@ -43929,7 +43929,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1617" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H1617" t="s">
         <v>9</v>
@@ -43955,7 +43955,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1618" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H1618" t="s">
         <v>9</v>
@@ -43981,7 +43981,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1619" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="H1619" t="s">
         <v>9</v>
@@ -44007,7 +44007,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1620" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="H1620" t="s">
         <v>9</v>
@@ -44033,7 +44033,7 @@
         <v>0.73199999332428</v>
       </c>
       <c r="G1621" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="H1621" t="s">
         <v>9</v>
@@ -44059,7 +44059,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1622" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1622" t="s">
         <v>9</v>
@@ -44085,7 +44085,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1623" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1623" t="s">
         <v>9</v>
@@ -44111,7 +44111,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1624" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="H1624" t="s">
         <v>9</v>
@@ -44137,7 +44137,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1625" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1625" t="s">
         <v>9</v>
@@ -44163,7 +44163,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1626" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="H1626" t="s">
         <v>9</v>
@@ -44189,7 +44189,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1627" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="H1627" t="s">
         <v>9</v>
@@ -44215,7 +44215,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1628" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1628" t="s">
         <v>9</v>
@@ -44241,7 +44241,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1629" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1629" t="s">
         <v>9</v>
@@ -44267,7 +44267,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1630" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1630" t="s">
         <v>9</v>
@@ -44293,7 +44293,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1631" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1631" t="s">
         <v>9</v>
@@ -44319,7 +44319,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1632" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1632" t="s">
         <v>9</v>
@@ -44345,7 +44345,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1633" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1633" t="s">
         <v>9</v>
@@ -44371,7 +44371,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1634" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1634" t="s">
         <v>9</v>
@@ -44397,7 +44397,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1635" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1635" t="s">
         <v>9</v>
@@ -44423,7 +44423,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1636" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1636" t="s">
         <v>9</v>
@@ -44449,7 +44449,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44475,7 +44475,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44501,7 +44501,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44527,7 +44527,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44553,7 +44553,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44579,7 +44579,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44605,7 +44605,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44631,7 +44631,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44657,7 +44657,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44683,7 +44683,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44709,7 +44709,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1647" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="H1647" t="s">
         <v>9</v>
@@ -44735,7 +44735,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44761,7 +44761,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44787,7 +44787,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44813,7 +44813,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44839,7 +44839,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44865,7 +44865,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44891,7 +44891,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44917,7 +44917,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44943,7 +44943,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44969,7 +44969,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44995,7 +44995,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45021,7 +45021,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45047,7 +45047,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45073,7 +45073,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45099,7 +45099,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45125,7 +45125,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45151,7 +45151,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45177,7 +45177,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45203,7 +45203,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45229,7 +45229,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45255,7 +45255,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45281,7 +45281,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45307,7 +45307,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45333,7 +45333,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45359,7 +45359,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45385,7 +45385,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45411,7 +45411,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45437,7 +45437,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45463,7 +45463,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45489,7 +45489,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45515,7 +45515,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45541,7 +45541,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45567,7 +45567,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45593,7 +45593,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45619,7 +45619,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45645,7 +45645,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1683" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1683" t="s">
         <v>9</v>
@@ -45671,7 +45671,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45697,7 +45697,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1685" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1685" t="s">
         <v>9</v>
@@ -45723,7 +45723,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45749,7 +45749,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45775,7 +45775,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45801,7 +45801,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45827,7 +45827,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45853,7 +45853,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45879,7 +45879,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45905,7 +45905,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45931,7 +45931,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45957,7 +45957,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45983,7 +45983,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46009,7 +46009,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46035,7 +46035,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46061,7 +46061,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46087,7 +46087,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46113,7 +46113,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46139,7 +46139,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46165,7 +46165,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46191,7 +46191,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46217,7 +46217,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46243,7 +46243,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46269,7 +46269,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46295,7 +46295,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46321,7 +46321,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46347,7 +46347,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46373,7 +46373,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46399,7 +46399,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46425,7 +46425,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46451,7 +46451,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46477,7 +46477,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46503,7 +46503,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1716" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="H1716" t="s">
         <v>9</v>
@@ -46529,7 +46529,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1717" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1717" t="s">
         <v>9</v>
@@ -46555,7 +46555,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1718" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="H1718" t="s">
         <v>9</v>
@@ -46581,7 +46581,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1719" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1719" t="s">
         <v>9</v>
@@ -46607,7 +46607,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1720" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1720" t="s">
         <v>9</v>
@@ -46633,7 +46633,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1721" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="H1721" t="s">
         <v>9</v>
@@ -46659,7 +46659,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1722" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1722" t="s">
         <v>9</v>
@@ -46685,7 +46685,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1723" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="H1723" t="s">
         <v>9</v>
@@ -46711,7 +46711,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G1724" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="H1724" t="s">
         <v>9</v>
@@ -46737,7 +46737,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1725" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="H1725" t="s">
         <v>9</v>
@@ -46763,7 +46763,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1726" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="H1726" t="s">
         <v>9</v>
@@ -46789,7 +46789,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1727" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="H1727" t="s">
         <v>9</v>
@@ -46815,7 +46815,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1728" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1728" t="s">
         <v>9</v>
@@ -46841,7 +46841,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1729" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="H1729" t="s">
         <v>9</v>
@@ -46867,7 +46867,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1730" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="H1730" t="s">
         <v>9</v>
@@ -46893,7 +46893,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1731" t="s">
-        <v>302</v>
+        <v>301</v>
       </c>
       <c r="H1731" t="s">
         <v>9</v>
@@ -46919,7 +46919,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1732" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1732" t="s">
         <v>9</v>
@@ -46945,7 +46945,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1733" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1733" t="s">
         <v>9</v>
@@ -46971,7 +46971,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1734" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1734" t="s">
         <v>9</v>
@@ -46997,7 +46997,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1735" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1735" t="s">
         <v>9</v>
@@ -47023,7 +47023,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1736" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1736" t="s">
         <v>9</v>
@@ -47049,7 +47049,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1737" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1737" t="s">
         <v>9</v>
@@ -47075,7 +47075,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1738" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="H1738" t="s">
         <v>9</v>
@@ -47101,7 +47101,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1739" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1739" t="s">
         <v>9</v>
@@ -47127,7 +47127,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1740" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1740" t="s">
         <v>9</v>
@@ -47153,7 +47153,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1741" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="H1741" t="s">
         <v>9</v>
@@ -47179,7 +47179,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1742" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="H1742" t="s">
         <v>9</v>
@@ -47205,7 +47205,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1743" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="H1743" t="s">
         <v>9</v>
@@ -47231,7 +47231,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1744" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1744" t="s">
         <v>9</v>
@@ -47257,7 +47257,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1745" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1745" t="s">
         <v>9</v>
@@ -47283,7 +47283,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1746" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1746" t="s">
         <v>9</v>
@@ -47309,7 +47309,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1747" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1747" t="s">
         <v>9</v>
@@ -47335,7 +47335,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1748" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1748" t="s">
         <v>9</v>
@@ -47361,7 +47361,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1749" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="H1749" t="s">
         <v>9</v>
@@ -47387,7 +47387,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1750" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="H1750" t="s">
         <v>9</v>
@@ -47413,7 +47413,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1751" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1751" t="s">
         <v>9</v>
@@ -47439,7 +47439,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1752" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1752" t="s">
         <v>9</v>
@@ -47465,7 +47465,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1753" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="H1753" t="s">
         <v>9</v>
@@ -47491,7 +47491,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1754" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1754" t="s">
         <v>9</v>
@@ -47517,7 +47517,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1755" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1755" t="s">
         <v>9</v>
@@ -47543,7 +47543,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1756" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="H1756" t="s">
         <v>9</v>
@@ -47569,7 +47569,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1757" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1757" t="s">
         <v>9</v>
@@ -47595,7 +47595,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1758" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="H1758" t="s">
         <v>9</v>
@@ -47621,7 +47621,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1759" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1759" t="s">
         <v>9</v>
@@ -47647,7 +47647,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1760" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1760" t="s">
         <v>9</v>
@@ -47673,7 +47673,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1761" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="H1761" t="s">
         <v>9</v>
@@ -47699,7 +47699,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1762" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1762" t="s">
         <v>9</v>
@@ -47725,7 +47725,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1763" t="s">
-        <v>296</v>
+        <v>295</v>
       </c>
       <c r="H1763" t="s">
         <v>9</v>
@@ -47751,7 +47751,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1764" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="H1764" t="s">
         <v>9</v>
@@ -47777,7 +47777,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1765" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1765" t="s">
         <v>9</v>
@@ -47803,7 +47803,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1766" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="H1766" t="s">
         <v>9</v>
@@ -47829,7 +47829,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1767" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H1767" t="s">
         <v>9</v>
@@ -47855,7 +47855,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1768" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="H1768" t="s">
         <v>9</v>
@@ -47881,7 +47881,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1769" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1769" t="s">
         <v>9</v>
@@ -47907,7 +47907,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1770" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1770" t="s">
         <v>9</v>
@@ -47933,7 +47933,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1771" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1771" t="s">
         <v>9</v>
@@ -47959,7 +47959,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1772" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="H1772" t="s">
         <v>9</v>
@@ -47985,7 +47985,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1773" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1773" t="s">
         <v>9</v>
@@ -48011,7 +48011,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1774" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1774" t="s">
         <v>9</v>
@@ -48037,7 +48037,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1775" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="H1775" t="s">
         <v>9</v>
@@ -48063,7 +48063,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1776" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1776" t="s">
         <v>9</v>
@@ -48089,7 +48089,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1777" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1777" t="s">
         <v>9</v>
@@ -48115,7 +48115,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1778" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="H1778" t="s">
         <v>9</v>
@@ -48141,7 +48141,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1779" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1779" t="s">
         <v>9</v>
@@ -48167,7 +48167,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1780" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1780" t="s">
         <v>9</v>
@@ -48193,7 +48193,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1781" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1781" t="s">
         <v>9</v>
@@ -48219,7 +48219,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1782" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="H1782" t="s">
         <v>9</v>
@@ -48245,7 +48245,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1783" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1783" t="s">
         <v>9</v>
@@ -48271,7 +48271,7 @@
         <v>0.726000010967255</v>
       </c>
       <c r="G1784" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="H1784" t="s">
         <v>9</v>
@@ -48297,7 +48297,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1785" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1785" t="s">
         <v>9</v>
@@ -48323,7 +48323,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1786" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1786" t="s">
         <v>9</v>
@@ -48349,7 +48349,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1787" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1787" t="s">
         <v>9</v>
@@ -48375,7 +48375,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1788" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1788" t="s">
         <v>9</v>
@@ -48401,7 +48401,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1789" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1789" t="s">
         <v>9</v>
@@ -48427,7 +48427,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1790" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1790" t="s">
         <v>9</v>
@@ -48453,7 +48453,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1791" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1791" t="s">
         <v>9</v>
@@ -48479,7 +48479,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1792" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1792" t="s">
         <v>9</v>
@@ -48505,7 +48505,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1793" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1793" t="s">
         <v>9</v>
@@ -48531,7 +48531,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1794" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1794" t="s">
         <v>9</v>
@@ -48557,7 +48557,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1795" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1795" t="s">
         <v>9</v>
@@ -48583,7 +48583,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1796" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1796" t="s">
         <v>9</v>
@@ -48609,7 +48609,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1797" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1797" t="s">
         <v>9</v>
@@ -48635,7 +48635,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1798" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1798" t="s">
         <v>9</v>
@@ -48661,7 +48661,7 @@
         <v>0.720000028610229</v>
       </c>
       <c r="G1799" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="H1799" t="s">
         <v>9</v>
@@ -48687,7 +48687,7 @@
         <v>0.727999985218048</v>
       </c>
       <c r="G1800" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="H1800" t="s">
         <v>9</v>
@@ -48713,7 +48713,7 @@
         <v>0.723999977111816</v>
       </c>
       <c r="G1801" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="H1801" t="s">
         <v>9</v>
@@ -48739,7 +48739,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1802" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="H1802" t="s">
         <v>9</v>
@@ -48765,7 +48765,7 @@
         <v>0.722000002861023</v>
       </c>
       <c r="G1803" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="H1803" t="s">
         <v>9</v>
@@ -48791,7 +48791,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1804" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="H1804" t="s">
         <v>9</v>
@@ -48817,7 +48817,7 @@
         <v>0.737999975681305</v>
       </c>
       <c r="G1805" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="H1805" t="s">
         <v>9</v>
@@ -48843,7 +48843,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1806" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1806" t="s">
         <v>9</v>
@@ -48869,7 +48869,7 @@
         <v>0.740000009536743</v>
       </c>
       <c r="G1807" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="H1807" t="s">
         <v>9</v>
@@ -48895,7 +48895,7 @@
         <v>0.744000017642975</v>
       </c>
       <c r="G1808" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="H1808" t="s">
         <v>9</v>
@@ -48921,7 +48921,7 @@
         <v>0.75</v>
       </c>
       <c r="G1809" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1809" t="s">
         <v>9</v>
@@ -48947,7 +48947,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1810" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1810" t="s">
         <v>9</v>
@@ -48973,7 +48973,7 @@
         <v>0.748000025749207</v>
       </c>
       <c r="G1811" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="H1811" t="s">
         <v>9</v>
@@ -48999,7 +48999,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1812" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1812" t="s">
         <v>9</v>
@@ -49025,7 +49025,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1813" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1813" t="s">
         <v>9</v>
@@ -49051,7 +49051,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1814" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1814" t="s">
         <v>9</v>
@@ -49077,7 +49077,7 @@
         <v>0.759999990463257</v>
       </c>
       <c r="G1815" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="H1815" t="s">
         <v>9</v>
@@ -49103,7 +49103,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1816" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1816" t="s">
         <v>9</v>
@@ -49129,7 +49129,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1817" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1817" t="s">
         <v>9</v>
@@ -49155,7 +49155,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1818" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1818" t="s">
         <v>9</v>
@@ -49181,7 +49181,7 @@
         <v>0.824000000953674</v>
       </c>
       <c r="G1819" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="H1819" t="s">
         <v>9</v>
@@ -49207,7 +49207,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1820" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1820" t="s">
         <v>9</v>
@@ -49233,7 +49233,7 @@
         <v>0.811999976634979</v>
       </c>
       <c r="G1821" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="H1821" t="s">
         <v>9</v>
@@ -49259,7 +49259,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1822" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1822" t="s">
         <v>9</v>
@@ -49285,7 +49285,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1823" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1823" t="s">
         <v>9</v>
@@ -49311,7 +49311,7 @@
         <v>0.819999992847443</v>
       </c>
       <c r="G1824" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="H1824" t="s">
         <v>9</v>
@@ -49337,7 +49337,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1825" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1825" t="s">
         <v>9</v>
@@ -49363,7 +49363,7 @@
         <v>0.822000026702881</v>
       </c>
       <c r="G1826" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="H1826" t="s">
         <v>9</v>
@@ -49389,7 +49389,7 @@
         <v>0.832000017166138</v>
       </c>
       <c r="G1827" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="H1827" t="s">
         <v>9</v>
@@ -49415,7 +49415,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1828" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1828" t="s">
         <v>9</v>
@@ -49441,7 +49441,7 @@
         <v>0.829999983310699</v>
       </c>
       <c r="G1829" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="H1829" t="s">
         <v>9</v>
@@ -49467,7 +49467,7 @@
         <v>0.837999999523163</v>
       </c>
       <c r="G1830" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="H1830" t="s">
         <v>9</v>
@@ -49493,7 +49493,7 @@
         <v>0.828000009059906</v>
       </c>
       <c r="G1831" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="H1831" t="s">
         <v>9</v>
@@ -49519,7 +49519,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1832" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1832" t="s">
         <v>9</v>
@@ -49545,7 +49545,7 @@
         <v>0.78600001335144</v>
       </c>
       <c r="G1833" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="H1833" t="s">
         <v>9</v>
@@ -49571,7 +49571,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1834" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1834" t="s">
         <v>9</v>
@@ -49597,7 +49597,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1835" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1835" t="s">
         <v>9</v>
@@ -49623,7 +49623,7 @@
         <v>0.782000005245209</v>
       </c>
       <c r="G1836" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="H1836" t="s">
         <v>9</v>
@@ -49649,7 +49649,7 @@
         <v>0.787999987602234</v>
       </c>
       <c r="G1837" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="H1837" t="s">
         <v>9</v>
@@ -49675,7 +49675,7 @@
         <v>0.777999997138977</v>
       </c>
       <c r="G1838" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="H1838" t="s">
         <v>9</v>
@@ -49701,7 +49701,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1839" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1839" t="s">
         <v>9</v>
@@ -49727,7 +49727,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1840" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1840" t="s">
         <v>9</v>
@@ -49753,7 +49753,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1841" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1841" t="s">
         <v>9</v>
@@ -49779,7 +49779,7 @@
         <v>0.791999995708466</v>
       </c>
       <c r="G1842" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="H1842" t="s">
         <v>9</v>
@@ -49805,7 +49805,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1843" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1843" t="s">
         <v>9</v>
@@ -49831,7 +49831,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1844" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1844" t="s">
         <v>9</v>
@@ -49857,7 +49857,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1845" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1845" t="s">
         <v>9</v>
@@ -49883,7 +49883,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1846" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1846" t="s">
         <v>9</v>
@@ -49909,7 +49909,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1847" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1847" t="s">
         <v>9</v>
@@ -49935,7 +49935,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1848" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1848" t="s">
         <v>9</v>
@@ -49961,7 +49961,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1849" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1849" t="s">
         <v>9</v>
@@ -49987,7 +49987,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1850" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1850" t="s">
         <v>9</v>
@@ -50013,7 +50013,7 @@
         <v>0.75</v>
       </c>
       <c r="G1851" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="H1851" t="s">
         <v>9</v>
@@ -50039,7 +50039,7 @@
         <v>0.751999974250793</v>
       </c>
       <c r="G1852" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="H1852" t="s">
         <v>9</v>
@@ -50065,7 +50065,7 @@
         <v>0.755999982357025</v>
       </c>
       <c r="G1853" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="H1853" t="s">
         <v>9</v>
@@ -50091,7 +50091,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1854" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1854" t="s">
         <v>9</v>
@@ -50117,7 +50117,7 @@
         <v>0.763999998569489</v>
       </c>
       <c r="G1855" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="H1855" t="s">
         <v>9</v>
@@ -50143,7 +50143,7 @@
         <v>0.754000008106232</v>
       </c>
       <c r="G1856" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="H1856" t="s">
         <v>9</v>
@@ -50169,7 +50169,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1857" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1857" t="s">
         <v>9</v>
@@ -50195,7 +50195,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1858" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1858" t="s">
         <v>9</v>
@@ -50221,7 +50221,7 @@
         <v>0.741999983787537</v>
       </c>
       <c r="G1859" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="H1859" t="s">
         <v>9</v>
@@ -50247,7 +50247,7 @@
         <v>0.769999980926514</v>
       </c>
       <c r="G1860" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="H1860" t="s">
         <v>9</v>
@@ -50273,7 +50273,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1861" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1861" t="s">
         <v>9</v>
@@ -50299,7 +50299,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1862" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1862" t="s">
         <v>9</v>
@@ -50325,7 +50325,7 @@
         <v>0.804000020027161</v>
       </c>
       <c r="G1863" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="H1863" t="s">
         <v>9</v>
@@ -50351,7 +50351,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1864" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1864" t="s">
         <v>9</v>
@@ -50377,7 +50377,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1865" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1865" t="s">
         <v>9</v>
@@ -50403,7 +50403,7 @@
         <v>0.805999994277954</v>
       </c>
       <c r="G1866" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="H1866" t="s">
         <v>9</v>
@@ -50429,7 +50429,7 @@
         <v>0.796000003814697</v>
       </c>
       <c r="G1867" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="H1867" t="s">
         <v>9</v>
@@ -50455,7 +50455,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1868" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1868" t="s">
         <v>9</v>
@@ -50481,7 +50481,7 @@
         <v>0.810000002384186</v>
       </c>
       <c r="G1869" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="H1869" t="s">
         <v>9</v>
@@ -50507,7 +50507,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1870" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1870" t="s">
         <v>9</v>
@@ -50533,7 +50533,7 @@
         <v>0.797999978065491</v>
       </c>
       <c r="G1871" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="H1871" t="s">
         <v>9</v>
@@ -50559,7 +50559,7 @@
         <v>0.814000010490417</v>
       </c>
       <c r="G1872" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="H1872" t="s">
         <v>9</v>
@@ -50585,7 +50585,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1873" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1873" t="s">
         <v>9</v>
@@ -50611,7 +50611,7 @@
         <v>0.801999986171722</v>
       </c>
       <c r="G1874" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="H1874" t="s">
         <v>9</v>
@@ -50637,7 +50637,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1875" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1875" t="s">
         <v>9</v>
@@ -50663,7 +50663,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1876" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1876" t="s">
         <v>9</v>
@@ -50689,7 +50689,7 @@
         <v>0.794000029563904</v>
       </c>
       <c r="G1877" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="H1877" t="s">
         <v>9</v>
@@ -50715,7 +50715,7 @@
         <v>0.800000011920929</v>
       </c>
       <c r="G1878" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="H1878" t="s">
         <v>9</v>
@@ -50741,7 +50741,7 @@
         <v>0.808000028133392</v>
       </c>
       <c r="G1879" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="H1879" t="s">
         <v>9</v>
@@ -50767,7 +50767,7 @@
         <v>0.790000021457672</v>
       </c>
       <c r="G1880" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="H1880" t="s">
         <v>9</v>
@@ -50793,7 +50793,7 @@
         <v>0.772000014781952</v>
       </c>
       <c r="G1881" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="H1881" t="s">
         <v>9</v>
@@ -50819,7 +50819,7 @@
         <v>0.776000022888184</v>
       </c>
       <c r="G1882" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="H1882" t="s">
         <v>9</v>
@@ -50845,7 +50845,7 @@
         <v>0.762000024318695</v>
       </c>
       <c r="G1883" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="H1883" t="s">
         <v>9</v>
@@ -50871,7 +50871,7 @@
         <v>0.76800000667572</v>
       </c>
       <c r="G1884" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="H1884" t="s">
         <v>9</v>
@@ -50897,7 +50897,7 @@
         <v>0.734000027179718</v>
       </c>
       <c r="G1885" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="H1885" t="s">
         <v>9</v>
@@ -50923,7 +50923,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1886" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="H1886" t="s">
         <v>9</v>
@@ -50949,7 +50949,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1887" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="H1887" t="s">
         <v>9</v>
@@ -50975,7 +50975,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1888" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1888" t="s">
         <v>9</v>
@@ -51001,7 +51001,7 @@
         <v>0.730000019073486</v>
       </c>
       <c r="G1889" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="H1889" t="s">
         <v>9</v>
@@ -51027,7 +51027,7 @@
         <v>0.717999994754791</v>
       </c>
       <c r="G1890" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="H1890" t="s">
         <v>9</v>
@@ -51053,7 +51053,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1891" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1891" t="s">
         <v>9</v>
@@ -51079,7 +51079,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1892" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1892" t="s">
         <v>9</v>
@@ -51105,7 +51105,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1893" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1893" t="s">
         <v>9</v>
@@ -51131,7 +51131,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1894" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1894" t="s">
         <v>9</v>
@@ -51157,7 +51157,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1895" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1895" t="s">
         <v>9</v>
@@ -51183,7 +51183,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1896" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1896" t="s">
         <v>9</v>
@@ -51209,7 +51209,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51287,7 +51287,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1900" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1900" t="s">
         <v>9</v>
@@ -51313,7 +51313,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1901" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1901" t="s">
         <v>9</v>
@@ -51339,7 +51339,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1902" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1902" t="s">
         <v>9</v>
@@ -51365,7 +51365,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1903" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1903" t="s">
         <v>9</v>
@@ -51443,7 +51443,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1906" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1906" t="s">
         <v>9</v>
@@ -51547,7 +51547,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1910" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1910" t="s">
         <v>9</v>
@@ -51625,7 +51625,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1913" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1913" t="s">
         <v>9</v>
@@ -51651,7 +51651,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1914" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1914" t="s">
         <v>9</v>
@@ -51677,7 +51677,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1915" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1915" t="s">
         <v>9</v>
@@ -51755,7 +51755,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1918" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1918" t="s">
         <v>9</v>
@@ -51833,7 +51833,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1921" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1921" t="s">
         <v>9</v>
@@ -51859,7 +51859,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51885,7 +51885,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1923" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1923" t="s">
         <v>9</v>
@@ -51911,7 +51911,7 @@
         <v>0.712000012397766</v>
       </c>
       <c r="G1924" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="H1924" t="s">
         <v>9</v>
@@ -51989,7 +51989,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G1927" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H1927" t="s">
         <v>9</v>
@@ -52015,7 +52015,7 @@
         <v>0.709999978542328</v>
       </c>
       <c r="G1928" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="H1928" t="s">
         <v>9</v>
@@ -52067,7 +52067,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52145,7 +52145,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52223,7 +52223,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1936" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1936" t="s">
         <v>9</v>
@@ -52249,7 +52249,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1937" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1937" t="s">
         <v>9</v>
@@ -52301,7 +52301,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>329</v>
+        <v>379</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52353,7 +52353,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1941" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1941" t="s">
         <v>9</v>
@@ -52483,7 +52483,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1946" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1946" t="s">
         <v>9</v>
@@ -52509,7 +52509,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1947" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H1947" t="s">
         <v>9</v>
@@ -54537,7 +54537,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2025" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2025" t="s">
         <v>9</v>
@@ -54563,7 +54563,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2026" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2026" t="s">
         <v>9</v>
@@ -57085,7 +57085,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G2123" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="H2123" t="s">
         <v>9</v>
@@ -57163,7 +57163,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2126" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2126" t="s">
         <v>9</v>
@@ -58151,7 +58151,7 @@
         <v>0.702000021934509</v>
       </c>
       <c r="G2164" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="H2164" t="s">
         <v>9</v>
@@ -67285,7 +67285,7 @@
     </row>
     <row r="2516">
       <c r="A2516" s="1" t="n">
-        <v>45981.6173958333</v>
+        <v>45981.3333333333</v>
       </c>
       <c r="B2516" t="n">
         <v>15000</v>
@@ -67306,6 +67306,32 @@
         <v>514</v>
       </c>
       <c r="H2516" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2517">
+      <c r="A2517" s="1" t="n">
+        <v>45982.6609722222</v>
+      </c>
+      <c r="B2517" t="n">
+        <v>8020</v>
+      </c>
+      <c r="C2517" t="n">
+        <v>0.555999994277954</v>
+      </c>
+      <c r="D2517" t="n">
+        <v>0.550000011920929</v>
+      </c>
+      <c r="E2517" t="n">
+        <v>0.555999994277954</v>
+      </c>
+      <c r="F2517" t="n">
+        <v>0.554000020027161</v>
+      </c>
+      <c r="G2517" t="s">
+        <v>511</v>
+      </c>
+      <c r="H2517" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -38,85 +38,85 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815495252609</t>
+    <t xml:space="preserve">0.235815480351448</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394701361656</t>
+    <t xml:space="preserve">0.235394716262817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249117732048</t>
+    <t xml:space="preserve">0.228249087929726</t>
   </si>
   <si>
     <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581333756447</t>
+    <t xml:space="preserve">0.218581348657608</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099103093147</t>
+    <t xml:space="preserve">0.211099117994308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21731986105442</t>
+    <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921487927437</t>
+    <t xml:space="preserve">0.228921517729759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071791887283</t>
+    <t xml:space="preserve">0.227071806788445</t>
   </si>
   <si>
     <t xml:space="preserve">0.233293384313583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228417411446571</t>
+    <t xml:space="preserve">0.22841739654541</t>
   </si>
   <si>
     <t xml:space="preserve">0.231527790427208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.229762211441994</t>
+    <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598274230957</t>
+    <t xml:space="preserve">0.239598229527473</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310569405556</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
     <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784891724586</t>
+    <t xml:space="preserve">0.222784906625748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.21437780559063</t>
+    <t xml:space="preserve">0.214377820491791</t>
   </si>
   <si>
     <t xml:space="preserve">0.211014956235886</t>
   </si>
   <si>
-    <t xml:space="preserve">0.20597068965435</t>
+    <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767146587372</t>
+    <t xml:space="preserve">0.201767131686211</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563588619232</t>
+    <t xml:space="preserve">0.197563603520393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360045552254</t>
+    <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.196722894906998</t>
+    <t xml:space="preserve">0.196722880005836</t>
   </si>
   <si>
     <t xml:space="preserve">0.202355399727821</t>
@@ -128,88 +128,88 @@
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214157700539</t>
+    <t xml:space="preserve">0.205214127898216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.208912745118141</t>
+    <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
     <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218514204025</t>
+    <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616583108902</t>
+    <t xml:space="preserve">0.222616568207741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22698763012886</t>
+    <t xml:space="preserve">0.226987615227699</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031881809235</t>
+    <t xml:space="preserve">0.232031852006912</t>
   </si>
   <si>
     <t xml:space="preserve">0.236235424876213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.24127970635891</t>
+    <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483219623566</t>
+    <t xml:space="preserve">0.245483204722404</t>
   </si>
   <si>
-    <t xml:space="preserve">0.252208918333054</t>
+    <t xml:space="preserve">0.252208948135376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093863725662</t>
+    <t xml:space="preserve">0.258093923330307</t>
   </si>
   <si>
-    <t xml:space="preserve">0.263138145208359</t>
+    <t xml:space="preserve">0.263138175010681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.268182396888733</t>
+    <t xml:space="preserve">0.268182426691055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.273226648569107</t>
+    <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281632959842682</t>
+    <t xml:space="preserve">0.281632989645004</t>
   </si>
   <si>
-    <t xml:space="preserve">0.285836517810822</t>
+    <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
     <t xml:space="preserve">0.292562186717987</t>
   </si>
   <si>
-    <t xml:space="preserve">0.298447132110596</t>
+    <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332137107849</t>
+    <t xml:space="preserve">0.304332166910172</t>
   </si>
   <si>
     <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531049251556</t>
+    <t xml:space="preserve">0.317531079053879</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827816009521</t>
+    <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336279153823853</t>
+    <t xml:space="preserve">0.336279183626175</t>
   </si>
   <si>
     <t xml:space="preserve">0.356455355882645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36318102478981</t>
+    <t xml:space="preserve">0.363181054592133</t>
   </si>
   <si>
     <t xml:space="preserve">0.378313809633255</t>
   </si>
   <si>
-    <t xml:space="preserve">0.411941379308701</t>
+    <t xml:space="preserve">0.411941409111023</t>
   </si>
   <si>
     <t xml:space="preserve">0.42034849524498</t>
@@ -224,49 +224,49 @@
     <t xml:space="preserve">0.472471743822098</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400881290436</t>
+    <t xml:space="preserve">0.483400911092758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055836677551</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
   </si>
   <si>
-    <t xml:space="preserve">0.496011644601822</t>
+    <t xml:space="preserve">0.496011584997177</t>
   </si>
   <si>
     <t xml:space="preserve">0.49651563167572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.492307901382446</t>
+    <t xml:space="preserve">0.492307871580124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670952796936</t>
+    <t xml:space="preserve">0.580670833587646</t>
   </si>
   <si>
     <t xml:space="preserve">0.589086413383484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.63957953453064</t>
+    <t xml:space="preserve">0.639579594135284</t>
   </si>
   <si>
     <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241674900055</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641051530838</t>
+    <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61854076385498</t>
+    <t xml:space="preserve">0.618540823459625</t>
   </si>
   <si>
     <t xml:space="preserve">0.622748494148254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.572255432605743</t>
+    <t xml:space="preserve">0.572255313396454</t>
   </si>
   <si>
     <t xml:space="preserve">0.525970041751862</t>
@@ -275,19 +275,19 @@
     <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100171089172</t>
+    <t xml:space="preserve">0.488100200891495</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931211471558</t>
+    <t xml:space="preserve">0.504931271076202</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008752822876</t>
+    <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
     <t xml:space="preserve">0.509139001369476</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892381191254</t>
+    <t xml:space="preserve">0.483892410993576</t>
   </si>
   <si>
     <t xml:space="preserve">0.51334673166275</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554461956024</t>
+    <t xml:space="preserve">0.517554521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269100904465</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061430215836</t>
+    <t xml:space="preserve">0.467061370611191</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853580713272</t>
+    <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
     <t xml:space="preserve">0.479684621095657</t>
@@ -317,28 +317,28 @@
     <t xml:space="preserve">0.43339928984642</t>
   </si>
   <si>
-    <t xml:space="preserve">0.437607079744339</t>
+    <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
     <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230360031128</t>
+    <t xml:space="preserve">0.450230300426483</t>
   </si>
   <si>
     <t xml:space="preserve">0.446022540330887</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645850419998</t>
+    <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944969177246</t>
+    <t xml:space="preserve">0.403944909572601</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776009559631</t>
+    <t xml:space="preserve">0.420776039361954</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191529750824</t>
+    <t xml:space="preserve">0.429191559553146</t>
   </si>
   <si>
     <t xml:space="preserve">0.534385502338409</t>
@@ -347,7 +347,7 @@
     <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
-    <t xml:space="preserve">0.475476861000061</t>
+    <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
     <t xml:space="preserve">0.410677373409271</t>
@@ -356,10 +356,10 @@
     <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409807443619</t>
+    <t xml:space="preserve">0.417409777641296</t>
   </si>
   <si>
-    <t xml:space="preserve">0.380381494760513</t>
+    <t xml:space="preserve">0.380381524562836</t>
   </si>
   <si>
     <t xml:space="preserve">0.414043605327606</t>
@@ -368,67 +368,67 @@
     <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726661682129</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
-    <t xml:space="preserve">0.441814750432968</t>
+    <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092923402786</t>
+    <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
     <t xml:space="preserve">0.405628055334091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.408994257450104</t>
+    <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
     <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.392163217067719</t>
+    <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895680904388</t>
+    <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
     <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846333026886</t>
+    <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.402261853218079</t>
+    <t xml:space="preserve">0.402261823415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529419183731</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113928794861</t>
+    <t xml:space="preserve">0.387113898992538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649060726166</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
-    <t xml:space="preserve">0.323155999183655</t>
+    <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
     <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620837450027</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32988840341568</t>
+    <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32820525765419</t>
+    <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522171497345</t>
+    <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3248390853405</t>
+    <t xml:space="preserve">0.324839115142822</t>
   </si>
   <si>
     <t xml:space="preserve">0.353451818227768</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768761873245</t>
+    <t xml:space="preserve">0.3517687022686</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036327838898</t>
@@ -446,19 +446,19 @@
     <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
-    <t xml:space="preserve">0.338303923606873</t>
+    <t xml:space="preserve">0.33830389380455</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34335321187973</t>
+    <t xml:space="preserve">0.343353182077408</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33325457572937</t>
+    <t xml:space="preserve">0.333254635334015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.31978976726532</t>
+    <t xml:space="preserve">0.319789797067642</t>
   </si>
   <si>
     <t xml:space="preserve">0.334937691688538</t>
@@ -470,13 +470,13 @@
     <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358501195907593</t>
+    <t xml:space="preserve">0.358501136302948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.368599772453308</t>
+    <t xml:space="preserve">0.36859980225563</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363550513982773</t>
+    <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
     <t xml:space="preserve">0.390480130910873</t>
@@ -488,16 +488,16 @@
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797014951706</t>
+    <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698378801346</t>
+    <t xml:space="preserve">0.378698408603668</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
   </si>
   <si>
-    <t xml:space="preserve">0.375332236289978</t>
+    <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
     <t xml:space="preserve">0.370282888412476</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">0.377015352249146</t>
   </si>
   <si>
-    <t xml:space="preserve">0.371965974569321</t>
+    <t xml:space="preserve">0.371966004371643</t>
   </si>
   <si>
     <t xml:space="preserve">0.385430842638016</t>
   </si>
   <si>
-    <t xml:space="preserve">0.365233570337296</t>
+    <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
     <t xml:space="preserve">0.538593232631683</t>
@@ -521,31 +521,31 @@
     <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216602325439</t>
+    <t xml:space="preserve">0.55121648311615</t>
   </si>
   <si>
-    <t xml:space="preserve">0.489783316850662</t>
+    <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733879566193</t>
+    <t xml:space="preserve">0.484733909368515</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47631847858429</t>
+    <t xml:space="preserve">0.476318418979645</t>
   </si>
   <si>
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466343402863</t>
+    <t xml:space="preserve">0.491466403007507</t>
   </si>
   <si>
-    <t xml:space="preserve">0.498198837041855</t>
+    <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
     <t xml:space="preserve">0.553741276264191</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528494715690613</t>
+    <t xml:space="preserve">0.528494656085968</t>
   </si>
   <si>
     <t xml:space="preserve">0.520079076290131</t>
@@ -560,52 +560,52 @@
     <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.523445308208466</t>
+    <t xml:space="preserve">0.52344536781311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.506614327430725</t>
+    <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
     <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50324809551239</t>
+    <t xml:space="preserve">0.503248035907745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297383785248</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501564979553223</t>
+    <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149489164352</t>
+    <t xml:space="preserve">0.49314945936203</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029907226562</t>
+    <t xml:space="preserve">0.515029788017273</t>
   </si>
   <si>
     <t xml:space="preserve">0.53354400396347</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473620891571</t>
+    <t xml:space="preserve">0.560473680496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227060317993</t>
+    <t xml:space="preserve">0.535227119922638</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107448577881</t>
+    <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550374925136566</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396079540253</t>
+    <t xml:space="preserve">0.518396019935608</t>
   </si>
   <si>
     <t xml:space="preserve">0.516712963581085</t>
@@ -626,25 +626,25 @@
     <t xml:space="preserve">0.526592314243317</t>
   </si>
   <si>
-    <t xml:space="preserve">0.528330147266388</t>
+    <t xml:space="preserve">0.528330206871033</t>
   </si>
   <si>
-    <t xml:space="preserve">0.545709550380707</t>
+    <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
     <t xml:space="preserve">0.552661180496216</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185335636139</t>
+    <t xml:space="preserve">0.549185395240784</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447383403778</t>
+    <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399192333221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971538543701</t>
+    <t xml:space="preserve">0.543971598148346</t>
   </si>
   <si>
     <t xml:space="preserve">0.54223358631134</t>
@@ -659,40 +659,40 @@
     <t xml:space="preserve">0.568302571773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559612929821014</t>
+    <t xml:space="preserve">0.55961287021637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550923228263855</t>
+    <t xml:space="preserve">0.5509232878685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378517150879</t>
+    <t xml:space="preserve">0.521378576755524</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.514426827430725</t>
+    <t xml:space="preserve">0.51442676782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.502261221408844</t>
+    <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503999173641205</t>
+    <t xml:space="preserve">0.50399923324585</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491833746433258</t>
+    <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571609258652</t>
+    <t xml:space="preserve">0.493571698665619</t>
   </si>
   <si>
-    <t xml:space="preserve">0.524854302406311</t>
+    <t xml:space="preserve">0.524854362010956</t>
   </si>
   <si>
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640564918518</t>
+    <t xml:space="preserve">0.519640505313873</t>
   </si>
   <si>
     <t xml:space="preserve">0.608274936676025</t>
@@ -701,22 +701,22 @@
     <t xml:space="preserve">0.587419748306274</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323187351227</t>
+    <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585294723511</t>
+    <t xml:space="preserve">0.599585235118866</t>
   </si>
   <si>
     <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594371497631073</t>
+    <t xml:space="preserve">0.594371557235718</t>
   </si>
   <si>
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58915764093399</t>
+    <t xml:space="preserve">0.589157700538635</t>
   </si>
   <si>
     <t xml:space="preserve">0.639557600021362</t>
@@ -728,28 +728,28 @@
     <t xml:space="preserve">0.714288592338562</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364478111267</t>
+    <t xml:space="preserve">0.667364418506622</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061079978943</t>
+    <t xml:space="preserve">0.603061139583588</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61696445941925</t>
+    <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392113208771</t>
+    <t xml:space="preserve">0.627392053604126</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605850696564</t>
+    <t xml:space="preserve">0.632605791091919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653461039066315</t>
+    <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6447713971138</t>
+    <t xml:space="preserve">0.644771337509155</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
@@ -773,25 +773,25 @@
     <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943903446198</t>
+    <t xml:space="preserve">0.583943963050842</t>
   </si>
   <si>
     <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604798972606659</t>
+    <t xml:space="preserve">0.604799032211304</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778416633606</t>
+    <t xml:space="preserve">0.571778476238251</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50573718547821</t>
+    <t xml:space="preserve">0.505737125873566</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557874977588654</t>
+    <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
     <t xml:space="preserve">0.573516368865967</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">0.634343862533569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985194206238</t>
+    <t xml:space="preserve">0.649985134601593</t>
   </si>
   <si>
     <t xml:space="preserve">0.648247241973877</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636081755161285</t>
+    <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
     <t xml:space="preserve">0.683005809783936</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743762016296</t>
+    <t xml:space="preserve">0.684743702411652</t>
   </si>
   <si>
-    <t xml:space="preserve">0.662150740623474</t>
+    <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316167831421</t>
+    <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656936824321747</t>
+    <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674776554108</t>
+    <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509408950806</t>
+    <t xml:space="preserve">0.646509349346161</t>
   </si>
   <si>
-    <t xml:space="preserve">0.606537044048309</t>
+    <t xml:space="preserve">0.606536984443665</t>
   </si>
   <si>
-    <t xml:space="preserve">0.615226686000824</t>
+    <t xml:space="preserve">0.615226626396179</t>
   </si>
   <si>
     <t xml:space="preserve">0.613488674163818</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">0.64178854227066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.636410355567932</t>
+    <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
     <t xml:space="preserve">0.632824957370758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629239618778229</t>
+    <t xml:space="preserve">0.629239559173584</t>
   </si>
   <si>
-    <t xml:space="preserve">0.614897966384888</t>
+    <t xml:space="preserve">0.614897906780243</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
   </si>
   <si>
-    <t xml:space="preserve">0.620276033878326</t>
+    <t xml:space="preserve">0.620276093482971</t>
   </si>
   <si>
     <t xml:space="preserve">0.609519839286804</t>
@@ -884,22 +884,22 @@
     <t xml:space="preserve">0.600556254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602348983287811</t>
+    <t xml:space="preserve">0.602349042892456</t>
   </si>
   <si>
     <t xml:space="preserve">0.607727110385895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596970856189728</t>
+    <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
     <t xml:space="preserve">0.6238614320755</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690635681152</t>
+    <t xml:space="preserve">0.616690695285797</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618483364582062</t>
+    <t xml:space="preserve">0.618483304977417</t>
   </si>
   <si>
     <t xml:space="preserve">0.604141712188721</t>
@@ -908,34 +908,34 @@
     <t xml:space="preserve">0.588007390499115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.58980005979538</t>
+    <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577251136302948</t>
+    <t xml:space="preserve">0.577251076698303</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593385457992554</t>
+    <t xml:space="preserve">0.593385517597198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573665738105774</t>
+    <t xml:space="preserve">0.573665678501129</t>
   </si>
   <si>
     <t xml:space="preserve">0.580836534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582629263401031</t>
+    <t xml:space="preserve">0.582629203796387</t>
   </si>
   <si>
     <t xml:space="preserve">0.579043924808502</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559324085712433</t>
+    <t xml:space="preserve">0.559324026107788</t>
   </si>
   <si>
     <t xml:space="preserve">0.56828761100769</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552153289318085</t>
+    <t xml:space="preserve">0.55215322971344</t>
   </si>
   <si>
     <t xml:space="preserve">0.571873068809509</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">0.598763585090637</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595178127288818</t>
+    <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
     <t xml:space="preserve">0.631032347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613105237483978</t>
+    <t xml:space="preserve">0.613105297088623</t>
   </si>
   <si>
     <t xml:space="preserve">0.611312508583069</t>
@@ -980,7 +980,7 @@
     <t xml:space="preserve">0.566494941711426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.564702153205872</t>
+    <t xml:space="preserve">0.564702212810516</t>
   </si>
   <si>
     <t xml:space="preserve">0.622068762779236</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">0.648959338665009</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650752127170563</t>
+    <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
     <t xml:space="preserve">0.654337525367737</t>
@@ -1022,19 +1022,19 @@
     <t xml:space="preserve">0.645374000072479</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544736862183</t>
+    <t xml:space="preserve">0.652544677257538</t>
   </si>
   <si>
     <t xml:space="preserve">0.64358127117157</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166669368744</t>
+    <t xml:space="preserve">0.647166609764099</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264456748962</t>
+    <t xml:space="preserve">0.672264575958252</t>
   </si>
   <si>
-    <t xml:space="preserve">0.670471847057343</t>
+    <t xml:space="preserve">0.670471787452698</t>
   </si>
   <si>
     <t xml:space="preserve">0.684813439846039</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">0.683020770549774</t>
   </si>
   <si>
-    <t xml:space="preserve">0.690191566944122</t>
+    <t xml:space="preserve">0.690191626548767</t>
   </si>
   <si>
     <t xml:space="preserve">0.681228041648865</t>
@@ -1052,55 +1052,55 @@
     <t xml:space="preserve">0.715289413928986</t>
   </si>
   <si>
-    <t xml:space="preserve">0.738594591617584</t>
+    <t xml:space="preserve">0.738594651222229</t>
   </si>
   <si>
     <t xml:space="preserve">0.743972718715668</t>
   </si>
   <si>
-    <t xml:space="preserve">0.711704075336456</t>
+    <t xml:space="preserve">0.711704015731812</t>
   </si>
   <si>
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.735009133815765</t>
+    <t xml:space="preserve">0.73500919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460329532623</t>
+    <t xml:space="preserve">0.722460210323334</t>
   </si>
   <si>
     <t xml:space="preserve">0.745765447616577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73680192232132</t>
+    <t xml:space="preserve">0.736801981925964</t>
   </si>
   <si>
-    <t xml:space="preserve">0.751143515110016</t>
+    <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742180049419403</t>
+    <t xml:space="preserve">0.742180109024048</t>
   </si>
   <si>
-    <t xml:space="preserve">0.708118677139282</t>
+    <t xml:space="preserve">0.708118617534637</t>
   </si>
   <si>
     <t xml:space="preserve">0.704533219337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713496744632721</t>
+    <t xml:space="preserve">0.713496804237366</t>
   </si>
   <si>
     <t xml:space="preserve">0.700947821140289</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706325948238373</t>
+    <t xml:space="preserve">0.706325888633728</t>
   </si>
   <si>
-    <t xml:space="preserve">0.697362422943115</t>
+    <t xml:space="preserve">0.69736236333847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.71708220243454</t>
+    <t xml:space="preserve">0.717082142829895</t>
   </si>
   <si>
     <t xml:space="preserve">0.724252998828888</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">0.688398838043213</t>
   </si>
   <si>
-    <t xml:space="preserve">0.677642583847046</t>
+    <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
     <t xml:space="preserve">0.675849914550781</t>
@@ -1121,7 +1121,7 @@
     <t xml:space="preserve">0.720667600631714</t>
   </si>
   <si>
-    <t xml:space="preserve">0.726045727729797</t>
+    <t xml:space="preserve">0.726045668125153</t>
   </si>
   <si>
     <t xml:space="preserve">0.718874871730804</t>
@@ -1133,22 +1133,22 @@
     <t xml:space="preserve">0.691984295845032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695569694042206</t>
+    <t xml:space="preserve">0.695569753646851</t>
   </si>
   <si>
     <t xml:space="preserve">0.665459334850311</t>
   </si>
   <si>
-    <t xml:space="preserve">0.659898400306702</t>
+    <t xml:space="preserve">0.659898459911346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.650630235671997</t>
+    <t xml:space="preserve">0.650630176067352</t>
   </si>
   <si>
     <t xml:space="preserve">0.658044755458832</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652483880519867</t>
+    <t xml:space="preserve">0.652483820915222</t>
   </si>
   <si>
     <t xml:space="preserve">0.654337465763092</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">0.661752045154572</t>
   </si>
   <si>
-    <t xml:space="preserve">0.663605690002441</t>
+    <t xml:space="preserve">0.663605749607086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646922945976257</t>
+    <t xml:space="preserve">0.646922886371613</t>
   </si>
   <si>
     <t xml:space="preserve">0.645069241523743</t>
@@ -1181,7 +1181,7 @@
     <t xml:space="preserve">0.643215596675873</t>
   </si>
   <si>
-    <t xml:space="preserve">0.635801017284393</t>
+    <t xml:space="preserve">0.635800957679749</t>
   </si>
   <si>
     <t xml:space="preserve">0.633947372436523</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">0.62097179889679</t>
   </si>
   <si>
-    <t xml:space="preserve">0.626532733440399</t>
+    <t xml:space="preserve">0.626532793045044</t>
   </si>
   <si>
     <t xml:space="preserve">0.613557279109955</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">0.572776973247528</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583898842334747</t>
+    <t xml:space="preserve">0.583898901939392</t>
   </si>
   <si>
     <t xml:space="preserve">0.578337907791138</t>
@@ -1220,16 +1220,16 @@
     <t xml:space="preserve">0.602435350418091</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604289054870605</t>
+    <t xml:space="preserve">0.604288995265961</t>
   </si>
   <si>
-    <t xml:space="preserve">0.593167126178741</t>
+    <t xml:space="preserve">0.593167066574097</t>
   </si>
   <si>
     <t xml:space="preserve">0.600581705570221</t>
   </si>
   <si>
-    <t xml:space="preserve">0.595020771026611</t>
+    <t xml:space="preserve">0.595020830631256</t>
   </si>
   <si>
     <t xml:space="preserve">0.589459776878357</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">0.557947814464569</t>
   </si>
   <si>
-    <t xml:space="preserve">0.541264951229095</t>
+    <t xml:space="preserve">0.54126501083374</t>
   </si>
   <si>
     <t xml:space="preserve">0.546825885772705</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">0.563508749008179</t>
   </si>
   <si>
-    <t xml:space="preserve">0.570923388004303</t>
+    <t xml:space="preserve">0.570923328399658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.61726450920105</t>
+    <t xml:space="preserve">0.617264568805695</t>
   </si>
   <si>
     <t xml:space="preserve">0.624679148197174</t>
@@ -67311,10 +67311,10 @@
     </row>
     <row r="2517">
       <c r="A2517" s="1" t="n">
-        <v>45982.6609722222</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2517" t="n">
-        <v>8020</v>
+        <v>15000</v>
       </c>
       <c r="C2517" t="n">
         <v>0.555999994277954</v>
@@ -67332,6 +67332,32 @@
         <v>511</v>
       </c>
       <c r="H2517" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2518">
+      <c r="A2518" s="1" t="n">
+        <v>45985.5829976852</v>
+      </c>
+      <c r="B2518" t="n">
+        <v>33283</v>
+      </c>
+      <c r="C2518" t="n">
+        <v>0.558000028133392</v>
+      </c>
+      <c r="D2518" t="n">
+        <v>0.547999978065491</v>
+      </c>
+      <c r="E2518" t="n">
+        <v>0.554000020027161</v>
+      </c>
+      <c r="F2518" t="n">
+        <v>0.558000028133392</v>
+      </c>
+      <c r="G2518" t="s">
+        <v>513</v>
+      </c>
+      <c r="H2518" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="515">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235815480351448</t>
+    <t xml:space="preserve">0.23581551015377</t>
   </si>
   <si>
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394716262817</t>
+    <t xml:space="preserve">0.235394701361656</t>
   </si>
   <si>
     <t xml:space="preserve">0.228249087929726</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">0.216899931430817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.218581348657608</t>
+    <t xml:space="preserve">0.218581363558769</t>
   </si>
   <si>
     <t xml:space="preserve">0.21017424762249</t>
   </si>
   <si>
-    <t xml:space="preserve">0.211099117994308</t>
+    <t xml:space="preserve">0.211099103093147</t>
   </si>
   <si>
     <t xml:space="preserve">0.217319875955582</t>
@@ -68,13 +68,13 @@
     <t xml:space="preserve">0.228921517729759</t>
   </si>
   <si>
-    <t xml:space="preserve">0.227071806788445</t>
+    <t xml:space="preserve">0.227071791887283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293384313583</t>
+    <t xml:space="preserve">0.233293399214745</t>
   </si>
   <si>
-    <t xml:space="preserve">0.22841739654541</t>
+    <t xml:space="preserve">0.228417411446571</t>
   </si>
   <si>
     <t xml:space="preserve">0.231527790427208</t>
@@ -83,13 +83,13 @@
     <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598229527473</t>
+    <t xml:space="preserve">0.239598274230957</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310584306717</t>
+    <t xml:space="preserve">0.235310599207878</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868219017982</t>
+    <t xml:space="preserve">0.222868233919144</t>
   </si>
   <si>
     <t xml:space="preserve">0.222784906625748</t>
@@ -104,16 +104,16 @@
     <t xml:space="preserve">0.205970704555511</t>
   </si>
   <si>
-    <t xml:space="preserve">0.201767131686211</t>
+    <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
     <t xml:space="preserve">0.197563603520393</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360030651093</t>
+    <t xml:space="preserve">0.193360045552254</t>
   </si>
   <si>
-    <t xml:space="preserve">0.1936125010252</t>
+    <t xml:space="preserve">0.193612515926361</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
@@ -122,25 +122,25 @@
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607855200768</t>
+    <t xml:space="preserve">0.202607870101929</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187076210976</t>
   </si>
   <si>
-    <t xml:space="preserve">0.205214127898216</t>
+    <t xml:space="preserve">0.205214142799377</t>
   </si>
   <si>
     <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762500762939</t>
+    <t xml:space="preserve">0.210762515664101</t>
   </si>
   <si>
     <t xml:space="preserve">0.215218499302864</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616568207741</t>
+    <t xml:space="preserve">0.222616598010063</t>
   </si>
   <si>
     <t xml:space="preserve">0.226987615227699</t>
@@ -155,13 +155,13 @@
     <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483204722404</t>
+    <t xml:space="preserve">0.245483234524727</t>
   </si>
   <si>
     <t xml:space="preserve">0.252208948135376</t>
   </si>
   <si>
-    <t xml:space="preserve">0.258093923330307</t>
+    <t xml:space="preserve">0.258093893527985</t>
   </si>
   <si>
     <t xml:space="preserve">0.263138175010681</t>
@@ -173,13 +173,13 @@
     <t xml:space="preserve">0.273226678371429</t>
   </si>
   <si>
-    <t xml:space="preserve">0.281632989645004</t>
+    <t xml:space="preserve">0.281632959842682</t>
   </si>
   <si>
     <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562186717987</t>
+    <t xml:space="preserve">0.292562156915665</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">0.311057806015015</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531079053879</t>
+    <t xml:space="preserve">0.317531049251556</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827786207199</t>
+    <t xml:space="preserve">0.322827816009521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336279183626175</t>
+    <t xml:space="preserve">0.336279153823853</t>
   </si>
   <si>
-    <t xml:space="preserve">0.356455355882645</t>
+    <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
     <t xml:space="preserve">0.363181054592133</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">0.439684808254242</t>
   </si>
   <si>
-    <t xml:space="preserve">0.472471743822098</t>
+    <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400911092758</t>
+    <t xml:space="preserve">0.483400940895081</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055896282196</t>
+    <t xml:space="preserve">0.501055836677551</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
@@ -248,19 +248,19 @@
     <t xml:space="preserve">0.589086413383484</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639579594135284</t>
+    <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
     <t xml:space="preserve">0.715319216251373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.67324161529541</t>
+    <t xml:space="preserve">0.673241555690765</t>
   </si>
   <si>
-    <t xml:space="preserve">0.656410574913025</t>
+    <t xml:space="preserve">0.65641051530838</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618540823459625</t>
+    <t xml:space="preserve">0.618540704250336</t>
   </si>
   <si>
     <t xml:space="preserve">0.622748494148254</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">0.572255313396454</t>
   </si>
   <si>
-    <t xml:space="preserve">0.525970041751862</t>
+    <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
     <t xml:space="preserve">0.521762251853943</t>
   </si>
   <si>
-    <t xml:space="preserve">0.488100200891495</t>
+    <t xml:space="preserve">0.48810014128685</t>
   </si>
   <si>
     <t xml:space="preserve">0.504931271076202</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">0.547008812427521</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509139001369476</t>
+    <t xml:space="preserve">0.509138941764832</t>
   </si>
   <si>
     <t xml:space="preserve">0.483892410993576</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">0.530177772045135</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554521560669</t>
+    <t xml:space="preserve">0.517554461956024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269160509109</t>
+    <t xml:space="preserve">0.471269130706787</t>
   </si>
   <si>
-    <t xml:space="preserve">0.467061370611191</t>
+    <t xml:space="preserve">0.467061340808868</t>
   </si>
   <si>
     <t xml:space="preserve">0.500723481178284</t>
@@ -311,7 +311,7 @@
     <t xml:space="preserve">0.462853640317917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.479684621095657</t>
+    <t xml:space="preserve">0.47968465089798</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
@@ -320,7 +320,7 @@
     <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454438090324402</t>
+    <t xml:space="preserve">0.454438060522079</t>
   </si>
   <si>
     <t xml:space="preserve">0.450230300426483</t>
@@ -332,28 +332,28 @@
     <t xml:space="preserve">0.458645880222321</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944909572601</t>
+    <t xml:space="preserve">0.403944939374924</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420776039361954</t>
+    <t xml:space="preserve">0.420775979757309</t>
   </si>
   <si>
-    <t xml:space="preserve">0.429191559553146</t>
+    <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
     <t xml:space="preserve">0.534385502338409</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542801022529602</t>
+    <t xml:space="preserve">0.542801082134247</t>
   </si>
   <si>
     <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677373409271</t>
+    <t xml:space="preserve">0.410677403211594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983769655228</t>
+    <t xml:space="preserve">0.424983739852905</t>
   </si>
   <si>
     <t xml:space="preserve">0.417409777641296</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726691484451</t>
+    <t xml:space="preserve">0.415726661682129</t>
   </si>
   <si>
     <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092893600464</t>
+    <t xml:space="preserve">0.419092923402786</t>
   </si>
   <si>
     <t xml:space="preserve">0.405628055334091</t>
@@ -383,31 +383,31 @@
     <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311171293259</t>
+    <t xml:space="preserve">0.407311141490936</t>
   </si>
   <si>
     <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895651102066</t>
+    <t xml:space="preserve">0.398895621299744</t>
   </si>
   <si>
     <t xml:space="preserve">0.400578767061234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846362829208</t>
+    <t xml:space="preserve">0.393846333026886</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261823415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529419183731</t>
+    <t xml:space="preserve">0.395529448986053</t>
   </si>
   <si>
-    <t xml:space="preserve">0.387113898992538</t>
+    <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649090528488</t>
+    <t xml:space="preserve">0.373649120330811</t>
   </si>
   <si>
     <t xml:space="preserve">0.323155969381332</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">0.311374247074127</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620807647705</t>
+    <t xml:space="preserve">0.336620777845383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.329888373613358</t>
+    <t xml:space="preserve">0.32988840341568</t>
   </si>
   <si>
-    <t xml:space="preserve">0.328205287456512</t>
+    <t xml:space="preserve">0.32820525765419</t>
   </si>
   <si>
-    <t xml:space="preserve">0.326522201299667</t>
+    <t xml:space="preserve">0.32652223110199</t>
   </si>
   <si>
-    <t xml:space="preserve">0.324839115142822</t>
+    <t xml:space="preserve">0.3248390853405</t>
   </si>
   <si>
     <t xml:space="preserve">0.353451818227768</t>
@@ -437,40 +437,40 @@
     <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3517687022686</t>
+    <t xml:space="preserve">0.351768732070923</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036327838898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.350085645914078</t>
+    <t xml:space="preserve">0.3500856757164</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33830389380455</t>
+    <t xml:space="preserve">0.338303923606873</t>
   </si>
   <si>
     <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.343353182077408</t>
+    <t xml:space="preserve">0.34335321187973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.333254635334015</t>
+    <t xml:space="preserve">0.333254605531693</t>
   </si>
   <si>
-    <t xml:space="preserve">0.319789797067642</t>
+    <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.334937691688538</t>
+    <t xml:space="preserve">0.33493772149086</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33998703956604</t>
+    <t xml:space="preserve">0.339987009763718</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
   </si>
   <si>
-    <t xml:space="preserve">0.358501136302948</t>
+    <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
     <t xml:space="preserve">0.36859980225563</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">0.36355048418045</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480130910873</t>
+    <t xml:space="preserve">0.390480101108551</t>
   </si>
   <si>
     <t xml:space="preserve">0.397212564945221</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">0.388797044754028</t>
   </si>
   <si>
-    <t xml:space="preserve">0.378698408603668</t>
+    <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
     <t xml:space="preserve">0.382064610719681</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282888412476</t>
+    <t xml:space="preserve">0.370282858610153</t>
   </si>
   <si>
     <t xml:space="preserve">0.377015352249146</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">0.365233540534973</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538593232631683</t>
+    <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632122516632</t>
+    <t xml:space="preserve">0.559632182121277</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55121648311615</t>
+    <t xml:space="preserve">0.551216542720795</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.484733909368515</t>
+    <t xml:space="preserve">0.48473396897316</t>
   </si>
   <si>
     <t xml:space="preserve">0.476318418979645</t>
@@ -542,7 +542,7 @@
     <t xml:space="preserve">0.498198807239532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553741276264191</t>
+    <t xml:space="preserve">0.553741216659546</t>
   </si>
   <si>
     <t xml:space="preserve">0.528494656085968</t>
@@ -569,37 +569,37 @@
     <t xml:space="preserve">0.511663615703583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.503248035907745</t>
+    <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297443389893</t>
+    <t xml:space="preserve">0.508297383785248</t>
   </si>
   <si>
     <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.49314945936203</t>
+    <t xml:space="preserve">0.493149518966675</t>
   </si>
   <si>
     <t xml:space="preserve">0.50998055934906</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029788017273</t>
+    <t xml:space="preserve">0.515029847621918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53354400396347</t>
+    <t xml:space="preserve">0.533544063568115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.560473680496216</t>
+    <t xml:space="preserve">0.560473740100861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.535227119922638</t>
+    <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
     <t xml:space="preserve">0.557107508182526</t>
   </si>
   <si>
-    <t xml:space="preserve">0.550375044345856</t>
+    <t xml:space="preserve">0.5503751039505</t>
   </si>
   <si>
     <t xml:space="preserve">0.531860888004303</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">0.516712963581085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019789218903</t>
+    <t xml:space="preserve">0.537019848823547</t>
   </si>
   <si>
     <t xml:space="preserve">0.53180605173111</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">0.535281896591187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526592314243317</t>
+    <t xml:space="preserve">0.526592254638672</t>
   </si>
   <si>
     <t xml:space="preserve">0.528330206871033</t>
@@ -641,7 +641,7 @@
     <t xml:space="preserve">0.547447443008423</t>
   </si>
   <si>
-    <t xml:space="preserve">0.554399192333221</t>
+    <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
     <t xml:space="preserve">0.543971598148346</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">0.54223358631134</t>
   </si>
   <si>
-    <t xml:space="preserve">0.538757801055908</t>
+    <t xml:space="preserve">0.538757741451263</t>
   </si>
   <si>
     <t xml:space="preserve">0.540495693683624</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">0.568302571773529</t>
   </si>
   <si>
-    <t xml:space="preserve">0.55961287021637</t>
+    <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
     <t xml:space="preserve">0.5509232878685</t>
@@ -692,25 +692,25 @@
     <t xml:space="preserve">0.523116409778595</t>
   </si>
   <si>
-    <t xml:space="preserve">0.519640505313873</t>
+    <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
     <t xml:space="preserve">0.608274936676025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.587419748306274</t>
+    <t xml:space="preserve">0.587419807910919</t>
   </si>
   <si>
     <t xml:space="preserve">0.601323246955872</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585235118866</t>
+    <t xml:space="preserve">0.599585294723511</t>
   </si>
   <si>
     <t xml:space="preserve">0.590895652770996</t>
   </si>
   <si>
-    <t xml:space="preserve">0.594371557235718</t>
+    <t xml:space="preserve">0.594371497631073</t>
   </si>
   <si>
     <t xml:space="preserve">0.585681855678558</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">0.589157700538635</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557600021362</t>
+    <t xml:space="preserve">0.639557540416718</t>
   </si>
   <si>
     <t xml:space="preserve">0.669102430343628</t>
   </si>
   <si>
-    <t xml:space="preserve">0.714288592338562</t>
+    <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
     <t xml:space="preserve">0.667364418506622</t>
@@ -737,31 +737,31 @@
     <t xml:space="preserve">0.616964519023895</t>
   </si>
   <si>
-    <t xml:space="preserve">0.627392053604126</t>
+    <t xml:space="preserve">0.627392113208771</t>
   </si>
   <si>
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605791091919</t>
+    <t xml:space="preserve">0.632605850696564</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65346097946167</t>
+    <t xml:space="preserve">0.653461039066315</t>
   </si>
   <si>
-    <t xml:space="preserve">0.644771337509155</t>
+    <t xml:space="preserve">0.6447713971138</t>
   </si>
   <si>
     <t xml:space="preserve">0.629130005836487</t>
   </si>
   <si>
-    <t xml:space="preserve">0.625654220581055</t>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
     <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819707393646</t>
+    <t xml:space="preserve">0.637819647789001</t>
   </si>
   <si>
     <t xml:space="preserve">0.643033444881439</t>
@@ -773,13 +773,13 @@
     <t xml:space="preserve">0.610012829303741</t>
   </si>
   <si>
-    <t xml:space="preserve">0.583943963050842</t>
+    <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
     <t xml:space="preserve">0.592633545398712</t>
   </si>
   <si>
-    <t xml:space="preserve">0.604799032211304</t>
+    <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
     <t xml:space="preserve">0.571778476238251</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516368865967</t>
+    <t xml:space="preserve">0.573516428470612</t>
   </si>
   <si>
     <t xml:space="preserve">0.596109390258789</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">0.611750781536102</t>
   </si>
   <si>
-    <t xml:space="preserve">0.634343862533569</t>
+    <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
     <t xml:space="preserve">0.649985134601593</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">0.688219606876373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.684743702411652</t>
+    <t xml:space="preserve">0.684743762016296</t>
   </si>
   <si>
     <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316227436066</t>
+    <t xml:space="preserve">0.674316167831421</t>
   </si>
   <si>
     <t xml:space="preserve">0.656936883926392</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">0.658674836158752</t>
   </si>
   <si>
-    <t xml:space="preserve">0.646509349346161</t>
+    <t xml:space="preserve">0.646509289741516</t>
   </si>
   <si>
     <t xml:space="preserve">0.606536984443665</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">0.636410415172577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632824957370758</t>
+    <t xml:space="preserve">0.632825016975403</t>
   </si>
   <si>
     <t xml:space="preserve">0.629239559173584</t>
@@ -878,13 +878,13 @@
     <t xml:space="preserve">0.609519839286804</t>
   </si>
   <si>
-    <t xml:space="preserve">0.591592788696289</t>
+    <t xml:space="preserve">0.591592848300934</t>
   </si>
   <si>
     <t xml:space="preserve">0.600556254386902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.602349042892456</t>
+    <t xml:space="preserve">0.602348983287811</t>
   </si>
   <si>
     <t xml:space="preserve">0.607727110385895</t>
@@ -893,25 +893,25 @@
     <t xml:space="preserve">0.596970915794373</t>
   </si>
   <si>
-    <t xml:space="preserve">0.6238614320755</t>
+    <t xml:space="preserve">0.623861491680145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.616690695285797</t>
+    <t xml:space="preserve">0.616690635681152</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618483304977417</t>
+    <t xml:space="preserve">0.618483364582062</t>
   </si>
   <si>
     <t xml:space="preserve">0.604141712188721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.588007390499115</t>
+    <t xml:space="preserve">0.58800733089447</t>
   </si>
   <si>
     <t xml:space="preserve">0.589800119400024</t>
   </si>
   <si>
-    <t xml:space="preserve">0.577251076698303</t>
+    <t xml:space="preserve">0.577251136302948</t>
   </si>
   <si>
     <t xml:space="preserve">0.593385517597198</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">0.580836534500122</t>
   </si>
   <si>
-    <t xml:space="preserve">0.582629203796387</t>
+    <t xml:space="preserve">0.582629263401031</t>
   </si>
   <si>
     <t xml:space="preserve">0.579043924808502</t>
@@ -938,7 +938,7 @@
     <t xml:space="preserve">0.55215322971344</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571873068809509</t>
+    <t xml:space="preserve">0.571873009204865</t>
   </si>
   <si>
     <t xml:space="preserve">0.586214661598206</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">0.595178186893463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.631032347679138</t>
+    <t xml:space="preserve">0.631032288074493</t>
   </si>
   <si>
-    <t xml:space="preserve">0.613105297088623</t>
+    <t xml:space="preserve">0.613105237483978</t>
   </si>
   <si>
     <t xml:space="preserve">0.611312508583069</t>
   </si>
   <si>
-    <t xml:space="preserve">0.605934381484985</t>
+    <t xml:space="preserve">0.60593444108963</t>
   </si>
   <si>
     <t xml:space="preserve">0.548567831516266</t>
@@ -968,10 +968,10 @@
     <t xml:space="preserve">0.546775162220001</t>
   </si>
   <si>
-    <t xml:space="preserve">0.555738687515259</t>
+    <t xml:space="preserve">0.555738627910614</t>
   </si>
   <si>
-    <t xml:space="preserve">0.553945899009705</t>
+    <t xml:space="preserve">0.553945958614349</t>
   </si>
   <si>
     <t xml:space="preserve">0.557531356811523</t>
@@ -998,40 +998,40 @@
     <t xml:space="preserve">0.650752067565918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.654337525367737</t>
+    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.66330099105835</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674057185649872</t>
+    <t xml:space="preserve">0.674057245254517</t>
   </si>
   <si>
-    <t xml:space="preserve">0.66150826215744</t>
+    <t xml:space="preserve">0.661508321762085</t>
   </si>
   <si>
-    <t xml:space="preserve">0.657922923564911</t>
+    <t xml:space="preserve">0.657922863960266</t>
   </si>
   <si>
-    <t xml:space="preserve">0.665093660354614</t>
+    <t xml:space="preserve">0.665093719959259</t>
   </si>
   <si>
-    <t xml:space="preserve">0.666886448860168</t>
+    <t xml:space="preserve">0.666886389255524</t>
   </si>
   <si>
-    <t xml:space="preserve">0.645374000072479</t>
+    <t xml:space="preserve">0.645373940467834</t>
   </si>
   <si>
-    <t xml:space="preserve">0.652544677257538</t>
+    <t xml:space="preserve">0.652544736862183</t>
   </si>
   <si>
-    <t xml:space="preserve">0.64358127117157</t>
+    <t xml:space="preserve">0.643581211566925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.647166609764099</t>
+    <t xml:space="preserve">0.647166669368744</t>
   </si>
   <si>
-    <t xml:space="preserve">0.672264575958252</t>
+    <t xml:space="preserve">0.672264516353607</t>
   </si>
   <si>
     <t xml:space="preserve">0.670471787452698</t>
@@ -1064,22 +1064,22 @@
     <t xml:space="preserve">0.727838397026062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.73500919342041</t>
+    <t xml:space="preserve">0.735009253025055</t>
   </si>
   <si>
-    <t xml:space="preserve">0.722460210323334</t>
+    <t xml:space="preserve">0.722460269927979</t>
   </si>
   <si>
-    <t xml:space="preserve">0.745765447616577</t>
+    <t xml:space="preserve">0.745765507221222</t>
   </si>
   <si>
-    <t xml:space="preserve">0.736801981925964</t>
+    <t xml:space="preserve">0.73680192232132</t>
   </si>
   <si>
     <t xml:space="preserve">0.751143574714661</t>
   </si>
   <si>
-    <t xml:space="preserve">0.742180109024048</t>
+    <t xml:space="preserve">0.742180049419403</t>
   </si>
   <si>
     <t xml:space="preserve">0.708118617534637</t>
@@ -1088,19 +1088,19 @@
     <t xml:space="preserve">0.704533219337463</t>
   </si>
   <si>
-    <t xml:space="preserve">0.713496804237366</t>
+    <t xml:space="preserve">0.713496744632721</t>
   </si>
   <si>
-    <t xml:space="preserve">0.700947821140289</t>
+    <t xml:space="preserve">0.700947761535645</t>
   </si>
   <si>
-    <t xml:space="preserve">0.706325888633728</t>
+    <t xml:space="preserve">0.706325948238373</t>
   </si>
   <si>
     <t xml:space="preserve">0.69736236333847</t>
   </si>
   <si>
-    <t xml:space="preserve">0.717082142829895</t>
+    <t xml:space="preserve">0.71708220243454</t>
   </si>
   <si>
     <t xml:space="preserve">0.724252998828888</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">0.677642643451691</t>
   </si>
   <si>
-    <t xml:space="preserve">0.675849914550781</t>
+    <t xml:space="preserve">0.675849974155426</t>
   </si>
   <si>
     <t xml:space="preserve">0.720667600631714</t>
@@ -1133,7 +1133,7 @@
     <t xml:space="preserve">0.691984295845032</t>
   </si>
   <si>
-    <t xml:space="preserve">0.695569753646851</t>
+    <t xml:space="preserve">0.695569694042206</t>
   </si>
   <si>
     <t xml:space="preserve">0.665459334850311</t>
@@ -1149,9 +1149,6 @@
   </si>
   <si>
     <t xml:space="preserve">0.652483820915222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">0.654337465763092</t>
   </si>
   <si>
     <t xml:space="preserve">0.661752045154572</t>
@@ -51209,7 +51206,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1897" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1897" t="s">
         <v>9</v>
@@ -51235,7 +51232,7 @@
         <v>0.71399998664856</v>
       </c>
       <c r="G1898" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="H1898" t="s">
         <v>9</v>
@@ -51261,7 +51258,7 @@
         <v>0.716000020503998</v>
       </c>
       <c r="G1899" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="H1899" t="s">
         <v>9</v>
@@ -51391,7 +51388,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1904" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1904" t="s">
         <v>9</v>
@@ -51417,7 +51414,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1905" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1905" t="s">
         <v>9</v>
@@ -51469,7 +51466,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1907" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1907" t="s">
         <v>9</v>
@@ -51495,7 +51492,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1908" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1908" t="s">
         <v>9</v>
@@ -51521,7 +51518,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1909" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1909" t="s">
         <v>9</v>
@@ -51573,7 +51570,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1911" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1911" t="s">
         <v>9</v>
@@ -51599,7 +51596,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1912" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1912" t="s">
         <v>9</v>
@@ -51703,7 +51700,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1916" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1916" t="s">
         <v>9</v>
@@ -51729,7 +51726,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1917" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1917" t="s">
         <v>9</v>
@@ -51781,7 +51778,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1919" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1919" t="s">
         <v>9</v>
@@ -51807,7 +51804,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1920" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1920" t="s">
         <v>9</v>
@@ -51859,7 +51856,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1922" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1922" t="s">
         <v>9</v>
@@ -51937,7 +51934,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1925" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1925" t="s">
         <v>9</v>
@@ -51963,7 +51960,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1926" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1926" t="s">
         <v>9</v>
@@ -52041,7 +52038,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1929" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1929" t="s">
         <v>9</v>
@@ -52067,7 +52064,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1930" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1930" t="s">
         <v>9</v>
@@ -52093,7 +52090,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1931" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1931" t="s">
         <v>9</v>
@@ -52119,7 +52116,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1932" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1932" t="s">
         <v>9</v>
@@ -52145,7 +52142,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1933" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1933" t="s">
         <v>9</v>
@@ -52171,7 +52168,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1934" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1934" t="s">
         <v>9</v>
@@ -52197,7 +52194,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1935" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H1935" t="s">
         <v>9</v>
@@ -52275,7 +52272,7 @@
         <v>0.708000004291534</v>
       </c>
       <c r="G1938" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="H1938" t="s">
         <v>9</v>
@@ -52301,7 +52298,7 @@
         <v>0.705999970436096</v>
       </c>
       <c r="G1939" t="s">
-        <v>379</v>
+        <v>328</v>
       </c>
       <c r="H1939" t="s">
         <v>9</v>
@@ -52327,7 +52324,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1940" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1940" t="s">
         <v>9</v>
@@ -52379,7 +52376,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1942" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1942" t="s">
         <v>9</v>
@@ -52405,7 +52402,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1943" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H1943" t="s">
         <v>9</v>
@@ -52431,7 +52428,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1944" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1944" t="s">
         <v>9</v>
@@ -52457,7 +52454,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1945" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1945" t="s">
         <v>9</v>
@@ -52535,7 +52532,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1948" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1948" t="s">
         <v>9</v>
@@ -52561,7 +52558,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1949" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1949" t="s">
         <v>9</v>
@@ -52587,7 +52584,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1950" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H1950" t="s">
         <v>9</v>
@@ -52613,7 +52610,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1951" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1951" t="s">
         <v>9</v>
@@ -52639,7 +52636,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1952" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H1952" t="s">
         <v>9</v>
@@ -52665,7 +52662,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1953" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1953" t="s">
         <v>9</v>
@@ -52691,7 +52688,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1954" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1954" t="s">
         <v>9</v>
@@ -52717,7 +52714,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1955" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1955" t="s">
         <v>9</v>
@@ -52743,7 +52740,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1956" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1956" t="s">
         <v>9</v>
@@ -52769,7 +52766,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G1957" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H1957" t="s">
         <v>9</v>
@@ -52795,7 +52792,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1958" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1958" t="s">
         <v>9</v>
@@ -52821,7 +52818,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1959" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1959" t="s">
         <v>9</v>
@@ -52847,7 +52844,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1960" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H1960" t="s">
         <v>9</v>
@@ -52873,7 +52870,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1961" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1961" t="s">
         <v>9</v>
@@ -52899,7 +52896,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G1962" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H1962" t="s">
         <v>9</v>
@@ -52925,7 +52922,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1963" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1963" t="s">
         <v>9</v>
@@ -52951,7 +52948,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1964" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H1964" t="s">
         <v>9</v>
@@ -52977,7 +52974,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1965" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1965" t="s">
         <v>9</v>
@@ -53003,7 +53000,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1966" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H1966" t="s">
         <v>9</v>
@@ -53029,7 +53026,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1967" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1967" t="s">
         <v>9</v>
@@ -53055,7 +53052,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1968" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1968" t="s">
         <v>9</v>
@@ -53081,7 +53078,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1969" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1969" t="s">
         <v>9</v>
@@ -53107,7 +53104,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1970" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H1970" t="s">
         <v>9</v>
@@ -53133,7 +53130,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1971" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H1971" t="s">
         <v>9</v>
@@ -53159,7 +53156,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1972" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1972" t="s">
         <v>9</v>
@@ -53185,7 +53182,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1973" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H1973" t="s">
         <v>9</v>
@@ -53211,7 +53208,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1974" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="H1974" t="s">
         <v>9</v>
@@ -53237,7 +53234,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1975" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1975" t="s">
         <v>9</v>
@@ -53263,7 +53260,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1976" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1976" t="s">
         <v>9</v>
@@ -53289,7 +53286,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1977" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1977" t="s">
         <v>9</v>
@@ -53315,7 +53312,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1978" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1978" t="s">
         <v>9</v>
@@ -53341,7 +53338,7 @@
         <v>0.621999979019165</v>
       </c>
       <c r="G1979" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="H1979" t="s">
         <v>9</v>
@@ -53367,7 +53364,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1980" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H1980" t="s">
         <v>9</v>
@@ -53393,7 +53390,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G1981" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H1981" t="s">
         <v>9</v>
@@ -53419,7 +53416,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1982" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1982" t="s">
         <v>9</v>
@@ -53445,7 +53442,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1983" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H1983" t="s">
         <v>9</v>
@@ -53471,7 +53468,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G1984" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="H1984" t="s">
         <v>9</v>
@@ -53497,7 +53494,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G1985" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="H1985" t="s">
         <v>9</v>
@@ -53523,7 +53520,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1986" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H1986" t="s">
         <v>9</v>
@@ -53549,7 +53546,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1987" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H1987" t="s">
         <v>9</v>
@@ -53575,7 +53572,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G1988" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H1988" t="s">
         <v>9</v>
@@ -53601,7 +53598,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1989" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1989" t="s">
         <v>9</v>
@@ -53627,7 +53624,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1990" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="H1990" t="s">
         <v>9</v>
@@ -53653,7 +53650,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G1991" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H1991" t="s">
         <v>9</v>
@@ -53679,7 +53676,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1992" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="H1992" t="s">
         <v>9</v>
@@ -53705,7 +53702,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G1993" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H1993" t="s">
         <v>9</v>
@@ -53731,7 +53728,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G1994" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="H1994" t="s">
         <v>9</v>
@@ -53757,7 +53754,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G1995" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="H1995" t="s">
         <v>9</v>
@@ -53783,7 +53780,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G1996" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="H1996" t="s">
         <v>9</v>
@@ -53809,7 +53806,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G1997" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="H1997" t="s">
         <v>9</v>
@@ -53835,7 +53832,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G1998" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H1998" t="s">
         <v>9</v>
@@ -53861,7 +53858,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1999" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H1999" t="s">
         <v>9</v>
@@ -53887,7 +53884,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2000" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2000" t="s">
         <v>9</v>
@@ -53913,7 +53910,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2001" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2001" t="s">
         <v>9</v>
@@ -53939,7 +53936,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2002" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="H2002" t="s">
         <v>9</v>
@@ -53965,7 +53962,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2003" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="H2003" t="s">
         <v>9</v>
@@ -53991,7 +53988,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2004" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="H2004" t="s">
         <v>9</v>
@@ -54017,7 +54014,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2005" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2005" t="s">
         <v>9</v>
@@ -54043,7 +54040,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2006" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2006" t="s">
         <v>9</v>
@@ -54069,7 +54066,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2007" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="H2007" t="s">
         <v>9</v>
@@ -54095,7 +54092,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G2008" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="H2008" t="s">
         <v>9</v>
@@ -54121,7 +54118,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2009" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="H2009" t="s">
         <v>9</v>
@@ -54147,7 +54144,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2010" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="H2010" t="s">
         <v>9</v>
@@ -54173,7 +54170,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2011" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2011" t="s">
         <v>9</v>
@@ -54199,7 +54196,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G2012" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="H2012" t="s">
         <v>9</v>
@@ -54225,7 +54222,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2013" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2013" t="s">
         <v>9</v>
@@ -54251,7 +54248,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2014" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2014" t="s">
         <v>9</v>
@@ -54277,7 +54274,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2015" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2015" t="s">
         <v>9</v>
@@ -54303,7 +54300,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2016" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2016" t="s">
         <v>9</v>
@@ -54329,7 +54326,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2017" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2017" t="s">
         <v>9</v>
@@ -54355,7 +54352,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2018" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2018" t="s">
         <v>9</v>
@@ -54381,7 +54378,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2019" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2019" t="s">
         <v>9</v>
@@ -54407,7 +54404,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2020" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2020" t="s">
         <v>9</v>
@@ -54433,7 +54430,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2021" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2021" t="s">
         <v>9</v>
@@ -54459,7 +54456,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2022" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2022" t="s">
         <v>9</v>
@@ -54485,7 +54482,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2023" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2023" t="s">
         <v>9</v>
@@ -54511,7 +54508,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2024" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2024" t="s">
         <v>9</v>
@@ -54589,7 +54586,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2027" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2027" t="s">
         <v>9</v>
@@ -54615,7 +54612,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2028" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2028" t="s">
         <v>9</v>
@@ -54641,7 +54638,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2029" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2029" t="s">
         <v>9</v>
@@ -54667,7 +54664,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2030" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2030" t="s">
         <v>9</v>
@@ -54693,7 +54690,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2031" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2031" t="s">
         <v>9</v>
@@ -54719,7 +54716,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2032" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2032" t="s">
         <v>9</v>
@@ -54745,7 +54742,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2033" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2033" t="s">
         <v>9</v>
@@ -54771,7 +54768,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2034" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2034" t="s">
         <v>9</v>
@@ -54797,7 +54794,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2035" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2035" t="s">
         <v>9</v>
@@ -54823,7 +54820,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2036" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2036" t="s">
         <v>9</v>
@@ -54849,7 +54846,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2037" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2037" t="s">
         <v>9</v>
@@ -54875,7 +54872,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2038" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2038" t="s">
         <v>9</v>
@@ -54901,7 +54898,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2039" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2039" t="s">
         <v>9</v>
@@ -54927,7 +54924,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2040" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2040" t="s">
         <v>9</v>
@@ -54953,7 +54950,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2041" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2041" t="s">
         <v>9</v>
@@ -54979,7 +54976,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2042" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2042" t="s">
         <v>9</v>
@@ -55005,7 +55002,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2043" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2043" t="s">
         <v>9</v>
@@ -55031,7 +55028,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2044" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2044" t="s">
         <v>9</v>
@@ -55057,7 +55054,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2045" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2045" t="s">
         <v>9</v>
@@ -55083,7 +55080,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2046" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2046" t="s">
         <v>9</v>
@@ -55109,7 +55106,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2047" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2047" t="s">
         <v>9</v>
@@ -55135,7 +55132,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2048" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2048" t="s">
         <v>9</v>
@@ -55161,7 +55158,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2049" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2049" t="s">
         <v>9</v>
@@ -55187,7 +55184,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2050" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2050" t="s">
         <v>9</v>
@@ -55213,7 +55210,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2051" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2051" t="s">
         <v>9</v>
@@ -55239,7 +55236,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2052" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2052" t="s">
         <v>9</v>
@@ -55265,7 +55262,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2053" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2053" t="s">
         <v>9</v>
@@ -55291,7 +55288,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2054" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2054" t="s">
         <v>9</v>
@@ -55317,7 +55314,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2055" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2055" t="s">
         <v>9</v>
@@ -55343,7 +55340,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2056" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2056" t="s">
         <v>9</v>
@@ -55369,7 +55366,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2057" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2057" t="s">
         <v>9</v>
@@ -55395,7 +55392,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2058" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2058" t="s">
         <v>9</v>
@@ -55421,7 +55418,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2059" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2059" t="s">
         <v>9</v>
@@ -55447,7 +55444,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2060" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2060" t="s">
         <v>9</v>
@@ -55473,7 +55470,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2061" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2061" t="s">
         <v>9</v>
@@ -55499,7 +55496,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2062" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2062" t="s">
         <v>9</v>
@@ -55525,7 +55522,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2063" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2063" t="s">
         <v>9</v>
@@ -55551,7 +55548,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2064" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="H2064" t="s">
         <v>9</v>
@@ -55577,7 +55574,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2065" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="H2065" t="s">
         <v>9</v>
@@ -55603,7 +55600,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2066" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
       <c r="H2066" t="s">
         <v>9</v>
@@ -55629,7 +55626,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2067" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2067" t="s">
         <v>9</v>
@@ -55655,7 +55652,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2068" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="H2068" t="s">
         <v>9</v>
@@ -55681,7 +55678,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2069" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2069" t="s">
         <v>9</v>
@@ -55707,7 +55704,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2070" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="H2070" t="s">
         <v>9</v>
@@ -55733,7 +55730,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2071" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2071" t="s">
         <v>9</v>
@@ -55759,7 +55756,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2072" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2072" t="s">
         <v>9</v>
@@ -55785,7 +55782,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2073" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2073" t="s">
         <v>9</v>
@@ -55811,7 +55808,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2074" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2074" t="s">
         <v>9</v>
@@ -55837,7 +55834,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2075" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2075" t="s">
         <v>9</v>
@@ -55863,7 +55860,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2076" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2076" t="s">
         <v>9</v>
@@ -55889,7 +55886,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2077" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="H2077" t="s">
         <v>9</v>
@@ -55915,7 +55912,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2078" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2078" t="s">
         <v>9</v>
@@ -55941,7 +55938,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2079" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="H2079" t="s">
         <v>9</v>
@@ -55967,7 +55964,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2080" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2080" t="s">
         <v>9</v>
@@ -55993,7 +55990,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2081" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2081" t="s">
         <v>9</v>
@@ -56019,7 +56016,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2082" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2082" t="s">
         <v>9</v>
@@ -56045,7 +56042,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2083" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2083" t="s">
         <v>9</v>
@@ -56071,7 +56068,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2084" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2084" t="s">
         <v>9</v>
@@ -56097,7 +56094,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2085" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="H2085" t="s">
         <v>9</v>
@@ -56123,7 +56120,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2086" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2086" t="s">
         <v>9</v>
@@ -56149,7 +56146,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2087" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="H2087" t="s">
         <v>9</v>
@@ -56175,7 +56172,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2088" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2088" t="s">
         <v>9</v>
@@ -56201,7 +56198,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2089" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2089" t="s">
         <v>9</v>
@@ -56227,7 +56224,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2090" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2090" t="s">
         <v>9</v>
@@ -56253,7 +56250,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2091" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2091" t="s">
         <v>9</v>
@@ -56279,7 +56276,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2092" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2092" t="s">
         <v>9</v>
@@ -56305,7 +56302,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2093" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2093" t="s">
         <v>9</v>
@@ -56331,7 +56328,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2094" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2094" t="s">
         <v>9</v>
@@ -56357,7 +56354,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2095" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2095" t="s">
         <v>9</v>
@@ -56383,7 +56380,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2096" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2096" t="s">
         <v>9</v>
@@ -56409,7 +56406,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2097" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2097" t="s">
         <v>9</v>
@@ -56435,7 +56432,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2098" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2098" t="s">
         <v>9</v>
@@ -56461,7 +56458,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2099" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2099" t="s">
         <v>9</v>
@@ -56487,7 +56484,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2100" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2100" t="s">
         <v>9</v>
@@ -56513,7 +56510,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2101" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2101" t="s">
         <v>9</v>
@@ -56539,7 +56536,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2102" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2102" t="s">
         <v>9</v>
@@ -56565,7 +56562,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2103" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2103" t="s">
         <v>9</v>
@@ -56591,7 +56588,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2104" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2104" t="s">
         <v>9</v>
@@ -56617,7 +56614,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2105" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2105" t="s">
         <v>9</v>
@@ -56643,7 +56640,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2106" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2106" t="s">
         <v>9</v>
@@ -56669,7 +56666,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2107" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2107" t="s">
         <v>9</v>
@@ -56695,7 +56692,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2108" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2108" t="s">
         <v>9</v>
@@ -56721,7 +56718,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2109" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2109" t="s">
         <v>9</v>
@@ -56747,7 +56744,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2110" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2110" t="s">
         <v>9</v>
@@ -56773,7 +56770,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2111" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2111" t="s">
         <v>9</v>
@@ -56799,7 +56796,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2112" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2112" t="s">
         <v>9</v>
@@ -56825,7 +56822,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2113" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2113" t="s">
         <v>9</v>
@@ -56851,7 +56848,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2114" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2114" t="s">
         <v>9</v>
@@ -56877,7 +56874,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2115" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2115" t="s">
         <v>9</v>
@@ -56903,7 +56900,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2116" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2116" t="s">
         <v>9</v>
@@ -56929,7 +56926,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2117" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2117" t="s">
         <v>9</v>
@@ -56955,7 +56952,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2118" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2118" t="s">
         <v>9</v>
@@ -56981,7 +56978,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2119" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2119" t="s">
         <v>9</v>
@@ -57007,7 +57004,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2120" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2120" t="s">
         <v>9</v>
@@ -57033,7 +57030,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2121" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2121" t="s">
         <v>9</v>
@@ -57059,7 +57056,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2122" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2122" t="s">
         <v>9</v>
@@ -57111,7 +57108,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2124" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2124" t="s">
         <v>9</v>
@@ -57137,7 +57134,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2125" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2125" t="s">
         <v>9</v>
@@ -57189,7 +57186,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2127" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2127" t="s">
         <v>9</v>
@@ -57215,7 +57212,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2128" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2128" t="s">
         <v>9</v>
@@ -57241,7 +57238,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2129" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2129" t="s">
         <v>9</v>
@@ -57267,7 +57264,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2130" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2130" t="s">
         <v>9</v>
@@ -57293,7 +57290,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2131" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2131" t="s">
         <v>9</v>
@@ -57319,7 +57316,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2132" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2132" t="s">
         <v>9</v>
@@ -57345,7 +57342,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2133" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2133" t="s">
         <v>9</v>
@@ -57371,7 +57368,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2134" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2134" t="s">
         <v>9</v>
@@ -57397,7 +57394,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2135" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2135" t="s">
         <v>9</v>
@@ -57423,7 +57420,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2136" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="H2136" t="s">
         <v>9</v>
@@ -57449,7 +57446,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2137" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="H2137" t="s">
         <v>9</v>
@@ -57475,7 +57472,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G2138" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="H2138" t="s">
         <v>9</v>
@@ -57501,7 +57498,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2139" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2139" t="s">
         <v>9</v>
@@ -57527,7 +57524,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2140" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="H2140" t="s">
         <v>9</v>
@@ -57553,7 +57550,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G2141" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="H2141" t="s">
         <v>9</v>
@@ -57579,7 +57576,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2142" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2142" t="s">
         <v>9</v>
@@ -57605,7 +57602,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2143" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2143" t="s">
         <v>9</v>
@@ -57631,7 +57628,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2144" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2144" t="s">
         <v>9</v>
@@ -57657,7 +57654,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2145" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2145" t="s">
         <v>9</v>
@@ -57683,7 +57680,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2146" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2146" t="s">
         <v>9</v>
@@ -57709,7 +57706,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2147" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2147" t="s">
         <v>9</v>
@@ -57735,7 +57732,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2148" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2148" t="s">
         <v>9</v>
@@ -57761,7 +57758,7 @@
         <v>0.685999989509583</v>
       </c>
       <c r="G2149" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="H2149" t="s">
         <v>9</v>
@@ -57787,7 +57784,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2150" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2150" t="s">
         <v>9</v>
@@ -57813,7 +57810,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G2151" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="H2151" t="s">
         <v>9</v>
@@ -57839,7 +57836,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G2152" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="H2152" t="s">
         <v>9</v>
@@ -57865,7 +57862,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2153" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2153" t="s">
         <v>9</v>
@@ -57891,7 +57888,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2154" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2154" t="s">
         <v>9</v>
@@ -57917,7 +57914,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2155" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2155" t="s">
         <v>9</v>
@@ -57943,7 +57940,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G2156" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="H2156" t="s">
         <v>9</v>
@@ -57969,7 +57966,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2157" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2157" t="s">
         <v>9</v>
@@ -57995,7 +57992,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2158" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="H2158" t="s">
         <v>9</v>
@@ -58021,7 +58018,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2159" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2159" t="s">
         <v>9</v>
@@ -58047,7 +58044,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2160" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2160" t="s">
         <v>9</v>
@@ -58073,7 +58070,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2161" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2161" t="s">
         <v>9</v>
@@ -58099,7 +58096,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2162" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2162" t="s">
         <v>9</v>
@@ -58125,7 +58122,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2163" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2163" t="s">
         <v>9</v>
@@ -58177,7 +58174,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2165" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2165" t="s">
         <v>9</v>
@@ -58203,7 +58200,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G2166" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="H2166" t="s">
         <v>9</v>
@@ -58229,7 +58226,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2167" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2167" t="s">
         <v>9</v>
@@ -58255,7 +58252,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2168" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2168" t="s">
         <v>9</v>
@@ -58281,7 +58278,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G2169" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="H2169" t="s">
         <v>9</v>
@@ -58307,7 +58304,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G2170" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="H2170" t="s">
         <v>9</v>
@@ -58333,7 +58330,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G2171" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="H2171" t="s">
         <v>9</v>
@@ -58359,7 +58356,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2172" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2172" t="s">
         <v>9</v>
@@ -58385,7 +58382,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2173" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2173" t="s">
         <v>9</v>
@@ -58411,7 +58408,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2174" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2174" t="s">
         <v>9</v>
@@ -58437,7 +58434,7 @@
         <v>0.694000005722046</v>
       </c>
       <c r="G2175" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="H2175" t="s">
         <v>9</v>
@@ -58463,7 +58460,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G2176" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="H2176" t="s">
         <v>9</v>
@@ -58489,7 +58486,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G2177" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2177" t="s">
         <v>9</v>
@@ -58515,7 +58512,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2178" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2178" t="s">
         <v>9</v>
@@ -58541,7 +58538,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G2179" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="H2179" t="s">
         <v>9</v>
@@ -58567,7 +58564,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G2180" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="H2180" t="s">
         <v>9</v>
@@ -58593,7 +58590,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2181" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2181" t="s">
         <v>9</v>
@@ -58619,7 +58616,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2182" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2182" t="s">
         <v>9</v>
@@ -58645,7 +58642,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G2183" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="H2183" t="s">
         <v>9</v>
@@ -58671,7 +58668,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G2184" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="H2184" t="s">
         <v>9</v>
@@ -58697,7 +58694,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G2185" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="H2185" t="s">
         <v>9</v>
@@ -58723,7 +58720,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2186" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2186" t="s">
         <v>9</v>
@@ -58749,7 +58746,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G2187" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="H2187" t="s">
         <v>9</v>
@@ -58775,7 +58772,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2188" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2188" t="s">
         <v>9</v>
@@ -58801,7 +58798,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G2189" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="H2189" t="s">
         <v>9</v>
@@ -58827,7 +58824,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2190" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2190" t="s">
         <v>9</v>
@@ -58853,7 +58850,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2191" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2191" t="s">
         <v>9</v>
@@ -58879,7 +58876,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G2192" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="H2192" t="s">
         <v>9</v>
@@ -58905,7 +58902,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2193" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2193" t="s">
         <v>9</v>
@@ -58931,7 +58928,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2194" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2194" t="s">
         <v>9</v>
@@ -58957,7 +58954,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G2195" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="H2195" t="s">
         <v>9</v>
@@ -58983,7 +58980,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2196" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2196" t="s">
         <v>9</v>
@@ -59009,7 +59006,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2197" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2197" t="s">
         <v>9</v>
@@ -59035,7 +59032,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2198" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2198" t="s">
         <v>9</v>
@@ -59061,7 +59058,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2199" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2199" t="s">
         <v>9</v>
@@ -59087,7 +59084,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G2200" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="H2200" t="s">
         <v>9</v>
@@ -59113,7 +59110,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2201" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2201" t="s">
         <v>9</v>
@@ -59139,7 +59136,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2202" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2202" t="s">
         <v>9</v>
@@ -59165,7 +59162,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G2203" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="H2203" t="s">
         <v>9</v>
@@ -59191,7 +59188,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2204" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2204" t="s">
         <v>9</v>
@@ -59217,7 +59214,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2205" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2205" t="s">
         <v>9</v>
@@ -59243,7 +59240,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G2206" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="H2206" t="s">
         <v>9</v>
@@ -59269,7 +59266,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G2207" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="H2207" t="s">
         <v>9</v>
@@ -59295,7 +59292,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2208" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2208" t="s">
         <v>9</v>
@@ -59321,7 +59318,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G2209" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="H2209" t="s">
         <v>9</v>
@@ -59347,7 +59344,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2210" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2210" t="s">
         <v>9</v>
@@ -59373,7 +59370,7 @@
         <v>0.65200001001358</v>
       </c>
       <c r="G2211" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="H2211" t="s">
         <v>9</v>
@@ -59399,7 +59396,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2212" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2212" t="s">
         <v>9</v>
@@ -59425,7 +59422,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2213" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2213" t="s">
         <v>9</v>
@@ -59451,7 +59448,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2214" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2214" t="s">
         <v>9</v>
@@ -59477,7 +59474,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2215" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2215" t="s">
         <v>9</v>
@@ -59503,7 +59500,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2216" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2216" t="s">
         <v>9</v>
@@ -59529,7 +59526,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2217" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2217" t="s">
         <v>9</v>
@@ -59555,7 +59552,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2218" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2218" t="s">
         <v>9</v>
@@ -59581,7 +59578,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2219" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2219" t="s">
         <v>9</v>
@@ -59607,7 +59604,7 @@
         <v>0.642000019550323</v>
       </c>
       <c r="G2220" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="H2220" t="s">
         <v>9</v>
@@ -59633,7 +59630,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2221" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2221" t="s">
         <v>9</v>
@@ -59659,7 +59656,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G2222" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="H2222" t="s">
         <v>9</v>
@@ -59685,7 +59682,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2223" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2223" t="s">
         <v>9</v>
@@ -59711,7 +59708,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2224" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2224" t="s">
         <v>9</v>
@@ -59737,7 +59734,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2225" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2225" t="s">
         <v>9</v>
@@ -59763,7 +59760,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2226" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2226" t="s">
         <v>9</v>
@@ -59789,7 +59786,7 @@
         <v>0.635999977588654</v>
       </c>
       <c r="G2227" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="H2227" t="s">
         <v>9</v>
@@ -59815,7 +59812,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2228" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2228" t="s">
         <v>9</v>
@@ -59841,7 +59838,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2229" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2229" t="s">
         <v>9</v>
@@ -59867,7 +59864,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2230" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2230" t="s">
         <v>9</v>
@@ -59893,7 +59890,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2231" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2231" t="s">
         <v>9</v>
@@ -59919,7 +59916,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2232" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2232" t="s">
         <v>9</v>
@@ -59945,7 +59942,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2233" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2233" t="s">
         <v>9</v>
@@ -59971,7 +59968,7 @@
         <v>0.628000020980835</v>
       </c>
       <c r="G2234" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="H2234" t="s">
         <v>9</v>
@@ -59997,7 +59994,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2235" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2235" t="s">
         <v>9</v>
@@ -60023,7 +60020,7 @@
         <v>0.632000029087067</v>
       </c>
       <c r="G2236" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="H2236" t="s">
         <v>9</v>
@@ -60049,7 +60046,7 @@
         <v>0.629999995231628</v>
       </c>
       <c r="G2237" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="H2237" t="s">
         <v>9</v>
@@ -60075,7 +60072,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2238" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2238" t="s">
         <v>9</v>
@@ -60101,7 +60098,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G2239" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="H2239" t="s">
         <v>9</v>
@@ -60127,7 +60124,7 @@
         <v>0.625999987125397</v>
       </c>
       <c r="G2240" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="H2240" t="s">
         <v>9</v>
@@ -60153,7 +60150,7 @@
         <v>0.620000004768372</v>
       </c>
       <c r="G2241" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="H2241" t="s">
         <v>9</v>
@@ -60179,7 +60176,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2242" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2242" t="s">
         <v>9</v>
@@ -60205,7 +60202,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G2243" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="H2243" t="s">
         <v>9</v>
@@ -60231,7 +60228,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2244" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2244" t="s">
         <v>9</v>
@@ -60257,7 +60254,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2245" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2245" t="s">
         <v>9</v>
@@ -60283,7 +60280,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2246" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2246" t="s">
         <v>9</v>
@@ -60309,7 +60306,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2247" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2247" t="s">
         <v>9</v>
@@ -60335,7 +60332,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2248" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2248" t="s">
         <v>9</v>
@@ -60361,7 +60358,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2249" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2249" t="s">
         <v>9</v>
@@ -60387,7 +60384,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2250" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2250" t="s">
         <v>9</v>
@@ -60413,7 +60410,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2251" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2251" t="s">
         <v>9</v>
@@ -60439,7 +60436,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2252" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2252" t="s">
         <v>9</v>
@@ -60465,7 +60462,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2253" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2253" t="s">
         <v>9</v>
@@ -60491,7 +60488,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2254" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2254" t="s">
         <v>9</v>
@@ -60517,7 +60514,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2255" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2255" t="s">
         <v>9</v>
@@ -60543,7 +60540,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2256" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2256" t="s">
         <v>9</v>
@@ -60569,7 +60566,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2257" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2257" t="s">
         <v>9</v>
@@ -60595,7 +60592,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2258" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2258" t="s">
         <v>9</v>
@@ -60621,7 +60618,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2259" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2259" t="s">
         <v>9</v>
@@ -60647,7 +60644,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2260" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2260" t="s">
         <v>9</v>
@@ -60673,7 +60670,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2261" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2261" t="s">
         <v>9</v>
@@ -60699,7 +60696,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2262" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2262" t="s">
         <v>9</v>
@@ -60725,7 +60722,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2263" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2263" t="s">
         <v>9</v>
@@ -60751,7 +60748,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2264" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2264" t="s">
         <v>9</v>
@@ -60777,7 +60774,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2265" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2265" t="s">
         <v>9</v>
@@ -60803,7 +60800,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2266" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2266" t="s">
         <v>9</v>
@@ -60829,7 +60826,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2267" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2267" t="s">
         <v>9</v>
@@ -60855,7 +60852,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2268" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2268" t="s">
         <v>9</v>
@@ -60881,7 +60878,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2269" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2269" t="s">
         <v>9</v>
@@ -60907,7 +60904,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2270" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2270" t="s">
         <v>9</v>
@@ -60933,7 +60930,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2271" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2271" t="s">
         <v>9</v>
@@ -60959,7 +60956,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2272" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2272" t="s">
         <v>9</v>
@@ -60985,7 +60982,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2273" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2273" t="s">
         <v>9</v>
@@ -61011,7 +61008,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2274" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2274" t="s">
         <v>9</v>
@@ -61037,7 +61034,7 @@
         <v>0.527999997138977</v>
       </c>
       <c r="G2275" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="H2275" t="s">
         <v>9</v>
@@ -61063,7 +61060,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2276" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2276" t="s">
         <v>9</v>
@@ -61089,7 +61086,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2277" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2277" t="s">
         <v>9</v>
@@ -61115,7 +61112,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2278" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2278" t="s">
         <v>9</v>
@@ -61141,7 +61138,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2279" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2279" t="s">
         <v>9</v>
@@ -61167,7 +61164,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2280" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2280" t="s">
         <v>9</v>
@@ -61193,7 +61190,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2281" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2281" t="s">
         <v>9</v>
@@ -61219,7 +61216,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2282" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2282" t="s">
         <v>9</v>
@@ -61245,7 +61242,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2283" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2283" t="s">
         <v>9</v>
@@ -61271,7 +61268,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2284" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2284" t="s">
         <v>9</v>
@@ -61297,7 +61294,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2285" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2285" t="s">
         <v>9</v>
@@ -61323,7 +61320,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2286" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2286" t="s">
         <v>9</v>
@@ -61349,7 +61346,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2287" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2287" t="s">
         <v>9</v>
@@ -61375,7 +61372,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2288" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="H2288" t="s">
         <v>9</v>
@@ -61401,7 +61398,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2289" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2289" t="s">
         <v>9</v>
@@ -61427,7 +61424,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2290" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2290" t="s">
         <v>9</v>
@@ -61453,7 +61450,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2291" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2291" t="s">
         <v>9</v>
@@ -61479,7 +61476,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2292" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2292" t="s">
         <v>9</v>
@@ -61505,7 +61502,7 @@
         <v>0.617999970912933</v>
       </c>
       <c r="G2293" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="H2293" t="s">
         <v>9</v>
@@ -61531,7 +61528,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2294" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2294" t="s">
         <v>9</v>
@@ -61557,7 +61554,7 @@
         <v>0.610000014305115</v>
       </c>
       <c r="G2295" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="H2295" t="s">
         <v>9</v>
@@ -61583,7 +61580,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2296" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2296" t="s">
         <v>9</v>
@@ -61609,7 +61606,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2297" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2297" t="s">
         <v>9</v>
@@ -61635,7 +61632,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2298" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2298" t="s">
         <v>9</v>
@@ -61661,7 +61658,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2299" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2299" t="s">
         <v>9</v>
@@ -61687,7 +61684,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2300" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2300" t="s">
         <v>9</v>
@@ -61713,7 +61710,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2301" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2301" t="s">
         <v>9</v>
@@ -61739,7 +61736,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2302" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2302" t="s">
         <v>9</v>
@@ -61765,7 +61762,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2303" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2303" t="s">
         <v>9</v>
@@ -61791,7 +61788,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2304" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2304" t="s">
         <v>9</v>
@@ -61817,7 +61814,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2305" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2305" t="s">
         <v>9</v>
@@ -61843,7 +61840,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2306" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2306" t="s">
         <v>9</v>
@@ -61869,7 +61866,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2307" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2307" t="s">
         <v>9</v>
@@ -61895,7 +61892,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2308" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2308" t="s">
         <v>9</v>
@@ -61921,7 +61918,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2309" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2309" t="s">
         <v>9</v>
@@ -61947,7 +61944,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2310" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2310" t="s">
         <v>9</v>
@@ -61973,7 +61970,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2311" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2311" t="s">
         <v>9</v>
@@ -61999,7 +61996,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2312" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2312" t="s">
         <v>9</v>
@@ -62025,7 +62022,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2313" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2313" t="s">
         <v>9</v>
@@ -62051,7 +62048,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2314" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2314" t="s">
         <v>9</v>
@@ -62077,7 +62074,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2315" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2315" t="s">
         <v>9</v>
@@ -62103,7 +62100,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2316" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2316" t="s">
         <v>9</v>
@@ -62129,7 +62126,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2317" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2317" t="s">
         <v>9</v>
@@ -62155,7 +62152,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2318" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="H2318" t="s">
         <v>9</v>
@@ -62181,7 +62178,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2319" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2319" t="s">
         <v>9</v>
@@ -62207,7 +62204,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2320" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2320" t="s">
         <v>9</v>
@@ -62233,7 +62230,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2321" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="H2321" t="s">
         <v>9</v>
@@ -62259,7 +62256,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2322" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2322" t="s">
         <v>9</v>
@@ -62285,7 +62282,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2323" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2323" t="s">
         <v>9</v>
@@ -62311,7 +62308,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2324" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2324" t="s">
         <v>9</v>
@@ -62337,7 +62334,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2325" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2325" t="s">
         <v>9</v>
@@ -62363,7 +62360,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2326" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2326" t="s">
         <v>9</v>
@@ -62389,7 +62386,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2327" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2327" t="s">
         <v>9</v>
@@ -62415,7 +62412,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2328" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2328" t="s">
         <v>9</v>
@@ -62441,7 +62438,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2329" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2329" t="s">
         <v>9</v>
@@ -62467,7 +62464,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2330" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2330" t="s">
         <v>9</v>
@@ -62493,7 +62490,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2331" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2331" t="s">
         <v>9</v>
@@ -62519,7 +62516,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2332" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2332" t="s">
         <v>9</v>
@@ -62545,7 +62542,7 @@
         <v>0.533999979496002</v>
       </c>
       <c r="G2333" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="H2333" t="s">
         <v>9</v>
@@ -62571,7 +62568,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2334" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2334" t="s">
         <v>9</v>
@@ -62597,7 +62594,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2335" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2335" t="s">
         <v>9</v>
@@ -62623,7 +62620,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2336" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2336" t="s">
         <v>9</v>
@@ -62649,7 +62646,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2337" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2337" t="s">
         <v>9</v>
@@ -62675,7 +62672,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2338" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2338" t="s">
         <v>9</v>
@@ -62701,7 +62698,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2339" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2339" t="s">
         <v>9</v>
@@ -62727,7 +62724,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2340" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2340" t="s">
         <v>9</v>
@@ -62753,7 +62750,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2341" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2341" t="s">
         <v>9</v>
@@ -62779,7 +62776,7 @@
         <v>0.541999995708466</v>
       </c>
       <c r="G2342" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="H2342" t="s">
         <v>9</v>
@@ -62805,7 +62802,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2343" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2343" t="s">
         <v>9</v>
@@ -62831,7 +62828,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2344" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2344" t="s">
         <v>9</v>
@@ -62857,7 +62854,7 @@
         <v>0.544000029563904</v>
       </c>
       <c r="G2345" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="H2345" t="s">
         <v>9</v>
@@ -62883,7 +62880,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2346" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2346" t="s">
         <v>9</v>
@@ -62909,7 +62906,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2347" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="H2347" t="s">
         <v>9</v>
@@ -62935,7 +62932,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2348" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2348" t="s">
         <v>9</v>
@@ -62961,7 +62958,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2349" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2349" t="s">
         <v>9</v>
@@ -62987,7 +62984,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2350" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2350" t="s">
         <v>9</v>
@@ -63013,7 +63010,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2351" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2351" t="s">
         <v>9</v>
@@ -63039,7 +63036,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2352" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="H2352" t="s">
         <v>9</v>
@@ -63065,7 +63062,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2353" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="H2353" t="s">
         <v>9</v>
@@ -63091,7 +63088,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2354" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="H2354" t="s">
         <v>9</v>
@@ -63117,7 +63114,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2355" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2355" t="s">
         <v>9</v>
@@ -63143,7 +63140,7 @@
         <v>0.53600001335144</v>
       </c>
       <c r="G2356" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="H2356" t="s">
         <v>9</v>
@@ -63169,7 +63166,7 @@
         <v>0.540000021457672</v>
       </c>
       <c r="G2357" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="H2357" t="s">
         <v>9</v>
@@ -63195,7 +63192,7 @@
         <v>0.546000003814697</v>
       </c>
       <c r="G2358" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="H2358" t="s">
         <v>9</v>
@@ -63221,7 +63218,7 @@
         <v>0.532000005245209</v>
       </c>
       <c r="G2359" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="H2359" t="s">
         <v>9</v>
@@ -63247,7 +63244,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2360" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2360" t="s">
         <v>9</v>
@@ -63273,7 +63270,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2361" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2361" t="s">
         <v>9</v>
@@ -63299,7 +63296,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2362" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2362" t="s">
         <v>9</v>
@@ -63325,7 +63322,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2363" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="H2363" t="s">
         <v>9</v>
@@ -63351,7 +63348,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2364" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2364" t="s">
         <v>9</v>
@@ -63377,7 +63374,7 @@
         <v>0.547999978065491</v>
       </c>
       <c r="G2365" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="H2365" t="s">
         <v>9</v>
@@ -63403,7 +63400,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2366" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2366" t="s">
         <v>9</v>
@@ -63429,7 +63426,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2367" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2367" t="s">
         <v>9</v>
@@ -63455,7 +63452,7 @@
         <v>0.575999975204468</v>
       </c>
       <c r="G2368" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="H2368" t="s">
         <v>9</v>
@@ -63481,7 +63478,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2369" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2369" t="s">
         <v>9</v>
@@ -63507,7 +63504,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2370" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2370" t="s">
         <v>9</v>
@@ -63533,7 +63530,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2371" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2371" t="s">
         <v>9</v>
@@ -63559,7 +63556,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2372" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2372" t="s">
         <v>9</v>
@@ -63585,7 +63582,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2373" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="H2373" t="s">
         <v>9</v>
@@ -63611,7 +63608,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2374" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2374" t="s">
         <v>9</v>
@@ -63637,7 +63634,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2375" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2375" t="s">
         <v>9</v>
@@ -63663,7 +63660,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2376" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2376" t="s">
         <v>9</v>
@@ -63689,7 +63686,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2377" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2377" t="s">
         <v>9</v>
@@ -63715,7 +63712,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2378" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2378" t="s">
         <v>9</v>
@@ -63741,7 +63738,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2379" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2379" t="s">
         <v>9</v>
@@ -63767,7 +63764,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2380" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2380" t="s">
         <v>9</v>
@@ -63793,7 +63790,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2381" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="H2381" t="s">
         <v>9</v>
@@ -63819,7 +63816,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2382" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2382" t="s">
         <v>9</v>
@@ -63845,7 +63842,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2383" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2383" t="s">
         <v>9</v>
@@ -63871,7 +63868,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2384" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2384" t="s">
         <v>9</v>
@@ -63897,7 +63894,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2385" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2385" t="s">
         <v>9</v>
@@ -63923,7 +63920,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2386" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="H2386" t="s">
         <v>9</v>
@@ -63949,7 +63946,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2387" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="H2387" t="s">
         <v>9</v>
@@ -63975,7 +63972,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2388" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2388" t="s">
         <v>9</v>
@@ -64001,7 +63998,7 @@
         <v>0.551999986171722</v>
       </c>
       <c r="G2389" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="H2389" t="s">
         <v>9</v>
@@ -64027,7 +64024,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2390" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="H2390" t="s">
         <v>9</v>
@@ -64053,7 +64050,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2391" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="H2391" t="s">
         <v>9</v>
@@ -64079,7 +64076,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2392" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2392" t="s">
         <v>9</v>
@@ -64105,7 +64102,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2393" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="H2393" t="s">
         <v>9</v>
@@ -64131,7 +64128,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2394" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="H2394" t="s">
         <v>9</v>
@@ -64157,7 +64154,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2395" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2395" t="s">
         <v>9</v>
@@ -64183,7 +64180,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2396" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2396" t="s">
         <v>9</v>
@@ -64209,7 +64206,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2397" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="H2397" t="s">
         <v>9</v>
@@ -64235,7 +64232,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2398" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2398" t="s">
         <v>9</v>
@@ -64261,7 +64258,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2399" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2399" t="s">
         <v>9</v>
@@ -64287,7 +64284,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2400" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="H2400" t="s">
         <v>9</v>
@@ -64313,7 +64310,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2401" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="H2401" t="s">
         <v>9</v>
@@ -64339,7 +64336,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2402" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="H2402" t="s">
         <v>9</v>
@@ -64365,7 +64362,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2403" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="H2403" t="s">
         <v>9</v>
@@ -64391,7 +64388,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2404" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2404" t="s">
         <v>9</v>
@@ -64417,7 +64414,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2405" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2405" t="s">
         <v>9</v>
@@ -64443,7 +64440,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2406" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2406" t="s">
         <v>9</v>
@@ -64469,7 +64466,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2407" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2407" t="s">
         <v>9</v>
@@ -64495,7 +64492,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2408" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2408" t="s">
         <v>9</v>
@@ -64521,7 +64518,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2409" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2409" t="s">
         <v>9</v>
@@ -64547,7 +64544,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2410" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2410" t="s">
         <v>9</v>
@@ -64573,7 +64570,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2411" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2411" t="s">
         <v>9</v>
@@ -64599,7 +64596,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2412" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="H2412" t="s">
         <v>9</v>
@@ -64625,7 +64622,7 @@
         <v>0.601999998092651</v>
       </c>
       <c r="G2413" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="H2413" t="s">
         <v>9</v>
@@ -64651,7 +64648,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2414" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2414" t="s">
         <v>9</v>
@@ -64677,7 +64674,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2415" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2415" t="s">
         <v>9</v>
@@ -64703,7 +64700,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2416" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2416" t="s">
         <v>9</v>
@@ -64729,7 +64726,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2417" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2417" t="s">
         <v>9</v>
@@ -64755,7 +64752,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2418" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2418" t="s">
         <v>9</v>
@@ -64781,7 +64778,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2419" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2419" t="s">
         <v>9</v>
@@ -64807,7 +64804,7 @@
         <v>0.603999972343445</v>
       </c>
       <c r="G2420" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="H2420" t="s">
         <v>9</v>
@@ -64833,7 +64830,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2421" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2421" t="s">
         <v>9</v>
@@ -64859,7 +64856,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2422" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="H2422" t="s">
         <v>9</v>
@@ -64885,7 +64882,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2423" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2423" t="s">
         <v>9</v>
@@ -64911,7 +64908,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2424" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2424" t="s">
         <v>9</v>
@@ -64937,7 +64934,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2425" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2425" t="s">
         <v>9</v>
@@ -64963,7 +64960,7 @@
         <v>0.606000006198883</v>
       </c>
       <c r="G2426" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="H2426" t="s">
         <v>9</v>
@@ -64989,7 +64986,7 @@
         <v>0.614000022411346</v>
       </c>
       <c r="G2427" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="H2427" t="s">
         <v>9</v>
@@ -65015,7 +65012,7 @@
         <v>0.607999980449677</v>
       </c>
       <c r="G2428" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2428" t="s">
         <v>9</v>
@@ -65041,7 +65038,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2429" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2429" t="s">
         <v>9</v>
@@ -65067,7 +65064,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2430" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2430" t="s">
         <v>9</v>
@@ -65093,7 +65090,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2431" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2431" t="s">
         <v>9</v>
@@ -65119,7 +65116,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2432" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2432" t="s">
         <v>9</v>
@@ -65145,7 +65142,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2433" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2433" t="s">
         <v>9</v>
@@ -65171,7 +65168,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2434" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2434" t="s">
         <v>9</v>
@@ -65197,7 +65194,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2435" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2435" t="s">
         <v>9</v>
@@ -65223,7 +65220,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2436" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2436" t="s">
         <v>9</v>
@@ -65249,7 +65246,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2437" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2437" t="s">
         <v>9</v>
@@ -65275,7 +65272,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2438" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2438" t="s">
         <v>9</v>
@@ -65301,7 +65298,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2439" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2439" t="s">
         <v>9</v>
@@ -65327,7 +65324,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2440" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2440" t="s">
         <v>9</v>
@@ -65353,7 +65350,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2441" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2441" t="s">
         <v>9</v>
@@ -65379,7 +65376,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2442" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2442" t="s">
         <v>9</v>
@@ -65405,7 +65402,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2443" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2443" t="s">
         <v>9</v>
@@ -65431,7 +65428,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2444" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2444" t="s">
         <v>9</v>
@@ -65457,7 +65454,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2445" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2445" t="s">
         <v>9</v>
@@ -65483,7 +65480,7 @@
         <v>0.600000023841858</v>
       </c>
       <c r="G2446" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="H2446" t="s">
         <v>9</v>
@@ -65509,7 +65506,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2447" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2447" t="s">
         <v>9</v>
@@ -65535,7 +65532,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2448" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2448" t="s">
         <v>9</v>
@@ -65561,7 +65558,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2449" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2449" t="s">
         <v>9</v>
@@ -65587,7 +65584,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2450" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2450" t="s">
         <v>9</v>
@@ -65613,7 +65610,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2451" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2451" t="s">
         <v>9</v>
@@ -65639,7 +65636,7 @@
         <v>0.592000007629395</v>
       </c>
       <c r="G2452" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="H2452" t="s">
         <v>9</v>
@@ -65665,7 +65662,7 @@
         <v>0.593999981880188</v>
       </c>
       <c r="G2453" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="H2453" t="s">
         <v>9</v>
@@ -65691,7 +65688,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2454" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2454" t="s">
         <v>9</v>
@@ -65717,7 +65714,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2455" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2455" t="s">
         <v>9</v>
@@ -65743,7 +65740,7 @@
         <v>0.59799998998642</v>
       </c>
       <c r="G2456" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="H2456" t="s">
         <v>9</v>
@@ -65769,7 +65766,7 @@
         <v>0.596000015735626</v>
       </c>
       <c r="G2457" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="H2457" t="s">
         <v>9</v>
@@ -65795,7 +65792,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2458" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2458" t="s">
         <v>9</v>
@@ -65821,7 +65818,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2459" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2459" t="s">
         <v>9</v>
@@ -65847,7 +65844,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2460" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2460" t="s">
         <v>9</v>
@@ -65873,7 +65870,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2461" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2461" t="s">
         <v>9</v>
@@ -65899,7 +65896,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2462" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2462" t="s">
         <v>9</v>
@@ -65925,7 +65922,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2463" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2463" t="s">
         <v>9</v>
@@ -65951,7 +65948,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2464" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2464" t="s">
         <v>9</v>
@@ -65977,7 +65974,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2465" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2465" t="s">
         <v>9</v>
@@ -66003,7 +66000,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2466" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2466" t="s">
         <v>9</v>
@@ -66029,7 +66026,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2467" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2467" t="s">
         <v>9</v>
@@ -66055,7 +66052,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2468" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2468" t="s">
         <v>9</v>
@@ -66081,7 +66078,7 @@
         <v>0.589999973773956</v>
       </c>
       <c r="G2469" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="H2469" t="s">
         <v>9</v>
@@ -66107,7 +66104,7 @@
         <v>0.583999991416931</v>
       </c>
       <c r="G2470" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="H2470" t="s">
         <v>9</v>
@@ -66133,7 +66130,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2471" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2471" t="s">
         <v>9</v>
@@ -66159,7 +66156,7 @@
         <v>0.586000025272369</v>
       </c>
       <c r="G2472" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="H2472" t="s">
         <v>9</v>
@@ -66185,7 +66182,7 @@
         <v>0.587999999523163</v>
       </c>
       <c r="G2473" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="H2473" t="s">
         <v>9</v>
@@ -66211,7 +66208,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2474" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2474" t="s">
         <v>9</v>
@@ -66237,7 +66234,7 @@
         <v>0.582000017166138</v>
       </c>
       <c r="G2475" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="H2475" t="s">
         <v>9</v>
@@ -66263,7 +66260,7 @@
         <v>0.574000000953674</v>
       </c>
       <c r="G2476" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="H2476" t="s">
         <v>9</v>
@@ -66289,7 +66286,7 @@
         <v>0.579999983310699</v>
       </c>
       <c r="G2477" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="H2477" t="s">
         <v>9</v>
@@ -66315,7 +66312,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2478" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2478" t="s">
         <v>9</v>
@@ -66341,7 +66338,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2479" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2479" t="s">
         <v>9</v>
@@ -66367,7 +66364,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2480" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2480" t="s">
         <v>9</v>
@@ -66393,7 +66390,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2481" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2481" t="s">
         <v>9</v>
@@ -66419,7 +66416,7 @@
         <v>0.564000010490417</v>
       </c>
       <c r="G2482" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="H2482" t="s">
         <v>9</v>
@@ -66445,7 +66442,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2483" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2483" t="s">
         <v>9</v>
@@ -66471,7 +66468,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2484" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2484" t="s">
         <v>9</v>
@@ -66497,7 +66494,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2485" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2485" t="s">
         <v>9</v>
@@ -66523,7 +66520,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2486" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2486" t="s">
         <v>9</v>
@@ -66549,7 +66546,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2487" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2487" t="s">
         <v>9</v>
@@ -66575,7 +66572,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2488" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2488" t="s">
         <v>9</v>
@@ -66601,7 +66598,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2489" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2489" t="s">
         <v>9</v>
@@ -66627,7 +66624,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2490" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2490" t="s">
         <v>9</v>
@@ -66653,7 +66650,7 @@
         <v>0.578000009059906</v>
       </c>
       <c r="G2491" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="H2491" t="s">
         <v>9</v>
@@ -66679,7 +66676,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2492" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2492" t="s">
         <v>9</v>
@@ -66705,7 +66702,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2493" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2493" t="s">
         <v>9</v>
@@ -66731,7 +66728,7 @@
         <v>0.565999984741211</v>
       </c>
       <c r="G2494" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="H2494" t="s">
         <v>9</v>
@@ -66757,7 +66754,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2495" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2495" t="s">
         <v>9</v>
@@ -66783,7 +66780,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2496" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2496" t="s">
         <v>9</v>
@@ -66809,7 +66806,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2497" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2497" t="s">
         <v>9</v>
@@ -66835,7 +66832,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2498" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2498" t="s">
         <v>9</v>
@@ -66861,7 +66858,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2499" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2499" t="s">
         <v>9</v>
@@ -66887,7 +66884,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2500" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2500" t="s">
         <v>9</v>
@@ -66913,7 +66910,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2501" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2501" t="s">
         <v>9</v>
@@ -66939,7 +66936,7 @@
         <v>0.572000026702881</v>
       </c>
       <c r="G2502" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="H2502" t="s">
         <v>9</v>
@@ -66965,7 +66962,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2503" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2503" t="s">
         <v>9</v>
@@ -66991,7 +66988,7 @@
         <v>0.569999992847443</v>
       </c>
       <c r="G2504" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="H2504" t="s">
         <v>9</v>
@@ -67017,7 +67014,7 @@
         <v>0.561999976634979</v>
       </c>
       <c r="G2505" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="H2505" t="s">
         <v>9</v>
@@ -67043,7 +67040,7 @@
         <v>0.568000018596649</v>
       </c>
       <c r="G2506" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="H2506" t="s">
         <v>9</v>
@@ -67069,7 +67066,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2507" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2507" t="s">
         <v>9</v>
@@ -67095,7 +67092,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2508" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2508" t="s">
         <v>9</v>
@@ -67121,7 +67118,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2509" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2509" t="s">
         <v>9</v>
@@ -67147,7 +67144,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2510" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2510" t="s">
         <v>9</v>
@@ -67173,7 +67170,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2511" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2511" t="s">
         <v>9</v>
@@ -67199,7 +67196,7 @@
         <v>0.550000011920929</v>
       </c>
       <c r="G2512" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="H2512" t="s">
         <v>9</v>
@@ -67225,7 +67222,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2513" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2513" t="s">
         <v>9</v>
@@ -67251,7 +67248,7 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2514" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2514" t="s">
         <v>9</v>
@@ -67277,7 +67274,7 @@
         <v>0.560000002384186</v>
       </c>
       <c r="G2515" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="H2515" t="s">
         <v>9</v>
@@ -67303,7 +67300,7 @@
         <v>0.555999994277954</v>
       </c>
       <c r="G2516" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="H2516" t="s">
         <v>9</v>
@@ -67329,7 +67326,7 @@
         <v>0.554000020027161</v>
       </c>
       <c r="G2517" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="H2517" t="s">
         <v>9</v>
@@ -67337,7 +67334,7 @@
     </row>
     <row r="2518">
       <c r="A2518" s="1" t="n">
-        <v>45985.5829976852</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2518" t="n">
         <v>33283</v>
@@ -67355,9 +67352,35 @@
         <v>0.558000028133392</v>
       </c>
       <c r="G2518" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="H2518" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2519">
+      <c r="A2519" s="1" t="n">
+        <v>45986.6913078704</v>
+      </c>
+      <c r="B2519" t="n">
+        <v>45999</v>
+      </c>
+      <c r="C2519" t="n">
+        <v>0.569999992847443</v>
+      </c>
+      <c r="D2519" t="n">
+        <v>0.551999986171722</v>
+      </c>
+      <c r="E2519" t="n">
+        <v>0.558000028133392</v>
+      </c>
+      <c r="F2519" t="n">
+        <v>0.560000002384186</v>
+      </c>
+      <c r="G2519" t="s">
+        <v>507</v>
+      </c>
+      <c r="H2519" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/BO.MI.xlsx
+++ b/data/BO.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="514">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="515" uniqueCount="515">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">BO.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235394701361656</t>
+    <t xml:space="preserve">0.235394716262817</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228249087929726</t>
+    <t xml:space="preserve">0.228249102830887</t>
   </si>
   <si>
     <t xml:space="preserve">0.216899931430817</t>
@@ -65,34 +65,34 @@
     <t xml:space="preserve">0.217319875955582</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228921517729759</t>
+    <t xml:space="preserve">0.228921502828598</t>
   </si>
   <si>
     <t xml:space="preserve">0.227071791887283</t>
   </si>
   <si>
-    <t xml:space="preserve">0.233293399214745</t>
+    <t xml:space="preserve">0.233293384313583</t>
   </si>
   <si>
-    <t xml:space="preserve">0.228417411446571</t>
+    <t xml:space="preserve">0.22841739654541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.231527790427208</t>
+    <t xml:space="preserve">0.231527775526047</t>
   </si>
   <si>
     <t xml:space="preserve">0.229762196540833</t>
   </si>
   <si>
-    <t xml:space="preserve">0.239598274230957</t>
+    <t xml:space="preserve">0.239598259329796</t>
   </si>
   <si>
-    <t xml:space="preserve">0.235310599207878</t>
+    <t xml:space="preserve">0.235310584306717</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222868233919144</t>
+    <t xml:space="preserve">0.222868219017982</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222784906625748</t>
+    <t xml:space="preserve">0.222784891724586</t>
   </si>
   <si>
     <t xml:space="preserve">0.214377820491791</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">0.201767146587372</t>
   </si>
   <si>
-    <t xml:space="preserve">0.197563603520393</t>
+    <t xml:space="preserve">0.197563588619232</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193360045552254</t>
+    <t xml:space="preserve">0.193360030651093</t>
   </si>
   <si>
-    <t xml:space="preserve">0.193612515926361</t>
+    <t xml:space="preserve">0.1936125010252</t>
   </si>
   <si>
     <t xml:space="preserve">0.196722880005836</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">0.202355399727821</t>
   </si>
   <si>
-    <t xml:space="preserve">0.202607870101929</t>
+    <t xml:space="preserve">0.202607855200768</t>
   </si>
   <si>
     <t xml:space="preserve">0.202187076210976</t>
@@ -134,28 +134,28 @@
     <t xml:space="preserve">0.208912760019302</t>
   </si>
   <si>
-    <t xml:space="preserve">0.210762515664101</t>
+    <t xml:space="preserve">0.210762500762939</t>
   </si>
   <si>
-    <t xml:space="preserve">0.215218499302864</t>
+    <t xml:space="preserve">0.215218514204025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.222616598010063</t>
+    <t xml:space="preserve">0.222616583108902</t>
   </si>
   <si>
-    <t xml:space="preserve">0.226987615227699</t>
+    <t xml:space="preserve">0.226987600326538</t>
   </si>
   <si>
-    <t xml:space="preserve">0.232031852006912</t>
+    <t xml:space="preserve">0.232031866908073</t>
   </si>
   <si>
-    <t xml:space="preserve">0.236235424876213</t>
+    <t xml:space="preserve">0.236235439777374</t>
   </si>
   <si>
     <t xml:space="preserve">0.241279691457748</t>
   </si>
   <si>
-    <t xml:space="preserve">0.245483234524727</t>
+    <t xml:space="preserve">0.245483219623566</t>
   </si>
   <si>
     <t xml:space="preserve">0.252208948135376</t>
@@ -179,22 +179,22 @@
     <t xml:space="preserve">0.285836488008499</t>
   </si>
   <si>
-    <t xml:space="preserve">0.292562156915665</t>
+    <t xml:space="preserve">0.292562216520309</t>
   </si>
   <si>
     <t xml:space="preserve">0.298447161912918</t>
   </si>
   <si>
-    <t xml:space="preserve">0.304332166910172</t>
+    <t xml:space="preserve">0.304332137107849</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311057806015015</t>
+    <t xml:space="preserve">0.311057776212692</t>
   </si>
   <si>
-    <t xml:space="preserve">0.317531049251556</t>
+    <t xml:space="preserve">0.317531019449234</t>
   </si>
   <si>
-    <t xml:space="preserve">0.322827816009521</t>
+    <t xml:space="preserve">0.322827786207199</t>
   </si>
   <si>
     <t xml:space="preserve">0.336279153823853</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">0.356455326080322</t>
   </si>
   <si>
-    <t xml:space="preserve">0.363181054592133</t>
+    <t xml:space="preserve">0.36318102478981</t>
   </si>
   <si>
     <t xml:space="preserve">0.378313809633255</t>
@@ -224,10 +224,10 @@
     <t xml:space="preserve">0.47247177362442</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483400940895081</t>
+    <t xml:space="preserve">0.483400911092758</t>
   </si>
   <si>
-    <t xml:space="preserve">0.501055836677551</t>
+    <t xml:space="preserve">0.501055896282196</t>
   </si>
   <si>
     <t xml:space="preserve">0.500215172767639</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">0.492307871580124</t>
   </si>
   <si>
-    <t xml:space="preserve">0.580670833587646</t>
+    <t xml:space="preserve">0.580670893192291</t>
   </si>
   <si>
     <t xml:space="preserve">0.589086413383484</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">0.63957953453064</t>
   </si>
   <si>
-    <t xml:space="preserve">0.715319216251373</t>
+    <t xml:space="preserve">0.715319275856018</t>
   </si>
   <si>
-    <t xml:space="preserve">0.673241555690765</t>
+    <t xml:space="preserve">0.67324161529541</t>
   </si>
   <si>
-    <t xml:space="preserve">0.65641051530838</t>
+    <t xml:space="preserve">0.656410574913025</t>
   </si>
   <si>
-    <t xml:space="preserve">0.618540704250336</t>
+    <t xml:space="preserve">0.61854076385498</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622748494148254</t>
+    <t xml:space="preserve">0.62274843454361</t>
   </si>
   <si>
     <t xml:space="preserve">0.572255313396454</t>
@@ -272,34 +272,34 @@
     <t xml:space="preserve">0.525969982147217</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521762251853943</t>
+    <t xml:space="preserve">0.521762192249298</t>
   </si>
   <si>
     <t xml:space="preserve">0.48810014128685</t>
   </si>
   <si>
-    <t xml:space="preserve">0.504931271076202</t>
+    <t xml:space="preserve">0.504931211471558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547008812427521</t>
+    <t xml:space="preserve">0.547008752822876</t>
   </si>
   <si>
-    <t xml:space="preserve">0.509138941764832</t>
+    <t xml:space="preserve">0.509138882160187</t>
   </si>
   <si>
-    <t xml:space="preserve">0.483892410993576</t>
+    <t xml:space="preserve">0.483892351388931</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51334673166275</t>
+    <t xml:space="preserve">0.513346791267395</t>
   </si>
   <si>
-    <t xml:space="preserve">0.530177772045135</t>
+    <t xml:space="preserve">0.530177712440491</t>
   </si>
   <si>
-    <t xml:space="preserve">0.517554461956024</t>
+    <t xml:space="preserve">0.517554521560669</t>
   </si>
   <si>
-    <t xml:space="preserve">0.471269130706787</t>
+    <t xml:space="preserve">0.471269160509109</t>
   </si>
   <si>
     <t xml:space="preserve">0.467061340808868</t>
@@ -308,10 +308,10 @@
     <t xml:space="preserve">0.500723481178284</t>
   </si>
   <si>
-    <t xml:space="preserve">0.462853640317917</t>
+    <t xml:space="preserve">0.462853610515594</t>
   </si>
   <si>
-    <t xml:space="preserve">0.47968465089798</t>
+    <t xml:space="preserve">0.479684591293335</t>
   </si>
   <si>
     <t xml:space="preserve">0.43339928984642</t>
@@ -320,43 +320,43 @@
     <t xml:space="preserve">0.437607049942017</t>
   </si>
   <si>
-    <t xml:space="preserve">0.454438060522079</t>
+    <t xml:space="preserve">0.454438090324402</t>
   </si>
   <si>
-    <t xml:space="preserve">0.450230300426483</t>
+    <t xml:space="preserve">0.450230330228806</t>
   </si>
   <si>
-    <t xml:space="preserve">0.446022540330887</t>
+    <t xml:space="preserve">0.446022570133209</t>
   </si>
   <si>
-    <t xml:space="preserve">0.458645880222321</t>
+    <t xml:space="preserve">0.458645850419998</t>
   </si>
   <si>
-    <t xml:space="preserve">0.403944939374924</t>
+    <t xml:space="preserve">0.403944969177246</t>
   </si>
   <si>
-    <t xml:space="preserve">0.420775979757309</t>
+    <t xml:space="preserve">0.420776009559631</t>
   </si>
   <si>
     <t xml:space="preserve">0.429191529750824</t>
   </si>
   <si>
-    <t xml:space="preserve">0.534385502338409</t>
+    <t xml:space="preserve">0.534385561943054</t>
   </si>
   <si>
-    <t xml:space="preserve">0.542801082134247</t>
+    <t xml:space="preserve">0.542801022529602</t>
   </si>
   <si>
     <t xml:space="preserve">0.475476890802383</t>
   </si>
   <si>
-    <t xml:space="preserve">0.410677403211594</t>
+    <t xml:space="preserve">0.410677373409271</t>
   </si>
   <si>
-    <t xml:space="preserve">0.424983739852905</t>
+    <t xml:space="preserve">0.424983769655228</t>
   </si>
   <si>
-    <t xml:space="preserve">0.417409777641296</t>
+    <t xml:space="preserve">0.417409807443619</t>
   </si>
   <si>
     <t xml:space="preserve">0.380381524562836</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">0.412360489368439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.415726661682129</t>
+    <t xml:space="preserve">0.415726691484451</t>
   </si>
   <si>
     <t xml:space="preserve">0.441814780235291</t>
   </si>
   <si>
-    <t xml:space="preserve">0.419092923402786</t>
+    <t xml:space="preserve">0.419092893600464</t>
   </si>
   <si>
     <t xml:space="preserve">0.405628055334091</t>
@@ -383,49 +383,49 @@
     <t xml:space="preserve">0.408994287252426</t>
   </si>
   <si>
-    <t xml:space="preserve">0.407311141490936</t>
+    <t xml:space="preserve">0.407311171293259</t>
   </si>
   <si>
     <t xml:space="preserve">0.392163246870041</t>
   </si>
   <si>
-    <t xml:space="preserve">0.398895621299744</t>
+    <t xml:space="preserve">0.398895651102066</t>
   </si>
   <si>
-    <t xml:space="preserve">0.400578767061234</t>
+    <t xml:space="preserve">0.400578737258911</t>
   </si>
   <si>
-    <t xml:space="preserve">0.393846333026886</t>
+    <t xml:space="preserve">0.393846362829208</t>
   </si>
   <si>
     <t xml:space="preserve">0.402261823415756</t>
   </si>
   <si>
-    <t xml:space="preserve">0.395529448986053</t>
+    <t xml:space="preserve">0.395529478788376</t>
   </si>
   <si>
     <t xml:space="preserve">0.387113928794861</t>
   </si>
   <si>
-    <t xml:space="preserve">0.373649120330811</t>
+    <t xml:space="preserve">0.373649090528488</t>
   </si>
   <si>
     <t xml:space="preserve">0.323155969381332</t>
   </si>
   <si>
-    <t xml:space="preserve">0.311374247074127</t>
+    <t xml:space="preserve">0.311374217271805</t>
   </si>
   <si>
-    <t xml:space="preserve">0.336620777845383</t>
+    <t xml:space="preserve">0.336620807647705</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32988840341568</t>
+    <t xml:space="preserve">0.329888373613358</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32820525765419</t>
+    <t xml:space="preserve">0.328205287456512</t>
   </si>
   <si>
-    <t xml:space="preserve">0.32652223110199</t>
+    <t xml:space="preserve">0.326522201299667</t>
   </si>
   <si>
     <t xml:space="preserve">0.3248390853405</t>
@@ -437,13 +437,13 @@
     <t xml:space="preserve">0.360184252262115</t>
   </si>
   <si>
-    <t xml:space="preserve">0.351768732070923</t>
+    <t xml:space="preserve">0.351768761873245</t>
   </si>
   <si>
     <t xml:space="preserve">0.345036327838898</t>
   </si>
   <si>
-    <t xml:space="preserve">0.3500856757164</t>
+    <t xml:space="preserve">0.350085645914078</t>
   </si>
   <si>
     <t xml:space="preserve">0.338303923606873</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">0.331571489572525</t>
   </si>
   <si>
-    <t xml:space="preserve">0.34335321187973</t>
+    <t xml:space="preserve">0.343353241682053</t>
   </si>
   <si>
     <t xml:space="preserve">0.333254605531693</t>
@@ -461,10 +461,10 @@
     <t xml:space="preserve">0.31978976726532</t>
   </si>
   <si>
-    <t xml:space="preserve">0.33493772149086</t>
+    <t xml:space="preserve">0.334937751293182</t>
   </si>
   <si>
-    <t xml:space="preserve">0.339987009763718</t>
+    <t xml:space="preserve">0.33998703956604</t>
   </si>
   <si>
     <t xml:space="preserve">0.366916656494141</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">0.35850116610527</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36859980225563</t>
+    <t xml:space="preserve">0.368599772453308</t>
   </si>
   <si>
-    <t xml:space="preserve">0.36355048418045</t>
+    <t xml:space="preserve">0.363550454378128</t>
   </si>
   <si>
-    <t xml:space="preserve">0.390480101108551</t>
+    <t xml:space="preserve">0.390480130910873</t>
   </si>
   <si>
     <t xml:space="preserve">0.397212564945221</t>
@@ -488,22 +488,22 @@
     <t xml:space="preserve">0.383747726678848</t>
   </si>
   <si>
-    <t xml:space="preserve">0.388797044754028</t>
+    <t xml:space="preserve">0.388797014951706</t>
   </si>
   <si>
     <t xml:space="preserve">0.378698378801346</t>
   </si>
   <si>
-    <t xml:space="preserve">0.382064610719681</t>
+    <t xml:space="preserve">0.382064640522003</t>
   </si>
   <si>
     <t xml:space="preserve">0.375332206487656</t>
   </si>
   <si>
-    <t xml:space="preserve">0.370282858610153</t>
+    <t xml:space="preserve">0.370282918214798</t>
   </si>
   <si>
-    <t xml:space="preserve">0.377015352249146</t>
+    <t xml:space="preserve">0.377015292644501</t>
   </si>
   <si>
     <t xml:space="preserve">0.371966004371643</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">0.538593292236328</t>
   </si>
   <si>
-    <t xml:space="preserve">0.559632182121277</t>
+    <t xml:space="preserve">0.559632122516632</t>
   </si>
   <si>
-    <t xml:space="preserve">0.551216542720795</t>
+    <t xml:space="preserve">0.55121648311615</t>
   </si>
   <si>
     <t xml:space="preserve">0.489783257246017</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">0.494832575321198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.491466403007507</t>
+    <t xml:space="preserve">0.49146643280983</t>
   </si>
   <si>
     <t xml:space="preserve">0.498198807239532</t>
@@ -551,40 +551,40 @@
     <t xml:space="preserve">0.520079076290131</t>
   </si>
   <si>
-    <t xml:space="preserve">0.526811599731445</t>
+    <t xml:space="preserve">0.526811540126801</t>
   </si>
   <si>
-    <t xml:space="preserve">0.536910176277161</t>
+    <t xml:space="preserve">0.536910235881805</t>
   </si>
   <si>
     <t xml:space="preserve">0.525128424167633</t>
   </si>
   <si>
-    <t xml:space="preserve">0.52344536781311</t>
+    <t xml:space="preserve">0.523445308208466</t>
   </si>
   <si>
     <t xml:space="preserve">0.50661426782608</t>
   </si>
   <si>
-    <t xml:space="preserve">0.511663615703583</t>
+    <t xml:space="preserve">0.511663675308228</t>
   </si>
   <si>
     <t xml:space="preserve">0.50324809551239</t>
   </si>
   <si>
-    <t xml:space="preserve">0.508297383785248</t>
+    <t xml:space="preserve">0.508297443389893</t>
   </si>
   <si>
     <t xml:space="preserve">0.501565039157867</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493149518966675</t>
+    <t xml:space="preserve">0.493149489164352</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50998055934906</t>
+    <t xml:space="preserve">0.509980499744415</t>
   </si>
   <si>
-    <t xml:space="preserve">0.515029847621918</t>
+    <t xml:space="preserve">0.515029788017273</t>
   </si>
   <si>
     <t xml:space="preserve">0.533544063568115</t>
@@ -596,25 +596,25 @@
     <t xml:space="preserve">0.535227060317993</t>
   </si>
   <si>
-    <t xml:space="preserve">0.557107508182526</t>
+    <t xml:space="preserve">0.557107448577881</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5503751039505</t>
+    <t xml:space="preserve">0.550375044345856</t>
   </si>
   <si>
-    <t xml:space="preserve">0.531860888004303</t>
+    <t xml:space="preserve">0.531860828399658</t>
   </si>
   <si>
-    <t xml:space="preserve">0.518396019935608</t>
+    <t xml:space="preserve">0.518396079540253</t>
   </si>
   <si>
-    <t xml:space="preserve">0.516712963581085</t>
+    <t xml:space="preserve">0.51671302318573</t>
   </si>
   <si>
-    <t xml:space="preserve">0.537019848823547</t>
+    <t xml:space="preserve">0.537019789218903</t>
   </si>
   <si>
-    <t xml:space="preserve">0.53180605173111</t>
+    <t xml:space="preserve">0.531805992126465</t>
   </si>
   <si>
     <t xml:space="preserve">0.530068159103394</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">0.545709490776062</t>
   </si>
   <si>
-    <t xml:space="preserve">0.552661180496216</t>
+    <t xml:space="preserve">0.552661120891571</t>
   </si>
   <si>
-    <t xml:space="preserve">0.549185395240784</t>
+    <t xml:space="preserve">0.549185335636139</t>
   </si>
   <si>
-    <t xml:space="preserve">0.547447443008423</t>
+    <t xml:space="preserve">0.547447383403778</t>
   </si>
   <si>
     <t xml:space="preserve">0.554399132728577</t>
   </si>
   <si>
-    <t xml:space="preserve">0.543971598148346</t>
+    <t xml:space="preserve">0.543971538543701</t>
   </si>
   <si>
-    <t xml:space="preserve">0.54223358631134</t>
+    <t xml:space="preserve">0.542233645915985</t>
   </si>
   <si>
     <t xml:space="preserve">0.538757741451263</t>
@@ -656,34 +656,34 @@
     <t xml:space="preserve">0.540495693683624</t>
   </si>
   <si>
-    <t xml:space="preserve">0.568302571773529</t>
+    <t xml:space="preserve">0.568302631378174</t>
   </si>
   <si>
     <t xml:space="preserve">0.559612929821014</t>
   </si>
   <si>
-    <t xml:space="preserve">0.5509232878685</t>
+    <t xml:space="preserve">0.550923347473145</t>
   </si>
   <si>
-    <t xml:space="preserve">0.521378576755524</t>
+    <t xml:space="preserve">0.521378517150879</t>
   </si>
   <si>
     <t xml:space="preserve">0.512688815593719</t>
   </si>
   <si>
-    <t xml:space="preserve">0.51442676782608</t>
+    <t xml:space="preserve">0.514426827430725</t>
   </si>
   <si>
     <t xml:space="preserve">0.502261281013489</t>
   </si>
   <si>
-    <t xml:space="preserve">0.50399923324585</t>
+    <t xml:space="preserve">0.503999173641205</t>
   </si>
   <si>
     <t xml:space="preserve">0.491833686828613</t>
   </si>
   <si>
-    <t xml:space="preserve">0.493571698665619</t>
+    <t xml:space="preserve">0.493571639060974</t>
   </si>
   <si>
     <t xml:space="preserve">0.524854362010956</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">0.519640564918518</t>
   </si>
   <si>
-    <t xml:space="preserve">0.608274936676025</t>
+    <t xml:space="preserve">0.608274877071381</t>
   </si>
   <si>
     <t xml:space="preserve">0.587419807910919</t>
   </si>
   <si>
-    <t xml:space="preserve">0.601323246955872</t>
+    <t xml:space="preserve">0.601323187351227</t>
   </si>
   <si>
-    <t xml:space="preserve">0.599585294723511</t>
+    <t xml:space="preserve">0.599585235118866</t>
   </si>
   <si>
-    <t xml:space="preserve">0.590895652770996</t>
+    <t xml:space="preserve">0.590895593166351</t>
   </si>
   <si>
     <t xml:space="preserve">0.594371497631073</t>
@@ -716,22 +716,22 @@
     <t xml:space="preserve">0.585681855678558</t>
   </si>
   <si>
-    <t xml:space="preserve">0.589157700538635</t>
+    <t xml:space="preserve">0.58915764093399</t>
   </si>
   <si>
-    <t xml:space="preserve">0.639557540416718</t>
+    <t xml:space="preserve">0.639557659626007</t>
   </si>
   <si>
-    <t xml:space="preserve">0.669102430343628</t>
+    <t xml:space="preserve">0.669102370738983</t>
   </si>
   <si>
     <t xml:space="preserve">0.714288532733917</t>
   </si>
   <si>
-    <t xml:space="preserve">0.667364418506622</t>
+    <t xml:space="preserve">0.667364478111267</t>
   </si>
   <si>
-    <t xml:space="preserve">0.603061139583588</t>
+    <t xml:space="preserve">0.603061079978943</t>
   </si>
   <si>
     <t xml:space="preserve">0.616964519023895</t>
@@ -743,31 +743,31 @@
     <t xml:space="preserve">0.618702471256256</t>
   </si>
   <si>
-    <t xml:space="preserve">0.632605850696564</t>
+    <t xml:space="preserve">0.632605910301208</t>
   </si>
   <si>
-    <t xml:space="preserve">0.653461039066315</t>
+    <t xml:space="preserve">0.65346097946167</t>
   </si>
   <si>
     <t xml:space="preserve">0.6447713971138</t>
   </si>
   <si>
-    <t xml:space="preserve">0.629130005836487</t>
+    <t xml:space="preserve">0.629129946231842</t>
   </si>
   <si>
-    <t xml:space="preserve">0.62565416097641</t>
+    <t xml:space="preserve">0.625654220581055</t>
   </si>
   <si>
     <t xml:space="preserve">0.620440363883972</t>
   </si>
   <si>
-    <t xml:space="preserve">0.637819647789001</t>
+    <t xml:space="preserve">0.637819707393646</t>
   </si>
   <si>
     <t xml:space="preserve">0.643033444881439</t>
   </si>
   <si>
-    <t xml:space="preserve">0.622178316116333</t>
+    <t xml:space="preserve">0.622178435325623</t>
   </si>
   <si>
     <t xml:space="preserve">0.610012829303741</t>
@@ -776,13 +776,13 @@
     <t xml:space="preserve">0.583943903446198</t>
   </si>
   <si>
-    <t xml:space="preserve">0.592633545398712</t>
+    <t xml:space="preserve">0.592633485794067</t>
   </si>
   <si>
     <t xml:space="preserve">0.604799091815948</t>
   </si>
   <si>
-    <t xml:space="preserve">0.571778476238251</t>
+    <t xml:space="preserve">0.571778416633606</t>
   </si>
   <si>
     <t xml:space="preserve">0.582205951213837</t>
@@ -794,10 +794,10 @@
     <t xml:space="preserve">0.557875037193298</t>
   </si>
   <si>
-    <t xml:space="preserve">0.573516428470612</t>
+    <t xml:space="preserve">0.573516368865967</t>
   </si>
   <si>
-    <t xml:space="preserve">0.596109390258789</t>
+    <t xml:space="preserve">0.596109449863434</t>
   </si>
   <si>
     <t xml:space="preserve">0.611750781536102</t>
@@ -806,16 +806,16 @@
     <t xml:space="preserve">0.634343802928925</t>
   </si>
   <si>
-    <t xml:space="preserve">0.649985134601593</t>
+    <t xml:space="preserve">0.649985253810883</t>
   </si>
   <si>
-    <t xml:space="preserve">0.648247241973877</t>
+    <t xml:space="preserve">0.648247301578522</t>
   </si>
   <si>
     <t xml:space="preserve">0.636081695556641</t>
   </si>
   <si>
-    <t xml:space="preserve">0.683005809783936</t>
+    <t xml:space="preserve">0.68300586938858</t>
   </si>
   <si>
     <t xml:space="preserve">0.689957499504089</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">0.662150681018829</t>
   </si>
   <si>
-    <t xml:space="preserve">0.674316167831421</t>
+    <t xml:space="preserve">0.674316227436066</t>
   </si>
   <si>
     <t xml:space="preserve">0.656936883926392</t>
   </si>
   <si>
-    <t xml:space="preserve">0.658674836158752</t>
+    <t xml:space="preserve">0.658674895763397</t>
   </si>
   <si>
     <t xml:space="preserve">0.646509289741516</t>
@@ -867,6 +867,9 @@
   </si>
   <si>
     <t xml:space="preserve">0.614897906780243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0.62565416097641</t>
   </si>
   <si>
     <t xml:space="preserve">0.627446889877319</t>
@@ -44446,7 +44449,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1637" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="H1637" t="s">
         <v>9</v>
@@ -44472,7 +44475,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1638" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1638" t="s">
         <v>9</v>
@@ -44498,7 +44501,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1639" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1639" t="s">
         <v>9</v>
@@ -44524,7 +44527,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1640" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1640" t="s">
         <v>9</v>
@@ -44550,7 +44553,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1641" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1641" t="s">
         <v>9</v>
@@ -44576,7 +44579,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1642" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1642" t="s">
         <v>9</v>
@@ -44602,7 +44605,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1643" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1643" t="s">
         <v>9</v>
@@ -44628,7 +44631,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1644" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1644" t="s">
         <v>9</v>
@@ -44654,7 +44657,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1645" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1645" t="s">
         <v>9</v>
@@ -44680,7 +44683,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1646" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1646" t="s">
         <v>9</v>
@@ -44732,7 +44735,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1648" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1648" t="s">
         <v>9</v>
@@ -44758,7 +44761,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1649" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1649" t="s">
         <v>9</v>
@@ -44784,7 +44787,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1650" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1650" t="s">
         <v>9</v>
@@ -44810,7 +44813,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1651" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1651" t="s">
         <v>9</v>
@@ -44836,7 +44839,7 @@
         <v>0.674000024795532</v>
       </c>
       <c r="G1652" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="H1652" t="s">
         <v>9</v>
@@ -44862,7 +44865,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1653" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1653" t="s">
         <v>9</v>
@@ -44888,7 +44891,7 @@
         <v>0.666000008583069</v>
       </c>
       <c r="G1654" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="H1654" t="s">
         <v>9</v>
@@ -44914,7 +44917,7 @@
         <v>0.657999992370605</v>
       </c>
       <c r="G1655" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="H1655" t="s">
         <v>9</v>
@@ -44940,7 +44943,7 @@
         <v>0.643999993801117</v>
       </c>
       <c r="G1656" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H1656" t="s">
         <v>9</v>
@@ -44966,7 +44969,7 @@
         <v>0.662000000476837</v>
       </c>
       <c r="G1657" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="H1657" t="s">
         <v>9</v>
@@ -44992,7 +44995,7 @@
         <v>0.639999985694885</v>
       </c>
       <c r="G1658" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="H1658" t="s">
         <v>9</v>
@@ -45018,7 +45021,7 @@
         <v>0.648000001907349</v>
       </c>
       <c r="G1659" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="H1659" t="s">
         <v>9</v>
@@ -45044,7 +45047,7 @@
         <v>0.649999976158142</v>
       </c>
       <c r="G1660" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="H1660" t="s">
         <v>9</v>
@@ -45070,7 +45073,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1661" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1661" t="s">
         <v>9</v>
@@ -45096,7 +45099,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1662" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1662" t="s">
         <v>9</v>
@@ -45122,7 +45125,7 @@
         <v>0.624000012874603</v>
       </c>
       <c r="G1663" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="H1663" t="s">
         <v>9</v>
@@ -45148,7 +45151,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1664" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1664" t="s">
         <v>9</v>
@@ -45174,7 +45177,7 @@
         <v>0.61599999666214</v>
       </c>
       <c r="G1665" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="H1665" t="s">
         <v>9</v>
@@ -45200,7 +45203,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1666" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1666" t="s">
         <v>9</v>
@@ -45226,7 +45229,7 @@
         <v>0.646000027656555</v>
       </c>
       <c r="G1667" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="H1667" t="s">
         <v>9</v>
@@ -45252,7 +45255,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1668" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1668" t="s">
         <v>9</v>
@@ -45278,7 +45281,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1669" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1669" t="s">
         <v>9</v>
@@ -45304,7 +45307,7 @@
         <v>0.667999982833862</v>
       </c>
       <c r="G1670" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="H1670" t="s">
         <v>9</v>
@@ -45330,7 +45333,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1671" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1671" t="s">
         <v>9</v>
@@ -45356,7 +45359,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1672" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1672" t="s">
         <v>9</v>
@@ -45382,7 +45385,7 @@
         <v>0.663999974727631</v>
       </c>
       <c r="G1673" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="H1673" t="s">
         <v>9</v>
@@ -45408,7 +45411,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1674" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1674" t="s">
         <v>9</v>
@@ -45434,7 +45437,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1675" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1675" t="s">
         <v>9</v>
@@ -45460,7 +45463,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1676" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1676" t="s">
         <v>9</v>
@@ -45486,7 +45489,7 @@
         <v>0.703999996185303</v>
       </c>
       <c r="G1677" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="H1677" t="s">
         <v>9</v>
@@ -45512,7 +45515,7 @@
         <v>0.677999973297119</v>
       </c>
       <c r="G1678" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="H1678" t="s">
         <v>9</v>
@@ -45538,7 +45541,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1679" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1679" t="s">
         <v>9</v>
@@ -45564,7 +45567,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1680" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="H1680" t="s">
         <v>9</v>
@@ -45590,7 +45593,7 @@
         <v>0.691999971866608</v>
       </c>
       <c r="G1681" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="H1681" t="s">
         <v>9</v>
@@ -45616,7 +45619,7 @@
         <v>0.699999988079071</v>
       </c>
       <c r="G1682" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="H1682" t="s">
         <v>9</v>
@@ -45668,7 +45671,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1684" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1684" t="s">
         <v>9</v>
@@ -45720,7 +45723,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1686" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1686" t="s">
         <v>9</v>
@@ -45746,7 +45749,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1687" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1687" t="s">
         <v>9</v>
@@ -45772,7 +45775,7 @@
         <v>0.698000013828278</v>
       </c>
       <c r="G1688" t="s">
-        <v>247</v>
+        <v>285</v>
       </c>
       <c r="H1688" t="s">
         <v>9</v>
@@ -45798,7 +45801,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1689" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1689" t="s">
         <v>9</v>
@@ -45824,7 +45827,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1690" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1690" t="s">
         <v>9</v>
@@ -45850,7 +45853,7 @@
         <v>0.688000023365021</v>
       </c>
       <c r="G1691" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="H1691" t="s">
         <v>9</v>
@@ -45876,7 +45879,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1692" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1692" t="s">
         <v>9</v>
@@ -45902,7 +45905,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1693" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1693" t="s">
         <v>9</v>
@@ -45928,7 +45931,7 @@
         <v>0.695999979972839</v>
       </c>
       <c r="G1694" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="H1694" t="s">
         <v>9</v>
@@ -45954,7 +45957,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1695" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1695" t="s">
         <v>9</v>
@@ -45980,7 +45983,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1696" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1696" t="s">
         <v>9</v>
@@ -46006,7 +46009,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1697" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1697" t="s">
         <v>9</v>
@@ -46032,7 +46035,7 @@
         <v>0.689999997615814</v>
       </c>
       <c r="G1698" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="H1698" t="s">
         <v>9</v>
@@ -46058,7 +46061,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1699" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1699" t="s">
         <v>9</v>
@@ -46084,7 +46087,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1700" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1700" t="s">
         <v>9</v>
@@ -46110,7 +46113,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1701" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1701" t="s">
         <v>9</v>
@@ -46136,7 +46139,7 @@
         <v>0.684000015258789</v>
       </c>
       <c r="G1702" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="H1702" t="s">
         <v>9</v>
@@ -46162,7 +46165,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1703" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1703" t="s">
         <v>9</v>
@@ -46188,7 +46191,7 @@
         <v>0.681999981403351</v>
       </c>
       <c r="G1704" t="s">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="H1704" t="s">
         <v>9</v>
@@ -46214,7 +46217,7 @@
         <v>0.675999999046326</v>
       </c>
       <c r="G1705" t="s">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="H1705" t="s">
         <v>9</v>
@@ -46240,7 +46243,7 @@
         <v>0.670000016689301</v>
       </c>
       <c r="G1706" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="H1706" t="s">
         <v>9</v>
@@ -46266,7 +46269,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1707" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1707" t="s">
         <v>9</v>
@@ -46292,7 +46295,7 @@
         <v>0.680000007152557</v>
       </c>
       <c r="G1708" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="H1708" t="s">
         <v>9</v>
@@ -46318,7 +46321,7 @@
         <v>0.671999990940094</v>
       </c>
       <c r="G1709" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="H1709" t="s">
         <v>9</v>
@@ -46344,7 +46347,7 @@
         <v>0.660000026226044</v>
       </c>
       <c r="G1710" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="H1710" t="s">
         <v>9</v>
@@ -46370,7 +46373,7 @@
         <v>0.653999984264374</v>
       </c>
       <c r="G1711" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="H1711" t="s">
         <v>9</v>
@@ -46396,7 +46399,7 @@
         <v>0.656000018119812</v>
       </c>
       <c r="G1712" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="H1712" t="s">
         <v>9</v>
@@ -46422,7 +46425,7 @@
         <v>0.638000011444092</v>
       </c>
       <c r="G1713" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="H1713" t="s">
         <v>9</v>
@@ -46448,7 +46451,7 @@
         <v>0.63400000333786</v>
       </c>
       <c r="G1714" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="H1714" t="s">
         <v>9</v>
@@ -46474,7 +46477,7 @@
         <v>0.611999988555908</v>
       </c>
       <c r="G1715" t="s">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="H1715" t="s">
         <v>9</v>
@@ -46500,7 +46503,7 @@
         <v>0.610000014305115</v>
       </c